--- a/Precipitacion/2025/2025_Ppt_Resumen_Datos.xlsx
+++ b/Precipitacion/2025/2025_Ppt_Resumen_Datos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Panama_Climate\Output_Raster_Files\Ppt\2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Clima_Agua_Panama\Output_Raster_Files\Ppt\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A2E39BC-E770-4AA4-B80E-27D3CB739A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15051042-F344-4583-8FD3-4D2FA4FB9047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8010" yWindow="21480" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="36">
   <si>
     <t>Jan</t>
   </si>
@@ -143,10 +143,10 @@
     <t>Cumu_Pen</t>
   </si>
   <si>
-    <t>Ppt_ave</t>
+    <t>Diff_meanVsNC</t>
   </si>
   <si>
-    <t>Diff_meanVsNC</t>
+    <t>Raster_ave</t>
   </si>
 </sst>
 </file>
@@ -570,7 +570,9 @@
       <c r="F2" s="4">
         <v>340.91782000000001</v>
       </c>
-      <c r="G2" s="4"/>
+      <c r="G2" s="4">
+        <v>383.32702999999998</v>
+      </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
@@ -579,7 +581,7 @@
       <c r="M2" s="4"/>
       <c r="N2" s="4">
         <f>SUM(B2:M2)</f>
-        <v>1285.7096200000001</v>
+        <v>1669.03665</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="18" x14ac:dyDescent="0.35">
@@ -601,7 +603,9 @@
       <c r="F3" s="4">
         <v>314.53122000000002</v>
       </c>
-      <c r="G3" s="4"/>
+      <c r="G3" s="4">
+        <v>245.99565000000001</v>
+      </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
@@ -610,7 +614,7 @@
       <c r="M3" s="4"/>
       <c r="N3" s="4">
         <f t="shared" ref="N3:N14" si="0">SUM(B3:M3)</f>
-        <v>573.59615099999996</v>
+        <v>819.59180100000003</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="18" x14ac:dyDescent="0.35">
@@ -632,7 +636,9 @@
       <c r="F4" s="4">
         <v>297.17520000000002</v>
       </c>
-      <c r="G4" s="4"/>
+      <c r="G4" s="4">
+        <v>355.76096000000001</v>
+      </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
@@ -641,7 +647,7 @@
       <c r="M4" s="4"/>
       <c r="N4" s="4">
         <f t="shared" si="0"/>
-        <v>1069.5792000000001</v>
+        <v>1425.3401600000002</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="18" x14ac:dyDescent="0.35">
@@ -663,7 +669,9 @@
       <c r="F5" s="4">
         <v>271.42219999999998</v>
       </c>
-      <c r="G5" s="4"/>
+      <c r="G5" s="4">
+        <v>324.73145</v>
+      </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
@@ -672,7 +680,7 @@
       <c r="M5" s="4"/>
       <c r="N5" s="4">
         <f t="shared" si="0"/>
-        <v>1142.1591699999999</v>
+        <v>1466.8906199999999</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="18" x14ac:dyDescent="0.35">
@@ -694,7 +702,9 @@
       <c r="F6" s="4">
         <v>570.01580000000001</v>
       </c>
-      <c r="G6" s="4"/>
+      <c r="G6" s="4">
+        <v>465.92676</v>
+      </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
@@ -703,7 +713,7 @@
       <c r="M6" s="4"/>
       <c r="N6" s="4">
         <f t="shared" si="0"/>
-        <v>1021.39323</v>
+        <v>1487.31999</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="18" x14ac:dyDescent="0.35">
@@ -725,7 +735,9 @@
       <c r="F7" s="4">
         <v>406.89202999999998</v>
       </c>
-      <c r="G7" s="4"/>
+      <c r="G7" s="4">
+        <v>329.61144999999999</v>
+      </c>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
@@ -734,7 +746,7 @@
       <c r="M7" s="4"/>
       <c r="N7" s="4">
         <f t="shared" si="0"/>
-        <v>1036.47983</v>
+        <v>1366.0912800000001</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="18" x14ac:dyDescent="0.35">
@@ -756,7 +768,9 @@
       <c r="F8" s="4">
         <v>549.37445000000002</v>
       </c>
-      <c r="G8" s="4"/>
+      <c r="G8" s="4">
+        <v>471.96606000000003</v>
+      </c>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
@@ -765,7 +779,7 @@
       <c r="M8" s="4"/>
       <c r="N8" s="4">
         <f t="shared" si="0"/>
-        <v>1258.3590199999999</v>
+        <v>1730.3250799999998</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="18" x14ac:dyDescent="0.35">
@@ -787,7 +801,9 @@
       <c r="F9" s="4">
         <v>280.16428000000002</v>
       </c>
-      <c r="G9" s="4"/>
+      <c r="G9" s="4">
+        <v>346.21960000000001</v>
+      </c>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
@@ -796,7 +812,7 @@
       <c r="M9" s="4"/>
       <c r="N9" s="4">
         <f t="shared" si="0"/>
-        <v>1094.5325800000001</v>
+        <v>1440.75218</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="18" x14ac:dyDescent="0.35">
@@ -818,7 +834,9 @@
       <c r="F10" s="4">
         <v>298.80074999999999</v>
       </c>
-      <c r="G10" s="4"/>
+      <c r="G10" s="4">
+        <v>224.68445</v>
+      </c>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
@@ -827,7 +845,7 @@
       <c r="M10" s="4"/>
       <c r="N10" s="4">
         <f t="shared" si="0"/>
-        <v>502.34142459999998</v>
+        <v>727.02587459999995</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="18" x14ac:dyDescent="0.35">
@@ -849,7 +867,9 @@
       <c r="F11" s="4">
         <v>212.33376000000001</v>
       </c>
-      <c r="G11" s="4"/>
+      <c r="G11" s="4">
+        <v>215.05295000000001</v>
+      </c>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
@@ -858,7 +878,7 @@
       <c r="M11" s="4"/>
       <c r="N11" s="4">
         <f t="shared" si="0"/>
-        <v>350.69861470000001</v>
+        <v>565.75156470000002</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="18" x14ac:dyDescent="0.35">
@@ -880,7 +900,9 @@
       <c r="F12" s="4">
         <v>322.11944999999997</v>
       </c>
-      <c r="G12" s="4"/>
+      <c r="G12" s="4">
+        <v>323.66699999999997</v>
+      </c>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
@@ -889,7 +911,7 @@
       <c r="M12" s="4"/>
       <c r="N12" s="4">
         <f t="shared" si="0"/>
-        <v>887.58757500000002</v>
+        <v>1211.2545749999999</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="18" x14ac:dyDescent="0.35">
@@ -911,7 +933,9 @@
       <c r="F13" s="4">
         <v>323.92804000000001</v>
       </c>
-      <c r="G13" s="4"/>
+      <c r="G13" s="4">
+        <v>246.55710999999999</v>
+      </c>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
@@ -920,7 +944,7 @@
       <c r="M13" s="4"/>
       <c r="N13" s="4">
         <f t="shared" si="0"/>
-        <v>568.438537</v>
+        <v>814.99564699999996</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="18" x14ac:dyDescent="0.35">
@@ -942,7 +966,9 @@
       <c r="F14" s="4">
         <v>458.78264999999999</v>
       </c>
-      <c r="G14" s="4"/>
+      <c r="G14" s="4">
+        <v>313.97109999999998</v>
+      </c>
       <c r="H14" s="4"/>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
@@ -951,7 +977,7 @@
       <c r="M14" s="4"/>
       <c r="N14" s="4">
         <f t="shared" si="0"/>
-        <v>829.29630999999995</v>
+        <v>1143.2674099999999</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="18" x14ac:dyDescent="0.35">
@@ -978,7 +1004,10 @@
         <f>AVERAGE(F2:F14)</f>
         <v>357.41981923076924</v>
       </c>
-      <c r="G15" s="7"/>
+      <c r="G15" s="7">
+        <f>AVERAGE(G2:G14)</f>
+        <v>326.72858230769236</v>
+      </c>
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
@@ -987,7 +1016,7 @@
       <c r="M15" s="7"/>
       <c r="N15" s="7">
         <f>SUM(B15:M15)</f>
-        <v>893.85932786923081</v>
+        <v>1220.5879101769233</v>
       </c>
     </row>
   </sheetData>
@@ -1070,7 +1099,9 @@
       <c r="F2" s="4">
         <v>328.20578</v>
       </c>
-      <c r="G2" s="4"/>
+      <c r="G2" s="4">
+        <v>313.48110000000003</v>
+      </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
@@ -1079,7 +1110,7 @@
       <c r="M2" s="4"/>
       <c r="N2" s="4">
         <f>SUM(B2:M2)</f>
-        <v>1035.61294</v>
+        <v>1349.0940399999999</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
@@ -1101,7 +1132,9 @@
       <c r="F3" s="4">
         <v>253.31544</v>
       </c>
-      <c r="G3" s="4"/>
+      <c r="G3" s="4">
+        <v>277.30727999999999</v>
+      </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
@@ -1110,7 +1143,7 @@
       <c r="M3" s="4"/>
       <c r="N3" s="4">
         <f t="shared" ref="N3:N15" si="0">SUM(B3:M3)</f>
-        <v>424.80278099999998</v>
+        <v>702.11006099999997</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
@@ -1132,7 +1165,9 @@
       <c r="F4" s="4">
         <v>309.09609999999998</v>
       </c>
-      <c r="G4" s="4"/>
+      <c r="G4" s="4">
+        <v>297.00170000000003</v>
+      </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
@@ -1141,7 +1176,7 @@
       <c r="M4" s="4"/>
       <c r="N4" s="4">
         <f t="shared" si="0"/>
-        <v>586.74008000000003</v>
+        <v>883.74178000000006</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.35">
@@ -1163,7 +1198,9 @@
       <c r="F5" s="4">
         <v>268.12189999999998</v>
       </c>
-      <c r="G5" s="4"/>
+      <c r="G5" s="4">
+        <v>260.90872000000002</v>
+      </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
@@ -1172,7 +1209,7 @@
       <c r="M5" s="4"/>
       <c r="N5" s="4">
         <f t="shared" si="0"/>
-        <v>532.76926099999991</v>
+        <v>793.67798099999993</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
@@ -1194,7 +1231,9 @@
       <c r="F6" s="4">
         <v>424.95312000000001</v>
       </c>
-      <c r="G6" s="4"/>
+      <c r="G6" s="4">
+        <v>417.40674000000001</v>
+      </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
@@ -1203,7 +1242,7 @@
       <c r="M6" s="4"/>
       <c r="N6" s="4">
         <f t="shared" si="0"/>
-        <v>729.82712400000003</v>
+        <v>1147.233864</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
@@ -1225,7 +1264,9 @@
       <c r="F7" s="4">
         <v>359.99014</v>
       </c>
-      <c r="G7" s="4"/>
+      <c r="G7" s="4">
+        <v>349.94116000000002</v>
+      </c>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
@@ -1234,7 +1275,7 @@
       <c r="M7" s="4"/>
       <c r="N7" s="4">
         <f t="shared" si="0"/>
-        <v>750.14509999999996</v>
+        <v>1100.08626</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
@@ -1256,7 +1297,9 @@
       <c r="F8" s="4">
         <v>431.39879999999999</v>
       </c>
-      <c r="G8" s="4"/>
+      <c r="G8" s="4">
+        <v>427.839</v>
+      </c>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
@@ -1265,7 +1308,7 @@
       <c r="M8" s="4"/>
       <c r="N8" s="4">
         <f t="shared" si="0"/>
-        <v>883.05897499999992</v>
+        <v>1310.8979749999999</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
@@ -1287,7 +1330,9 @@
       <c r="F9" s="4">
         <v>302.62795999999997</v>
       </c>
-      <c r="G9" s="4"/>
+      <c r="G9" s="4">
+        <v>301.58535999999998</v>
+      </c>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
@@ -1296,7 +1341,7 @@
       <c r="M9" s="4"/>
       <c r="N9" s="4">
         <f t="shared" si="0"/>
-        <v>554.90786299999991</v>
+        <v>856.49322299999994</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
@@ -1318,7 +1363,9 @@
       <c r="F10" s="4">
         <v>261.05153999999999</v>
       </c>
-      <c r="G10" s="4"/>
+      <c r="G10" s="4">
+        <v>251.28584000000001</v>
+      </c>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
@@ -1327,7 +1374,7 @@
       <c r="M10" s="4"/>
       <c r="N10" s="4">
         <f t="shared" si="0"/>
-        <v>361.39133949999996</v>
+        <v>612.67717949999997</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
@@ -1349,7 +1396,9 @@
       <c r="F11" s="4">
         <v>181.69147000000001</v>
       </c>
-      <c r="G11" s="4"/>
+      <c r="G11" s="4">
+        <v>204.78511</v>
+      </c>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
@@ -1358,7 +1407,7 @@
       <c r="M11" s="4"/>
       <c r="N11" s="4">
         <f t="shared" si="0"/>
-        <v>237.49712299999999</v>
+        <v>442.28223300000002</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
@@ -1380,7 +1429,9 @@
       <c r="F12" s="4">
         <v>286.03503000000001</v>
       </c>
-      <c r="G12" s="4"/>
+      <c r="G12" s="4">
+        <v>274.49588</v>
+      </c>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
@@ -1389,7 +1440,7 @@
       <c r="M12" s="4"/>
       <c r="N12" s="4">
         <f t="shared" si="0"/>
-        <v>471.16477900000001</v>
+        <v>745.66065900000001</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
@@ -1411,7 +1462,9 @@
       <c r="F13" s="4">
         <v>275.00815</v>
       </c>
-      <c r="G13" s="4"/>
+      <c r="G13" s="4">
+        <v>241.35033999999999</v>
+      </c>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
@@ -1420,7 +1473,7 @@
       <c r="M13" s="4"/>
       <c r="N13" s="4">
         <f t="shared" si="0"/>
-        <v>439.232553</v>
+        <v>680.58289300000001</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
@@ -1442,7 +1495,9 @@
       <c r="F14" s="4">
         <v>362.72550000000001</v>
       </c>
-      <c r="G14" s="4"/>
+      <c r="G14" s="4">
+        <v>349.34494000000001</v>
+      </c>
       <c r="H14" s="4"/>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
@@ -1450,39 +1505,47 @@
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
       <c r="N14" s="4">
-        <f t="shared" si="0"/>
-        <v>587.221588</v>
+        <f>SUM(B14:M14)</f>
+        <v>936.56652800000006</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="7">
+        <f>AVERAGE(B2:B14)</f>
         <v>67.513827307692296</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="7">
+        <f t="shared" ref="C15:G15" si="1">AVERAGE(C2:C14)</f>
         <v>41.752843615384613</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="7">
+        <f t="shared" si="1"/>
         <v>44.692282884615381</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="7">
+        <f t="shared" si="1"/>
         <v>119.12955207692309</v>
       </c>
-      <c r="F15" s="2">
-        <v>119.12955207692309</v>
-      </c>
-      <c r="G15" s="2"/>
+      <c r="F15" s="7">
+        <f t="shared" si="1"/>
+        <v>311.09391769230768</v>
+      </c>
+      <c r="G15" s="7">
+        <f t="shared" si="1"/>
+        <v>305.13332076923075</v>
+      </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
-      <c r="N15" s="2">
-        <f t="shared" si="0"/>
-        <v>392.21805796153853</v>
+      <c r="N15" s="7">
+        <f>SUM(B15:M15)</f>
+        <v>889.31574434615391</v>
       </c>
     </row>
   </sheetData>
@@ -1508,7 +1571,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>31</v>
@@ -2221,13 +2284,13 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
-        <v>51.443686999999997</v>
+        <v>50.438299999999998</v>
       </c>
       <c r="B32" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C32" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D32" s="3">
         <v>1</v>
@@ -2236,21 +2299,21 @@
         <v>1</v>
       </c>
       <c r="F32" s="5">
-        <v>45658</v>
+        <v>45809</v>
       </c>
       <c r="G32" s="3">
-        <v>51.443686999999997</v>
+        <v>609.90170000000001</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
-        <v>30.218036999999999</v>
+        <v>58.700428000000002</v>
       </c>
       <c r="B33" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C33" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D33" s="3">
         <v>2</v>
@@ -2259,21 +2322,21 @@
         <v>6</v>
       </c>
       <c r="F33" s="5">
-        <v>45663</v>
+        <v>45814</v>
       </c>
       <c r="G33" s="3">
-        <v>81.661730000000006</v>
+        <v>668.60209999999995</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
-        <v>7.7399344000000001</v>
+        <v>83.162850000000006</v>
       </c>
       <c r="B34" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C34" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D34" s="3">
         <v>3</v>
@@ -2282,21 +2345,21 @@
         <v>11</v>
       </c>
       <c r="F34" s="5">
-        <v>45668</v>
+        <v>45819</v>
       </c>
       <c r="G34" s="3">
-        <v>89.401660000000007</v>
+        <v>751.76495</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
-        <v>11.712353999999999</v>
+        <v>61.870975000000001</v>
       </c>
       <c r="B35" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C35" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D35" s="3">
         <v>4</v>
@@ -2305,21 +2368,21 @@
         <v>16</v>
       </c>
       <c r="F35" s="5">
-        <v>45673</v>
+        <v>45824</v>
       </c>
       <c r="G35" s="3">
-        <v>101.11400999999999</v>
+        <v>813.63589999999999</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
-        <v>8.5210749999999997</v>
+        <v>43.194775</v>
       </c>
       <c r="B36" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C36" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D36" s="3">
         <v>5</v>
@@ -2328,21 +2391,21 @@
         <v>21</v>
       </c>
       <c r="F36" s="5">
-        <v>45678</v>
+        <v>45829</v>
       </c>
       <c r="G36" s="3">
-        <v>109.635086</v>
+        <v>856.83069999999998</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
-        <v>9.6642530000000004</v>
+        <v>33.611854999999998</v>
       </c>
       <c r="B37" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C37" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D37" s="3">
         <v>6</v>
@@ -2351,21 +2414,21 @@
         <v>26</v>
       </c>
       <c r="F37" s="5">
-        <v>45683</v>
+        <v>45834</v>
       </c>
       <c r="G37" s="3">
-        <v>119.29934</v>
+        <v>890.44257000000005</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
-        <v>14.432333</v>
+        <v>51.443686999999997</v>
       </c>
       <c r="B38" s="3">
         <v>2025</v>
       </c>
       <c r="C38" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38" s="3">
         <v>1</v>
@@ -2374,21 +2437,21 @@
         <v>1</v>
       </c>
       <c r="F38" s="5">
-        <v>45689</v>
+        <v>45658</v>
       </c>
       <c r="G38" s="3">
-        <v>133.73167000000001</v>
+        <v>51.443686999999997</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="3">
-        <v>8.7800480000000007</v>
+        <v>30.218036999999999</v>
       </c>
       <c r="B39" s="3">
         <v>2025</v>
       </c>
       <c r="C39" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D39" s="3">
         <v>2</v>
@@ -2397,21 +2460,21 @@
         <v>6</v>
       </c>
       <c r="F39" s="5">
-        <v>45694</v>
+        <v>45663</v>
       </c>
       <c r="G39" s="3">
-        <v>142.51172</v>
+        <v>81.661730000000006</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
-        <v>36.847504000000001</v>
+        <v>7.7399344000000001</v>
       </c>
       <c r="B40" s="3">
         <v>2025</v>
       </c>
       <c r="C40" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D40" s="3">
         <v>3</v>
@@ -2420,21 +2483,21 @@
         <v>11</v>
       </c>
       <c r="F40" s="5">
-        <v>45699</v>
+        <v>45668</v>
       </c>
       <c r="G40" s="3">
-        <v>179.35921999999999</v>
+        <v>89.401660000000007</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="3">
-        <v>47.512680000000003</v>
+        <v>11.712353999999999</v>
       </c>
       <c r="B41" s="3">
         <v>2025</v>
       </c>
       <c r="C41" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D41" s="3">
         <v>4</v>
@@ -2443,21 +2506,21 @@
         <v>16</v>
       </c>
       <c r="F41" s="5">
-        <v>45704</v>
+        <v>45673</v>
       </c>
       <c r="G41" s="3">
-        <v>226.87190000000001</v>
+        <v>101.11400999999999</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
-        <v>11.339199000000001</v>
+        <v>8.5210749999999997</v>
       </c>
       <c r="B42" s="3">
         <v>2025</v>
       </c>
       <c r="C42" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D42" s="3">
         <v>5</v>
@@ -2466,21 +2529,21 @@
         <v>21</v>
       </c>
       <c r="F42" s="5">
-        <v>45709</v>
+        <v>45678</v>
       </c>
       <c r="G42" s="3">
-        <v>238.21109999999999</v>
+        <v>109.635086</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
-        <v>5.0655327000000003</v>
+        <v>9.6642530000000004</v>
       </c>
       <c r="B43" s="3">
         <v>2025</v>
       </c>
       <c r="C43" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43" s="3">
         <v>6</v>
@@ -2489,21 +2552,21 @@
         <v>26</v>
       </c>
       <c r="F43" s="5">
-        <v>45714</v>
+        <v>45683</v>
       </c>
       <c r="G43" s="3">
-        <v>243.27663999999999</v>
+        <v>119.29934</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
-        <v>6.6873063999999998</v>
+        <v>14.432333</v>
       </c>
       <c r="B44" s="3">
         <v>2025</v>
       </c>
       <c r="C44" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D44" s="3">
         <v>1</v>
@@ -2512,21 +2575,21 @@
         <v>1</v>
       </c>
       <c r="F44" s="5">
-        <v>45717</v>
+        <v>45689</v>
       </c>
       <c r="G44" s="3">
-        <v>249.96394000000001</v>
+        <v>133.73167000000001</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
-        <v>5.1503943999999997</v>
+        <v>8.7800480000000007</v>
       </c>
       <c r="B45" s="3">
         <v>2025</v>
       </c>
       <c r="C45" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D45" s="3">
         <v>2</v>
@@ -2535,21 +2598,21 @@
         <v>6</v>
       </c>
       <c r="F45" s="5">
-        <v>45722</v>
+        <v>45694</v>
       </c>
       <c r="G45" s="3">
-        <v>255.11433</v>
+        <v>142.51172</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="3">
-        <v>5.3021630000000002</v>
+        <v>36.847504000000001</v>
       </c>
       <c r="B46" s="3">
         <v>2025</v>
       </c>
       <c r="C46" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D46" s="3">
         <v>3</v>
@@ -2558,21 +2621,21 @@
         <v>11</v>
       </c>
       <c r="F46" s="5">
-        <v>45727</v>
+        <v>45699</v>
       </c>
       <c r="G46" s="3">
-        <v>260.41649999999998</v>
+        <v>179.35921999999999</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="3">
-        <v>7.7123569999999999</v>
+        <v>47.512680000000003</v>
       </c>
       <c r="B47" s="3">
         <v>2025</v>
       </c>
       <c r="C47" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D47" s="3">
         <v>4</v>
@@ -2581,21 +2644,21 @@
         <v>16</v>
       </c>
       <c r="F47" s="5">
-        <v>45732</v>
+        <v>45704</v>
       </c>
       <c r="G47" s="3">
-        <v>268.12885</v>
+        <v>226.87190000000001</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="3">
-        <v>24.789594999999998</v>
+        <v>11.339199000000001</v>
       </c>
       <c r="B48" s="3">
         <v>2025</v>
       </c>
       <c r="C48" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D48" s="3">
         <v>5</v>
@@ -2604,21 +2667,21 @@
         <v>21</v>
       </c>
       <c r="F48" s="5">
-        <v>45737</v>
+        <v>45709</v>
       </c>
       <c r="G48" s="3">
-        <v>292.91845999999998</v>
+        <v>238.21109999999999</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="3">
-        <v>23.760323</v>
+        <v>5.0655327000000003</v>
       </c>
       <c r="B49" s="3">
         <v>2025</v>
       </c>
       <c r="C49" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D49" s="3">
         <v>6</v>
@@ -2627,21 +2690,21 @@
         <v>26</v>
       </c>
       <c r="F49" s="5">
-        <v>45742</v>
+        <v>45714</v>
       </c>
       <c r="G49" s="3">
-        <v>316.67876999999999</v>
+        <v>243.27663999999999</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="3">
-        <v>30.345040000000001</v>
+        <v>6.6873063999999998</v>
       </c>
       <c r="B50" s="3">
         <v>2025</v>
       </c>
       <c r="C50" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D50" s="3">
         <v>1</v>
@@ -2650,21 +2713,21 @@
         <v>1</v>
       </c>
       <c r="F50" s="5">
-        <v>45748</v>
+        <v>45717</v>
       </c>
       <c r="G50" s="3">
-        <v>347.02379999999999</v>
+        <v>249.96394000000001</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="3">
-        <v>26.385961999999999</v>
+        <v>5.1503943999999997</v>
       </c>
       <c r="B51" s="3">
         <v>2025</v>
       </c>
       <c r="C51" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D51" s="3">
         <v>2</v>
@@ -2673,21 +2736,21 @@
         <v>6</v>
       </c>
       <c r="F51" s="5">
-        <v>45753</v>
+        <v>45722</v>
       </c>
       <c r="G51" s="3">
-        <v>373.40980000000002</v>
+        <v>255.11433</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="3">
-        <v>14.766463</v>
+        <v>5.3021630000000002</v>
       </c>
       <c r="B52" s="3">
         <v>2025</v>
       </c>
       <c r="C52" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D52" s="3">
         <v>3</v>
@@ -2696,21 +2759,21 @@
         <v>11</v>
       </c>
       <c r="F52" s="5">
-        <v>45758</v>
+        <v>45727</v>
       </c>
       <c r="G52" s="3">
-        <v>388.17624000000001</v>
+        <v>260.41649999999998</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="3">
-        <v>13.573518999999999</v>
+        <v>7.7123569999999999</v>
       </c>
       <c r="B53" s="3">
         <v>2025</v>
       </c>
       <c r="C53" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D53" s="3">
         <v>4</v>
@@ -2719,21 +2782,21 @@
         <v>16</v>
       </c>
       <c r="F53" s="5">
-        <v>45763</v>
+        <v>45732</v>
       </c>
       <c r="G53" s="3">
-        <v>401.74975999999998</v>
+        <v>268.12885</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="3">
-        <v>39.141010000000001</v>
+        <v>24.789594999999998</v>
       </c>
       <c r="B54" s="3">
         <v>2025</v>
       </c>
       <c r="C54" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D54" s="3">
         <v>5</v>
@@ -2742,21 +2805,21 @@
         <v>21</v>
       </c>
       <c r="F54" s="5">
-        <v>45768</v>
+        <v>45737</v>
       </c>
       <c r="G54" s="3">
-        <v>440.89078000000001</v>
+        <v>292.91845999999998</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="3">
-        <v>41.962490000000003</v>
+        <v>23.760323</v>
       </c>
       <c r="B55" s="3">
         <v>2025</v>
       </c>
       <c r="C55" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D55" s="3">
         <v>6</v>
@@ -2765,21 +2828,21 @@
         <v>26</v>
       </c>
       <c r="F55" s="5">
-        <v>45773</v>
+        <v>45742</v>
       </c>
       <c r="G55" s="3">
-        <v>482.85327000000001</v>
+        <v>316.67876999999999</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="3">
-        <v>55.322009999999999</v>
+        <v>30.345040000000001</v>
       </c>
       <c r="B56" s="3">
         <v>2025</v>
       </c>
       <c r="C56" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D56" s="3">
         <v>1</v>
@@ -2788,21 +2851,21 @@
         <v>1</v>
       </c>
       <c r="F56" s="5">
-        <v>45778</v>
+        <v>45748</v>
       </c>
       <c r="G56" s="3">
-        <v>538.17529999999999</v>
+        <v>347.02379999999999</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="3">
-        <v>48.162075000000002</v>
+        <v>26.385961999999999</v>
       </c>
       <c r="B57" s="3">
         <v>2025</v>
       </c>
       <c r="C57" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D57" s="3">
         <v>2</v>
@@ -2811,21 +2874,21 @@
         <v>6</v>
       </c>
       <c r="F57" s="5">
-        <v>45783</v>
+        <v>45753</v>
       </c>
       <c r="G57" s="3">
-        <v>586.33734000000004</v>
+        <v>373.40980000000002</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="3">
-        <v>73.489159999999998</v>
+        <v>14.766463</v>
       </c>
       <c r="B58" s="3">
         <v>2025</v>
       </c>
       <c r="C58" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D58" s="3">
         <v>3</v>
@@ -2834,21 +2897,21 @@
         <v>11</v>
       </c>
       <c r="F58" s="5">
-        <v>45788</v>
+        <v>45758</v>
       </c>
       <c r="G58" s="3">
-        <v>659.82654000000002</v>
+        <v>388.17624000000001</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="3">
-        <v>73.519165000000001</v>
+        <v>13.573518999999999</v>
       </c>
       <c r="B59" s="3">
         <v>2025</v>
       </c>
       <c r="C59" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D59" s="3">
         <v>4</v>
@@ -2857,21 +2920,21 @@
         <v>16</v>
       </c>
       <c r="F59" s="5">
-        <v>45793</v>
+        <v>45763</v>
       </c>
       <c r="G59" s="3">
-        <v>733.34569999999997</v>
+        <v>401.74975999999998</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="3">
-        <v>73.128426000000005</v>
+        <v>39.141010000000001</v>
       </c>
       <c r="B60" s="3">
         <v>2025</v>
       </c>
       <c r="C60" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D60" s="3">
         <v>5</v>
@@ -2880,21 +2943,21 @@
         <v>21</v>
       </c>
       <c r="F60" s="5">
-        <v>45798</v>
+        <v>45768</v>
       </c>
       <c r="G60" s="3">
-        <v>806.47410000000002</v>
+        <v>440.89078000000001</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="3">
-        <v>50.314039999999999</v>
+        <v>41.962490000000003</v>
       </c>
       <c r="B61" s="3">
         <v>2025</v>
       </c>
       <c r="C61" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D61" s="3">
         <v>6</v>
@@ -2903,21 +2966,21 @@
         <v>26</v>
       </c>
       <c r="F61" s="5">
-        <v>45803</v>
+        <v>45773</v>
       </c>
       <c r="G61" s="3">
-        <v>856.78814999999997</v>
+        <v>482.85327000000001</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="3">
-        <v>14.331683999999999</v>
+        <v>55.322009999999999</v>
       </c>
       <c r="B62" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C62" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D62" s="3">
         <v>1</v>
@@ -2926,21 +2989,21 @@
         <v>1</v>
       </c>
       <c r="F62" s="5">
-        <v>45658</v>
+        <v>45778</v>
       </c>
       <c r="G62" s="3">
-        <v>14.331683999999999</v>
+        <v>538.17529999999999</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="3">
-        <v>14.564731</v>
+        <v>48.162075000000002</v>
       </c>
       <c r="B63" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C63" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D63" s="3">
         <v>2</v>
@@ -2949,21 +3012,21 @@
         <v>6</v>
       </c>
       <c r="F63" s="5">
-        <v>45663</v>
+        <v>45783</v>
       </c>
       <c r="G63" s="3">
-        <v>28.896415999999999</v>
+        <v>586.33734000000004</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="3">
-        <v>10.498049</v>
+        <v>73.489159999999998</v>
       </c>
       <c r="B64" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C64" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D64" s="3">
         <v>3</v>
@@ -2972,21 +3035,21 @@
         <v>11</v>
       </c>
       <c r="F64" s="5">
-        <v>45668</v>
+        <v>45788</v>
       </c>
       <c r="G64" s="3">
-        <v>39.394463000000002</v>
+        <v>659.82654000000002</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="3">
-        <v>10.599313</v>
+        <v>73.519165000000001</v>
       </c>
       <c r="B65" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C65" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D65" s="3">
         <v>4</v>
@@ -2995,21 +3058,21 @@
         <v>16</v>
       </c>
       <c r="F65" s="5">
-        <v>45673</v>
+        <v>45793</v>
       </c>
       <c r="G65" s="3">
-        <v>49.993774000000002</v>
+        <v>733.34569999999997</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="3">
-        <v>9.7497159999999994</v>
+        <v>73.128426000000005</v>
       </c>
       <c r="B66" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C66" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D66" s="3">
         <v>5</v>
@@ -3018,21 +3081,21 @@
         <v>21</v>
       </c>
       <c r="F66" s="5">
-        <v>45678</v>
+        <v>45798</v>
       </c>
       <c r="G66" s="3">
-        <v>59.743492000000003</v>
+        <v>806.47410000000002</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="3">
-        <v>8.0435770000000009</v>
+        <v>50.314039999999999</v>
       </c>
       <c r="B67" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C67" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D67" s="3">
         <v>6</v>
@@ -3041,21 +3104,21 @@
         <v>26</v>
       </c>
       <c r="F67" s="5">
-        <v>45683</v>
+        <v>45803</v>
       </c>
       <c r="G67" s="3">
-        <v>67.78707</v>
+        <v>856.78814999999997</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="3">
-        <v>8.4454740000000008</v>
+        <v>56.4529</v>
       </c>
       <c r="B68" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C68" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D68" s="3">
         <v>1</v>
@@ -3064,21 +3127,21 @@
         <v>1</v>
       </c>
       <c r="F68" s="5">
-        <v>45689</v>
+        <v>45809</v>
       </c>
       <c r="G68" s="3">
-        <v>76.232544000000004</v>
+        <v>913.24099999999999</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="3">
-        <v>8.7416970000000003</v>
+        <v>77.087370000000007</v>
       </c>
       <c r="B69" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C69" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D69" s="3">
         <v>2</v>
@@ -3087,21 +3150,21 @@
         <v>6</v>
       </c>
       <c r="F69" s="5">
-        <v>45694</v>
+        <v>45814</v>
       </c>
       <c r="G69" s="3">
-        <v>84.974239999999995</v>
+        <v>990.32839999999999</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="3">
-        <v>9.234057</v>
+        <v>52.885750000000002</v>
       </c>
       <c r="B70" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C70" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D70" s="3">
         <v>3</v>
@@ -3110,21 +3173,21 @@
         <v>11</v>
       </c>
       <c r="F70" s="5">
-        <v>45699</v>
+        <v>45819</v>
       </c>
       <c r="G70" s="3">
-        <v>94.208299999999994</v>
+        <v>1043.2140999999999</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="3">
-        <v>8.8217879999999997</v>
+        <v>39.925694</v>
       </c>
       <c r="B71" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C71" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D71" s="3">
         <v>4</v>
@@ -3133,21 +3196,21 @@
         <v>16</v>
       </c>
       <c r="F71" s="5">
-        <v>45704</v>
+        <v>45824</v>
       </c>
       <c r="G71" s="3">
-        <v>103.03008</v>
+        <v>1083.1398999999999</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="3">
-        <v>7.0881577</v>
+        <v>77.791659999999993</v>
       </c>
       <c r="B72" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C72" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D72" s="3">
         <v>5</v>
@@ -3156,21 +3219,21 @@
         <v>21</v>
       </c>
       <c r="F72" s="5">
-        <v>45709</v>
+        <v>45829</v>
       </c>
       <c r="G72" s="3">
-        <v>110.11824</v>
+        <v>1160.9314999999999</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="3">
-        <v>5.2113975999999997</v>
+        <v>36.81955</v>
       </c>
       <c r="B73" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C73" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D73" s="3">
         <v>6</v>
@@ -3179,21 +3242,21 @@
         <v>26</v>
       </c>
       <c r="F73" s="5">
-        <v>45714</v>
+        <v>45834</v>
       </c>
       <c r="G73" s="3">
-        <v>115.32964</v>
+        <v>1197.7511</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="3">
-        <v>9.0188410000000001</v>
+        <v>14.331683999999999</v>
       </c>
       <c r="B74" s="3">
         <v>1991</v>
       </c>
       <c r="C74" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D74" s="3">
         <v>1</v>
@@ -3202,21 +3265,21 @@
         <v>1</v>
       </c>
       <c r="F74" s="5">
-        <v>45717</v>
+        <v>45658</v>
       </c>
       <c r="G74" s="3">
-        <v>124.34848</v>
+        <v>14.331683999999999</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="3">
-        <v>6.5476109999999998</v>
+        <v>14.564731</v>
       </c>
       <c r="B75" s="3">
         <v>1991</v>
       </c>
       <c r="C75" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D75" s="3">
         <v>2</v>
@@ -3225,21 +3288,21 @@
         <v>6</v>
       </c>
       <c r="F75" s="5">
-        <v>45722</v>
+        <v>45663</v>
       </c>
       <c r="G75" s="3">
-        <v>130.89608999999999</v>
+        <v>28.896415999999999</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="3">
-        <v>7.5543903999999999</v>
+        <v>10.498049</v>
       </c>
       <c r="B76" s="3">
         <v>1991</v>
       </c>
       <c r="C76" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D76" s="3">
         <v>3</v>
@@ -3248,21 +3311,21 @@
         <v>11</v>
       </c>
       <c r="F76" s="5">
-        <v>45727</v>
+        <v>45668</v>
       </c>
       <c r="G76" s="3">
-        <v>138.45049</v>
+        <v>39.394463000000002</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="3">
-        <v>10.259204</v>
+        <v>10.599313</v>
       </c>
       <c r="B77" s="3">
         <v>1991</v>
       </c>
       <c r="C77" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D77" s="3">
         <v>4</v>
@@ -3271,21 +3334,21 @@
         <v>16</v>
       </c>
       <c r="F77" s="5">
-        <v>45732</v>
+        <v>45673</v>
       </c>
       <c r="G77" s="3">
-        <v>148.70968999999999</v>
+        <v>49.993774000000002</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="3">
-        <v>8.8252439999999996</v>
+        <v>9.7497159999999994</v>
       </c>
       <c r="B78" s="3">
         <v>1991</v>
       </c>
       <c r="C78" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D78" s="3">
         <v>5</v>
@@ -3294,21 +3357,21 @@
         <v>21</v>
       </c>
       <c r="F78" s="5">
-        <v>45737</v>
+        <v>45678</v>
       </c>
       <c r="G78" s="3">
-        <v>157.53493</v>
+        <v>59.743492000000003</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="3">
-        <v>11.316482000000001</v>
+        <v>8.0435770000000009</v>
       </c>
       <c r="B79" s="3">
         <v>1991</v>
       </c>
       <c r="C79" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D79" s="3">
         <v>6</v>
@@ -3317,21 +3380,21 @@
         <v>26</v>
       </c>
       <c r="F79" s="5">
-        <v>45742</v>
+        <v>45683</v>
       </c>
       <c r="G79" s="3">
-        <v>168.85140999999999</v>
+        <v>67.78707</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="3">
-        <v>13.784658</v>
+        <v>8.4454740000000008</v>
       </c>
       <c r="B80" s="3">
         <v>1991</v>
       </c>
       <c r="C80" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D80" s="3">
         <v>1</v>
@@ -3340,21 +3403,21 @@
         <v>1</v>
       </c>
       <c r="F80" s="5">
-        <v>45748</v>
+        <v>45689</v>
       </c>
       <c r="G80" s="3">
-        <v>182.63607999999999</v>
+        <v>76.232544000000004</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="3">
-        <v>18.13364</v>
+        <v>8.7416970000000003</v>
       </c>
       <c r="B81" s="3">
         <v>1991</v>
       </c>
       <c r="C81" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D81" s="3">
         <v>2</v>
@@ -3363,21 +3426,21 @@
         <v>6</v>
       </c>
       <c r="F81" s="5">
-        <v>45753</v>
+        <v>45694</v>
       </c>
       <c r="G81" s="3">
-        <v>200.76971</v>
+        <v>84.974239999999995</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="3">
-        <v>14.012308000000001</v>
+        <v>9.234057</v>
       </c>
       <c r="B82" s="3">
         <v>1991</v>
       </c>
       <c r="C82" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D82" s="3">
         <v>3</v>
@@ -3386,21 +3449,21 @@
         <v>11</v>
       </c>
       <c r="F82" s="5">
-        <v>45758</v>
+        <v>45699</v>
       </c>
       <c r="G82" s="3">
-        <v>214.78201000000001</v>
+        <v>94.208299999999994</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="3">
-        <v>16.865030000000001</v>
+        <v>8.8217879999999997</v>
       </c>
       <c r="B83" s="3">
         <v>1991</v>
       </c>
       <c r="C83" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D83" s="3">
         <v>4</v>
@@ -3409,21 +3472,21 @@
         <v>16</v>
       </c>
       <c r="F83" s="5">
-        <v>45763</v>
+        <v>45704</v>
       </c>
       <c r="G83" s="3">
-        <v>231.64705000000001</v>
+        <v>103.03008</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="3">
-        <v>32.868423</v>
+        <v>7.0881577</v>
       </c>
       <c r="B84" s="3">
         <v>1991</v>
       </c>
       <c r="C84" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D84" s="3">
         <v>5</v>
@@ -3432,21 +3495,21 @@
         <v>21</v>
       </c>
       <c r="F84" s="5">
-        <v>45768</v>
+        <v>45709</v>
       </c>
       <c r="G84" s="3">
-        <v>264.51546999999999</v>
+        <v>110.11824</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="3">
-        <v>42.111977000000003</v>
+        <v>5.2113975999999997</v>
       </c>
       <c r="B85" s="3">
         <v>1991</v>
       </c>
       <c r="C85" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D85" s="3">
         <v>6</v>
@@ -3455,21 +3518,21 @@
         <v>26</v>
       </c>
       <c r="F85" s="5">
-        <v>45773</v>
+        <v>45714</v>
       </c>
       <c r="G85" s="3">
-        <v>306.62743999999998</v>
+        <v>115.32964</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="3">
-        <v>42.059672999999997</v>
+        <v>9.0188410000000001</v>
       </c>
       <c r="B86" s="3">
         <v>1991</v>
       </c>
       <c r="C86" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D86" s="3">
         <v>1</v>
@@ -3478,21 +3541,21 @@
         <v>1</v>
       </c>
       <c r="F86" s="5">
-        <v>45778</v>
+        <v>45717</v>
       </c>
       <c r="G86" s="3">
-        <v>348.68713000000002</v>
+        <v>124.34848</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="3">
-        <v>45.601909999999997</v>
+        <v>6.5476109999999998</v>
       </c>
       <c r="B87" s="3">
         <v>1991</v>
       </c>
       <c r="C87" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D87" s="3">
         <v>2</v>
@@ -3501,21 +3564,21 @@
         <v>6</v>
       </c>
       <c r="F87" s="5">
-        <v>45783</v>
+        <v>45722</v>
       </c>
       <c r="G87" s="3">
-        <v>394.28903000000003</v>
+        <v>130.89608999999999</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="3">
-        <v>50.457825</v>
+        <v>7.5543903999999999</v>
       </c>
       <c r="B88" s="3">
         <v>1991</v>
       </c>
       <c r="C88" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D88" s="3">
         <v>3</v>
@@ -3524,21 +3587,21 @@
         <v>11</v>
       </c>
       <c r="F88" s="5">
-        <v>45788</v>
+        <v>45727</v>
       </c>
       <c r="G88" s="3">
-        <v>444.74686000000003</v>
+        <v>138.45049</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="3">
-        <v>60.332355</v>
+        <v>10.259204</v>
       </c>
       <c r="B89" s="3">
         <v>1991</v>
       </c>
       <c r="C89" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D89" s="3">
         <v>4</v>
@@ -3547,21 +3610,21 @@
         <v>16</v>
       </c>
       <c r="F89" s="5">
-        <v>45793</v>
+        <v>45732</v>
       </c>
       <c r="G89" s="3">
-        <v>505.07922000000002</v>
+        <v>148.70968999999999</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="3">
-        <v>55.695160000000001</v>
+        <v>8.8252439999999996</v>
       </c>
       <c r="B90" s="3">
         <v>1991</v>
       </c>
       <c r="C90" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D90" s="3">
         <v>5</v>
@@ -3570,21 +3633,21 @@
         <v>21</v>
       </c>
       <c r="F90" s="5">
-        <v>45798</v>
+        <v>45737</v>
       </c>
       <c r="G90" s="3">
-        <v>560.77435000000003</v>
+        <v>157.53493</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="3">
-        <v>70.140879999999996</v>
+        <v>11.316482000000001</v>
       </c>
       <c r="B91" s="3">
         <v>1991</v>
       </c>
       <c r="C91" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D91" s="3">
         <v>6</v>
@@ -3593,73 +3656,433 @@
         <v>26</v>
       </c>
       <c r="F91" s="5">
+        <v>45742</v>
+      </c>
+      <c r="G91" s="3">
+        <v>168.85140999999999</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A92" s="3">
+        <v>13.784658</v>
+      </c>
+      <c r="B92" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C92" s="3">
+        <v>4</v>
+      </c>
+      <c r="D92" s="3">
+        <v>1</v>
+      </c>
+      <c r="E92" s="3">
+        <v>1</v>
+      </c>
+      <c r="F92" s="5">
+        <v>45748</v>
+      </c>
+      <c r="G92" s="3">
+        <v>182.63607999999999</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A93" s="3">
+        <v>18.13364</v>
+      </c>
+      <c r="B93" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C93" s="3">
+        <v>4</v>
+      </c>
+      <c r="D93" s="3">
+        <v>2</v>
+      </c>
+      <c r="E93" s="3">
+        <v>6</v>
+      </c>
+      <c r="F93" s="5">
+        <v>45753</v>
+      </c>
+      <c r="G93" s="3">
+        <v>200.76971</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A94" s="3">
+        <v>14.012308000000001</v>
+      </c>
+      <c r="B94" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C94" s="3">
+        <v>4</v>
+      </c>
+      <c r="D94" s="3">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3">
+        <v>11</v>
+      </c>
+      <c r="F94" s="5">
+        <v>45758</v>
+      </c>
+      <c r="G94" s="3">
+        <v>214.78201000000001</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A95" s="3">
+        <v>16.865030000000001</v>
+      </c>
+      <c r="B95" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C95" s="3">
+        <v>4</v>
+      </c>
+      <c r="D95" s="3">
+        <v>4</v>
+      </c>
+      <c r="E95" s="3">
+        <v>16</v>
+      </c>
+      <c r="F95" s="5">
+        <v>45763</v>
+      </c>
+      <c r="G95" s="3">
+        <v>231.64705000000001</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A96" s="3">
+        <v>32.868423</v>
+      </c>
+      <c r="B96" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C96" s="3">
+        <v>4</v>
+      </c>
+      <c r="D96" s="3">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3">
+        <v>21</v>
+      </c>
+      <c r="F96" s="5">
+        <v>45768</v>
+      </c>
+      <c r="G96" s="3">
+        <v>264.51546999999999</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A97" s="3">
+        <v>42.111977000000003</v>
+      </c>
+      <c r="B97" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C97" s="3">
+        <v>4</v>
+      </c>
+      <c r="D97" s="3">
+        <v>6</v>
+      </c>
+      <c r="E97" s="3">
+        <v>26</v>
+      </c>
+      <c r="F97" s="5">
+        <v>45773</v>
+      </c>
+      <c r="G97" s="3">
+        <v>306.62743999999998</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A98" s="3">
+        <v>42.059672999999997</v>
+      </c>
+      <c r="B98" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C98" s="3">
+        <v>5</v>
+      </c>
+      <c r="D98" s="3">
+        <v>1</v>
+      </c>
+      <c r="E98" s="3">
+        <v>1</v>
+      </c>
+      <c r="F98" s="5">
+        <v>45778</v>
+      </c>
+      <c r="G98" s="3">
+        <v>348.68713000000002</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A99" s="3">
+        <v>45.601909999999997</v>
+      </c>
+      <c r="B99" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C99" s="3">
+        <v>5</v>
+      </c>
+      <c r="D99" s="3">
+        <v>2</v>
+      </c>
+      <c r="E99" s="3">
+        <v>6</v>
+      </c>
+      <c r="F99" s="5">
+        <v>45783</v>
+      </c>
+      <c r="G99" s="3">
+        <v>394.28903000000003</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A100" s="3">
+        <v>50.457825</v>
+      </c>
+      <c r="B100" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C100" s="3">
+        <v>5</v>
+      </c>
+      <c r="D100" s="3">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3">
+        <v>11</v>
+      </c>
+      <c r="F100" s="5">
+        <v>45788</v>
+      </c>
+      <c r="G100" s="3">
+        <v>444.74686000000003</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A101" s="3">
+        <v>60.332355</v>
+      </c>
+      <c r="B101" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C101" s="3">
+        <v>5</v>
+      </c>
+      <c r="D101" s="3">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3">
+        <v>16</v>
+      </c>
+      <c r="F101" s="5">
+        <v>45793</v>
+      </c>
+      <c r="G101" s="3">
+        <v>505.07922000000002</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A102" s="3">
+        <v>55.695160000000001</v>
+      </c>
+      <c r="B102" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C102" s="3">
+        <v>5</v>
+      </c>
+      <c r="D102" s="3">
+        <v>5</v>
+      </c>
+      <c r="E102" s="3">
+        <v>21</v>
+      </c>
+      <c r="F102" s="5">
+        <v>45798</v>
+      </c>
+      <c r="G102" s="3">
+        <v>560.77435000000003</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A103" s="3">
+        <v>70.140879999999996</v>
+      </c>
+      <c r="B103" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C103" s="3">
+        <v>5</v>
+      </c>
+      <c r="D103" s="3">
+        <v>6</v>
+      </c>
+      <c r="E103" s="3">
+        <v>26</v>
+      </c>
+      <c r="F103" s="5">
         <v>45803</v>
       </c>
-      <c r="G91" s="3">
+      <c r="G103" s="3">
         <v>630.9153</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="F92" s="5"/>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="F93" s="5"/>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="F94" s="5"/>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="F95" s="5"/>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="F96" s="5"/>
-    </row>
-    <row r="97" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F97" s="5"/>
-    </row>
-    <row r="98" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F98" s="5"/>
-    </row>
-    <row r="99" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F99" s="5"/>
-    </row>
-    <row r="100" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F100" s="5"/>
-    </row>
-    <row r="101" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F101" s="5"/>
-    </row>
-    <row r="102" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F102" s="5"/>
-    </row>
-    <row r="103" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F103" s="5"/>
-    </row>
-    <row r="104" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F104" s="5"/>
-    </row>
-    <row r="105" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F105" s="5"/>
-    </row>
-    <row r="106" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F106" s="5"/>
-    </row>
-    <row r="107" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F107" s="5"/>
-    </row>
-    <row r="108" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F108" s="5"/>
-    </row>
-    <row r="109" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F109" s="5"/>
-    </row>
-    <row r="110" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A104" s="3">
+        <v>53.365273000000002</v>
+      </c>
+      <c r="B104" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C104" s="3">
+        <v>6</v>
+      </c>
+      <c r="D104" s="3">
+        <v>1</v>
+      </c>
+      <c r="E104" s="3">
+        <v>1</v>
+      </c>
+      <c r="F104" s="5">
+        <v>45809</v>
+      </c>
+      <c r="G104" s="3">
+        <v>684.28049999999996</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A105" s="3">
+        <v>50.324043000000003</v>
+      </c>
+      <c r="B105" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C105" s="3">
+        <v>6</v>
+      </c>
+      <c r="D105" s="3">
+        <v>2</v>
+      </c>
+      <c r="E105" s="3">
+        <v>6</v>
+      </c>
+      <c r="F105" s="5">
+        <v>45814</v>
+      </c>
+      <c r="G105" s="3">
+        <v>734.60455000000002</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A106" s="3">
+        <v>54.202570000000001</v>
+      </c>
+      <c r="B106" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C106" s="3">
+        <v>6</v>
+      </c>
+      <c r="D106" s="3">
+        <v>3</v>
+      </c>
+      <c r="E106" s="3">
+        <v>11</v>
+      </c>
+      <c r="F106" s="5">
+        <v>45819</v>
+      </c>
+      <c r="G106" s="3">
+        <v>788.80709999999999</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A107" s="3">
+        <v>52.986744000000002</v>
+      </c>
+      <c r="B107" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C107" s="3">
+        <v>6</v>
+      </c>
+      <c r="D107" s="3">
+        <v>4</v>
+      </c>
+      <c r="E107" s="3">
+        <v>16</v>
+      </c>
+      <c r="F107" s="5">
+        <v>45824</v>
+      </c>
+      <c r="G107" s="3">
+        <v>841.79390000000001</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A108" s="3">
+        <v>54.639809999999997</v>
+      </c>
+      <c r="B108" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C108" s="3">
+        <v>6</v>
+      </c>
+      <c r="D108" s="3">
+        <v>5</v>
+      </c>
+      <c r="E108" s="3">
+        <v>21</v>
+      </c>
+      <c r="F108" s="5">
+        <v>45829</v>
+      </c>
+      <c r="G108" s="3">
+        <v>896.43370000000004</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A109" s="3">
+        <v>53.125706000000001</v>
+      </c>
+      <c r="B109" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C109" s="3">
+        <v>6</v>
+      </c>
+      <c r="D109" s="3">
+        <v>6</v>
+      </c>
+      <c r="E109" s="3">
+        <v>26</v>
+      </c>
+      <c r="F109" s="5">
+        <v>45834</v>
+      </c>
+      <c r="G109" s="3">
+        <v>949.55939999999998</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="F110" s="5"/>
     </row>
-    <row r="111" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="F111" s="5"/>
     </row>
-    <row r="112" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="F112" s="5"/>
     </row>
     <row r="113" spans="6:6" x14ac:dyDescent="0.35">
@@ -3984,7 +4407,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FB690C8-F874-4A1B-874A-043689354636}">
-  <dimension ref="A1:D226"/>
+  <dimension ref="A1:D271"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -3996,13 +4419,13 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>30</v>
@@ -7156,6 +7579,636 @@
       </c>
       <c r="D226" s="1" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A227" s="1">
+        <v>412.42966000000001</v>
+      </c>
+      <c r="B227" s="1">
+        <v>1981</v>
+      </c>
+      <c r="C227" s="1">
+        <v>93.78546</v>
+      </c>
+      <c r="D227" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A228" s="1">
+        <v>388.90449999999998</v>
+      </c>
+      <c r="B228" s="1">
+        <v>2010</v>
+      </c>
+      <c r="C228" s="1">
+        <v>70.260315000000006</v>
+      </c>
+      <c r="D228" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A229" s="1">
+        <v>378.89055999999999</v>
+      </c>
+      <c r="B229" s="1">
+        <v>1999</v>
+      </c>
+      <c r="C229" s="1">
+        <v>60.246369999999999</v>
+      </c>
+      <c r="D229" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A230" s="1">
+        <v>375.75745000000001</v>
+      </c>
+      <c r="B230" s="1">
+        <v>2003</v>
+      </c>
+      <c r="C230" s="1">
+        <v>57.113250000000001</v>
+      </c>
+      <c r="D230" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A231" s="1">
+        <v>359.53635000000003</v>
+      </c>
+      <c r="B231" s="1">
+        <v>1984</v>
+      </c>
+      <c r="C231" s="1">
+        <v>40.892150000000001</v>
+      </c>
+      <c r="D231" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A232" s="1">
+        <v>359.04486000000003</v>
+      </c>
+      <c r="B232" s="1">
+        <v>1995</v>
+      </c>
+      <c r="C232" s="1">
+        <v>40.400664999999996</v>
+      </c>
+      <c r="D232" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A233" s="1">
+        <v>351.57596000000001</v>
+      </c>
+      <c r="B233" s="1">
+        <v>2000</v>
+      </c>
+      <c r="C233" s="1">
+        <v>32.931762999999997</v>
+      </c>
+      <c r="D233" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A234" s="1">
+        <v>350.67970000000003</v>
+      </c>
+      <c r="B234" s="1">
+        <v>1985</v>
+      </c>
+      <c r="C234" s="1">
+        <v>32.035491999999998</v>
+      </c>
+      <c r="D234" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A235" s="1">
+        <v>348.84714000000002</v>
+      </c>
+      <c r="B235" s="1">
+        <v>1996</v>
+      </c>
+      <c r="C235" s="1">
+        <v>30.202942</v>
+      </c>
+      <c r="D235" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A236" s="1">
+        <v>346.64746000000002</v>
+      </c>
+      <c r="B236" s="1">
+        <v>2022</v>
+      </c>
+      <c r="C236" s="1">
+        <v>28.003264999999999</v>
+      </c>
+      <c r="D236" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A237" s="1">
+        <v>340.96289999999999</v>
+      </c>
+      <c r="B237" s="1">
+        <v>2025</v>
+      </c>
+      <c r="C237" s="1">
+        <v>22.318695000000002</v>
+      </c>
+      <c r="D237" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A238" s="1">
+        <v>335.71597000000003</v>
+      </c>
+      <c r="B238" s="1">
+        <v>1993</v>
+      </c>
+      <c r="C238" s="1">
+        <v>17.071777000000001</v>
+      </c>
+      <c r="D238" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A239" s="1">
+        <v>334.69310000000002</v>
+      </c>
+      <c r="B239" s="1">
+        <v>2018</v>
+      </c>
+      <c r="C239" s="1">
+        <v>16.048919999999999</v>
+      </c>
+      <c r="D239" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A240" s="1">
+        <v>332.9051</v>
+      </c>
+      <c r="B240" s="1">
+        <v>1998</v>
+      </c>
+      <c r="C240" s="1">
+        <v>14.260895</v>
+      </c>
+      <c r="D240" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A241" s="1">
+        <v>331.78951999999998</v>
+      </c>
+      <c r="B241" s="1">
+        <v>2007</v>
+      </c>
+      <c r="C241" s="1">
+        <v>13.145325</v>
+      </c>
+      <c r="D241" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A242" s="1">
+        <v>330.98039999999997</v>
+      </c>
+      <c r="B242" s="1">
+        <v>2014</v>
+      </c>
+      <c r="C242" s="1">
+        <v>12.336212</v>
+      </c>
+      <c r="D242" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A243" s="1">
+        <v>330.97899999999998</v>
+      </c>
+      <c r="B243" s="1">
+        <v>2024</v>
+      </c>
+      <c r="C243" s="1">
+        <v>12.334808000000001</v>
+      </c>
+      <c r="D243" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A244" s="1">
+        <v>328.94098000000002</v>
+      </c>
+      <c r="B244" s="1">
+        <v>2009</v>
+      </c>
+      <c r="C244" s="1">
+        <v>10.296783</v>
+      </c>
+      <c r="D244" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A245" s="1">
+        <v>328.32137999999998</v>
+      </c>
+      <c r="B245" s="1">
+        <v>1986</v>
+      </c>
+      <c r="C245" s="1">
+        <v>9.6771849999999997</v>
+      </c>
+      <c r="D245" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A246" s="1">
+        <v>327.98214999999999</v>
+      </c>
+      <c r="B246" s="1">
+        <v>1989</v>
+      </c>
+      <c r="C246" s="1">
+        <v>9.3379519999999996</v>
+      </c>
+      <c r="D246" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A247" s="1">
+        <v>325.80446999999998</v>
+      </c>
+      <c r="B247" s="1">
+        <v>2017</v>
+      </c>
+      <c r="C247" s="1">
+        <v>7.1602782999999999</v>
+      </c>
+      <c r="D247" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A248" s="1">
+        <v>324.33422999999999</v>
+      </c>
+      <c r="B248" s="1">
+        <v>2005</v>
+      </c>
+      <c r="C248" s="1">
+        <v>5.6900329999999997</v>
+      </c>
+      <c r="D248" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A249" s="1">
+        <v>320.15359999999998</v>
+      </c>
+      <c r="B249" s="1">
+        <v>2020</v>
+      </c>
+      <c r="C249" s="1">
+        <v>1.5093993999999999</v>
+      </c>
+      <c r="D249" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A250" s="1">
+        <v>319.02042</v>
+      </c>
+      <c r="B250" s="1">
+        <v>2011</v>
+      </c>
+      <c r="C250" s="1">
+        <v>0.37622070000000002</v>
+      </c>
+      <c r="D250" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A251" s="1">
+        <v>317.09717000000001</v>
+      </c>
+      <c r="B251" s="1">
+        <v>1994</v>
+      </c>
+      <c r="C251" s="1">
+        <v>-1.5470276000000001</v>
+      </c>
+      <c r="D251" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A252" s="1">
+        <v>316.98219999999998</v>
+      </c>
+      <c r="B252" s="1">
+        <v>1988</v>
+      </c>
+      <c r="C252" s="1">
+        <v>-1.6619873000000001</v>
+      </c>
+      <c r="D252" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A253" s="1">
+        <v>309.26373000000001</v>
+      </c>
+      <c r="B253" s="1">
+        <v>2006</v>
+      </c>
+      <c r="C253" s="1">
+        <v>-9.3804630000000007</v>
+      </c>
+      <c r="D253" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A254" s="1">
+        <v>309.02614999999997</v>
+      </c>
+      <c r="B254" s="1">
+        <v>1991</v>
+      </c>
+      <c r="C254" s="1">
+        <v>-9.6180420000000009</v>
+      </c>
+      <c r="D254" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A255" s="1">
+        <v>308.78082000000001</v>
+      </c>
+      <c r="B255" s="1">
+        <v>2019</v>
+      </c>
+      <c r="C255" s="1">
+        <v>-9.8633729999999993</v>
+      </c>
+      <c r="D255" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A256" s="1">
+        <v>306.12240000000003</v>
+      </c>
+      <c r="B256" s="1">
+        <v>1997</v>
+      </c>
+      <c r="C256" s="1">
+        <v>-12.521789999999999</v>
+      </c>
+      <c r="D256" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A257" s="1">
+        <v>300.94702000000001</v>
+      </c>
+      <c r="B257" s="1">
+        <v>2016</v>
+      </c>
+      <c r="C257" s="1">
+        <v>-17.697174</v>
+      </c>
+      <c r="D257" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A258" s="1">
+        <v>300.58987000000002</v>
+      </c>
+      <c r="B258" s="1">
+        <v>2008</v>
+      </c>
+      <c r="C258" s="1">
+        <v>-18.054321000000002</v>
+      </c>
+      <c r="D258" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A259" s="1">
+        <v>299.25803000000002</v>
+      </c>
+      <c r="B259" s="1">
+        <v>1982</v>
+      </c>
+      <c r="C259" s="1">
+        <v>-19.38617</v>
+      </c>
+      <c r="D259" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A260" s="1">
+        <v>296.29930000000002</v>
+      </c>
+      <c r="B260" s="1">
+        <v>2004</v>
+      </c>
+      <c r="C260" s="1">
+        <v>-22.344909999999999</v>
+      </c>
+      <c r="D260" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A261" s="1">
+        <v>294.9042</v>
+      </c>
+      <c r="B261" s="1">
+        <v>1983</v>
+      </c>
+      <c r="C261" s="1">
+        <v>-23.739989999999999</v>
+      </c>
+      <c r="D261" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A262" s="1">
+        <v>291.77699999999999</v>
+      </c>
+      <c r="B262" s="1">
+        <v>1987</v>
+      </c>
+      <c r="C262" s="1">
+        <v>-26.867187999999999</v>
+      </c>
+      <c r="D262" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A263" s="1">
+        <v>290.84426999999999</v>
+      </c>
+      <c r="B263" s="1">
+        <v>2013</v>
+      </c>
+      <c r="C263" s="1">
+        <v>-27.799927</v>
+      </c>
+      <c r="D263" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A264" s="1">
+        <v>289.06869999999998</v>
+      </c>
+      <c r="B264" s="1">
+        <v>2001</v>
+      </c>
+      <c r="C264" s="1">
+        <v>-29.575500000000002</v>
+      </c>
+      <c r="D264" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A265" s="1">
+        <v>278.96872000000002</v>
+      </c>
+      <c r="B265" s="1">
+        <v>1992</v>
+      </c>
+      <c r="C265" s="1">
+        <v>-39.675476000000003</v>
+      </c>
+      <c r="D265" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A266" s="1">
+        <v>276.43849999999998</v>
+      </c>
+      <c r="B266" s="1">
+        <v>2002</v>
+      </c>
+      <c r="C266" s="1">
+        <v>-42.205689999999997</v>
+      </c>
+      <c r="D266" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A267" s="1">
+        <v>270.19193000000001</v>
+      </c>
+      <c r="B267" s="1">
+        <v>1990</v>
+      </c>
+      <c r="C267" s="1">
+        <v>-48.452269999999999</v>
+      </c>
+      <c r="D267" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A268" s="1">
+        <v>270.07479999999998</v>
+      </c>
+      <c r="B268" s="1">
+        <v>2021</v>
+      </c>
+      <c r="C268" s="1">
+        <v>-48.569397000000002</v>
+      </c>
+      <c r="D268" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A269" s="1">
+        <v>267.18813999999998</v>
+      </c>
+      <c r="B269" s="1">
+        <v>2023</v>
+      </c>
+      <c r="C269" s="1">
+        <v>-51.456054999999999</v>
+      </c>
+      <c r="D269" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A270" s="1">
+        <v>245.10222999999999</v>
+      </c>
+      <c r="B270" s="1">
+        <v>2012</v>
+      </c>
+      <c r="C270" s="1">
+        <v>-73.541960000000003</v>
+      </c>
+      <c r="D270" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A271" s="1">
+        <v>243.41831999999999</v>
+      </c>
+      <c r="B271" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C271" s="1">
+        <v>-75.225876</v>
+      </c>
+      <c r="D271" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/Precipitacion/2025/2025_Ppt_Resumen_Datos.xlsx
+++ b/Precipitacion/2025/2025_Ppt_Resumen_Datos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Clima_Agua_Panama\Output_Raster_Files\Ppt\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15051042-F344-4583-8FD3-4D2FA4FB9047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B65A867E-9F47-4EC0-8C9F-67247ADE312B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8010" yWindow="21480" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="36">
   <si>
     <t>Jan</t>
   </si>
@@ -573,7 +573,9 @@
       <c r="G2" s="4">
         <v>383.32702999999998</v>
       </c>
-      <c r="H2" s="4"/>
+      <c r="H2" s="4">
+        <v>284.40334999999999</v>
+      </c>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
@@ -581,7 +583,7 @@
       <c r="M2" s="4"/>
       <c r="N2" s="4">
         <f>SUM(B2:M2)</f>
-        <v>1669.03665</v>
+        <v>1953.44</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="18" x14ac:dyDescent="0.35">
@@ -606,7 +608,9 @@
       <c r="G3" s="4">
         <v>245.99565000000001</v>
       </c>
-      <c r="H3" s="4"/>
+      <c r="H3" s="4">
+        <v>200.17044000000001</v>
+      </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
@@ -614,7 +618,7 @@
       <c r="M3" s="4"/>
       <c r="N3" s="4">
         <f t="shared" ref="N3:N14" si="0">SUM(B3:M3)</f>
-        <v>819.59180100000003</v>
+        <v>1019.762241</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="18" x14ac:dyDescent="0.35">
@@ -639,7 +643,9 @@
       <c r="G4" s="4">
         <v>355.76096000000001</v>
       </c>
-      <c r="H4" s="4"/>
+      <c r="H4" s="4">
+        <v>252.24438000000001</v>
+      </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
@@ -647,7 +653,7 @@
       <c r="M4" s="4"/>
       <c r="N4" s="4">
         <f t="shared" si="0"/>
-        <v>1425.3401600000002</v>
+        <v>1677.5845400000003</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="18" x14ac:dyDescent="0.35">
@@ -672,7 +678,9 @@
       <c r="G5" s="4">
         <v>324.73145</v>
       </c>
-      <c r="H5" s="4"/>
+      <c r="H5" s="4">
+        <v>194.70464999999999</v>
+      </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
@@ -680,7 +688,7 @@
       <c r="M5" s="4"/>
       <c r="N5" s="4">
         <f t="shared" si="0"/>
-        <v>1466.8906199999999</v>
+        <v>1661.5952699999998</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="18" x14ac:dyDescent="0.35">
@@ -705,7 +713,9 @@
       <c r="G6" s="4">
         <v>465.92676</v>
       </c>
-      <c r="H6" s="4"/>
+      <c r="H6" s="4">
+        <v>327.45929999999998</v>
+      </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
@@ -713,7 +723,7 @@
       <c r="M6" s="4"/>
       <c r="N6" s="4">
         <f t="shared" si="0"/>
-        <v>1487.31999</v>
+        <v>1814.7792899999999</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="18" x14ac:dyDescent="0.35">
@@ -738,7 +748,9 @@
       <c r="G7" s="4">
         <v>329.61144999999999</v>
       </c>
-      <c r="H7" s="4"/>
+      <c r="H7" s="4">
+        <v>315.71895999999998</v>
+      </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
@@ -746,7 +758,7 @@
       <c r="M7" s="4"/>
       <c r="N7" s="4">
         <f t="shared" si="0"/>
-        <v>1366.0912800000001</v>
+        <v>1681.81024</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="18" x14ac:dyDescent="0.35">
@@ -771,7 +783,9 @@
       <c r="G8" s="4">
         <v>471.96606000000003</v>
       </c>
-      <c r="H8" s="4"/>
+      <c r="H8" s="4">
+        <v>428.18927000000002</v>
+      </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
@@ -779,7 +793,7 @@
       <c r="M8" s="4"/>
       <c r="N8" s="4">
         <f t="shared" si="0"/>
-        <v>1730.3250799999998</v>
+        <v>2158.5143499999999</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="18" x14ac:dyDescent="0.35">
@@ -804,7 +818,9 @@
       <c r="G9" s="4">
         <v>346.21960000000001</v>
       </c>
-      <c r="H9" s="4"/>
+      <c r="H9" s="4">
+        <v>263.8451</v>
+      </c>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
@@ -812,7 +828,7 @@
       <c r="M9" s="4"/>
       <c r="N9" s="4">
         <f t="shared" si="0"/>
-        <v>1440.75218</v>
+        <v>1704.59728</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="18" x14ac:dyDescent="0.35">
@@ -837,7 +853,9 @@
       <c r="G10" s="4">
         <v>224.68445</v>
       </c>
-      <c r="H10" s="4"/>
+      <c r="H10" s="4">
+        <v>183.88315</v>
+      </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
@@ -845,7 +863,7 @@
       <c r="M10" s="4"/>
       <c r="N10" s="4">
         <f t="shared" si="0"/>
-        <v>727.02587459999995</v>
+        <v>910.90902459999995</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="18" x14ac:dyDescent="0.35">
@@ -870,7 +888,9 @@
       <c r="G11" s="4">
         <v>215.05295000000001</v>
       </c>
-      <c r="H11" s="4"/>
+      <c r="H11" s="4">
+        <v>155.66865999999999</v>
+      </c>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
@@ -878,7 +898,7 @@
       <c r="M11" s="4"/>
       <c r="N11" s="4">
         <f t="shared" si="0"/>
-        <v>565.75156470000002</v>
+        <v>721.42022470000006</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="18" x14ac:dyDescent="0.35">
@@ -903,7 +923,9 @@
       <c r="G12" s="4">
         <v>323.66699999999997</v>
       </c>
-      <c r="H12" s="4"/>
+      <c r="H12" s="4">
+        <v>179.92783</v>
+      </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
@@ -911,7 +933,7 @@
       <c r="M12" s="4"/>
       <c r="N12" s="4">
         <f t="shared" si="0"/>
-        <v>1211.2545749999999</v>
+        <v>1391.182405</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="18" x14ac:dyDescent="0.35">
@@ -936,7 +958,9 @@
       <c r="G13" s="4">
         <v>246.55710999999999</v>
       </c>
-      <c r="H13" s="4"/>
+      <c r="H13" s="4">
+        <v>181.36001999999999</v>
+      </c>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
@@ -944,7 +968,7 @@
       <c r="M13" s="4"/>
       <c r="N13" s="4">
         <f t="shared" si="0"/>
-        <v>814.99564699999996</v>
+        <v>996.35566699999993</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="18" x14ac:dyDescent="0.35">
@@ -969,7 +993,9 @@
       <c r="G14" s="4">
         <v>313.97109999999998</v>
       </c>
-      <c r="H14" s="4"/>
+      <c r="H14" s="4">
+        <v>283.88657000000001</v>
+      </c>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
@@ -977,7 +1003,7 @@
       <c r="M14" s="4"/>
       <c r="N14" s="4">
         <f t="shared" si="0"/>
-        <v>1143.2674099999999</v>
+        <v>1427.15398</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="18" x14ac:dyDescent="0.35">
@@ -985,30 +1011,33 @@
         <v>27</v>
       </c>
       <c r="B15" s="7">
-        <f>AVERAGE(B2:B14)</f>
+        <f t="shared" ref="B15:H15" si="1">AVERAGE(B2:B14)</f>
         <v>119.60806099999999</v>
       </c>
       <c r="C15" s="7">
-        <f>AVERAGE(C2:C14)</f>
+        <f t="shared" si="1"/>
         <v>141.85696423076922</v>
       </c>
       <c r="D15" s="7">
-        <f>AVERAGE(D2:D14)</f>
+        <f t="shared" si="1"/>
         <v>95.081919869230759</v>
       </c>
       <c r="E15" s="7">
-        <f>AVERAGE(E2:E14)</f>
+        <f t="shared" si="1"/>
         <v>179.89256353846156</v>
       </c>
       <c r="F15" s="7">
-        <f>AVERAGE(F2:F14)</f>
+        <f t="shared" si="1"/>
         <v>357.41981923076924</v>
       </c>
       <c r="G15" s="7">
-        <f>AVERAGE(G2:G14)</f>
+        <f t="shared" si="1"/>
         <v>326.72858230769236</v>
       </c>
-      <c r="H15" s="7"/>
+      <c r="H15" s="7">
+        <f t="shared" si="1"/>
+        <v>250.11243692307696</v>
+      </c>
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
@@ -1016,7 +1045,7 @@
       <c r="M15" s="7"/>
       <c r="N15" s="7">
         <f>SUM(B15:M15)</f>
-        <v>1220.5879101769233</v>
+        <v>1470.7003471000003</v>
       </c>
     </row>
   </sheetData>
@@ -1102,7 +1131,9 @@
       <c r="G2" s="4">
         <v>313.48110000000003</v>
       </c>
-      <c r="H2" s="4"/>
+      <c r="H2" s="4">
+        <v>322.49865999999997</v>
+      </c>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
@@ -1110,7 +1141,7 @@
       <c r="M2" s="4"/>
       <c r="N2" s="4">
         <f>SUM(B2:M2)</f>
-        <v>1349.0940399999999</v>
+        <v>1671.5926999999999</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
@@ -1135,15 +1166,17 @@
       <c r="G3" s="4">
         <v>277.30727999999999</v>
       </c>
-      <c r="H3" s="4"/>
+      <c r="H3" s="4">
+        <v>229.08197000000001</v>
+      </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4">
-        <f t="shared" ref="N3:N15" si="0">SUM(B3:M3)</f>
-        <v>702.11006099999997</v>
+        <f t="shared" ref="N3:N13" si="0">SUM(B3:M3)</f>
+        <v>931.19203100000004</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
@@ -1168,7 +1201,9 @@
       <c r="G4" s="4">
         <v>297.00170000000003</v>
       </c>
-      <c r="H4" s="4"/>
+      <c r="H4" s="4">
+        <v>284.52753000000001</v>
+      </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
@@ -1176,7 +1211,7 @@
       <c r="M4" s="4"/>
       <c r="N4" s="4">
         <f t="shared" si="0"/>
-        <v>883.74178000000006</v>
+        <v>1168.2693100000001</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.35">
@@ -1201,7 +1236,9 @@
       <c r="G5" s="4">
         <v>260.90872000000002</v>
       </c>
-      <c r="H5" s="4"/>
+      <c r="H5" s="4">
+        <v>251.78987000000001</v>
+      </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
@@ -1209,7 +1246,7 @@
       <c r="M5" s="4"/>
       <c r="N5" s="4">
         <f t="shared" si="0"/>
-        <v>793.67798099999993</v>
+        <v>1045.4678509999999</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
@@ -1234,7 +1271,9 @@
       <c r="G6" s="4">
         <v>417.40674000000001</v>
       </c>
-      <c r="H6" s="4"/>
+      <c r="H6" s="4">
+        <v>360.66199999999998</v>
+      </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
@@ -1242,7 +1281,7 @@
       <c r="M6" s="4"/>
       <c r="N6" s="4">
         <f t="shared" si="0"/>
-        <v>1147.233864</v>
+        <v>1507.8958640000001</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
@@ -1267,7 +1306,9 @@
       <c r="G7" s="4">
         <v>349.94116000000002</v>
       </c>
-      <c r="H7" s="4"/>
+      <c r="H7" s="4">
+        <v>365.65584999999999</v>
+      </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
@@ -1275,7 +1316,7 @@
       <c r="M7" s="4"/>
       <c r="N7" s="4">
         <f t="shared" si="0"/>
-        <v>1100.08626</v>
+        <v>1465.7421100000001</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
@@ -1300,7 +1341,9 @@
       <c r="G8" s="4">
         <v>427.839</v>
       </c>
-      <c r="H8" s="4"/>
+      <c r="H8" s="4">
+        <v>399.68682999999999</v>
+      </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
@@ -1308,7 +1351,7 @@
       <c r="M8" s="4"/>
       <c r="N8" s="4">
         <f t="shared" si="0"/>
-        <v>1310.8979749999999</v>
+        <v>1710.584805</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
@@ -1333,7 +1376,9 @@
       <c r="G9" s="4">
         <v>301.58535999999998</v>
       </c>
-      <c r="H9" s="4"/>
+      <c r="H9" s="4">
+        <v>291.41437000000002</v>
+      </c>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
@@ -1341,7 +1386,7 @@
       <c r="M9" s="4"/>
       <c r="N9" s="4">
         <f t="shared" si="0"/>
-        <v>856.49322299999994</v>
+        <v>1147.9075929999999</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
@@ -1366,7 +1411,9 @@
       <c r="G10" s="4">
         <v>251.28584000000001</v>
       </c>
-      <c r="H10" s="4"/>
+      <c r="H10" s="4">
+        <v>204.07721000000001</v>
+      </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
@@ -1374,7 +1421,7 @@
       <c r="M10" s="4"/>
       <c r="N10" s="4">
         <f t="shared" si="0"/>
-        <v>612.67717949999997</v>
+        <v>816.7543895</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
@@ -1399,7 +1446,9 @@
       <c r="G11" s="4">
         <v>204.78511</v>
       </c>
-      <c r="H11" s="4"/>
+      <c r="H11" s="4">
+        <v>191.22635</v>
+      </c>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
@@ -1407,7 +1456,7 @@
       <c r="M11" s="4"/>
       <c r="N11" s="4">
         <f t="shared" si="0"/>
-        <v>442.28223300000002</v>
+        <v>633.50858300000004</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
@@ -1432,7 +1481,9 @@
       <c r="G12" s="4">
         <v>274.49588</v>
       </c>
-      <c r="H12" s="4"/>
+      <c r="H12" s="4">
+        <v>241.55350000000001</v>
+      </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
@@ -1440,7 +1491,7 @@
       <c r="M12" s="4"/>
       <c r="N12" s="4">
         <f t="shared" si="0"/>
-        <v>745.66065900000001</v>
+        <v>987.214159</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
@@ -1465,7 +1516,9 @@
       <c r="G13" s="4">
         <v>241.35033999999999</v>
       </c>
-      <c r="H13" s="4"/>
+      <c r="H13" s="4">
+        <v>216.28813</v>
+      </c>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
@@ -1473,7 +1526,7 @@
       <c r="M13" s="4"/>
       <c r="N13" s="4">
         <f t="shared" si="0"/>
-        <v>680.58289300000001</v>
+        <v>896.87102300000004</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
@@ -1498,7 +1551,9 @@
       <c r="G14" s="4">
         <v>349.34494000000001</v>
       </c>
-      <c r="H14" s="4"/>
+      <c r="H14" s="4">
+        <v>329.54608000000002</v>
+      </c>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
@@ -1506,7 +1561,7 @@
       <c r="M14" s="4"/>
       <c r="N14" s="4">
         <f>SUM(B14:M14)</f>
-        <v>936.56652800000006</v>
+        <v>1266.1126080000001</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
@@ -1518,7 +1573,7 @@
         <v>67.513827307692296</v>
       </c>
       <c r="C15" s="7">
-        <f t="shared" ref="C15:G15" si="1">AVERAGE(C2:C14)</f>
+        <f t="shared" ref="C15:H15" si="1">AVERAGE(C2:C14)</f>
         <v>41.752843615384613</v>
       </c>
       <c r="D15" s="7">
@@ -1537,7 +1592,10 @@
         <f t="shared" si="1"/>
         <v>305.13332076923075</v>
       </c>
-      <c r="H15" s="2"/>
+      <c r="H15" s="7">
+        <f t="shared" si="1"/>
+        <v>283.69295</v>
+      </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
@@ -1545,7 +1603,7 @@
       <c r="M15" s="2"/>
       <c r="N15" s="7">
         <f>SUM(B15:M15)</f>
-        <v>889.31574434615391</v>
+        <v>1173.0086943461538</v>
       </c>
     </row>
   </sheetData>
@@ -2422,13 +2480,13 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
-        <v>51.443686999999997</v>
+        <v>48.680500000000002</v>
       </c>
       <c r="B38" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C38" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D38" s="3">
         <v>1</v>
@@ -2437,21 +2495,21 @@
         <v>1</v>
       </c>
       <c r="F38" s="5">
-        <v>45658</v>
+        <v>45839</v>
       </c>
       <c r="G38" s="3">
-        <v>51.443686999999997</v>
+        <v>939.12305000000003</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="3">
-        <v>30.218036999999999</v>
+        <v>35.615882999999997</v>
       </c>
       <c r="B39" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C39" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D39" s="3">
         <v>2</v>
@@ -2460,21 +2518,21 @@
         <v>6</v>
       </c>
       <c r="F39" s="5">
-        <v>45663</v>
+        <v>45844</v>
       </c>
       <c r="G39" s="3">
-        <v>81.661730000000006</v>
+        <v>974.73895000000005</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
-        <v>7.7399344000000001</v>
+        <v>46.791237000000002</v>
       </c>
       <c r="B40" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C40" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D40" s="3">
         <v>3</v>
@@ -2483,21 +2541,21 @@
         <v>11</v>
       </c>
       <c r="F40" s="5">
-        <v>45668</v>
+        <v>45849</v>
       </c>
       <c r="G40" s="3">
-        <v>89.401660000000007</v>
+        <v>1021.53015</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="3">
-        <v>11.712353999999999</v>
+        <v>50.363680000000002</v>
       </c>
       <c r="B41" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C41" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D41" s="3">
         <v>4</v>
@@ -2506,21 +2564,21 @@
         <v>16</v>
       </c>
       <c r="F41" s="5">
-        <v>45673</v>
+        <v>45854</v>
       </c>
       <c r="G41" s="3">
-        <v>101.11400999999999</v>
+        <v>1071.8938000000001</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
-        <v>8.5210749999999997</v>
+        <v>49.690567000000001</v>
       </c>
       <c r="B42" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C42" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D42" s="3">
         <v>5</v>
@@ -2529,21 +2587,21 @@
         <v>21</v>
       </c>
       <c r="F42" s="5">
-        <v>45678</v>
+        <v>45859</v>
       </c>
       <c r="G42" s="3">
-        <v>109.635086</v>
+        <v>1121.5844999999999</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
-        <v>9.6642530000000004</v>
+        <v>66.886566000000002</v>
       </c>
       <c r="B43" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C43" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D43" s="3">
         <v>6</v>
@@ -2552,21 +2610,21 @@
         <v>26</v>
       </c>
       <c r="F43" s="5">
-        <v>45683</v>
+        <v>45864</v>
       </c>
       <c r="G43" s="3">
-        <v>119.29934</v>
+        <v>1188.471</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
-        <v>14.432333</v>
+        <v>51.443686999999997</v>
       </c>
       <c r="B44" s="3">
         <v>2025</v>
       </c>
       <c r="C44" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D44" s="3">
         <v>1</v>
@@ -2575,21 +2633,21 @@
         <v>1</v>
       </c>
       <c r="F44" s="5">
-        <v>45689</v>
+        <v>45658</v>
       </c>
       <c r="G44" s="3">
-        <v>133.73167000000001</v>
+        <v>51.443686999999997</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
-        <v>8.7800480000000007</v>
+        <v>30.218036999999999</v>
       </c>
       <c r="B45" s="3">
         <v>2025</v>
       </c>
       <c r="C45" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D45" s="3">
         <v>2</v>
@@ -2598,21 +2656,21 @@
         <v>6</v>
       </c>
       <c r="F45" s="5">
-        <v>45694</v>
+        <v>45663</v>
       </c>
       <c r="G45" s="3">
-        <v>142.51172</v>
+        <v>81.661730000000006</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="3">
-        <v>36.847504000000001</v>
+        <v>7.7399344000000001</v>
       </c>
       <c r="B46" s="3">
         <v>2025</v>
       </c>
       <c r="C46" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46" s="3">
         <v>3</v>
@@ -2621,21 +2679,21 @@
         <v>11</v>
       </c>
       <c r="F46" s="5">
-        <v>45699</v>
+        <v>45668</v>
       </c>
       <c r="G46" s="3">
-        <v>179.35921999999999</v>
+        <v>89.401660000000007</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="3">
-        <v>47.512680000000003</v>
+        <v>11.712353999999999</v>
       </c>
       <c r="B47" s="3">
         <v>2025</v>
       </c>
       <c r="C47" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D47" s="3">
         <v>4</v>
@@ -2644,21 +2702,21 @@
         <v>16</v>
       </c>
       <c r="F47" s="5">
-        <v>45704</v>
+        <v>45673</v>
       </c>
       <c r="G47" s="3">
-        <v>226.87190000000001</v>
+        <v>101.11400999999999</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="3">
-        <v>11.339199000000001</v>
+        <v>8.5210749999999997</v>
       </c>
       <c r="B48" s="3">
         <v>2025</v>
       </c>
       <c r="C48" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D48" s="3">
         <v>5</v>
@@ -2667,21 +2725,21 @@
         <v>21</v>
       </c>
       <c r="F48" s="5">
-        <v>45709</v>
+        <v>45678</v>
       </c>
       <c r="G48" s="3">
-        <v>238.21109999999999</v>
+        <v>109.635086</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="3">
-        <v>5.0655327000000003</v>
+        <v>9.6642530000000004</v>
       </c>
       <c r="B49" s="3">
         <v>2025</v>
       </c>
       <c r="C49" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D49" s="3">
         <v>6</v>
@@ -2690,21 +2748,21 @@
         <v>26</v>
       </c>
       <c r="F49" s="5">
-        <v>45714</v>
+        <v>45683</v>
       </c>
       <c r="G49" s="3">
-        <v>243.27663999999999</v>
+        <v>119.29934</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="3">
-        <v>6.6873063999999998</v>
+        <v>14.432333</v>
       </c>
       <c r="B50" s="3">
         <v>2025</v>
       </c>
       <c r="C50" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D50" s="3">
         <v>1</v>
@@ -2713,21 +2771,21 @@
         <v>1</v>
       </c>
       <c r="F50" s="5">
-        <v>45717</v>
+        <v>45689</v>
       </c>
       <c r="G50" s="3">
-        <v>249.96394000000001</v>
+        <v>133.73167000000001</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="3">
-        <v>5.1503943999999997</v>
+        <v>8.7800480000000007</v>
       </c>
       <c r="B51" s="3">
         <v>2025</v>
       </c>
       <c r="C51" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D51" s="3">
         <v>2</v>
@@ -2736,21 +2794,21 @@
         <v>6</v>
       </c>
       <c r="F51" s="5">
-        <v>45722</v>
+        <v>45694</v>
       </c>
       <c r="G51" s="3">
-        <v>255.11433</v>
+        <v>142.51172</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="3">
-        <v>5.3021630000000002</v>
+        <v>36.847504000000001</v>
       </c>
       <c r="B52" s="3">
         <v>2025</v>
       </c>
       <c r="C52" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D52" s="3">
         <v>3</v>
@@ -2759,21 +2817,21 @@
         <v>11</v>
       </c>
       <c r="F52" s="5">
-        <v>45727</v>
+        <v>45699</v>
       </c>
       <c r="G52" s="3">
-        <v>260.41649999999998</v>
+        <v>179.35921999999999</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="3">
-        <v>7.7123569999999999</v>
+        <v>47.512680000000003</v>
       </c>
       <c r="B53" s="3">
         <v>2025</v>
       </c>
       <c r="C53" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D53" s="3">
         <v>4</v>
@@ -2782,21 +2840,21 @@
         <v>16</v>
       </c>
       <c r="F53" s="5">
-        <v>45732</v>
+        <v>45704</v>
       </c>
       <c r="G53" s="3">
-        <v>268.12885</v>
+        <v>226.87190000000001</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="3">
-        <v>24.789594999999998</v>
+        <v>11.339199000000001</v>
       </c>
       <c r="B54" s="3">
         <v>2025</v>
       </c>
       <c r="C54" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D54" s="3">
         <v>5</v>
@@ -2805,21 +2863,21 @@
         <v>21</v>
       </c>
       <c r="F54" s="5">
-        <v>45737</v>
+        <v>45709</v>
       </c>
       <c r="G54" s="3">
-        <v>292.91845999999998</v>
+        <v>238.21109999999999</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="3">
-        <v>23.760323</v>
+        <v>5.0655327000000003</v>
       </c>
       <c r="B55" s="3">
         <v>2025</v>
       </c>
       <c r="C55" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D55" s="3">
         <v>6</v>
@@ -2828,21 +2886,21 @@
         <v>26</v>
       </c>
       <c r="F55" s="5">
-        <v>45742</v>
+        <v>45714</v>
       </c>
       <c r="G55" s="3">
-        <v>316.67876999999999</v>
+        <v>243.27663999999999</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="3">
-        <v>30.345040000000001</v>
+        <v>6.6873063999999998</v>
       </c>
       <c r="B56" s="3">
         <v>2025</v>
       </c>
       <c r="C56" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D56" s="3">
         <v>1</v>
@@ -2851,21 +2909,21 @@
         <v>1</v>
       </c>
       <c r="F56" s="5">
-        <v>45748</v>
+        <v>45717</v>
       </c>
       <c r="G56" s="3">
-        <v>347.02379999999999</v>
+        <v>249.96394000000001</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="3">
-        <v>26.385961999999999</v>
+        <v>5.1503943999999997</v>
       </c>
       <c r="B57" s="3">
         <v>2025</v>
       </c>
       <c r="C57" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D57" s="3">
         <v>2</v>
@@ -2874,21 +2932,21 @@
         <v>6</v>
       </c>
       <c r="F57" s="5">
-        <v>45753</v>
+        <v>45722</v>
       </c>
       <c r="G57" s="3">
-        <v>373.40980000000002</v>
+        <v>255.11433</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="3">
-        <v>14.766463</v>
+        <v>5.3021630000000002</v>
       </c>
       <c r="B58" s="3">
         <v>2025</v>
       </c>
       <c r="C58" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D58" s="3">
         <v>3</v>
@@ -2897,21 +2955,21 @@
         <v>11</v>
       </c>
       <c r="F58" s="5">
-        <v>45758</v>
+        <v>45727</v>
       </c>
       <c r="G58" s="3">
-        <v>388.17624000000001</v>
+        <v>260.41649999999998</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="3">
-        <v>13.573518999999999</v>
+        <v>7.7123569999999999</v>
       </c>
       <c r="B59" s="3">
         <v>2025</v>
       </c>
       <c r="C59" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D59" s="3">
         <v>4</v>
@@ -2920,21 +2978,21 @@
         <v>16</v>
       </c>
       <c r="F59" s="5">
-        <v>45763</v>
+        <v>45732</v>
       </c>
       <c r="G59" s="3">
-        <v>401.74975999999998</v>
+        <v>268.12885</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="3">
-        <v>39.141010000000001</v>
+        <v>24.789594999999998</v>
       </c>
       <c r="B60" s="3">
         <v>2025</v>
       </c>
       <c r="C60" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D60" s="3">
         <v>5</v>
@@ -2943,21 +3001,21 @@
         <v>21</v>
       </c>
       <c r="F60" s="5">
-        <v>45768</v>
+        <v>45737</v>
       </c>
       <c r="G60" s="3">
-        <v>440.89078000000001</v>
+        <v>292.91845999999998</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="3">
-        <v>41.962490000000003</v>
+        <v>23.760323</v>
       </c>
       <c r="B61" s="3">
         <v>2025</v>
       </c>
       <c r="C61" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D61" s="3">
         <v>6</v>
@@ -2966,21 +3024,21 @@
         <v>26</v>
       </c>
       <c r="F61" s="5">
-        <v>45773</v>
+        <v>45742</v>
       </c>
       <c r="G61" s="3">
-        <v>482.85327000000001</v>
+        <v>316.67876999999999</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="3">
-        <v>55.322009999999999</v>
+        <v>30.345040000000001</v>
       </c>
       <c r="B62" s="3">
         <v>2025</v>
       </c>
       <c r="C62" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D62" s="3">
         <v>1</v>
@@ -2989,21 +3047,21 @@
         <v>1</v>
       </c>
       <c r="F62" s="5">
-        <v>45778</v>
+        <v>45748</v>
       </c>
       <c r="G62" s="3">
-        <v>538.17529999999999</v>
+        <v>347.02379999999999</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="3">
-        <v>48.162075000000002</v>
+        <v>26.385961999999999</v>
       </c>
       <c r="B63" s="3">
         <v>2025</v>
       </c>
       <c r="C63" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D63" s="3">
         <v>2</v>
@@ -3012,21 +3070,21 @@
         <v>6</v>
       </c>
       <c r="F63" s="5">
-        <v>45783</v>
+        <v>45753</v>
       </c>
       <c r="G63" s="3">
-        <v>586.33734000000004</v>
+        <v>373.40980000000002</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="3">
-        <v>73.489159999999998</v>
+        <v>14.766463</v>
       </c>
       <c r="B64" s="3">
         <v>2025</v>
       </c>
       <c r="C64" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D64" s="3">
         <v>3</v>
@@ -3035,21 +3093,21 @@
         <v>11</v>
       </c>
       <c r="F64" s="5">
-        <v>45788</v>
+        <v>45758</v>
       </c>
       <c r="G64" s="3">
-        <v>659.82654000000002</v>
+        <v>388.17624000000001</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="3">
-        <v>73.519165000000001</v>
+        <v>13.573518999999999</v>
       </c>
       <c r="B65" s="3">
         <v>2025</v>
       </c>
       <c r="C65" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D65" s="3">
         <v>4</v>
@@ -3058,21 +3116,21 @@
         <v>16</v>
       </c>
       <c r="F65" s="5">
-        <v>45793</v>
+        <v>45763</v>
       </c>
       <c r="G65" s="3">
-        <v>733.34569999999997</v>
+        <v>401.74975999999998</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="3">
-        <v>73.128426000000005</v>
+        <v>39.141010000000001</v>
       </c>
       <c r="B66" s="3">
         <v>2025</v>
       </c>
       <c r="C66" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D66" s="3">
         <v>5</v>
@@ -3081,21 +3139,21 @@
         <v>21</v>
       </c>
       <c r="F66" s="5">
-        <v>45798</v>
+        <v>45768</v>
       </c>
       <c r="G66" s="3">
-        <v>806.47410000000002</v>
+        <v>440.89078000000001</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="3">
-        <v>50.314039999999999</v>
+        <v>41.962490000000003</v>
       </c>
       <c r="B67" s="3">
         <v>2025</v>
       </c>
       <c r="C67" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D67" s="3">
         <v>6</v>
@@ -3104,21 +3162,21 @@
         <v>26</v>
       </c>
       <c r="F67" s="5">
-        <v>45803</v>
+        <v>45773</v>
       </c>
       <c r="G67" s="3">
-        <v>856.78814999999997</v>
+        <v>482.85327000000001</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="3">
-        <v>56.4529</v>
+        <v>55.322009999999999</v>
       </c>
       <c r="B68" s="3">
         <v>2025</v>
       </c>
       <c r="C68" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D68" s="3">
         <v>1</v>
@@ -3127,21 +3185,21 @@
         <v>1</v>
       </c>
       <c r="F68" s="5">
-        <v>45809</v>
+        <v>45778</v>
       </c>
       <c r="G68" s="3">
-        <v>913.24099999999999</v>
+        <v>538.17529999999999</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="3">
-        <v>77.087370000000007</v>
+        <v>48.162075000000002</v>
       </c>
       <c r="B69" s="3">
         <v>2025</v>
       </c>
       <c r="C69" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D69" s="3">
         <v>2</v>
@@ -3150,21 +3208,21 @@
         <v>6</v>
       </c>
       <c r="F69" s="5">
-        <v>45814</v>
+        <v>45783</v>
       </c>
       <c r="G69" s="3">
-        <v>990.32839999999999</v>
+        <v>586.33734000000004</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="3">
-        <v>52.885750000000002</v>
+        <v>73.489159999999998</v>
       </c>
       <c r="B70" s="3">
         <v>2025</v>
       </c>
       <c r="C70" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D70" s="3">
         <v>3</v>
@@ -3173,21 +3231,21 @@
         <v>11</v>
       </c>
       <c r="F70" s="5">
-        <v>45819</v>
+        <v>45788</v>
       </c>
       <c r="G70" s="3">
-        <v>1043.2140999999999</v>
+        <v>659.82654000000002</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="3">
-        <v>39.925694</v>
+        <v>73.519165000000001</v>
       </c>
       <c r="B71" s="3">
         <v>2025</v>
       </c>
       <c r="C71" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D71" s="3">
         <v>4</v>
@@ -3196,21 +3254,21 @@
         <v>16</v>
       </c>
       <c r="F71" s="5">
-        <v>45824</v>
+        <v>45793</v>
       </c>
       <c r="G71" s="3">
-        <v>1083.1398999999999</v>
+        <v>733.34569999999997</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="3">
-        <v>77.791659999999993</v>
+        <v>73.128426000000005</v>
       </c>
       <c r="B72" s="3">
         <v>2025</v>
       </c>
       <c r="C72" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D72" s="3">
         <v>5</v>
@@ -3219,21 +3277,21 @@
         <v>21</v>
       </c>
       <c r="F72" s="5">
-        <v>45829</v>
+        <v>45798</v>
       </c>
       <c r="G72" s="3">
-        <v>1160.9314999999999</v>
+        <v>806.47410000000002</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="3">
-        <v>36.81955</v>
+        <v>50.314039999999999</v>
       </c>
       <c r="B73" s="3">
         <v>2025</v>
       </c>
       <c r="C73" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D73" s="3">
         <v>6</v>
@@ -3242,21 +3300,21 @@
         <v>26</v>
       </c>
       <c r="F73" s="5">
-        <v>45834</v>
+        <v>45803</v>
       </c>
       <c r="G73" s="3">
-        <v>1197.7511</v>
+        <v>856.78814999999997</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="3">
-        <v>14.331683999999999</v>
+        <v>56.4529</v>
       </c>
       <c r="B74" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C74" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D74" s="3">
         <v>1</v>
@@ -3265,21 +3323,21 @@
         <v>1</v>
       </c>
       <c r="F74" s="5">
-        <v>45658</v>
+        <v>45809</v>
       </c>
       <c r="G74" s="3">
-        <v>14.331683999999999</v>
+        <v>913.24099999999999</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="3">
-        <v>14.564731</v>
+        <v>77.087370000000007</v>
       </c>
       <c r="B75" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C75" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D75" s="3">
         <v>2</v>
@@ -3288,21 +3346,21 @@
         <v>6</v>
       </c>
       <c r="F75" s="5">
-        <v>45663</v>
+        <v>45814</v>
       </c>
       <c r="G75" s="3">
-        <v>28.896415999999999</v>
+        <v>990.32839999999999</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="3">
-        <v>10.498049</v>
+        <v>52.885750000000002</v>
       </c>
       <c r="B76" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C76" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D76" s="3">
         <v>3</v>
@@ -3311,21 +3369,21 @@
         <v>11</v>
       </c>
       <c r="F76" s="5">
-        <v>45668</v>
+        <v>45819</v>
       </c>
       <c r="G76" s="3">
-        <v>39.394463000000002</v>
+        <v>1043.2140999999999</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="3">
-        <v>10.599313</v>
+        <v>39.925694</v>
       </c>
       <c r="B77" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C77" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D77" s="3">
         <v>4</v>
@@ -3334,21 +3392,21 @@
         <v>16</v>
       </c>
       <c r="F77" s="5">
-        <v>45673</v>
+        <v>45824</v>
       </c>
       <c r="G77" s="3">
-        <v>49.993774000000002</v>
+        <v>1083.1398999999999</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="3">
-        <v>9.7497159999999994</v>
+        <v>77.791659999999993</v>
       </c>
       <c r="B78" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C78" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D78" s="3">
         <v>5</v>
@@ -3357,21 +3415,21 @@
         <v>21</v>
       </c>
       <c r="F78" s="5">
-        <v>45678</v>
+        <v>45829</v>
       </c>
       <c r="G78" s="3">
-        <v>59.743492000000003</v>
+        <v>1160.9314999999999</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="3">
-        <v>8.0435770000000009</v>
+        <v>36.81955</v>
       </c>
       <c r="B79" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C79" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D79" s="3">
         <v>6</v>
@@ -3380,21 +3438,21 @@
         <v>26</v>
       </c>
       <c r="F79" s="5">
-        <v>45683</v>
+        <v>45834</v>
       </c>
       <c r="G79" s="3">
-        <v>67.78707</v>
+        <v>1197.7511</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="3">
-        <v>8.4454740000000008</v>
+        <v>57.959408000000003</v>
       </c>
       <c r="B80" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C80" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D80" s="3">
         <v>1</v>
@@ -3403,21 +3461,21 @@
         <v>1</v>
       </c>
       <c r="F80" s="5">
-        <v>45689</v>
+        <v>45839</v>
       </c>
       <c r="G80" s="3">
-        <v>76.232544000000004</v>
+        <v>1255.7103999999999</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="3">
-        <v>8.7416970000000003</v>
+        <v>46.852511999999997</v>
       </c>
       <c r="B81" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C81" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D81" s="3">
         <v>2</v>
@@ -3426,21 +3484,21 @@
         <v>6</v>
       </c>
       <c r="F81" s="5">
-        <v>45694</v>
+        <v>45844</v>
       </c>
       <c r="G81" s="3">
-        <v>84.974239999999995</v>
+        <v>1302.5630000000001</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="3">
-        <v>9.234057</v>
+        <v>33.046745000000001</v>
       </c>
       <c r="B82" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C82" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D82" s="3">
         <v>3</v>
@@ -3449,21 +3507,21 @@
         <v>11</v>
       </c>
       <c r="F82" s="5">
-        <v>45699</v>
+        <v>45849</v>
       </c>
       <c r="G82" s="3">
-        <v>94.208299999999994</v>
+        <v>1335.6097</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="3">
-        <v>8.8217879999999997</v>
+        <v>26.622522</v>
       </c>
       <c r="B83" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C83" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D83" s="3">
         <v>4</v>
@@ -3472,21 +3530,21 @@
         <v>16</v>
       </c>
       <c r="F83" s="5">
-        <v>45704</v>
+        <v>45854</v>
       </c>
       <c r="G83" s="3">
-        <v>103.03008</v>
+        <v>1362.2322999999999</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="3">
-        <v>7.0881577</v>
+        <v>49.471679999999999</v>
       </c>
       <c r="B84" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C84" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D84" s="3">
         <v>5</v>
@@ -3495,21 +3553,21 @@
         <v>21</v>
       </c>
       <c r="F84" s="5">
-        <v>45709</v>
+        <v>45859</v>
       </c>
       <c r="G84" s="3">
-        <v>110.11824</v>
+        <v>1411.704</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="3">
-        <v>5.2113975999999997</v>
+        <v>50.246727</v>
       </c>
       <c r="B85" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C85" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D85" s="3">
         <v>6</v>
@@ -3518,21 +3576,21 @@
         <v>26</v>
       </c>
       <c r="F85" s="5">
-        <v>45714</v>
+        <v>45864</v>
       </c>
       <c r="G85" s="3">
-        <v>115.32964</v>
+        <v>1461.9507000000001</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="3">
-        <v>9.0188410000000001</v>
+        <v>14.331683999999999</v>
       </c>
       <c r="B86" s="3">
         <v>1991</v>
       </c>
       <c r="C86" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D86" s="3">
         <v>1</v>
@@ -3541,21 +3599,21 @@
         <v>1</v>
       </c>
       <c r="F86" s="5">
-        <v>45717</v>
+        <v>45658</v>
       </c>
       <c r="G86" s="3">
-        <v>124.34848</v>
+        <v>14.331683999999999</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="3">
-        <v>6.5476109999999998</v>
+        <v>14.564731</v>
       </c>
       <c r="B87" s="3">
         <v>1991</v>
       </c>
       <c r="C87" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D87" s="3">
         <v>2</v>
@@ -3564,21 +3622,21 @@
         <v>6</v>
       </c>
       <c r="F87" s="5">
-        <v>45722</v>
+        <v>45663</v>
       </c>
       <c r="G87" s="3">
-        <v>130.89608999999999</v>
+        <v>28.896415999999999</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="3">
-        <v>7.5543903999999999</v>
+        <v>10.498049</v>
       </c>
       <c r="B88" s="3">
         <v>1991</v>
       </c>
       <c r="C88" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D88" s="3">
         <v>3</v>
@@ -3587,21 +3645,21 @@
         <v>11</v>
       </c>
       <c r="F88" s="5">
-        <v>45727</v>
+        <v>45668</v>
       </c>
       <c r="G88" s="3">
-        <v>138.45049</v>
+        <v>39.394463000000002</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="3">
-        <v>10.259204</v>
+        <v>10.599313</v>
       </c>
       <c r="B89" s="3">
         <v>1991</v>
       </c>
       <c r="C89" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D89" s="3">
         <v>4</v>
@@ -3610,21 +3668,21 @@
         <v>16</v>
       </c>
       <c r="F89" s="5">
-        <v>45732</v>
+        <v>45673</v>
       </c>
       <c r="G89" s="3">
-        <v>148.70968999999999</v>
+        <v>49.993774000000002</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="3">
-        <v>8.8252439999999996</v>
+        <v>9.7497159999999994</v>
       </c>
       <c r="B90" s="3">
         <v>1991</v>
       </c>
       <c r="C90" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D90" s="3">
         <v>5</v>
@@ -3633,21 +3691,21 @@
         <v>21</v>
       </c>
       <c r="F90" s="5">
-        <v>45737</v>
+        <v>45678</v>
       </c>
       <c r="G90" s="3">
-        <v>157.53493</v>
+        <v>59.743492000000003</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="3">
-        <v>11.316482000000001</v>
+        <v>8.0435770000000009</v>
       </c>
       <c r="B91" s="3">
         <v>1991</v>
       </c>
       <c r="C91" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D91" s="3">
         <v>6</v>
@@ -3656,21 +3714,21 @@
         <v>26</v>
       </c>
       <c r="F91" s="5">
-        <v>45742</v>
+        <v>45683</v>
       </c>
       <c r="G91" s="3">
-        <v>168.85140999999999</v>
+        <v>67.78707</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="3">
-        <v>13.784658</v>
+        <v>8.4454740000000008</v>
       </c>
       <c r="B92" s="3">
         <v>1991</v>
       </c>
       <c r="C92" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D92" s="3">
         <v>1</v>
@@ -3679,21 +3737,21 @@
         <v>1</v>
       </c>
       <c r="F92" s="5">
-        <v>45748</v>
+        <v>45689</v>
       </c>
       <c r="G92" s="3">
-        <v>182.63607999999999</v>
+        <v>76.232544000000004</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="3">
-        <v>18.13364</v>
+        <v>8.7416970000000003</v>
       </c>
       <c r="B93" s="3">
         <v>1991</v>
       </c>
       <c r="C93" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D93" s="3">
         <v>2</v>
@@ -3702,21 +3760,21 @@
         <v>6</v>
       </c>
       <c r="F93" s="5">
-        <v>45753</v>
+        <v>45694</v>
       </c>
       <c r="G93" s="3">
-        <v>200.76971</v>
+        <v>84.974239999999995</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="3">
-        <v>14.012308000000001</v>
+        <v>9.234057</v>
       </c>
       <c r="B94" s="3">
         <v>1991</v>
       </c>
       <c r="C94" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D94" s="3">
         <v>3</v>
@@ -3725,21 +3783,21 @@
         <v>11</v>
       </c>
       <c r="F94" s="5">
-        <v>45758</v>
+        <v>45699</v>
       </c>
       <c r="G94" s="3">
-        <v>214.78201000000001</v>
+        <v>94.208299999999994</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="3">
-        <v>16.865030000000001</v>
+        <v>8.8217879999999997</v>
       </c>
       <c r="B95" s="3">
         <v>1991</v>
       </c>
       <c r="C95" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D95" s="3">
         <v>4</v>
@@ -3748,21 +3806,21 @@
         <v>16</v>
       </c>
       <c r="F95" s="5">
-        <v>45763</v>
+        <v>45704</v>
       </c>
       <c r="G95" s="3">
-        <v>231.64705000000001</v>
+        <v>103.03008</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="3">
-        <v>32.868423</v>
+        <v>7.0881577</v>
       </c>
       <c r="B96" s="3">
         <v>1991</v>
       </c>
       <c r="C96" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D96" s="3">
         <v>5</v>
@@ -3771,21 +3829,21 @@
         <v>21</v>
       </c>
       <c r="F96" s="5">
-        <v>45768</v>
+        <v>45709</v>
       </c>
       <c r="G96" s="3">
-        <v>264.51546999999999</v>
+        <v>110.11824</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="3">
-        <v>42.111977000000003</v>
+        <v>5.2113975999999997</v>
       </c>
       <c r="B97" s="3">
         <v>1991</v>
       </c>
       <c r="C97" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D97" s="3">
         <v>6</v>
@@ -3794,21 +3852,21 @@
         <v>26</v>
       </c>
       <c r="F97" s="5">
-        <v>45773</v>
+        <v>45714</v>
       </c>
       <c r="G97" s="3">
-        <v>306.62743999999998</v>
+        <v>115.32964</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="3">
-        <v>42.059672999999997</v>
+        <v>9.0188410000000001</v>
       </c>
       <c r="B98" s="3">
         <v>1991</v>
       </c>
       <c r="C98" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D98" s="3">
         <v>1</v>
@@ -3817,21 +3875,21 @@
         <v>1</v>
       </c>
       <c r="F98" s="5">
-        <v>45778</v>
+        <v>45717</v>
       </c>
       <c r="G98" s="3">
-        <v>348.68713000000002</v>
+        <v>124.34848</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="3">
-        <v>45.601909999999997</v>
+        <v>6.5476109999999998</v>
       </c>
       <c r="B99" s="3">
         <v>1991</v>
       </c>
       <c r="C99" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D99" s="3">
         <v>2</v>
@@ -3840,21 +3898,21 @@
         <v>6</v>
       </c>
       <c r="F99" s="5">
-        <v>45783</v>
+        <v>45722</v>
       </c>
       <c r="G99" s="3">
-        <v>394.28903000000003</v>
+        <v>130.89608999999999</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="3">
-        <v>50.457825</v>
+        <v>7.5543903999999999</v>
       </c>
       <c r="B100" s="3">
         <v>1991</v>
       </c>
       <c r="C100" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D100" s="3">
         <v>3</v>
@@ -3863,21 +3921,21 @@
         <v>11</v>
       </c>
       <c r="F100" s="5">
-        <v>45788</v>
+        <v>45727</v>
       </c>
       <c r="G100" s="3">
-        <v>444.74686000000003</v>
+        <v>138.45049</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="3">
-        <v>60.332355</v>
+        <v>10.259204</v>
       </c>
       <c r="B101" s="3">
         <v>1991</v>
       </c>
       <c r="C101" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D101" s="3">
         <v>4</v>
@@ -3886,21 +3944,21 @@
         <v>16</v>
       </c>
       <c r="F101" s="5">
-        <v>45793</v>
+        <v>45732</v>
       </c>
       <c r="G101" s="3">
-        <v>505.07922000000002</v>
+        <v>148.70968999999999</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="3">
-        <v>55.695160000000001</v>
+        <v>8.8252439999999996</v>
       </c>
       <c r="B102" s="3">
         <v>1991</v>
       </c>
       <c r="C102" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D102" s="3">
         <v>5</v>
@@ -3909,21 +3967,21 @@
         <v>21</v>
       </c>
       <c r="F102" s="5">
-        <v>45798</v>
+        <v>45737</v>
       </c>
       <c r="G102" s="3">
-        <v>560.77435000000003</v>
+        <v>157.53493</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="3">
-        <v>70.140879999999996</v>
+        <v>11.316482000000001</v>
       </c>
       <c r="B103" s="3">
         <v>1991</v>
       </c>
       <c r="C103" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D103" s="3">
         <v>6</v>
@@ -3932,21 +3990,21 @@
         <v>26</v>
       </c>
       <c r="F103" s="5">
-        <v>45803</v>
+        <v>45742</v>
       </c>
       <c r="G103" s="3">
-        <v>630.9153</v>
+        <v>168.85140999999999</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="3">
-        <v>53.365273000000002</v>
+        <v>13.784658</v>
       </c>
       <c r="B104" s="3">
         <v>1991</v>
       </c>
       <c r="C104" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D104" s="3">
         <v>1</v>
@@ -3955,21 +4013,21 @@
         <v>1</v>
       </c>
       <c r="F104" s="5">
-        <v>45809</v>
+        <v>45748</v>
       </c>
       <c r="G104" s="3">
-        <v>684.28049999999996</v>
+        <v>182.63607999999999</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="3">
-        <v>50.324043000000003</v>
+        <v>18.13364</v>
       </c>
       <c r="B105" s="3">
         <v>1991</v>
       </c>
       <c r="C105" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D105" s="3">
         <v>2</v>
@@ -3978,21 +4036,21 @@
         <v>6</v>
       </c>
       <c r="F105" s="5">
-        <v>45814</v>
+        <v>45753</v>
       </c>
       <c r="G105" s="3">
-        <v>734.60455000000002</v>
+        <v>200.76971</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="3">
-        <v>54.202570000000001</v>
+        <v>14.012308000000001</v>
       </c>
       <c r="B106" s="3">
         <v>1991</v>
       </c>
       <c r="C106" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D106" s="3">
         <v>3</v>
@@ -4001,21 +4059,21 @@
         <v>11</v>
       </c>
       <c r="F106" s="5">
-        <v>45819</v>
+        <v>45758</v>
       </c>
       <c r="G106" s="3">
-        <v>788.80709999999999</v>
+        <v>214.78201000000001</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="3">
-        <v>52.986744000000002</v>
+        <v>16.865030000000001</v>
       </c>
       <c r="B107" s="3">
         <v>1991</v>
       </c>
       <c r="C107" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D107" s="3">
         <v>4</v>
@@ -4024,21 +4082,21 @@
         <v>16</v>
       </c>
       <c r="F107" s="5">
-        <v>45824</v>
+        <v>45763</v>
       </c>
       <c r="G107" s="3">
-        <v>841.79390000000001</v>
+        <v>231.64705000000001</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="3">
-        <v>54.639809999999997</v>
+        <v>32.868423</v>
       </c>
       <c r="B108" s="3">
         <v>1991</v>
       </c>
       <c r="C108" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D108" s="3">
         <v>5</v>
@@ -4047,21 +4105,21 @@
         <v>21</v>
       </c>
       <c r="F108" s="5">
-        <v>45829</v>
+        <v>45768</v>
       </c>
       <c r="G108" s="3">
-        <v>896.43370000000004</v>
+        <v>264.51546999999999</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="3">
-        <v>53.125706000000001</v>
+        <v>42.111977000000003</v>
       </c>
       <c r="B109" s="3">
         <v>1991</v>
       </c>
       <c r="C109" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D109" s="3">
         <v>6</v>
@@ -4070,67 +4128,427 @@
         <v>26</v>
       </c>
       <c r="F109" s="5">
+        <v>45773</v>
+      </c>
+      <c r="G109" s="3">
+        <v>306.62743999999998</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A110" s="3">
+        <v>42.059672999999997</v>
+      </c>
+      <c r="B110" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C110" s="3">
+        <v>5</v>
+      </c>
+      <c r="D110" s="3">
+        <v>1</v>
+      </c>
+      <c r="E110" s="3">
+        <v>1</v>
+      </c>
+      <c r="F110" s="5">
+        <v>45778</v>
+      </c>
+      <c r="G110" s="3">
+        <v>348.68713000000002</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A111" s="3">
+        <v>45.601909999999997</v>
+      </c>
+      <c r="B111" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C111" s="3">
+        <v>5</v>
+      </c>
+      <c r="D111" s="3">
+        <v>2</v>
+      </c>
+      <c r="E111" s="3">
+        <v>6</v>
+      </c>
+      <c r="F111" s="5">
+        <v>45783</v>
+      </c>
+      <c r="G111" s="3">
+        <v>394.28903000000003</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A112" s="3">
+        <v>50.457825</v>
+      </c>
+      <c r="B112" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C112" s="3">
+        <v>5</v>
+      </c>
+      <c r="D112" s="3">
+        <v>3</v>
+      </c>
+      <c r="E112" s="3">
+        <v>11</v>
+      </c>
+      <c r="F112" s="5">
+        <v>45788</v>
+      </c>
+      <c r="G112" s="3">
+        <v>444.74686000000003</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A113" s="3">
+        <v>60.332355</v>
+      </c>
+      <c r="B113" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C113" s="3">
+        <v>5</v>
+      </c>
+      <c r="D113" s="3">
+        <v>4</v>
+      </c>
+      <c r="E113" s="3">
+        <v>16</v>
+      </c>
+      <c r="F113" s="5">
+        <v>45793</v>
+      </c>
+      <c r="G113" s="3">
+        <v>505.07922000000002</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A114" s="3">
+        <v>55.695160000000001</v>
+      </c>
+      <c r="B114" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C114" s="3">
+        <v>5</v>
+      </c>
+      <c r="D114" s="3">
+        <v>5</v>
+      </c>
+      <c r="E114" s="3">
+        <v>21</v>
+      </c>
+      <c r="F114" s="5">
+        <v>45798</v>
+      </c>
+      <c r="G114" s="3">
+        <v>560.77435000000003</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A115" s="3">
+        <v>70.140879999999996</v>
+      </c>
+      <c r="B115" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C115" s="3">
+        <v>5</v>
+      </c>
+      <c r="D115" s="3">
+        <v>6</v>
+      </c>
+      <c r="E115" s="3">
+        <v>26</v>
+      </c>
+      <c r="F115" s="5">
+        <v>45803</v>
+      </c>
+      <c r="G115" s="3">
+        <v>630.9153</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A116" s="3">
+        <v>53.365273000000002</v>
+      </c>
+      <c r="B116" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C116" s="3">
+        <v>6</v>
+      </c>
+      <c r="D116" s="3">
+        <v>1</v>
+      </c>
+      <c r="E116" s="3">
+        <v>1</v>
+      </c>
+      <c r="F116" s="5">
+        <v>45809</v>
+      </c>
+      <c r="G116" s="3">
+        <v>684.28049999999996</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A117" s="3">
+        <v>50.324043000000003</v>
+      </c>
+      <c r="B117" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C117" s="3">
+        <v>6</v>
+      </c>
+      <c r="D117" s="3">
+        <v>2</v>
+      </c>
+      <c r="E117" s="3">
+        <v>6</v>
+      </c>
+      <c r="F117" s="5">
+        <v>45814</v>
+      </c>
+      <c r="G117" s="3">
+        <v>734.60455000000002</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A118" s="3">
+        <v>54.202570000000001</v>
+      </c>
+      <c r="B118" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C118" s="3">
+        <v>6</v>
+      </c>
+      <c r="D118" s="3">
+        <v>3</v>
+      </c>
+      <c r="E118" s="3">
+        <v>11</v>
+      </c>
+      <c r="F118" s="5">
+        <v>45819</v>
+      </c>
+      <c r="G118" s="3">
+        <v>788.80709999999999</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A119" s="3">
+        <v>52.986744000000002</v>
+      </c>
+      <c r="B119" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C119" s="3">
+        <v>6</v>
+      </c>
+      <c r="D119" s="3">
+        <v>4</v>
+      </c>
+      <c r="E119" s="3">
+        <v>16</v>
+      </c>
+      <c r="F119" s="5">
+        <v>45824</v>
+      </c>
+      <c r="G119" s="3">
+        <v>841.79390000000001</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A120" s="3">
+        <v>54.639809999999997</v>
+      </c>
+      <c r="B120" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C120" s="3">
+        <v>6</v>
+      </c>
+      <c r="D120" s="3">
+        <v>5</v>
+      </c>
+      <c r="E120" s="3">
+        <v>21</v>
+      </c>
+      <c r="F120" s="5">
+        <v>45829</v>
+      </c>
+      <c r="G120" s="3">
+        <v>896.43370000000004</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A121" s="3">
+        <v>53.125706000000001</v>
+      </c>
+      <c r="B121" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C121" s="3">
+        <v>6</v>
+      </c>
+      <c r="D121" s="3">
+        <v>6</v>
+      </c>
+      <c r="E121" s="3">
+        <v>26</v>
+      </c>
+      <c r="F121" s="5">
         <v>45834</v>
       </c>
-      <c r="G109" s="3">
+      <c r="G121" s="3">
         <v>949.55939999999998</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="F110" s="5"/>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="F111" s="5"/>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="F112" s="5"/>
-    </row>
-    <row r="113" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F113" s="5"/>
-    </row>
-    <row r="114" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F114" s="5"/>
-    </row>
-    <row r="115" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F115" s="5"/>
-    </row>
-    <row r="116" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F116" s="5"/>
-    </row>
-    <row r="117" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F117" s="5"/>
-    </row>
-    <row r="118" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F118" s="5"/>
-    </row>
-    <row r="119" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F119" s="5"/>
-    </row>
-    <row r="120" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F120" s="5"/>
-    </row>
-    <row r="121" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F121" s="5"/>
-    </row>
-    <row r="122" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F122" s="5"/>
-    </row>
-    <row r="123" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F123" s="5"/>
-    </row>
-    <row r="124" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F124" s="5"/>
-    </row>
-    <row r="125" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F125" s="5"/>
-    </row>
-    <row r="126" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F126" s="5"/>
-    </row>
-    <row r="127" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F127" s="5"/>
-    </row>
-    <row r="128" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A122" s="3">
+        <v>46.782597000000003</v>
+      </c>
+      <c r="B122" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C122" s="3">
+        <v>7</v>
+      </c>
+      <c r="D122" s="3">
+        <v>1</v>
+      </c>
+      <c r="E122" s="3">
+        <v>1</v>
+      </c>
+      <c r="F122" s="5">
+        <v>45839</v>
+      </c>
+      <c r="G122" s="3">
+        <v>996.34199999999998</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A123" s="3">
+        <v>47.738444999999999</v>
+      </c>
+      <c r="B123" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C123" s="3">
+        <v>7</v>
+      </c>
+      <c r="D123" s="3">
+        <v>2</v>
+      </c>
+      <c r="E123" s="3">
+        <v>6</v>
+      </c>
+      <c r="F123" s="5">
+        <v>45844</v>
+      </c>
+      <c r="G123" s="3">
+        <v>1044.0804000000001</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A124" s="3">
+        <v>48.982050000000001</v>
+      </c>
+      <c r="B124" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C124" s="3">
+        <v>7</v>
+      </c>
+      <c r="D124" s="3">
+        <v>3</v>
+      </c>
+      <c r="E124" s="3">
+        <v>11</v>
+      </c>
+      <c r="F124" s="5">
+        <v>45849</v>
+      </c>
+      <c r="G124" s="3">
+        <v>1093.0625</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A125" s="3">
+        <v>45.302666000000002</v>
+      </c>
+      <c r="B125" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C125" s="3">
+        <v>7</v>
+      </c>
+      <c r="D125" s="3">
+        <v>4</v>
+      </c>
+      <c r="E125" s="3">
+        <v>16</v>
+      </c>
+      <c r="F125" s="5">
+        <v>45854</v>
+      </c>
+      <c r="G125" s="3">
+        <v>1138.3651</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A126" s="3">
+        <v>45.867165</v>
+      </c>
+      <c r="B126" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C126" s="3">
+        <v>7</v>
+      </c>
+      <c r="D126" s="3">
+        <v>5</v>
+      </c>
+      <c r="E126" s="3">
+        <v>21</v>
+      </c>
+      <c r="F126" s="5">
+        <v>45859</v>
+      </c>
+      <c r="G126" s="3">
+        <v>1184.2322999999999</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A127" s="3">
+        <v>62.545997999999997</v>
+      </c>
+      <c r="B127" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C127" s="3">
+        <v>7</v>
+      </c>
+      <c r="D127" s="3">
+        <v>6</v>
+      </c>
+      <c r="E127" s="3">
+        <v>26</v>
+      </c>
+      <c r="F127" s="5">
+        <v>45864</v>
+      </c>
+      <c r="G127" s="3">
+        <v>1246.7782999999999</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="F128" s="5"/>
     </row>
     <row r="129" spans="6:6" x14ac:dyDescent="0.35">
@@ -4407,7 +4825,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FB690C8-F874-4A1B-874A-043689354636}">
-  <dimension ref="A1:D271"/>
+  <dimension ref="A1:D316"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -8211,6 +8629,636 @@
         <v>19</v>
       </c>
     </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A272" s="1">
+        <v>384.13630000000001</v>
+      </c>
+      <c r="B272" s="1">
+        <v>2010</v>
+      </c>
+      <c r="C272" s="1">
+        <v>86.917450000000002</v>
+      </c>
+      <c r="D272" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A273" s="1">
+        <v>375.09998000000002</v>
+      </c>
+      <c r="B273" s="1">
+        <v>2008</v>
+      </c>
+      <c r="C273" s="1">
+        <v>77.881134000000003</v>
+      </c>
+      <c r="D273" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A274" s="1">
+        <v>360.91469999999998</v>
+      </c>
+      <c r="B274" s="1">
+        <v>2006</v>
+      </c>
+      <c r="C274" s="1">
+        <v>63.695860000000003</v>
+      </c>
+      <c r="D274" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A275" s="1">
+        <v>353.62795999999997</v>
+      </c>
+      <c r="B275" s="1">
+        <v>1987</v>
+      </c>
+      <c r="C275" s="1">
+        <v>56.409120000000001</v>
+      </c>
+      <c r="D275" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A276" s="1">
+        <v>344.53307999999998</v>
+      </c>
+      <c r="B276" s="1">
+        <v>2011</v>
+      </c>
+      <c r="C276" s="1">
+        <v>47.314239999999998</v>
+      </c>
+      <c r="D276" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A277" s="1">
+        <v>340.25873000000001</v>
+      </c>
+      <c r="B277" s="1">
+        <v>2002</v>
+      </c>
+      <c r="C277" s="1">
+        <v>43.039886000000003</v>
+      </c>
+      <c r="D277" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A278" s="1">
+        <v>337.63740000000001</v>
+      </c>
+      <c r="B278" s="1">
+        <v>2003</v>
+      </c>
+      <c r="C278" s="1">
+        <v>40.418550000000003</v>
+      </c>
+      <c r="D278" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A279" s="1">
+        <v>336.08102000000002</v>
+      </c>
+      <c r="B279" s="1">
+        <v>2017</v>
+      </c>
+      <c r="C279" s="1">
+        <v>38.862183000000002</v>
+      </c>
+      <c r="D279" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A280" s="1">
+        <v>331.00583</v>
+      </c>
+      <c r="B280" s="1">
+        <v>1995</v>
+      </c>
+      <c r="C280" s="1">
+        <v>33.786987000000003</v>
+      </c>
+      <c r="D280" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A281" s="1">
+        <v>327.15552000000002</v>
+      </c>
+      <c r="B281" s="1">
+        <v>1998</v>
+      </c>
+      <c r="C281" s="1">
+        <v>29.936675999999999</v>
+      </c>
+      <c r="D281" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A282" s="1">
+        <v>325.19765999999998</v>
+      </c>
+      <c r="B282" s="1">
+        <v>1988</v>
+      </c>
+      <c r="C282" s="1">
+        <v>27.978819999999999</v>
+      </c>
+      <c r="D282" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A283" s="1">
+        <v>324.9468</v>
+      </c>
+      <c r="B283" s="1">
+        <v>1984</v>
+      </c>
+      <c r="C283" s="1">
+        <v>27.727965999999999</v>
+      </c>
+      <c r="D283" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A284" s="1">
+        <v>324.49083999999999</v>
+      </c>
+      <c r="B284" s="1">
+        <v>2016</v>
+      </c>
+      <c r="C284" s="1">
+        <v>27.272003000000002</v>
+      </c>
+      <c r="D284" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A285" s="1">
+        <v>320.53757000000002</v>
+      </c>
+      <c r="B285" s="1">
+        <v>1989</v>
+      </c>
+      <c r="C285" s="1">
+        <v>23.318726000000002</v>
+      </c>
+      <c r="D285" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A286" s="1">
+        <v>315.44607999999999</v>
+      </c>
+      <c r="B286" s="1">
+        <v>2013</v>
+      </c>
+      <c r="C286" s="1">
+        <v>18.227233999999999</v>
+      </c>
+      <c r="D286" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A287" s="1">
+        <v>308.05110000000002</v>
+      </c>
+      <c r="B287" s="1">
+        <v>1996</v>
+      </c>
+      <c r="C287" s="1">
+        <v>10.832245</v>
+      </c>
+      <c r="D287" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A288" s="1">
+        <v>303.59915000000001</v>
+      </c>
+      <c r="B288" s="1">
+        <v>2021</v>
+      </c>
+      <c r="C288" s="1">
+        <v>6.3803099999999997</v>
+      </c>
+      <c r="D288" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A289" s="1">
+        <v>300.92397999999997</v>
+      </c>
+      <c r="B289" s="1">
+        <v>1981</v>
+      </c>
+      <c r="C289" s="1">
+        <v>3.7051392000000001</v>
+      </c>
+      <c r="D289" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A290" s="1">
+        <v>300.08463</v>
+      </c>
+      <c r="B290" s="1">
+        <v>2012</v>
+      </c>
+      <c r="C290" s="1">
+        <v>2.8657837000000002</v>
+      </c>
+      <c r="D290" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A291" s="1">
+        <v>299.97539999999998</v>
+      </c>
+      <c r="B291" s="1">
+        <v>2004</v>
+      </c>
+      <c r="C291" s="1">
+        <v>2.7565613</v>
+      </c>
+      <c r="D291" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A292" s="1">
+        <v>298.02843999999999</v>
+      </c>
+      <c r="B292" s="1">
+        <v>2024</v>
+      </c>
+      <c r="C292" s="1">
+        <v>0.80960083000000005</v>
+      </c>
+      <c r="D292" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A293" s="1">
+        <v>295.58553999999998</v>
+      </c>
+      <c r="B293" s="1">
+        <v>1992</v>
+      </c>
+      <c r="C293" s="1">
+        <v>-1.6333008</v>
+      </c>
+      <c r="D293" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A294" s="1">
+        <v>293.31842</v>
+      </c>
+      <c r="B294" s="1">
+        <v>1990</v>
+      </c>
+      <c r="C294" s="1">
+        <v>-3.9004211</v>
+      </c>
+      <c r="D294" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A295" s="1">
+        <v>292.86966000000001</v>
+      </c>
+      <c r="B295" s="1">
+        <v>1991</v>
+      </c>
+      <c r="C295" s="1">
+        <v>-4.3491819999999999</v>
+      </c>
+      <c r="D295" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A296" s="1">
+        <v>292.09206999999998</v>
+      </c>
+      <c r="B296" s="1">
+        <v>2005</v>
+      </c>
+      <c r="C296" s="1">
+        <v>-5.1267699999999996</v>
+      </c>
+      <c r="D296" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A297" s="1">
+        <v>290.27050000000003</v>
+      </c>
+      <c r="B297" s="1">
+        <v>2007</v>
+      </c>
+      <c r="C297" s="1">
+        <v>-6.9483337000000001</v>
+      </c>
+      <c r="D297" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A298" s="1">
+        <v>289.45675999999997</v>
+      </c>
+      <c r="B298" s="1">
+        <v>1999</v>
+      </c>
+      <c r="C298" s="1">
+        <v>-7.7620849999999999</v>
+      </c>
+      <c r="D298" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A299" s="1">
+        <v>287.83704</v>
+      </c>
+      <c r="B299" s="1">
+        <v>2023</v>
+      </c>
+      <c r="C299" s="1">
+        <v>-9.3818049999999999</v>
+      </c>
+      <c r="D299" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A300" s="1">
+        <v>282.88977</v>
+      </c>
+      <c r="B300" s="1">
+        <v>2018</v>
+      </c>
+      <c r="C300" s="1">
+        <v>-14.329071000000001</v>
+      </c>
+      <c r="D300" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A301" s="1">
+        <v>282.83114999999998</v>
+      </c>
+      <c r="B301" s="1">
+        <v>2000</v>
+      </c>
+      <c r="C301" s="1">
+        <v>-14.387695000000001</v>
+      </c>
+      <c r="D301" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A302" s="1">
+        <v>279.86743000000001</v>
+      </c>
+      <c r="B302" s="1">
+        <v>2022</v>
+      </c>
+      <c r="C302" s="1">
+        <v>-17.351410000000001</v>
+      </c>
+      <c r="D302" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A303" s="1">
+        <v>276.93830000000003</v>
+      </c>
+      <c r="B303" s="1">
+        <v>1985</v>
+      </c>
+      <c r="C303" s="1">
+        <v>-20.280548</v>
+      </c>
+      <c r="D303" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A304" s="1">
+        <v>276.37966999999998</v>
+      </c>
+      <c r="B304" s="1">
+        <v>1994</v>
+      </c>
+      <c r="C304" s="1">
+        <v>-20.839172000000001</v>
+      </c>
+      <c r="D304" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A305" s="1">
+        <v>276.28750000000002</v>
+      </c>
+      <c r="B305" s="1">
+        <v>1982</v>
+      </c>
+      <c r="C305" s="1">
+        <v>-20.931335000000001</v>
+      </c>
+      <c r="D305" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A306" s="1">
+        <v>271.15012000000002</v>
+      </c>
+      <c r="B306" s="1">
+        <v>1983</v>
+      </c>
+      <c r="C306" s="1">
+        <v>-26.068726000000002</v>
+      </c>
+      <c r="D306" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A307" s="1">
+        <v>264.19961999999998</v>
+      </c>
+      <c r="B307" s="1">
+        <v>2025</v>
+      </c>
+      <c r="C307" s="1">
+        <v>-33.019226000000003</v>
+      </c>
+      <c r="D307" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A308" s="1">
+        <v>263.38528000000002</v>
+      </c>
+      <c r="B308" s="1">
+        <v>2001</v>
+      </c>
+      <c r="C308" s="1">
+        <v>-33.833556999999999</v>
+      </c>
+      <c r="D308" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A309" s="1">
+        <v>262.84636999999998</v>
+      </c>
+      <c r="B309" s="1">
+        <v>2009</v>
+      </c>
+      <c r="C309" s="1">
+        <v>-34.372467</v>
+      </c>
+      <c r="D309" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A310" s="1">
+        <v>255.26889</v>
+      </c>
+      <c r="B310" s="1">
+        <v>2020</v>
+      </c>
+      <c r="C310" s="1">
+        <v>-41.949950000000001</v>
+      </c>
+      <c r="D310" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A311" s="1">
+        <v>254.50862000000001</v>
+      </c>
+      <c r="B311" s="1">
+        <v>2019</v>
+      </c>
+      <c r="C311" s="1">
+        <v>-42.71022</v>
+      </c>
+      <c r="D311" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A312" s="1">
+        <v>245.72756999999999</v>
+      </c>
+      <c r="B312" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C312" s="1">
+        <v>-51.491272000000002</v>
+      </c>
+      <c r="D312" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A313" s="1">
+        <v>236.36233999999999</v>
+      </c>
+      <c r="B313" s="1">
+        <v>1993</v>
+      </c>
+      <c r="C313" s="1">
+        <v>-60.856506000000003</v>
+      </c>
+      <c r="D313" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A314" s="1">
+        <v>231.09157999999999</v>
+      </c>
+      <c r="B314" s="1">
+        <v>1986</v>
+      </c>
+      <c r="C314" s="1">
+        <v>-66.127260000000007</v>
+      </c>
+      <c r="D314" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A315" s="1">
+        <v>218.43191999999999</v>
+      </c>
+      <c r="B315" s="1">
+        <v>1997</v>
+      </c>
+      <c r="C315" s="1">
+        <v>-78.786929999999998</v>
+      </c>
+      <c r="D315" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A316" s="1">
+        <v>192.78855999999999</v>
+      </c>
+      <c r="B316" s="1">
+        <v>2014</v>
+      </c>
+      <c r="C316" s="1">
+        <v>-104.43028</v>
+      </c>
+      <c r="D316" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Precipitacion/2025/2025_Ppt_Resumen_Datos.xlsx
+++ b/Precipitacion/2025/2025_Ppt_Resumen_Datos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Clima_Agua_Panama\Output_Raster_Files\Ppt\2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bobby\Documents\GitHub\Clima_Agua_Panama\Precipitacion\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B65A867E-9F47-4EC0-8C9F-67247ADE312B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04D0EE6F-3B82-46AB-9497-1223B4A23B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8010" yWindow="21480" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="36">
   <si>
     <t>Jan</t>
   </si>
@@ -501,13 +501,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5303065C-BA00-4360-894E-DBC69C8D51A1}">
   <dimension ref="A1:N15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>26</v>
       </c>
@@ -551,7 +551,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -576,17 +576,21 @@
       <c r="H2" s="4">
         <v>284.40334999999999</v>
       </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
+      <c r="I2" s="4">
+        <v>243.4537</v>
+      </c>
+      <c r="J2" s="4">
+        <v>236.7088</v>
+      </c>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
       <c r="N2" s="4">
         <f>SUM(B2:M2)</f>
-        <v>1953.44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+        <v>2433.6025</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -611,17 +615,21 @@
       <c r="H3" s="4">
         <v>200.17044000000001</v>
       </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
+      <c r="I3" s="4">
+        <v>187.75885</v>
+      </c>
+      <c r="J3" s="4">
+        <v>292.02276999999998</v>
+      </c>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4">
         <f t="shared" ref="N3:N14" si="0">SUM(B3:M3)</f>
-        <v>1019.762241</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+        <v>1499.5438610000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>7</v>
       </c>
@@ -646,17 +654,21 @@
       <c r="H4" s="4">
         <v>252.24438000000001</v>
       </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
+      <c r="I4" s="4">
+        <v>240.20253</v>
+      </c>
+      <c r="J4" s="4">
+        <v>208.57945000000001</v>
+      </c>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4">
         <f t="shared" si="0"/>
-        <v>1677.5845400000003</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+        <v>2126.3665200000005</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
@@ -681,17 +693,21 @@
       <c r="H5" s="4">
         <v>194.70464999999999</v>
       </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
+      <c r="I5" s="4">
+        <v>316.97638000000001</v>
+      </c>
+      <c r="J5" s="4">
+        <v>224.00785999999999</v>
+      </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
       <c r="N5" s="4">
         <f t="shared" si="0"/>
-        <v>1661.5952699999998</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+        <v>2202.57951</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
@@ -716,17 +732,21 @@
       <c r="H6" s="4">
         <v>327.45929999999998</v>
       </c>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
+      <c r="I6" s="4">
+        <v>397.61959999999999</v>
+      </c>
+      <c r="J6" s="4">
+        <v>469.45013</v>
+      </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4">
         <f t="shared" si="0"/>
-        <v>1814.7792899999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+        <v>2681.8490200000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
@@ -751,17 +771,21 @@
       <c r="H7" s="4">
         <v>315.71895999999998</v>
       </c>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
+      <c r="I7" s="4">
+        <v>332.46071999999998</v>
+      </c>
+      <c r="J7" s="4">
+        <v>268.71422999999999</v>
+      </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
       <c r="N7" s="4">
         <f t="shared" si="0"/>
-        <v>1681.81024</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+        <v>2282.9851899999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>11</v>
       </c>
@@ -786,17 +810,21 @@
       <c r="H8" s="4">
         <v>428.18927000000002</v>
       </c>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
+      <c r="I8" s="4">
+        <v>438.5804</v>
+      </c>
+      <c r="J8" s="4">
+        <v>425.11250000000001</v>
+      </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4">
         <f t="shared" si="0"/>
-        <v>2158.5143499999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+        <v>3022.2072499999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>12</v>
       </c>
@@ -821,17 +849,21 @@
       <c r="H9" s="4">
         <v>263.8451</v>
       </c>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
+      <c r="I9" s="4">
+        <v>232.34575000000001</v>
+      </c>
+      <c r="J9" s="4">
+        <v>218.42221000000001</v>
+      </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
       <c r="N9" s="4">
         <f t="shared" si="0"/>
-        <v>1704.59728</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+        <v>2155.3652400000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>13</v>
       </c>
@@ -856,17 +888,21 @@
       <c r="H10" s="4">
         <v>183.88315</v>
       </c>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
+      <c r="I10" s="4">
+        <v>179.79578000000001</v>
+      </c>
+      <c r="J10" s="4">
+        <v>316.54852</v>
+      </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4">
         <f t="shared" si="0"/>
-        <v>910.90902459999995</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+        <v>1407.2533246</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>14</v>
       </c>
@@ -891,17 +927,21 @@
       <c r="H11" s="4">
         <v>155.66865999999999</v>
       </c>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
+      <c r="I11" s="4">
+        <v>163.51232999999999</v>
+      </c>
+      <c r="J11" s="4">
+        <v>279.64080000000001</v>
+      </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
       <c r="N11" s="4">
         <f t="shared" si="0"/>
-        <v>721.42022470000006</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+        <v>1164.5733547</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>15</v>
       </c>
@@ -926,17 +966,21 @@
       <c r="H12" s="4">
         <v>179.92783</v>
       </c>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
+      <c r="I12" s="4">
+        <v>296.00366000000002</v>
+      </c>
+      <c r="J12" s="4">
+        <v>285.97573999999997</v>
+      </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
       <c r="N12" s="4">
         <f t="shared" si="0"/>
-        <v>1391.182405</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+        <v>1973.1618050000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>16</v>
       </c>
@@ -961,17 +1005,21 @@
       <c r="H13" s="4">
         <v>181.36001999999999</v>
       </c>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
+      <c r="I13" s="4">
+        <v>238.34253000000001</v>
+      </c>
+      <c r="J13" s="4">
+        <v>288.40285999999998</v>
+      </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
       <c r="N13" s="4">
         <f t="shared" si="0"/>
-        <v>996.35566699999993</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+        <v>1523.1010569999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>17</v>
       </c>
@@ -996,22 +1044,26 @@
       <c r="H14" s="4">
         <v>283.88657000000001</v>
       </c>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
+      <c r="I14" s="4">
+        <v>374.95287999999999</v>
+      </c>
+      <c r="J14" s="4">
+        <v>433.15170000000001</v>
+      </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
       <c r="N14" s="4">
         <f t="shared" si="0"/>
-        <v>1427.15398</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+        <v>2235.2585600000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>27</v>
       </c>
       <c r="B15" s="7">
-        <f t="shared" ref="B15:H15" si="1">AVERAGE(B2:B14)</f>
+        <f t="shared" ref="B15:J15" si="1">AVERAGE(B2:B14)</f>
         <v>119.60806099999999</v>
       </c>
       <c r="C15" s="7">
@@ -1038,14 +1090,20 @@
         <f t="shared" si="1"/>
         <v>250.11243692307696</v>
       </c>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
+      <c r="I15" s="7">
+        <f t="shared" si="1"/>
+        <v>280.15423923076918</v>
+      </c>
+      <c r="J15" s="7">
+        <f t="shared" si="1"/>
+        <v>303.59519769230769</v>
+      </c>
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
       <c r="M15" s="7"/>
       <c r="N15" s="7">
         <f>SUM(B15:M15)</f>
-        <v>1470.7003471000003</v>
+        <v>2054.449784023077</v>
       </c>
     </row>
   </sheetData>
@@ -1057,15 +1115,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N15"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="13" width="8.88671875" style="3"/>
-    <col min="14" max="14" width="10.21875" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.88671875" style="3"/>
+    <col min="1" max="1" width="11.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="13" width="8.85546875" style="3"/>
+    <col min="14" max="14" width="10.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.85546875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>26</v>
       </c>
@@ -1109,7 +1167,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -1134,17 +1192,21 @@
       <c r="H2" s="4">
         <v>322.49865999999997</v>
       </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
+      <c r="I2" s="4">
+        <v>296.71570000000003</v>
+      </c>
+      <c r="J2" s="4">
+        <v>273.32483000000002</v>
+      </c>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
       <c r="N2" s="4">
         <f>SUM(B2:M2)</f>
-        <v>1671.5926999999999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+        <v>2241.6332299999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1169,17 +1231,21 @@
       <c r="H3" s="4">
         <v>229.08197000000001</v>
       </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
+      <c r="I3" s="4">
+        <v>269.72811999999999</v>
+      </c>
+      <c r="J3" s="4">
+        <v>313.45443999999998</v>
+      </c>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4">
         <f t="shared" ref="N3:N13" si="0">SUM(B3:M3)</f>
-        <v>931.19203100000004</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+        <v>1514.374591</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1204,17 +1270,21 @@
       <c r="H4" s="4">
         <v>284.52753000000001</v>
       </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
+      <c r="I4" s="4">
+        <v>296.21469999999999</v>
+      </c>
+      <c r="J4" s="4">
+        <v>277.55306999999999</v>
+      </c>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4">
         <f t="shared" si="0"/>
-        <v>1168.2693100000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+        <v>1742.0370800000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -1239,17 +1309,21 @@
       <c r="H5" s="4">
         <v>251.78987000000001</v>
       </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
+      <c r="I5" s="4">
+        <v>273.99392999999998</v>
+      </c>
+      <c r="J5" s="4">
+        <v>230.79230999999999</v>
+      </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
       <c r="N5" s="4">
         <f t="shared" si="0"/>
-        <v>1045.4678509999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+        <v>1550.254091</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -1274,17 +1348,21 @@
       <c r="H6" s="4">
         <v>360.66199999999998</v>
       </c>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
+      <c r="I6" s="4">
+        <v>437.28802000000002</v>
+      </c>
+      <c r="J6" s="4">
+        <v>517.72249999999997</v>
+      </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4">
         <f t="shared" si="0"/>
-        <v>1507.8958640000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+        <v>2462.9063839999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -1309,17 +1387,21 @@
       <c r="H7" s="4">
         <v>365.65584999999999</v>
       </c>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
+      <c r="I7" s="4">
+        <v>368.97500000000002</v>
+      </c>
+      <c r="J7" s="4">
+        <v>312.03244000000001</v>
+      </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
       <c r="N7" s="4">
         <f t="shared" si="0"/>
-        <v>1465.7421100000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+        <v>2146.74955</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
@@ -1344,17 +1426,21 @@
       <c r="H8" s="4">
         <v>399.68682999999999</v>
       </c>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
+      <c r="I8" s="4">
+        <v>427.21129999999999</v>
+      </c>
+      <c r="J8" s="4">
+        <v>458.21069999999997</v>
+      </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4">
         <f t="shared" si="0"/>
-        <v>1710.584805</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+        <v>2596.006805</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -1379,17 +1465,21 @@
       <c r="H9" s="4">
         <v>291.41437000000002</v>
       </c>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
+      <c r="I9" s="4">
+        <v>287.89109999999999</v>
+      </c>
+      <c r="J9" s="4">
+        <v>288.94130000000001</v>
+      </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
       <c r="N9" s="4">
         <f t="shared" si="0"/>
-        <v>1147.9075929999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+        <v>1724.7399929999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
@@ -1414,17 +1504,21 @@
       <c r="H10" s="4">
         <v>204.07721000000001</v>
       </c>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
+      <c r="I10" s="4">
+        <v>245.80893</v>
+      </c>
+      <c r="J10" s="4">
+        <v>325.31155000000001</v>
+      </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4">
         <f t="shared" si="0"/>
-        <v>816.7543895</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+        <v>1387.8748694999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
@@ -1449,17 +1543,21 @@
       <c r="H11" s="4">
         <v>191.22635</v>
       </c>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
+      <c r="I11" s="4">
+        <v>214.82140999999999</v>
+      </c>
+      <c r="J11" s="4">
+        <v>248.78128000000001</v>
+      </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
       <c r="N11" s="4">
         <f t="shared" si="0"/>
-        <v>633.50858300000004</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+        <v>1097.111273</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
@@ -1484,17 +1582,21 @@
       <c r="H12" s="4">
         <v>241.55350000000001</v>
       </c>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
+      <c r="I12" s="4">
+        <v>276.13459999999998</v>
+      </c>
+      <c r="J12" s="4">
+        <v>300.47494999999998</v>
+      </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
       <c r="N12" s="4">
         <f t="shared" si="0"/>
-        <v>987.214159</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+        <v>1563.823709</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
@@ -1519,17 +1621,21 @@
       <c r="H13" s="4">
         <v>216.28813</v>
       </c>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
+      <c r="I13" s="4">
+        <v>251.04628</v>
+      </c>
+      <c r="J13" s="4">
+        <v>293.80295000000001</v>
+      </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
       <c r="N13" s="4">
         <f t="shared" si="0"/>
-        <v>896.87102300000004</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+        <v>1441.720253</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -1554,17 +1660,21 @@
       <c r="H14" s="4">
         <v>329.54608000000002</v>
       </c>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
+      <c r="I14" s="4">
+        <v>402.06801999999999</v>
+      </c>
+      <c r="J14" s="4">
+        <v>484.0908</v>
+      </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
       <c r="N14" s="4">
         <f>SUM(B14:M14)</f>
-        <v>1266.1126080000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+        <v>2152.271428</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>27</v>
       </c>
@@ -1573,7 +1683,7 @@
         <v>67.513827307692296</v>
       </c>
       <c r="C15" s="7">
-        <f t="shared" ref="C15:H15" si="1">AVERAGE(C2:C14)</f>
+        <f t="shared" ref="C15:J15" si="1">AVERAGE(C2:C14)</f>
         <v>41.752843615384613</v>
       </c>
       <c r="D15" s="7">
@@ -1596,14 +1706,20 @@
         <f t="shared" si="1"/>
         <v>283.69295</v>
       </c>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
+      <c r="I15" s="7">
+        <f t="shared" si="1"/>
+        <v>311.37670076923075</v>
+      </c>
+      <c r="J15" s="7">
+        <f t="shared" si="1"/>
+        <v>332.65331692307694</v>
+      </c>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
       <c r="N15" s="7">
         <f>SUM(B15:M15)</f>
-        <v>1173.0086943461538</v>
+        <v>1817.0387120384617</v>
       </c>
     </row>
   </sheetData>
@@ -1616,18 +1732,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A60AD28-2719-49E3-BF40-EE869E54613A}">
   <dimension ref="A1:G217"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>35</v>
       </c>
@@ -1650,9 +1766,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
-        <v>5.2492570000000001</v>
+        <v>5.2492599999999996</v>
       </c>
       <c r="B2" s="3">
         <v>2024</v>
@@ -1670,10 +1786,10 @@
         <v>45658</v>
       </c>
       <c r="G2" s="3">
-        <v>5.2492570000000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+        <v>5.2492599999999996</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>4.5963326000000002</v>
       </c>
@@ -1693,12 +1809,12 @@
         <v>45663</v>
       </c>
       <c r="G3" s="3">
-        <v>9.8455899999999996</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+        <v>9.8455925000000004</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
-        <v>9.4176009999999994</v>
+        <v>9.417605</v>
       </c>
       <c r="B4" s="3">
         <v>2024</v>
@@ -1716,12 +1832,12 @@
         <v>45668</v>
       </c>
       <c r="G4" s="3">
-        <v>19.263190999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+        <v>19.263199</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
-        <v>3.9451466000000002</v>
+        <v>3.945147</v>
       </c>
       <c r="B5" s="3">
         <v>2024</v>
@@ -1739,12 +1855,12 @@
         <v>45673</v>
       </c>
       <c r="G5" s="3">
-        <v>23.208335999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+        <v>23.208345000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
-        <v>5.0826324999999999</v>
+        <v>5.0826297</v>
       </c>
       <c r="B6" s="3">
         <v>2024</v>
@@ -1762,12 +1878,12 @@
         <v>45678</v>
       </c>
       <c r="G6" s="3">
-        <v>28.290970000000002</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+        <v>28.290973999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
-        <v>13.980486000000001</v>
+        <v>13.980487</v>
       </c>
       <c r="B7" s="3">
         <v>2024</v>
@@ -1785,12 +1901,12 @@
         <v>45683</v>
       </c>
       <c r="G7" s="3">
-        <v>42.271453999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+        <v>42.271459999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
-        <v>9.941395</v>
+        <v>9.9413990000000005</v>
       </c>
       <c r="B8" s="3">
         <v>2024</v>
@@ -1808,12 +1924,12 @@
         <v>45689</v>
       </c>
       <c r="G8" s="3">
-        <v>52.212851999999998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+        <v>52.212859999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
-        <v>4.7953590000000004</v>
+        <v>4.7953580000000002</v>
       </c>
       <c r="B9" s="3">
         <v>2024</v>
@@ -1831,10 +1947,10 @@
         <v>45694</v>
       </c>
       <c r="G9" s="3">
-        <v>57.008209999999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+        <v>57.008217000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>3.6274492999999999</v>
       </c>
@@ -1854,12 +1970,12 @@
         <v>45699</v>
       </c>
       <c r="G10" s="3">
-        <v>60.635660000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+        <v>60.635666000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
-        <v>7.8164870000000004</v>
+        <v>7.8164879999999997</v>
       </c>
       <c r="B11" s="3">
         <v>2024</v>
@@ -1877,12 +1993,12 @@
         <v>45704</v>
       </c>
       <c r="G11" s="3">
-        <v>68.452150000000003</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+        <v>68.452156000000002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
-        <v>3.8636959000000002</v>
+        <v>3.8636946999999999</v>
       </c>
       <c r="B12" s="3">
         <v>2024</v>
@@ -1900,12 +2016,12 @@
         <v>45709</v>
       </c>
       <c r="G12" s="3">
-        <v>72.315839999999994</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+        <v>72.315849999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
-        <v>3.0973332</v>
+        <v>3.0973334000000001</v>
       </c>
       <c r="B13" s="3">
         <v>2024</v>
@@ -1923,12 +2039,12 @@
         <v>45714</v>
       </c>
       <c r="G13" s="3">
-        <v>75.413179999999997</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+        <v>75.413184999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
-        <v>2.8400251999999999</v>
+        <v>2.8400240000000001</v>
       </c>
       <c r="B14" s="3">
         <v>2024</v>
@@ -1946,12 +2062,12 @@
         <v>45717</v>
       </c>
       <c r="G14" s="3">
-        <v>78.253200000000007</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+        <v>78.253203999999997</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
-        <v>1.6105007</v>
+        <v>1.6105003</v>
       </c>
       <c r="B15" s="3">
         <v>2024</v>
@@ -1969,12 +2085,12 @@
         <v>45722</v>
       </c>
       <c r="G15" s="3">
-        <v>79.863699999999994</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+        <v>79.863709999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
-        <v>2.9749859999999999</v>
+        <v>2.9749854</v>
       </c>
       <c r="B16" s="3">
         <v>2024</v>
@@ -1992,12 +2108,12 @@
         <v>45727</v>
       </c>
       <c r="G16" s="3">
-        <v>82.838684000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+        <v>82.83869</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
-        <v>5.1857705000000003</v>
+        <v>5.1857699999999998</v>
       </c>
       <c r="B17" s="3">
         <v>2024</v>
@@ -2018,9 +2134,9 @@
         <v>88.024460000000005</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
-        <v>4.8315429999999999</v>
+        <v>4.8315444000000003</v>
       </c>
       <c r="B18" s="3">
         <v>2024</v>
@@ -2038,12 +2154,12 @@
         <v>45737</v>
       </c>
       <c r="G18" s="3">
-        <v>92.855999999999995</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+        <v>92.856009999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
-        <v>9.8148970000000002</v>
+        <v>9.8148940000000007</v>
       </c>
       <c r="B19" s="3">
         <v>2024</v>
@@ -2064,9 +2180,9 @@
         <v>102.6709</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
-        <v>8.4280469999999994</v>
+        <v>8.4280430000000006</v>
       </c>
       <c r="B20" s="3">
         <v>2024</v>
@@ -2087,9 +2203,9 @@
         <v>111.098946</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
-        <v>51.836436999999997</v>
+        <v>51.836410000000001</v>
       </c>
       <c r="B21" s="3">
         <v>2024</v>
@@ -2107,12 +2223,12 @@
         <v>45753</v>
       </c>
       <c r="G21" s="3">
-        <v>162.93538000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+        <v>162.93536</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
-        <v>3.5840266000000001</v>
+        <v>3.5840244000000001</v>
       </c>
       <c r="B22" s="3">
         <v>2024</v>
@@ -2130,12 +2246,12 @@
         <v>45758</v>
       </c>
       <c r="G22" s="3">
-        <v>166.51940999999999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+        <v>166.51938000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
-        <v>4.5789795</v>
+        <v>4.5789790000000004</v>
       </c>
       <c r="B23" s="3">
         <v>2024</v>
@@ -2153,12 +2269,12 @@
         <v>45763</v>
       </c>
       <c r="G23" s="3">
-        <v>171.09838999999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+        <v>171.09836000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
-        <v>35.190956</v>
+        <v>35.190944999999999</v>
       </c>
       <c r="B24" s="3">
         <v>2024</v>
@@ -2176,12 +2292,12 @@
         <v>45768</v>
       </c>
       <c r="G24" s="3">
-        <v>206.28934000000001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+        <v>206.2893</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
-        <v>49.291491999999998</v>
+        <v>49.291473000000003</v>
       </c>
       <c r="B25" s="3">
         <v>2024</v>
@@ -2199,12 +2315,12 @@
         <v>45773</v>
       </c>
       <c r="G25" s="3">
-        <v>255.58083999999999</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+        <v>255.58078</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
-        <v>27.345015</v>
+        <v>27.345006999999999</v>
       </c>
       <c r="B26" s="3">
         <v>2024</v>
@@ -2222,12 +2338,12 @@
         <v>45778</v>
       </c>
       <c r="G26" s="3">
-        <v>282.92583999999999</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+        <v>282.92577999999997</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
-        <v>50.558684999999997</v>
+        <v>50.558692999999998</v>
       </c>
       <c r="B27" s="3">
         <v>2024</v>
@@ -2245,12 +2361,12 @@
         <v>45783</v>
       </c>
       <c r="G27" s="3">
-        <v>333.48453000000001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+        <v>333.48446999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
-        <v>68.892166000000003</v>
+        <v>68.892129999999995</v>
       </c>
       <c r="B28" s="3">
         <v>2024</v>
@@ -2268,12 +2384,12 @@
         <v>45788</v>
       </c>
       <c r="G28" s="3">
-        <v>402.37670000000003</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+        <v>402.3766</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
-        <v>51.80883</v>
+        <v>51.808804000000002</v>
       </c>
       <c r="B29" s="3">
         <v>2024</v>
@@ -2291,12 +2407,12 @@
         <v>45793</v>
       </c>
       <c r="G29" s="3">
-        <v>454.18554999999998</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+        <v>454.18540000000002</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
-        <v>52.960228000000001</v>
+        <v>52.960239999999999</v>
       </c>
       <c r="B30" s="3">
         <v>2024</v>
@@ -2314,12 +2430,12 @@
         <v>45798</v>
       </c>
       <c r="G30" s="3">
-        <v>507.14575000000002</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+        <v>507.14562999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
-        <v>52.317616000000001</v>
+        <v>52.317590000000003</v>
       </c>
       <c r="B31" s="3">
         <v>2024</v>
@@ -2337,10 +2453,10 @@
         <v>45803</v>
       </c>
       <c r="G31" s="3">
-        <v>559.46339999999998</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+        <v>559.46325999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>50.438299999999998</v>
       </c>
@@ -2360,12 +2476,12 @@
         <v>45809</v>
       </c>
       <c r="G32" s="3">
-        <v>609.90170000000001</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+        <v>609.90155000000004</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
-        <v>58.700428000000002</v>
+        <v>58.700417000000002</v>
       </c>
       <c r="B33" s="3">
         <v>2024</v>
@@ -2383,12 +2499,12 @@
         <v>45814</v>
       </c>
       <c r="G33" s="3">
-        <v>668.60209999999995</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+        <v>668.6019</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
-        <v>83.162850000000006</v>
+        <v>83.162800000000004</v>
       </c>
       <c r="B34" s="3">
         <v>2024</v>
@@ -2406,12 +2522,12 @@
         <v>45819</v>
       </c>
       <c r="G34" s="3">
-        <v>751.76495</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+        <v>751.76480000000004</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
-        <v>61.870975000000001</v>
+        <v>61.870980000000003</v>
       </c>
       <c r="B35" s="3">
         <v>2024</v>
@@ -2429,12 +2545,12 @@
         <v>45824</v>
       </c>
       <c r="G35" s="3">
-        <v>813.63589999999999</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+        <v>813.63574000000006</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
-        <v>43.194775</v>
+        <v>43.194755999999998</v>
       </c>
       <c r="B36" s="3">
         <v>2024</v>
@@ -2452,12 +2568,12 @@
         <v>45829</v>
       </c>
       <c r="G36" s="3">
-        <v>856.83069999999998</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+        <v>856.83050000000003</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
-        <v>33.611854999999998</v>
+        <v>33.611879999999999</v>
       </c>
       <c r="B37" s="3">
         <v>2024</v>
@@ -2475,12 +2591,12 @@
         <v>45834</v>
       </c>
       <c r="G37" s="3">
-        <v>890.44257000000005</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+        <v>890.44240000000002</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
-        <v>48.680500000000002</v>
+        <v>48.680484999999997</v>
       </c>
       <c r="B38" s="3">
         <v>2024</v>
@@ -2498,12 +2614,12 @@
         <v>45839</v>
       </c>
       <c r="G38" s="3">
-        <v>939.12305000000003</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+        <v>939.12285999999995</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
-        <v>35.615882999999997</v>
+        <v>35.615887000000001</v>
       </c>
       <c r="B39" s="3">
         <v>2024</v>
@@ -2521,12 +2637,12 @@
         <v>45844</v>
       </c>
       <c r="G39" s="3">
-        <v>974.73895000000005</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+        <v>974.73879999999997</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
-        <v>46.791237000000002</v>
+        <v>46.791220000000003</v>
       </c>
       <c r="B40" s="3">
         <v>2024</v>
@@ -2544,12 +2660,12 @@
         <v>45849</v>
       </c>
       <c r="G40" s="3">
-        <v>1021.53015</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1021.52997</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
-        <v>50.363680000000002</v>
+        <v>50.363697000000002</v>
       </c>
       <c r="B41" s="3">
         <v>2024</v>
@@ -2567,12 +2683,12 @@
         <v>45854</v>
       </c>
       <c r="G41" s="3">
-        <v>1071.8938000000001</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1071.8937000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
-        <v>49.690567000000001</v>
+        <v>49.690550000000002</v>
       </c>
       <c r="B42" s="3">
         <v>2024</v>
@@ -2590,12 +2706,12 @@
         <v>45859</v>
       </c>
       <c r="G42" s="3">
-        <v>1121.5844999999999</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1121.5842</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
-        <v>66.886566000000002</v>
+        <v>66.886579999999995</v>
       </c>
       <c r="B43" s="3">
         <v>2024</v>
@@ -2613,18 +2729,18 @@
         <v>45864</v>
       </c>
       <c r="G43" s="3">
-        <v>1188.471</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1188.4708000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
-        <v>51.443686999999997</v>
+        <v>48.587234000000002</v>
       </c>
       <c r="B44" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C44" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D44" s="3">
         <v>1</v>
@@ -2633,21 +2749,21 @@
         <v>1</v>
       </c>
       <c r="F44" s="5">
-        <v>45658</v>
+        <v>45870</v>
       </c>
       <c r="G44" s="3">
-        <v>51.443686999999997</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1237.058</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
-        <v>30.218036999999999</v>
+        <v>68.053039999999996</v>
       </c>
       <c r="B45" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C45" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D45" s="3">
         <v>2</v>
@@ -2656,21 +2772,21 @@
         <v>6</v>
       </c>
       <c r="F45" s="5">
-        <v>45663</v>
+        <v>45875</v>
       </c>
       <c r="G45" s="3">
-        <v>81.661730000000006</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1305.1111000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
-        <v>7.7399344000000001</v>
+        <v>42.254092999999997</v>
       </c>
       <c r="B46" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C46" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D46" s="3">
         <v>3</v>
@@ -2679,21 +2795,21 @@
         <v>11</v>
       </c>
       <c r="F46" s="5">
-        <v>45668</v>
+        <v>45880</v>
       </c>
       <c r="G46" s="3">
-        <v>89.401660000000007</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1347.3651</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
-        <v>11.712353999999999</v>
+        <v>62.352615</v>
       </c>
       <c r="B47" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C47" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D47" s="3">
         <v>4</v>
@@ -2702,21 +2818,21 @@
         <v>16</v>
       </c>
       <c r="F47" s="5">
-        <v>45673</v>
+        <v>45885</v>
       </c>
       <c r="G47" s="3">
-        <v>101.11400999999999</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1409.7177999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
-        <v>8.5210749999999997</v>
+        <v>66.438575999999998</v>
       </c>
       <c r="B48" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C48" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D48" s="3">
         <v>5</v>
@@ -2725,21 +2841,21 @@
         <v>21</v>
       </c>
       <c r="F48" s="5">
-        <v>45678</v>
+        <v>45890</v>
       </c>
       <c r="G48" s="3">
-        <v>109.635086</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1476.1564000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
-        <v>9.6642530000000004</v>
+        <v>48.39085</v>
       </c>
       <c r="B49" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C49" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D49" s="3">
         <v>6</v>
@@ -2748,21 +2864,21 @@
         <v>26</v>
       </c>
       <c r="F49" s="5">
-        <v>45683</v>
+        <v>45895</v>
       </c>
       <c r="G49" s="3">
-        <v>119.29934</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1524.5472</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
-        <v>14.432333</v>
+        <v>61.745944999999999</v>
       </c>
       <c r="B50" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C50" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D50" s="3">
         <v>1</v>
@@ -2771,21 +2887,21 @@
         <v>1</v>
       </c>
       <c r="F50" s="5">
-        <v>45689</v>
+        <v>45901</v>
       </c>
       <c r="G50" s="3">
-        <v>133.73167000000001</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1586.2932000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
-        <v>8.7800480000000007</v>
+        <v>55.749302</v>
       </c>
       <c r="B51" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C51" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D51" s="3">
         <v>2</v>
@@ -2794,21 +2910,21 @@
         <v>6</v>
       </c>
       <c r="F51" s="5">
-        <v>45694</v>
+        <v>45906</v>
       </c>
       <c r="G51" s="3">
-        <v>142.51172</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1642.0425</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
-        <v>36.847504000000001</v>
+        <v>44.363680000000002</v>
       </c>
       <c r="B52" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C52" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D52" s="3">
         <v>3</v>
@@ -2817,21 +2933,21 @@
         <v>11</v>
       </c>
       <c r="F52" s="5">
-        <v>45699</v>
+        <v>45911</v>
       </c>
       <c r="G52" s="3">
-        <v>179.35921999999999</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1686.4060999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
-        <v>47.512680000000003</v>
+        <v>61.65296</v>
       </c>
       <c r="B53" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C53" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D53" s="3">
         <v>4</v>
@@ -2840,21 +2956,21 @@
         <v>16</v>
       </c>
       <c r="F53" s="5">
-        <v>45704</v>
+        <v>45916</v>
       </c>
       <c r="G53" s="3">
-        <v>226.87190000000001</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1748.0590999999999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
-        <v>11.339199000000001</v>
+        <v>67.535849999999996</v>
       </c>
       <c r="B54" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C54" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D54" s="3">
         <v>5</v>
@@ -2863,21 +2979,21 @@
         <v>21</v>
       </c>
       <c r="F54" s="5">
-        <v>45709</v>
+        <v>45921</v>
       </c>
       <c r="G54" s="3">
-        <v>238.21109999999999</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1815.595</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
-        <v>5.0655327000000003</v>
+        <v>89.081023999999999</v>
       </c>
       <c r="B55" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C55" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D55" s="3">
         <v>6</v>
@@ -2886,21 +3002,21 @@
         <v>26</v>
       </c>
       <c r="F55" s="5">
-        <v>45714</v>
+        <v>45926</v>
       </c>
       <c r="G55" s="3">
-        <v>243.27663999999999</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1904.6759999999999</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
-        <v>6.6873063999999998</v>
+        <v>51.443665000000003</v>
       </c>
       <c r="B56" s="3">
         <v>2025</v>
       </c>
       <c r="C56" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D56" s="3">
         <v>1</v>
@@ -2909,21 +3025,21 @@
         <v>1</v>
       </c>
       <c r="F56" s="5">
-        <v>45717</v>
+        <v>45658</v>
       </c>
       <c r="G56" s="3">
-        <v>249.96394000000001</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+        <v>51.443665000000003</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
-        <v>5.1503943999999997</v>
+        <v>30.218014</v>
       </c>
       <c r="B57" s="3">
         <v>2025</v>
       </c>
       <c r="C57" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D57" s="3">
         <v>2</v>
@@ -2932,21 +3048,21 @@
         <v>6</v>
       </c>
       <c r="F57" s="5">
-        <v>45722</v>
+        <v>45663</v>
       </c>
       <c r="G57" s="3">
-        <v>255.11433</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+        <v>81.661680000000004</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
-        <v>5.3021630000000002</v>
+        <v>7.739935</v>
       </c>
       <c r="B58" s="3">
         <v>2025</v>
       </c>
       <c r="C58" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D58" s="3">
         <v>3</v>
@@ -2955,21 +3071,21 @@
         <v>11</v>
       </c>
       <c r="F58" s="5">
-        <v>45727</v>
+        <v>45668</v>
       </c>
       <c r="G58" s="3">
-        <v>260.41649999999998</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+        <v>89.401610000000005</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
-        <v>7.7123569999999999</v>
+        <v>11.712355000000001</v>
       </c>
       <c r="B59" s="3">
         <v>2025</v>
       </c>
       <c r="C59" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D59" s="3">
         <v>4</v>
@@ -2978,21 +3094,21 @@
         <v>16</v>
       </c>
       <c r="F59" s="5">
-        <v>45732</v>
+        <v>45673</v>
       </c>
       <c r="G59" s="3">
-        <v>268.12885</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+        <v>101.11396999999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
-        <v>24.789594999999998</v>
+        <v>8.5210740000000005</v>
       </c>
       <c r="B60" s="3">
         <v>2025</v>
       </c>
       <c r="C60" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D60" s="3">
         <v>5</v>
@@ -3001,21 +3117,21 @@
         <v>21</v>
       </c>
       <c r="F60" s="5">
-        <v>45737</v>
+        <v>45678</v>
       </c>
       <c r="G60" s="3">
-        <v>292.91845999999998</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+        <v>109.63504</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
-        <v>23.760323</v>
+        <v>9.6642499999999991</v>
       </c>
       <c r="B61" s="3">
         <v>2025</v>
       </c>
       <c r="C61" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D61" s="3">
         <v>6</v>
@@ -3024,21 +3140,21 @@
         <v>26</v>
       </c>
       <c r="F61" s="5">
-        <v>45742</v>
+        <v>45683</v>
       </c>
       <c r="G61" s="3">
-        <v>316.67876999999999</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+        <v>119.29929</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
-        <v>30.345040000000001</v>
+        <v>14.432331</v>
       </c>
       <c r="B62" s="3">
         <v>2025</v>
       </c>
       <c r="C62" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D62" s="3">
         <v>1</v>
@@ -3047,21 +3163,21 @@
         <v>1</v>
       </c>
       <c r="F62" s="5">
-        <v>45748</v>
+        <v>45689</v>
       </c>
       <c r="G62" s="3">
-        <v>347.02379999999999</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+        <v>133.73163</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
-        <v>26.385961999999999</v>
+        <v>8.7800454999999999</v>
       </c>
       <c r="B63" s="3">
         <v>2025</v>
       </c>
       <c r="C63" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D63" s="3">
         <v>2</v>
@@ -3070,21 +3186,21 @@
         <v>6</v>
       </c>
       <c r="F63" s="5">
-        <v>45753</v>
+        <v>45694</v>
       </c>
       <c r="G63" s="3">
-        <v>373.40980000000002</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+        <v>142.51167000000001</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
-        <v>14.766463</v>
+        <v>36.847520000000003</v>
       </c>
       <c r="B64" s="3">
         <v>2025</v>
       </c>
       <c r="C64" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D64" s="3">
         <v>3</v>
@@ -3093,21 +3209,21 @@
         <v>11</v>
       </c>
       <c r="F64" s="5">
-        <v>45758</v>
+        <v>45699</v>
       </c>
       <c r="G64" s="3">
-        <v>388.17624000000001</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+        <v>179.35919000000001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
-        <v>13.573518999999999</v>
+        <v>47.512675999999999</v>
       </c>
       <c r="B65" s="3">
         <v>2025</v>
       </c>
       <c r="C65" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D65" s="3">
         <v>4</v>
@@ -3116,21 +3232,21 @@
         <v>16</v>
       </c>
       <c r="F65" s="5">
-        <v>45763</v>
+        <v>45704</v>
       </c>
       <c r="G65" s="3">
-        <v>401.74975999999998</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+        <v>226.87186</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
-        <v>39.141010000000001</v>
+        <v>11.339198</v>
       </c>
       <c r="B66" s="3">
         <v>2025</v>
       </c>
       <c r="C66" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D66" s="3">
         <v>5</v>
@@ -3139,21 +3255,21 @@
         <v>21</v>
       </c>
       <c r="F66" s="5">
-        <v>45768</v>
+        <v>45709</v>
       </c>
       <c r="G66" s="3">
-        <v>440.89078000000001</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+        <v>238.21106</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
-        <v>41.962490000000003</v>
+        <v>5.0655340000000004</v>
       </c>
       <c r="B67" s="3">
         <v>2025</v>
       </c>
       <c r="C67" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D67" s="3">
         <v>6</v>
@@ -3162,21 +3278,21 @@
         <v>26</v>
       </c>
       <c r="F67" s="5">
-        <v>45773</v>
+        <v>45714</v>
       </c>
       <c r="G67" s="3">
-        <v>482.85327000000001</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+        <v>243.2766</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
-        <v>55.322009999999999</v>
+        <v>6.6873073999999999</v>
       </c>
       <c r="B68" s="3">
         <v>2025</v>
       </c>
       <c r="C68" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D68" s="3">
         <v>1</v>
@@ -3185,21 +3301,21 @@
         <v>1</v>
       </c>
       <c r="F68" s="5">
-        <v>45778</v>
+        <v>45717</v>
       </c>
       <c r="G68" s="3">
-        <v>538.17529999999999</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+        <v>249.9639</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
-        <v>48.162075000000002</v>
+        <v>5.1503972999999998</v>
       </c>
       <c r="B69" s="3">
         <v>2025</v>
       </c>
       <c r="C69" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D69" s="3">
         <v>2</v>
@@ -3208,21 +3324,21 @@
         <v>6</v>
       </c>
       <c r="F69" s="5">
-        <v>45783</v>
+        <v>45722</v>
       </c>
       <c r="G69" s="3">
-        <v>586.33734000000004</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+        <v>255.11429999999999</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
-        <v>73.489159999999998</v>
+        <v>5.3021646000000002</v>
       </c>
       <c r="B70" s="3">
         <v>2025</v>
       </c>
       <c r="C70" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D70" s="3">
         <v>3</v>
@@ -3231,21 +3347,21 @@
         <v>11</v>
       </c>
       <c r="F70" s="5">
-        <v>45788</v>
+        <v>45727</v>
       </c>
       <c r="G70" s="3">
-        <v>659.82654000000002</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+        <v>260.41647</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
-        <v>73.519165000000001</v>
+        <v>7.7123600000000003</v>
       </c>
       <c r="B71" s="3">
         <v>2025</v>
       </c>
       <c r="C71" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D71" s="3">
         <v>4</v>
@@ -3254,21 +3370,21 @@
         <v>16</v>
       </c>
       <c r="F71" s="5">
-        <v>45793</v>
+        <v>45732</v>
       </c>
       <c r="G71" s="3">
-        <v>733.34569999999997</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+        <v>268.12880000000001</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
-        <v>73.128426000000005</v>
+        <v>24.789614</v>
       </c>
       <c r="B72" s="3">
         <v>2025</v>
       </c>
       <c r="C72" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D72" s="3">
         <v>5</v>
@@ -3277,21 +3393,21 @@
         <v>21</v>
       </c>
       <c r="F72" s="5">
-        <v>45798</v>
+        <v>45737</v>
       </c>
       <c r="G72" s="3">
-        <v>806.47410000000002</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+        <v>292.91843</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
-        <v>50.314039999999999</v>
+        <v>23.760328000000001</v>
       </c>
       <c r="B73" s="3">
         <v>2025</v>
       </c>
       <c r="C73" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D73" s="3">
         <v>6</v>
@@ -3300,21 +3416,21 @@
         <v>26</v>
       </c>
       <c r="F73" s="5">
-        <v>45803</v>
+        <v>45742</v>
       </c>
       <c r="G73" s="3">
-        <v>856.78814999999997</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+        <v>316.67876999999999</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
-        <v>56.4529</v>
+        <v>30.345040000000001</v>
       </c>
       <c r="B74" s="3">
         <v>2025</v>
       </c>
       <c r="C74" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D74" s="3">
         <v>1</v>
@@ -3323,21 +3439,21 @@
         <v>1</v>
       </c>
       <c r="F74" s="5">
-        <v>45809</v>
+        <v>45748</v>
       </c>
       <c r="G74" s="3">
-        <v>913.24099999999999</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+        <v>347.02379999999999</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
-        <v>77.087370000000007</v>
+        <v>26.385967000000001</v>
       </c>
       <c r="B75" s="3">
         <v>2025</v>
       </c>
       <c r="C75" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D75" s="3">
         <v>2</v>
@@ -3346,21 +3462,21 @@
         <v>6</v>
       </c>
       <c r="F75" s="5">
-        <v>45814</v>
+        <v>45753</v>
       </c>
       <c r="G75" s="3">
-        <v>990.32839999999999</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+        <v>373.40980000000002</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
-        <v>52.885750000000002</v>
+        <v>14.766455000000001</v>
       </c>
       <c r="B76" s="3">
         <v>2025</v>
       </c>
       <c r="C76" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D76" s="3">
         <v>3</v>
@@ -3369,21 +3485,21 @@
         <v>11</v>
       </c>
       <c r="F76" s="5">
-        <v>45819</v>
+        <v>45758</v>
       </c>
       <c r="G76" s="3">
-        <v>1043.2140999999999</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+        <v>388.17624000000001</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
-        <v>39.925694</v>
+        <v>13.573517000000001</v>
       </c>
       <c r="B77" s="3">
         <v>2025</v>
       </c>
       <c r="C77" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D77" s="3">
         <v>4</v>
@@ -3392,21 +3508,21 @@
         <v>16</v>
       </c>
       <c r="F77" s="5">
-        <v>45824</v>
+        <v>45763</v>
       </c>
       <c r="G77" s="3">
-        <v>1083.1398999999999</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+        <v>401.74975999999998</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
-        <v>77.791659999999993</v>
+        <v>39.140994999999997</v>
       </c>
       <c r="B78" s="3">
         <v>2025</v>
       </c>
       <c r="C78" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D78" s="3">
         <v>5</v>
@@ -3415,21 +3531,21 @@
         <v>21</v>
       </c>
       <c r="F78" s="5">
-        <v>45829</v>
+        <v>45768</v>
       </c>
       <c r="G78" s="3">
-        <v>1160.9314999999999</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+        <v>440.89075000000003</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
-        <v>36.81955</v>
+        <v>41.962490000000003</v>
       </c>
       <c r="B79" s="3">
         <v>2025</v>
       </c>
       <c r="C79" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D79" s="3">
         <v>6</v>
@@ -3438,21 +3554,21 @@
         <v>26</v>
       </c>
       <c r="F79" s="5">
-        <v>45834</v>
+        <v>45773</v>
       </c>
       <c r="G79" s="3">
-        <v>1197.7511</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+        <v>482.85324000000003</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
-        <v>57.959408000000003</v>
+        <v>55.322018</v>
       </c>
       <c r="B80" s="3">
         <v>2025</v>
       </c>
       <c r="C80" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D80" s="3">
         <v>1</v>
@@ -3461,21 +3577,21 @@
         <v>1</v>
       </c>
       <c r="F80" s="5">
-        <v>45839</v>
+        <v>45778</v>
       </c>
       <c r="G80" s="3">
-        <v>1255.7103999999999</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+        <v>538.17523000000006</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
-        <v>46.852511999999997</v>
+        <v>48.162059999999997</v>
       </c>
       <c r="B81" s="3">
         <v>2025</v>
       </c>
       <c r="C81" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D81" s="3">
         <v>2</v>
@@ -3484,21 +3600,21 @@
         <v>6</v>
       </c>
       <c r="F81" s="5">
-        <v>45844</v>
+        <v>45783</v>
       </c>
       <c r="G81" s="3">
-        <v>1302.5630000000001</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+        <v>586.33730000000003</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
-        <v>33.046745000000001</v>
+        <v>73.48912</v>
       </c>
       <c r="B82" s="3">
         <v>2025</v>
       </c>
       <c r="C82" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D82" s="3">
         <v>3</v>
@@ -3507,21 +3623,21 @@
         <v>11</v>
       </c>
       <c r="F82" s="5">
-        <v>45849</v>
+        <v>45788</v>
       </c>
       <c r="G82" s="3">
-        <v>1335.6097</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
+        <v>659.82640000000004</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
-        <v>26.622522</v>
+        <v>73.519159999999999</v>
       </c>
       <c r="B83" s="3">
         <v>2025</v>
       </c>
       <c r="C83" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D83" s="3">
         <v>4</v>
@@ -3530,21 +3646,21 @@
         <v>16</v>
       </c>
       <c r="F83" s="5">
-        <v>45854</v>
+        <v>45793</v>
       </c>
       <c r="G83" s="3">
-        <v>1362.2322999999999</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+        <v>733.34559999999999</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
-        <v>49.471679999999999</v>
+        <v>73.128389999999996</v>
       </c>
       <c r="B84" s="3">
         <v>2025</v>
       </c>
       <c r="C84" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D84" s="3">
         <v>5</v>
@@ -3553,21 +3669,21 @@
         <v>21</v>
       </c>
       <c r="F84" s="5">
-        <v>45859</v>
+        <v>45798</v>
       </c>
       <c r="G84" s="3">
-        <v>1411.704</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
+        <v>806.47400000000005</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
-        <v>50.246727</v>
+        <v>50.314033999999999</v>
       </c>
       <c r="B85" s="3">
         <v>2025</v>
       </c>
       <c r="C85" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D85" s="3">
         <v>6</v>
@@ -3576,21 +3692,21 @@
         <v>26</v>
       </c>
       <c r="F85" s="5">
-        <v>45864</v>
+        <v>45803</v>
       </c>
       <c r="G85" s="3">
-        <v>1461.9507000000001</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
+        <v>856.78800000000001</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
-        <v>14.331683999999999</v>
+        <v>56.452938000000003</v>
       </c>
       <c r="B86" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C86" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D86" s="3">
         <v>1</v>
@@ -3599,21 +3715,21 @@
         <v>1</v>
       </c>
       <c r="F86" s="5">
-        <v>45658</v>
+        <v>45809</v>
       </c>
       <c r="G86" s="3">
-        <v>14.331683999999999</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+        <v>913.24096999999995</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
-        <v>14.564731</v>
+        <v>77.087310000000002</v>
       </c>
       <c r="B87" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C87" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D87" s="3">
         <v>2</v>
@@ -3622,21 +3738,21 @@
         <v>6</v>
       </c>
       <c r="F87" s="5">
-        <v>45663</v>
+        <v>45814</v>
       </c>
       <c r="G87" s="3">
-        <v>28.896415999999999</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+        <v>990.32825000000003</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
-        <v>10.498049</v>
+        <v>52.885773</v>
       </c>
       <c r="B88" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C88" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D88" s="3">
         <v>3</v>
@@ -3645,21 +3761,21 @@
         <v>11</v>
       </c>
       <c r="F88" s="5">
-        <v>45668</v>
+        <v>45819</v>
       </c>
       <c r="G88" s="3">
-        <v>39.394463000000002</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1043.2139999999999</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
-        <v>10.599313</v>
+        <v>39.925713000000002</v>
       </c>
       <c r="B89" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C89" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D89" s="3">
         <v>4</v>
@@ -3668,21 +3784,21 @@
         <v>16</v>
       </c>
       <c r="F89" s="5">
-        <v>45673</v>
+        <v>45824</v>
       </c>
       <c r="G89" s="3">
-        <v>49.993774000000002</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1083.1397999999999</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
-        <v>9.7497159999999994</v>
+        <v>77.791625999999994</v>
       </c>
       <c r="B90" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C90" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D90" s="3">
         <v>5</v>
@@ -3691,21 +3807,21 @@
         <v>21</v>
       </c>
       <c r="F90" s="5">
-        <v>45678</v>
+        <v>45829</v>
       </c>
       <c r="G90" s="3">
-        <v>59.743492000000003</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1160.9313999999999</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
-        <v>8.0435770000000009</v>
+        <v>36.81955</v>
       </c>
       <c r="B91" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C91" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D91" s="3">
         <v>6</v>
@@ -3714,21 +3830,21 @@
         <v>26</v>
       </c>
       <c r="F91" s="5">
-        <v>45683</v>
+        <v>45834</v>
       </c>
       <c r="G91" s="3">
-        <v>67.78707</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1197.751</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
-        <v>8.4454740000000008</v>
+        <v>57.959434999999999</v>
       </c>
       <c r="B92" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C92" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D92" s="3">
         <v>1</v>
@@ -3737,21 +3853,21 @@
         <v>1</v>
       </c>
       <c r="F92" s="5">
-        <v>45689</v>
+        <v>45839</v>
       </c>
       <c r="G92" s="3">
-        <v>76.232544000000004</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1255.7103</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
-        <v>8.7416970000000003</v>
+        <v>46.852519999999998</v>
       </c>
       <c r="B93" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C93" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D93" s="3">
         <v>2</v>
@@ -3760,21 +3876,21 @@
         <v>6</v>
       </c>
       <c r="F93" s="5">
-        <v>45694</v>
+        <v>45844</v>
       </c>
       <c r="G93" s="3">
-        <v>84.974239999999995</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1302.5628999999999</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
-        <v>9.234057</v>
+        <v>33.046756999999999</v>
       </c>
       <c r="B94" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C94" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D94" s="3">
         <v>3</v>
@@ -3783,21 +3899,21 @@
         <v>11</v>
       </c>
       <c r="F94" s="5">
-        <v>45699</v>
+        <v>45849</v>
       </c>
       <c r="G94" s="3">
-        <v>94.208299999999994</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1335.6096</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
-        <v>8.8217879999999997</v>
+        <v>26.622537999999999</v>
       </c>
       <c r="B95" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C95" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D95" s="3">
         <v>4</v>
@@ -3806,21 +3922,21 @@
         <v>16</v>
       </c>
       <c r="F95" s="5">
-        <v>45704</v>
+        <v>45854</v>
       </c>
       <c r="G95" s="3">
-        <v>103.03008</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1362.2321999999999</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
-        <v>7.0881577</v>
+        <v>49.471690000000002</v>
       </c>
       <c r="B96" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C96" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D96" s="3">
         <v>5</v>
@@ -3829,21 +3945,21 @@
         <v>21</v>
       </c>
       <c r="F96" s="5">
-        <v>45709</v>
+        <v>45859</v>
       </c>
       <c r="G96" s="3">
-        <v>110.11824</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1411.7039</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
-        <v>5.2113975999999997</v>
+        <v>50.246704000000001</v>
       </c>
       <c r="B97" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C97" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D97" s="3">
         <v>6</v>
@@ -3852,21 +3968,21 @@
         <v>26</v>
       </c>
       <c r="F97" s="5">
-        <v>45714</v>
+        <v>45864</v>
       </c>
       <c r="G97" s="3">
-        <v>115.32964</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1461.9505999999999</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
-        <v>9.0188410000000001</v>
+        <v>65.807159999999996</v>
       </c>
       <c r="B98" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C98" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D98" s="3">
         <v>1</v>
@@ -3875,21 +3991,21 @@
         <v>1</v>
       </c>
       <c r="F98" s="5">
-        <v>45717</v>
+        <v>45870</v>
       </c>
       <c r="G98" s="3">
-        <v>124.34848</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1527.7577000000001</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
-        <v>6.5476109999999998</v>
+        <v>19.735720000000001</v>
       </c>
       <c r="B99" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C99" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D99" s="3">
         <v>2</v>
@@ -3898,21 +4014,21 @@
         <v>6</v>
       </c>
       <c r="F99" s="5">
-        <v>45722</v>
+        <v>45875</v>
       </c>
       <c r="G99" s="3">
-        <v>130.89608999999999</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1547.4934000000001</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
-        <v>7.5543903999999999</v>
+        <v>53.463833000000001</v>
       </c>
       <c r="B100" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C100" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D100" s="3">
         <v>3</v>
@@ -3921,21 +4037,21 @@
         <v>11</v>
       </c>
       <c r="F100" s="5">
-        <v>45727</v>
+        <v>45880</v>
       </c>
       <c r="G100" s="3">
-        <v>138.45049</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1600.9573</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
-        <v>10.259204</v>
+        <v>45.599589999999999</v>
       </c>
       <c r="B101" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C101" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D101" s="3">
         <v>4</v>
@@ -3944,21 +4060,21 @@
         <v>16</v>
       </c>
       <c r="F101" s="5">
-        <v>45732</v>
+        <v>45885</v>
       </c>
       <c r="G101" s="3">
-        <v>148.70968999999999</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1646.5569</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
-        <v>8.8252439999999996</v>
+        <v>47.053730000000002</v>
       </c>
       <c r="B102" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C102" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D102" s="3">
         <v>5</v>
@@ -3967,21 +4083,21 @@
         <v>21</v>
       </c>
       <c r="F102" s="5">
-        <v>45737</v>
+        <v>45890</v>
       </c>
       <c r="G102" s="3">
-        <v>157.53493</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1693.6106</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
-        <v>11.316482000000001</v>
+        <v>63.832836</v>
       </c>
       <c r="B103" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C103" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D103" s="3">
         <v>6</v>
@@ -3990,21 +4106,21 @@
         <v>26</v>
       </c>
       <c r="F103" s="5">
-        <v>45742</v>
+        <v>45895</v>
       </c>
       <c r="G103" s="3">
-        <v>168.85140999999999</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1757.4435000000001</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
-        <v>13.784658</v>
+        <v>50.112952999999997</v>
       </c>
       <c r="B104" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C104" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D104" s="3">
         <v>1</v>
@@ -4013,21 +4129,21 @@
         <v>1</v>
       </c>
       <c r="F104" s="5">
-        <v>45748</v>
+        <v>45901</v>
       </c>
       <c r="G104" s="3">
-        <v>182.63607999999999</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1807.5563999999999</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
-        <v>18.13364</v>
+        <v>39.404277999999998</v>
       </c>
       <c r="B105" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C105" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D105" s="3">
         <v>2</v>
@@ -4036,21 +4152,21 @@
         <v>6</v>
       </c>
       <c r="F105" s="5">
-        <v>45753</v>
+        <v>45906</v>
       </c>
       <c r="G105" s="3">
-        <v>200.76971</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1846.9607000000001</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
-        <v>14.012308000000001</v>
+        <v>57.028472999999998</v>
       </c>
       <c r="B106" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C106" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D106" s="3">
         <v>3</v>
@@ -4059,21 +4175,21 @@
         <v>11</v>
       </c>
       <c r="F106" s="5">
-        <v>45758</v>
+        <v>45911</v>
       </c>
       <c r="G106" s="3">
-        <v>214.78201000000001</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1903.9891</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
-        <v>16.865030000000001</v>
+        <v>52.184063000000002</v>
       </c>
       <c r="B107" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C107" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D107" s="3">
         <v>4</v>
@@ -4082,21 +4198,21 @@
         <v>16</v>
       </c>
       <c r="F107" s="5">
-        <v>45763</v>
+        <v>45916</v>
       </c>
       <c r="G107" s="3">
-        <v>231.64705000000001</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1956.1732</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
-        <v>32.868423</v>
+        <v>59.124560000000002</v>
       </c>
       <c r="B108" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C108" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D108" s="3">
         <v>5</v>
@@ -4105,21 +4221,21 @@
         <v>21</v>
       </c>
       <c r="F108" s="5">
-        <v>45768</v>
+        <v>45921</v>
       </c>
       <c r="G108" s="3">
-        <v>264.51546999999999</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
+        <v>2015.2977000000001</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
-        <v>42.111977000000003</v>
+        <v>57.502459999999999</v>
       </c>
       <c r="B109" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C109" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D109" s="3">
         <v>6</v>
@@ -4128,21 +4244,21 @@
         <v>26</v>
       </c>
       <c r="F109" s="5">
-        <v>45773</v>
+        <v>45926</v>
       </c>
       <c r="G109" s="3">
-        <v>306.62743999999998</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
+        <v>2072.8002999999999</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="3">
-        <v>42.059672999999997</v>
+        <v>14.331683999999999</v>
       </c>
       <c r="B110" s="3">
         <v>1991</v>
       </c>
       <c r="C110" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D110" s="3">
         <v>1</v>
@@ -4151,21 +4267,21 @@
         <v>1</v>
       </c>
       <c r="F110" s="5">
-        <v>45778</v>
+        <v>45658</v>
       </c>
       <c r="G110" s="3">
-        <v>348.68713000000002</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
+        <v>14.331683999999999</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
-        <v>45.601909999999997</v>
+        <v>14.56471</v>
       </c>
       <c r="B111" s="3">
         <v>1991</v>
       </c>
       <c r="C111" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D111" s="3">
         <v>2</v>
@@ -4174,21 +4290,21 @@
         <v>6</v>
       </c>
       <c r="F111" s="5">
-        <v>45783</v>
+        <v>45663</v>
       </c>
       <c r="G111" s="3">
-        <v>394.28903000000003</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
+        <v>28.896393</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
-        <v>50.457825</v>
+        <v>10.498047</v>
       </c>
       <c r="B112" s="3">
         <v>1991</v>
       </c>
       <c r="C112" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D112" s="3">
         <v>3</v>
@@ -4197,21 +4313,21 @@
         <v>11</v>
       </c>
       <c r="F112" s="5">
-        <v>45788</v>
+        <v>45668</v>
       </c>
       <c r="G112" s="3">
-        <v>444.74686000000003</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
+        <v>39.394440000000003</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
-        <v>60.332355</v>
+        <v>10.599316999999999</v>
       </c>
       <c r="B113" s="3">
         <v>1991</v>
       </c>
       <c r="C113" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D113" s="3">
         <v>4</v>
@@ -4220,21 +4336,21 @@
         <v>16</v>
       </c>
       <c r="F113" s="5">
-        <v>45793</v>
+        <v>45673</v>
       </c>
       <c r="G113" s="3">
-        <v>505.07922000000002</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
+        <v>49.993760000000002</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="3">
-        <v>55.695160000000001</v>
+        <v>9.7497159999999994</v>
       </c>
       <c r="B114" s="3">
         <v>1991</v>
       </c>
       <c r="C114" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D114" s="3">
         <v>5</v>
@@ -4243,21 +4359,21 @@
         <v>21</v>
       </c>
       <c r="F114" s="5">
-        <v>45798</v>
+        <v>45678</v>
       </c>
       <c r="G114" s="3">
-        <v>560.77435000000003</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
+        <v>59.743473000000002</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
-        <v>70.140879999999996</v>
+        <v>8.0435789999999994</v>
       </c>
       <c r="B115" s="3">
         <v>1991</v>
       </c>
       <c r="C115" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D115" s="3">
         <v>6</v>
@@ -4266,21 +4382,21 @@
         <v>26</v>
       </c>
       <c r="F115" s="5">
-        <v>45803</v>
+        <v>45683</v>
       </c>
       <c r="G115" s="3">
-        <v>630.9153</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
+        <v>67.787049999999994</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="3">
-        <v>53.365273000000002</v>
+        <v>8.4454689999999992</v>
       </c>
       <c r="B116" s="3">
         <v>1991</v>
       </c>
       <c r="C116" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D116" s="3">
         <v>1</v>
@@ -4289,21 +4405,21 @@
         <v>1</v>
       </c>
       <c r="F116" s="5">
-        <v>45809</v>
+        <v>45689</v>
       </c>
       <c r="G116" s="3">
-        <v>684.28049999999996</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
+        <v>76.232519999999994</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
-        <v>50.324043000000003</v>
+        <v>8.741695</v>
       </c>
       <c r="B117" s="3">
         <v>1991</v>
       </c>
       <c r="C117" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D117" s="3">
         <v>2</v>
@@ -4312,21 +4428,21 @@
         <v>6</v>
       </c>
       <c r="F117" s="5">
-        <v>45814</v>
+        <v>45694</v>
       </c>
       <c r="G117" s="3">
-        <v>734.60455000000002</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
+        <v>84.974209999999999</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="3">
-        <v>54.202570000000001</v>
+        <v>9.2340560000000007</v>
       </c>
       <c r="B118" s="3">
         <v>1991</v>
       </c>
       <c r="C118" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D118" s="3">
         <v>3</v>
@@ -4335,21 +4451,21 @@
         <v>11</v>
       </c>
       <c r="F118" s="5">
-        <v>45819</v>
+        <v>45699</v>
       </c>
       <c r="G118" s="3">
-        <v>788.80709999999999</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
+        <v>94.208275</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="3">
-        <v>52.986744000000002</v>
+        <v>8.82179</v>
       </c>
       <c r="B119" s="3">
         <v>1991</v>
       </c>
       <c r="C119" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D119" s="3">
         <v>4</v>
@@ -4358,21 +4474,21 @@
         <v>16</v>
       </c>
       <c r="F119" s="5">
-        <v>45824</v>
+        <v>45704</v>
       </c>
       <c r="G119" s="3">
-        <v>841.79390000000001</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+        <v>103.03006000000001</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" s="3">
-        <v>54.639809999999997</v>
+        <v>7.0881604999999999</v>
       </c>
       <c r="B120" s="3">
         <v>1991</v>
       </c>
       <c r="C120" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D120" s="3">
         <v>5</v>
@@ -4381,21 +4497,21 @@
         <v>21</v>
       </c>
       <c r="F120" s="5">
-        <v>45829</v>
+        <v>45709</v>
       </c>
       <c r="G120" s="3">
-        <v>896.43370000000004</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+        <v>110.118225</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" s="3">
-        <v>53.125706000000001</v>
+        <v>5.2113990000000001</v>
       </c>
       <c r="B121" s="3">
         <v>1991</v>
       </c>
       <c r="C121" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D121" s="3">
         <v>6</v>
@@ -4404,21 +4520,21 @@
         <v>26</v>
       </c>
       <c r="F121" s="5">
-        <v>45834</v>
+        <v>45714</v>
       </c>
       <c r="G121" s="3">
-        <v>949.55939999999998</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
+        <v>115.32962000000001</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" s="3">
-        <v>46.782597000000003</v>
+        <v>9.0188430000000004</v>
       </c>
       <c r="B122" s="3">
         <v>1991</v>
       </c>
       <c r="C122" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D122" s="3">
         <v>1</v>
@@ -4427,21 +4543,21 @@
         <v>1</v>
       </c>
       <c r="F122" s="5">
-        <v>45839</v>
+        <v>45717</v>
       </c>
       <c r="G122" s="3">
-        <v>996.34199999999998</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
+        <v>124.348465</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" s="3">
-        <v>47.738444999999999</v>
+        <v>6.5476146000000002</v>
       </c>
       <c r="B123" s="3">
         <v>1991</v>
       </c>
       <c r="C123" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D123" s="3">
         <v>2</v>
@@ -4450,21 +4566,21 @@
         <v>6</v>
       </c>
       <c r="F123" s="5">
-        <v>45844</v>
+        <v>45722</v>
       </c>
       <c r="G123" s="3">
-        <v>1044.0804000000001</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+        <v>130.89607000000001</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" s="3">
-        <v>48.982050000000001</v>
+        <v>7.5543930000000001</v>
       </c>
       <c r="B124" s="3">
         <v>1991</v>
       </c>
       <c r="C124" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D124" s="3">
         <v>3</v>
@@ -4473,21 +4589,21 @@
         <v>11</v>
       </c>
       <c r="F124" s="5">
-        <v>45849</v>
+        <v>45727</v>
       </c>
       <c r="G124" s="3">
-        <v>1093.0625</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+        <v>138.45047</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" s="3">
-        <v>45.302666000000002</v>
+        <v>10.259205</v>
       </c>
       <c r="B125" s="3">
         <v>1991</v>
       </c>
       <c r="C125" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D125" s="3">
         <v>4</v>
@@ -4496,21 +4612,21 @@
         <v>16</v>
       </c>
       <c r="F125" s="5">
-        <v>45854</v>
+        <v>45732</v>
       </c>
       <c r="G125" s="3">
-        <v>1138.3651</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
+        <v>148.70966999999999</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="3">
-        <v>45.867165</v>
+        <v>8.8252400000000009</v>
       </c>
       <c r="B126" s="3">
         <v>1991</v>
       </c>
       <c r="C126" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D126" s="3">
         <v>5</v>
@@ -4519,21 +4635,21 @@
         <v>21</v>
       </c>
       <c r="F126" s="5">
-        <v>45859</v>
+        <v>45737</v>
       </c>
       <c r="G126" s="3">
-        <v>1184.2322999999999</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
+        <v>157.53491</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" s="3">
-        <v>62.545997999999997</v>
+        <v>11.316477000000001</v>
       </c>
       <c r="B127" s="3">
         <v>1991</v>
       </c>
       <c r="C127" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D127" s="3">
         <v>6</v>
@@ -4542,280 +4658,1000 @@
         <v>26</v>
       </c>
       <c r="F127" s="5">
+        <v>45742</v>
+      </c>
+      <c r="G127" s="3">
+        <v>168.85140000000001</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A128" s="3">
+        <v>13.784653</v>
+      </c>
+      <c r="B128" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C128" s="3">
+        <v>4</v>
+      </c>
+      <c r="D128" s="3">
+        <v>1</v>
+      </c>
+      <c r="E128" s="3">
+        <v>1</v>
+      </c>
+      <c r="F128" s="5">
+        <v>45748</v>
+      </c>
+      <c r="G128" s="3">
+        <v>182.63605000000001</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A129" s="3">
+        <v>18.133655999999998</v>
+      </c>
+      <c r="B129" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C129" s="3">
+        <v>4</v>
+      </c>
+      <c r="D129" s="3">
+        <v>2</v>
+      </c>
+      <c r="E129" s="3">
+        <v>6</v>
+      </c>
+      <c r="F129" s="5">
+        <v>45753</v>
+      </c>
+      <c r="G129" s="3">
+        <v>200.7697</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A130" s="3">
+        <v>14.012309</v>
+      </c>
+      <c r="B130" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C130" s="3">
+        <v>4</v>
+      </c>
+      <c r="D130" s="3">
+        <v>3</v>
+      </c>
+      <c r="E130" s="3">
+        <v>11</v>
+      </c>
+      <c r="F130" s="5">
+        <v>45758</v>
+      </c>
+      <c r="G130" s="3">
+        <v>214.78201000000001</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A131" s="3">
+        <v>16.865026</v>
+      </c>
+      <c r="B131" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C131" s="3">
+        <v>4</v>
+      </c>
+      <c r="D131" s="3">
+        <v>4</v>
+      </c>
+      <c r="E131" s="3">
+        <v>16</v>
+      </c>
+      <c r="F131" s="5">
+        <v>45763</v>
+      </c>
+      <c r="G131" s="3">
+        <v>231.64703</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A132" s="3">
+        <v>32.86842</v>
+      </c>
+      <c r="B132" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C132" s="3">
+        <v>4</v>
+      </c>
+      <c r="D132" s="3">
+        <v>5</v>
+      </c>
+      <c r="E132" s="3">
+        <v>21</v>
+      </c>
+      <c r="F132" s="5">
+        <v>45768</v>
+      </c>
+      <c r="G132" s="3">
+        <v>264.51544000000001</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A133" s="3">
+        <v>42.111977000000003</v>
+      </c>
+      <c r="B133" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C133" s="3">
+        <v>4</v>
+      </c>
+      <c r="D133" s="3">
+        <v>6</v>
+      </c>
+      <c r="E133" s="3">
+        <v>26</v>
+      </c>
+      <c r="F133" s="5">
+        <v>45773</v>
+      </c>
+      <c r="G133" s="3">
+        <v>306.62743999999998</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A134" s="3">
+        <v>42.059685000000002</v>
+      </c>
+      <c r="B134" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C134" s="3">
+        <v>5</v>
+      </c>
+      <c r="D134" s="3">
+        <v>1</v>
+      </c>
+      <c r="E134" s="3">
+        <v>1</v>
+      </c>
+      <c r="F134" s="5">
+        <v>45778</v>
+      </c>
+      <c r="G134" s="3">
+        <v>348.68713000000002</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A135" s="3">
+        <v>45.601883000000001</v>
+      </c>
+      <c r="B135" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C135" s="3">
+        <v>5</v>
+      </c>
+      <c r="D135" s="3">
+        <v>2</v>
+      </c>
+      <c r="E135" s="3">
+        <v>6</v>
+      </c>
+      <c r="F135" s="5">
+        <v>45783</v>
+      </c>
+      <c r="G135" s="3">
+        <v>394.28899999999999</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A136" s="3">
+        <v>50.457782999999999</v>
+      </c>
+      <c r="B136" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C136" s="3">
+        <v>5</v>
+      </c>
+      <c r="D136" s="3">
+        <v>3</v>
+      </c>
+      <c r="E136" s="3">
+        <v>11</v>
+      </c>
+      <c r="F136" s="5">
+        <v>45788</v>
+      </c>
+      <c r="G136" s="3">
+        <v>444.74680000000001</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A137" s="3">
+        <v>60.332332999999998</v>
+      </c>
+      <c r="B137" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C137" s="3">
+        <v>5</v>
+      </c>
+      <c r="D137" s="3">
+        <v>4</v>
+      </c>
+      <c r="E137" s="3">
+        <v>16</v>
+      </c>
+      <c r="F137" s="5">
+        <v>45793</v>
+      </c>
+      <c r="G137" s="3">
+        <v>505.07909999999998</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A138" s="3">
+        <v>55.695149999999998</v>
+      </c>
+      <c r="B138" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C138" s="3">
+        <v>5</v>
+      </c>
+      <c r="D138" s="3">
+        <v>5</v>
+      </c>
+      <c r="E138" s="3">
+        <v>21</v>
+      </c>
+      <c r="F138" s="5">
+        <v>45798</v>
+      </c>
+      <c r="G138" s="3">
+        <v>560.77430000000004</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A139" s="3">
+        <v>70.140854000000004</v>
+      </c>
+      <c r="B139" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C139" s="3">
+        <v>5</v>
+      </c>
+      <c r="D139" s="3">
+        <v>6</v>
+      </c>
+      <c r="E139" s="3">
+        <v>26</v>
+      </c>
+      <c r="F139" s="5">
+        <v>45803</v>
+      </c>
+      <c r="G139" s="3">
+        <v>630.91510000000005</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A140" s="3">
+        <v>53.365290000000002</v>
+      </c>
+      <c r="B140" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C140" s="3">
+        <v>6</v>
+      </c>
+      <c r="D140" s="3">
+        <v>1</v>
+      </c>
+      <c r="E140" s="3">
+        <v>1</v>
+      </c>
+      <c r="F140" s="5">
+        <v>45809</v>
+      </c>
+      <c r="G140" s="3">
+        <v>684.28039999999999</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A141" s="3">
+        <v>50.324066000000002</v>
+      </c>
+      <c r="B141" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C141" s="3">
+        <v>6</v>
+      </c>
+      <c r="D141" s="3">
+        <v>2</v>
+      </c>
+      <c r="E141" s="3">
+        <v>6</v>
+      </c>
+      <c r="F141" s="5">
+        <v>45814</v>
+      </c>
+      <c r="G141" s="3">
+        <v>734.60450000000003</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A142" s="3">
+        <v>54.202564000000002</v>
+      </c>
+      <c r="B142" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C142" s="3">
+        <v>6</v>
+      </c>
+      <c r="D142" s="3">
+        <v>3</v>
+      </c>
+      <c r="E142" s="3">
+        <v>11</v>
+      </c>
+      <c r="F142" s="5">
+        <v>45819</v>
+      </c>
+      <c r="G142" s="3">
+        <v>788.80700000000002</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A143" s="3">
+        <v>52.986739999999998</v>
+      </c>
+      <c r="B143" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C143" s="3">
+        <v>6</v>
+      </c>
+      <c r="D143" s="3">
+        <v>4</v>
+      </c>
+      <c r="E143" s="3">
+        <v>16</v>
+      </c>
+      <c r="F143" s="5">
+        <v>45824</v>
+      </c>
+      <c r="G143" s="3">
+        <v>841.79376000000002</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A144" s="3">
+        <v>54.639823999999997</v>
+      </c>
+      <c r="B144" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C144" s="3">
+        <v>6</v>
+      </c>
+      <c r="D144" s="3">
+        <v>5</v>
+      </c>
+      <c r="E144" s="3">
+        <v>21</v>
+      </c>
+      <c r="F144" s="5">
+        <v>45829</v>
+      </c>
+      <c r="G144" s="3">
+        <v>896.43359999999996</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A145" s="3">
+        <v>53.125689999999999</v>
+      </c>
+      <c r="B145" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C145" s="3">
+        <v>6</v>
+      </c>
+      <c r="D145" s="3">
+        <v>6</v>
+      </c>
+      <c r="E145" s="3">
+        <v>26</v>
+      </c>
+      <c r="F145" s="5">
+        <v>45834</v>
+      </c>
+      <c r="G145" s="3">
+        <v>949.55926999999997</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A146" s="3">
+        <v>46.782573999999997</v>
+      </c>
+      <c r="B146" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C146" s="3">
+        <v>7</v>
+      </c>
+      <c r="D146" s="3">
+        <v>1</v>
+      </c>
+      <c r="E146" s="3">
+        <v>1</v>
+      </c>
+      <c r="F146" s="5">
+        <v>45839</v>
+      </c>
+      <c r="G146" s="3">
+        <v>996.34186</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A147" s="3">
+        <v>47.738422</v>
+      </c>
+      <c r="B147" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C147" s="3">
+        <v>7</v>
+      </c>
+      <c r="D147" s="3">
+        <v>2</v>
+      </c>
+      <c r="E147" s="3">
+        <v>6</v>
+      </c>
+      <c r="F147" s="5">
+        <v>45844</v>
+      </c>
+      <c r="G147" s="3">
+        <v>1044.0803000000001</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A148" s="3">
+        <v>48.982067000000001</v>
+      </c>
+      <c r="B148" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C148" s="3">
+        <v>7</v>
+      </c>
+      <c r="D148" s="3">
+        <v>3</v>
+      </c>
+      <c r="E148" s="3">
+        <v>11</v>
+      </c>
+      <c r="F148" s="5">
+        <v>45849</v>
+      </c>
+      <c r="G148" s="3">
+        <v>1093.0624</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A149" s="3">
+        <v>45.302653999999997</v>
+      </c>
+      <c r="B149" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C149" s="3">
+        <v>7</v>
+      </c>
+      <c r="D149" s="3">
+        <v>4</v>
+      </c>
+      <c r="E149" s="3">
+        <v>16</v>
+      </c>
+      <c r="F149" s="5">
+        <v>45854</v>
+      </c>
+      <c r="G149" s="3">
+        <v>1138.365</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A150" s="3">
+        <v>45.867170000000002</v>
+      </c>
+      <c r="B150" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C150" s="3">
+        <v>7</v>
+      </c>
+      <c r="D150" s="3">
+        <v>5</v>
+      </c>
+      <c r="E150" s="3">
+        <v>21</v>
+      </c>
+      <c r="F150" s="5">
+        <v>45859</v>
+      </c>
+      <c r="G150" s="3">
+        <v>1184.2321999999999</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A151" s="3">
+        <v>62.54598</v>
+      </c>
+      <c r="B151" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C151" s="3">
+        <v>7</v>
+      </c>
+      <c r="D151" s="3">
+        <v>6</v>
+      </c>
+      <c r="E151" s="3">
+        <v>26</v>
+      </c>
+      <c r="F151" s="5">
         <v>45864</v>
       </c>
-      <c r="G127" s="3">
-        <v>1246.7782999999999</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="F128" s="5"/>
-    </row>
-    <row r="129" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F129" s="5"/>
-    </row>
-    <row r="130" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F130" s="5"/>
-    </row>
-    <row r="131" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F131" s="5"/>
-    </row>
-    <row r="132" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F132" s="5"/>
-    </row>
-    <row r="133" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F133" s="5"/>
-    </row>
-    <row r="134" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F134" s="5"/>
-    </row>
-    <row r="135" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F135" s="5"/>
-    </row>
-    <row r="136" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F136" s="5"/>
-    </row>
-    <row r="137" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F137" s="5"/>
-    </row>
-    <row r="138" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F138" s="5"/>
-    </row>
-    <row r="139" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F139" s="5"/>
-    </row>
-    <row r="140" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F140" s="5"/>
-    </row>
-    <row r="141" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F141" s="5"/>
-    </row>
-    <row r="142" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F142" s="5"/>
-    </row>
-    <row r="143" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F143" s="5"/>
-    </row>
-    <row r="144" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F144" s="5"/>
-    </row>
-    <row r="145" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F145" s="5"/>
-    </row>
-    <row r="146" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F146" s="5"/>
-    </row>
-    <row r="147" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F147" s="5"/>
-    </row>
-    <row r="148" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F148" s="5"/>
-    </row>
-    <row r="149" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F149" s="5"/>
-    </row>
-    <row r="150" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F150" s="5"/>
-    </row>
-    <row r="151" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F151" s="5"/>
-    </row>
-    <row r="152" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F152" s="5"/>
-    </row>
-    <row r="153" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F153" s="5"/>
-    </row>
-    <row r="154" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F154" s="5"/>
-    </row>
-    <row r="155" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F155" s="5"/>
-    </row>
-    <row r="156" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F156" s="5"/>
-    </row>
-    <row r="157" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F157" s="5"/>
-    </row>
-    <row r="158" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F158" s="5"/>
-    </row>
-    <row r="159" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F159" s="5"/>
-    </row>
-    <row r="160" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F160" s="5"/>
-    </row>
-    <row r="161" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F161" s="5"/>
-    </row>
-    <row r="162" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F162" s="5"/>
-    </row>
-    <row r="163" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F163" s="5"/>
-    </row>
-    <row r="164" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="G151" s="3">
+        <v>1246.7782</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A152" s="3">
+        <v>45.043132999999997</v>
+      </c>
+      <c r="B152" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C152" s="3">
+        <v>8</v>
+      </c>
+      <c r="D152" s="3">
+        <v>1</v>
+      </c>
+      <c r="E152" s="3">
+        <v>1</v>
+      </c>
+      <c r="F152" s="5">
+        <v>45870</v>
+      </c>
+      <c r="G152" s="3">
+        <v>1291.8213000000001</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A153" s="3">
+        <v>53.149116999999997</v>
+      </c>
+      <c r="B153" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C153" s="3">
+        <v>8</v>
+      </c>
+      <c r="D153" s="3">
+        <v>2</v>
+      </c>
+      <c r="E153" s="3">
+        <v>6</v>
+      </c>
+      <c r="F153" s="5">
+        <v>45875</v>
+      </c>
+      <c r="G153" s="3">
+        <v>1344.9704999999999</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A154" s="3">
+        <v>55.673830000000002</v>
+      </c>
+      <c r="B154" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C154" s="3">
+        <v>8</v>
+      </c>
+      <c r="D154" s="3">
+        <v>3</v>
+      </c>
+      <c r="E154" s="3">
+        <v>11</v>
+      </c>
+      <c r="F154" s="5">
+        <v>45880</v>
+      </c>
+      <c r="G154" s="3">
+        <v>1400.6442999999999</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A155" s="3">
+        <v>51.891243000000003</v>
+      </c>
+      <c r="B155" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C155" s="3">
+        <v>8</v>
+      </c>
+      <c r="D155" s="3">
+        <v>4</v>
+      </c>
+      <c r="E155" s="3">
+        <v>16</v>
+      </c>
+      <c r="F155" s="5">
+        <v>45885</v>
+      </c>
+      <c r="G155" s="3">
+        <v>1452.5355</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A156" s="3">
+        <v>55.258389999999999</v>
+      </c>
+      <c r="B156" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C156" s="3">
+        <v>8</v>
+      </c>
+      <c r="D156" s="3">
+        <v>5</v>
+      </c>
+      <c r="E156" s="3">
+        <v>21</v>
+      </c>
+      <c r="F156" s="5">
+        <v>45890</v>
+      </c>
+      <c r="G156" s="3">
+        <v>1507.7937999999999</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A157" s="3">
+        <v>65.58399</v>
+      </c>
+      <c r="B157" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C157" s="3">
+        <v>8</v>
+      </c>
+      <c r="D157" s="3">
+        <v>6</v>
+      </c>
+      <c r="E157" s="3">
+        <v>26</v>
+      </c>
+      <c r="F157" s="5">
+        <v>45895</v>
+      </c>
+      <c r="G157" s="3">
+        <v>1573.3778</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A158" s="3">
+        <v>54.274096999999998</v>
+      </c>
+      <c r="B158" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C158" s="3">
+        <v>9</v>
+      </c>
+      <c r="D158" s="3">
+        <v>1</v>
+      </c>
+      <c r="E158" s="3">
+        <v>1</v>
+      </c>
+      <c r="F158" s="5">
+        <v>45901</v>
+      </c>
+      <c r="G158" s="3">
+        <v>1627.652</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A159" s="3">
+        <v>54.068072999999998</v>
+      </c>
+      <c r="B159" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C159" s="3">
+        <v>9</v>
+      </c>
+      <c r="D159" s="3">
+        <v>2</v>
+      </c>
+      <c r="E159" s="3">
+        <v>6</v>
+      </c>
+      <c r="F159" s="5">
+        <v>45906</v>
+      </c>
+      <c r="G159" s="3">
+        <v>1681.72</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A160" s="3">
+        <v>62.027008000000002</v>
+      </c>
+      <c r="B160" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C160" s="3">
+        <v>9</v>
+      </c>
+      <c r="D160" s="3">
+        <v>3</v>
+      </c>
+      <c r="E160" s="3">
+        <v>11</v>
+      </c>
+      <c r="F160" s="5">
+        <v>45911</v>
+      </c>
+      <c r="G160" s="3">
+        <v>1743.7471</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A161" s="3">
+        <v>60.091434</v>
+      </c>
+      <c r="B161" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C161" s="3">
+        <v>9</v>
+      </c>
+      <c r="D161" s="3">
+        <v>4</v>
+      </c>
+      <c r="E161" s="3">
+        <v>16</v>
+      </c>
+      <c r="F161" s="5">
+        <v>45916</v>
+      </c>
+      <c r="G161" s="3">
+        <v>1803.8385000000001</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A162" s="3">
+        <v>61.807850000000002</v>
+      </c>
+      <c r="B162" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C162" s="3">
+        <v>9</v>
+      </c>
+      <c r="D162" s="3">
+        <v>5</v>
+      </c>
+      <c r="E162" s="3">
+        <v>21</v>
+      </c>
+      <c r="F162" s="5">
+        <v>45921</v>
+      </c>
+      <c r="G162" s="3">
+        <v>1865.6464000000001</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A163" s="3">
+        <v>60.098236</v>
+      </c>
+      <c r="B163" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C163" s="3">
+        <v>9</v>
+      </c>
+      <c r="D163" s="3">
+        <v>6</v>
+      </c>
+      <c r="E163" s="3">
+        <v>26</v>
+      </c>
+      <c r="F163" s="5">
+        <v>45926</v>
+      </c>
+      <c r="G163" s="3">
+        <v>1925.7445</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F164" s="5"/>
     </row>
-    <row r="165" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F165" s="5"/>
     </row>
-    <row r="166" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F166" s="5"/>
     </row>
-    <row r="167" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F167" s="5"/>
     </row>
-    <row r="168" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F168" s="5"/>
     </row>
-    <row r="169" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F169" s="5"/>
     </row>
-    <row r="170" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F170" s="5"/>
     </row>
-    <row r="171" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F171" s="5"/>
     </row>
-    <row r="172" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F172" s="5"/>
     </row>
-    <row r="173" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F173" s="5"/>
     </row>
-    <row r="174" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F174" s="5"/>
     </row>
-    <row r="175" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F175" s="5"/>
     </row>
-    <row r="176" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F176" s="5"/>
     </row>
-    <row r="177" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="177" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F177" s="5"/>
     </row>
-    <row r="178" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="178" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F178" s="5"/>
     </row>
-    <row r="179" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="179" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F179" s="5"/>
     </row>
-    <row r="180" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="180" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F180" s="5"/>
     </row>
-    <row r="181" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="181" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F181" s="5"/>
     </row>
-    <row r="182" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="182" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F182" s="5"/>
     </row>
-    <row r="183" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="183" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F183" s="5"/>
     </row>
-    <row r="184" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="184" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F184" s="5"/>
     </row>
-    <row r="185" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="185" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F185" s="5"/>
     </row>
-    <row r="186" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="186" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F186" s="5"/>
     </row>
-    <row r="187" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="187" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F187" s="5"/>
     </row>
-    <row r="188" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="188" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F188" s="5"/>
     </row>
-    <row r="189" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="189" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F189" s="5"/>
     </row>
-    <row r="190" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="190" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F190" s="5"/>
     </row>
-    <row r="191" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="191" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F191" s="5"/>
     </row>
-    <row r="192" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="192" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F192" s="5"/>
     </row>
-    <row r="193" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="193" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F193" s="5"/>
     </row>
-    <row r="194" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="194" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F194" s="5"/>
     </row>
-    <row r="195" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="195" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F195" s="5"/>
     </row>
-    <row r="196" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="196" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F196" s="5"/>
     </row>
-    <row r="197" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="197" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F197" s="5"/>
     </row>
-    <row r="198" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="198" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F198" s="5"/>
     </row>
-    <row r="199" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="199" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F199" s="5"/>
     </row>
-    <row r="200" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="200" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F200" s="5"/>
     </row>
-    <row r="201" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="201" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F201" s="5"/>
     </row>
-    <row r="202" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="202" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F202" s="5"/>
     </row>
-    <row r="203" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="203" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F203" s="5"/>
     </row>
-    <row r="204" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="204" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F204" s="5"/>
     </row>
-    <row r="205" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="205" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F205" s="5"/>
     </row>
-    <row r="206" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="206" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F206" s="5"/>
     </row>
-    <row r="207" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="207" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F207" s="5"/>
     </row>
-    <row r="208" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="208" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F208" s="5"/>
     </row>
-    <row r="209" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="209" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F209" s="5"/>
     </row>
-    <row r="210" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="210" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F210" s="5"/>
     </row>
-    <row r="211" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="211" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F211" s="5"/>
     </row>
-    <row r="212" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="212" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F212" s="5"/>
     </row>
-    <row r="213" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="213" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F213" s="5"/>
     </row>
-    <row r="214" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="214" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F214" s="5"/>
     </row>
-    <row r="215" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="215" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F215" s="5"/>
     </row>
-    <row r="216" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="216" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F216" s="5"/>
     </row>
-    <row r="217" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="217" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F217" s="5"/>
     </row>
   </sheetData>
@@ -4825,17 +5661,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FB690C8-F874-4A1B-874A-043689354636}">
-  <dimension ref="A1:D316"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D406"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>35</v>
       </c>
@@ -4849,7 +5685,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>53.862403999999998</v>
       </c>
@@ -4863,7 +5699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>109.52607</v>
       </c>
@@ -4877,7 +5713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>37.068626000000002</v>
       </c>
@@ -4891,7 +5727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>72.829350000000005</v>
       </c>
@@ -4905,7 +5741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>39.770695000000003</v>
       </c>
@@ -4919,7 +5755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>54.600383999999998</v>
       </c>
@@ -4933,7 +5769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>42.631515999999998</v>
       </c>
@@ -4947,7 +5783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>52.790140000000001</v>
       </c>
@@ -4961,7 +5797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>56.183880000000002</v>
       </c>
@@ -4975,7 +5811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>90.713509999999999</v>
       </c>
@@ -4989,7 +5825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>36.689667</v>
       </c>
@@ -5003,7 +5839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>29.419882000000001</v>
       </c>
@@ -5017,7 +5853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>121.8254</v>
       </c>
@@ -5031,7 +5867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>42.493744</v>
       </c>
@@ -5045,7 +5881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>39.743155999999999</v>
       </c>
@@ -5059,7 +5895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>172.15523999999999</v>
       </c>
@@ -5073,7 +5909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>58.738399999999999</v>
       </c>
@@ -5087,7 +5923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>23.370730999999999</v>
       </c>
@@ -5101,7 +5937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>103.20663</v>
       </c>
@@ -5115,7 +5951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>83.246099999999998</v>
       </c>
@@ -5129,7 +5965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>73.203800000000001</v>
       </c>
@@ -5143,7 +5979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>79.051770000000005</v>
       </c>
@@ -5157,7 +5993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>27.616893999999998</v>
       </c>
@@ -5171,7 +6007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>40.249504000000002</v>
       </c>
@@ -5185,7 +6021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>101.869484</v>
       </c>
@@ -5199,7 +6035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>112.162254</v>
       </c>
@@ -5213,7 +6049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>43.749865999999997</v>
       </c>
@@ -5227,7 +6063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>41.308052000000004</v>
       </c>
@@ -5241,7 +6077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>77.664709999999999</v>
       </c>
@@ -5255,7 +6091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>44.908946999999998</v>
       </c>
@@ -5269,7 +6105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>84.654754999999994</v>
       </c>
@@ -5283,7 +6119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>39.380093000000002</v>
       </c>
@@ -5297,7 +6133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24.891857000000002</v>
       </c>
@@ -5311,7 +6147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>54.203712000000003</v>
       </c>
@@ -5325,7 +6161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>79.719710000000006</v>
       </c>
@@ -5339,7 +6175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>38.609932000000001</v>
       </c>
@@ -5353,7 +6189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>45.219653999999998</v>
       </c>
@@ -5367,7 +6203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>166.74823000000001</v>
       </c>
@@ -5381,7 +6217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>33.346615</v>
       </c>
@@ -5395,7 +6231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>76.794550000000001</v>
       </c>
@@ -5409,7 +6245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>86.438980000000001</v>
       </c>
@@ -5423,7 +6259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>28.074266000000001</v>
       </c>
@@ -5437,7 +6273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>79.049094999999994</v>
       </c>
@@ -5451,7 +6287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>34.256610000000002</v>
       </c>
@@ -5465,7 +6301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>120.1815</v>
       </c>
@@ -5479,7 +6315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>52.978450000000002</v>
       </c>
@@ -5493,7 +6329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>38.164340000000003</v>
       </c>
@@ -5507,7 +6343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>29.440784000000001</v>
       </c>
@@ -5521,7 +6357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>102.63451000000001</v>
       </c>
@@ -5535,7 +6371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>31.274666</v>
       </c>
@@ -5549,7 +6385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>39.991149999999998</v>
       </c>
@@ -5563,7 +6399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>29.485769999999999</v>
       </c>
@@ -5577,7 +6413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>34.547896999999999</v>
       </c>
@@ -5591,7 +6427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>44.945050000000002</v>
       </c>
@@ -5605,7 +6441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>37.052370000000003</v>
       </c>
@@ -5619,7 +6455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>31.673293999999999</v>
       </c>
@@ -5633,7 +6469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>33.673878000000002</v>
       </c>
@@ -5647,7 +6483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>29.172964</v>
       </c>
@@ -5661,7 +6497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>25.892277</v>
       </c>
@@ -5675,7 +6511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>23.489878000000001</v>
       </c>
@@ -5689,7 +6525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>91.997159999999994</v>
       </c>
@@ -5703,7 +6539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>86.714929999999995</v>
       </c>
@@ -5717,7 +6553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>52.931759999999997</v>
       </c>
@@ -5731,7 +6567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>87.845214999999996</v>
       </c>
@@ -5745,7 +6581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>50.547879999999999</v>
       </c>
@@ -5759,7 +6595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>30.622472999999999</v>
       </c>
@@ -5773,7 +6609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>33.613014</v>
       </c>
@@ -5787,7 +6623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>29.359780000000001</v>
       </c>
@@ -5801,7 +6637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>28.806056999999999</v>
       </c>
@@ -5815,7 +6651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>26.899681000000001</v>
       </c>
@@ -5829,7 +6665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>52.781570000000002</v>
       </c>
@@ -5843,7 +6679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>22.815199</v>
       </c>
@@ -5857,7 +6693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>75.868200000000002</v>
       </c>
@@ -5871,7 +6707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>55.837623999999998</v>
       </c>
@@ -5885,7 +6721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>72.962459999999993</v>
       </c>
@@ -5899,7 +6735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>50.02872</v>
       </c>
@@ -5913,7 +6749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>24.565756</v>
       </c>
@@ -5927,7 +6763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>28.205870000000001</v>
       </c>
@@ -5941,7 +6777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>24.171285999999998</v>
       </c>
@@ -5955,7 +6791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>48.388039999999997</v>
       </c>
@@ -5969,7 +6805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>20.789180000000002</v>
       </c>
@@ -5983,7 +6819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>29.337392999999999</v>
       </c>
@@ -5997,7 +6833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>19.968198999999998</v>
       </c>
@@ -6011,7 +6847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>19.779437999999999</v>
       </c>
@@ -6025,7 +6861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>21.047138</v>
       </c>
@@ -6039,7 +6875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>58.323177000000001</v>
       </c>
@@ -6053,7 +6889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>58.003895</v>
       </c>
@@ -6067,7 +6903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>19.329172</v>
       </c>
@@ -6081,7 +6917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>39.468890000000002</v>
       </c>
@@ -6095,7 +6931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>152.07509999999999</v>
       </c>
@@ -6109,7 +6945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>118.39973000000001</v>
       </c>
@@ -6123,7 +6959,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>111.5752</v>
       </c>
@@ -6137,7 +6973,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>97.059950000000001</v>
       </c>
@@ -6151,7 +6987,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>87.746216000000004</v>
       </c>
@@ -6165,7 +7001,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>85.192279999999997</v>
       </c>
@@ -6179,7 +7015,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>74.557143999999994</v>
       </c>
@@ -6193,7 +7029,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>71.971649999999997</v>
       </c>
@@ -6207,7 +7043,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>70.703050000000005</v>
       </c>
@@ -6221,7 +7057,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>69.262889999999999</v>
       </c>
@@ -6235,7 +7071,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>67.65325</v>
       </c>
@@ -6249,7 +7085,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>63.196390000000001</v>
       </c>
@@ -6263,7 +7099,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>62.626792999999999</v>
       </c>
@@ -6277,7 +7113,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>61.477027999999997</v>
       </c>
@@ -6291,7 +7127,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>56.278553000000002</v>
       </c>
@@ -6305,7 +7141,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>55.360030000000002</v>
       </c>
@@ -6319,7 +7155,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>53.411503000000003</v>
       </c>
@@ -6333,7 +7169,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>52.090297999999997</v>
       </c>
@@ -6347,7 +7183,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>51.580246000000002</v>
       </c>
@@ -6361,7 +7197,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>51.516502000000003</v>
       </c>
@@ -6375,7 +7211,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>51.150641999999998</v>
       </c>
@@ -6389,7 +7225,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>50.474865000000001</v>
       </c>
@@ -6403,7 +7239,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>48.576701999999997</v>
       </c>
@@ -6417,7 +7253,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>47.463805999999998</v>
       </c>
@@ -6431,7 +7267,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>41.244624999999999</v>
       </c>
@@ -6445,7 +7281,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>40.919918000000003</v>
       </c>
@@ -6459,7 +7295,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>39.276333000000001</v>
       </c>
@@ -6473,7 +7309,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>38.869210000000002</v>
       </c>
@@ -6487,7 +7323,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>38.456584999999997</v>
       </c>
@@ -6501,7 +7337,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>38.31653</v>
       </c>
@@ -6515,7 +7351,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>37.809193</v>
       </c>
@@ -6529,7 +7365,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>37.368789999999997</v>
       </c>
@@ -6543,7 +7379,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>36.500210000000003</v>
       </c>
@@ -6557,7 +7393,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>33.947189999999999</v>
       </c>
@@ -6571,7 +7407,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>32.955219999999997</v>
       </c>
@@ -6585,7 +7421,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>32.621380000000002</v>
       </c>
@@ -6599,7 +7435,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>31.222657999999999</v>
       </c>
@@ -6613,7 +7449,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>30.581795</v>
       </c>
@@ -6627,7 +7463,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>27.575645000000002</v>
       </c>
@@ -6641,7 +7477,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>27.146778000000001</v>
       </c>
@@ -6655,7 +7491,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>25.50722</v>
       </c>
@@ -6669,7 +7505,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>25.139116000000001</v>
       </c>
@@ -6683,7 +7519,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>24.512025999999999</v>
       </c>
@@ -6697,7 +7533,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>23.560552999999999</v>
       </c>
@@ -6711,7 +7547,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>18.591137</v>
       </c>
@@ -6725,7 +7561,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>16.928915</v>
       </c>
@@ -6739,7 +7575,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>389.6309</v>
       </c>
@@ -6753,7 +7589,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>263.75742000000002</v>
       </c>
@@ -6767,7 +7603,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>250.22147000000001</v>
       </c>
@@ -6781,7 +7617,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>208.05008000000001</v>
       </c>
@@ -6795,7 +7631,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>202.12851000000001</v>
       </c>
@@ -6809,7 +7645,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>188.8357</v>
       </c>
@@ -6823,7 +7659,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>179.94785999999999</v>
       </c>
@@ -6837,7 +7673,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>177.69807</v>
       </c>
@@ -6851,7 +7687,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>175.58258000000001</v>
       </c>
@@ -6865,7 +7701,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>172.70023</v>
       </c>
@@ -6879,7 +7715,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>158.82599999999999</v>
       </c>
@@ -6893,7 +7729,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>150.34482</v>
       </c>
@@ -6907,7 +7743,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>148.48703</v>
       </c>
@@ -6921,7 +7757,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>146.05897999999999</v>
       </c>
@@ -6935,7 +7771,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>141.99160000000001</v>
       </c>
@@ -6949,7 +7785,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>136.62003999999999</v>
       </c>
@@ -6963,7 +7799,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>133.26865000000001</v>
       </c>
@@ -6977,7 +7813,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>132.25406000000001</v>
       </c>
@@ -6991,7 +7827,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>132.15321</v>
       </c>
@@ -7005,7 +7841,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>129.33850000000001</v>
       </c>
@@ -7019,7 +7855,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>122.095665</v>
       </c>
@@ -7033,7 +7869,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>121.34650000000001</v>
       </c>
@@ -7047,7 +7883,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>117.116806</v>
       </c>
@@ -7061,7 +7897,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>115.701035</v>
       </c>
@@ -7075,7 +7911,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>115.17889</v>
       </c>
@@ -7089,7 +7925,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>113.10147000000001</v>
       </c>
@@ -7103,7 +7939,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>112.26778</v>
       </c>
@@ -7117,7 +7953,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>107.50543999999999</v>
       </c>
@@ -7131,7 +7967,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>103.01748000000001</v>
       </c>
@@ -7145,7 +7981,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>99.991810000000001</v>
       </c>
@@ -7159,7 +7995,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>98.398629999999997</v>
       </c>
@@ -7173,7 +8009,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>97.924289999999999</v>
       </c>
@@ -7187,7 +8023,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>97.353639999999999</v>
       </c>
@@ -7201,7 +8037,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>93.988119999999995</v>
       </c>
@@ -7215,7 +8051,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>93.000389999999996</v>
       </c>
@@ -7229,7 +8065,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>89.416610000000006</v>
       </c>
@@ -7243,7 +8079,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>88.826620000000005</v>
       </c>
@@ -7257,7 +8093,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>78.390334999999993</v>
       </c>
@@ -7271,7 +8107,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>78.055279999999996</v>
       </c>
@@ -7285,7 +8121,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>70.522193999999999</v>
       </c>
@@ -7299,7 +8135,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>62.836326999999997</v>
       </c>
@@ -7313,7 +8149,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>60.422127000000003</v>
       </c>
@@ -7327,7 +8163,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>57.241714000000002</v>
       </c>
@@ -7341,7 +8177,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>53.707301999999999</v>
       </c>
@@ -7355,7 +8191,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>41.221446999999998</v>
       </c>
@@ -7369,7 +8205,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>444.86754999999999</v>
       </c>
@@ -7383,7 +8219,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>413.02704</v>
       </c>
@@ -7397,7 +8233,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>408.29422</v>
       </c>
@@ -7411,7 +8247,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>388.89330000000001</v>
       </c>
@@ -7425,7 +8261,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>381.62470000000002</v>
       </c>
@@ -7439,7 +8275,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>373.9348</v>
       </c>
@@ -7453,7 +8289,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>372.83386000000002</v>
       </c>
@@ -7467,7 +8303,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>358.40660000000003</v>
       </c>
@@ -7481,7 +8317,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>353.61757999999998</v>
       </c>
@@ -7495,7 +8331,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>339.32616999999999</v>
       </c>
@@ -7509,7 +8345,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>338.84848</v>
       </c>
@@ -7523,7 +8359,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>338.18389999999999</v>
       </c>
@@ -7537,7 +8373,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>333.53503000000001</v>
       </c>
@@ -7551,7 +8387,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>332.00189999999998</v>
       </c>
@@ -7565,7 +8401,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>331.87909999999999</v>
       </c>
@@ -7579,7 +8415,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>327.70245</v>
       </c>
@@ -7593,7 +8429,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>327.61743000000001</v>
       </c>
@@ -7607,7 +8443,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>324.43182000000002</v>
       </c>
@@ -7621,7 +8457,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>321.59924000000001</v>
       </c>
@@ -7635,7 +8471,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <v>318.41674999999998</v>
       </c>
@@ -7649,7 +8485,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
         <v>317.60242</v>
       </c>
@@ -7663,7 +8499,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <v>313.53982999999999</v>
       </c>
@@ -7677,7 +8513,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <v>311.5797</v>
       </c>
@@ -7691,7 +8527,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>307.38483000000002</v>
       </c>
@@ -7705,7 +8541,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <v>305.39681999999999</v>
       </c>
@@ -7719,7 +8555,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <v>304.20812999999998</v>
       </c>
@@ -7733,7 +8569,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <v>303.88254000000001</v>
       </c>
@@ -7747,7 +8583,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <v>303.76285000000001</v>
       </c>
@@ -7761,7 +8597,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <v>300.4941</v>
       </c>
@@ -7775,7 +8611,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
         <v>300.411</v>
       </c>
@@ -7789,7 +8625,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <v>299.52636999999999</v>
       </c>
@@ -7803,7 +8639,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
         <v>297.57100000000003</v>
       </c>
@@ -7817,7 +8653,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
         <v>295.76587000000001</v>
       </c>
@@ -7831,7 +8667,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <v>292.71260000000001</v>
       </c>
@@ -7845,7 +8681,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
         <v>292.54784999999998</v>
       </c>
@@ -7859,7 +8695,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
         <v>287.29126000000002</v>
       </c>
@@ -7873,7 +8709,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
         <v>284.22160000000002</v>
       </c>
@@ -7887,7 +8723,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
         <v>281.4708</v>
       </c>
@@ -7901,7 +8737,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
         <v>275.98311999999999</v>
       </c>
@@ -7915,7 +8751,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
         <v>269.20785999999998</v>
       </c>
@@ -7929,7 +8765,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
         <v>266.87752999999998</v>
       </c>
@@ -7943,7 +8779,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
         <v>259.18970000000002</v>
       </c>
@@ -7957,7 +8793,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
         <v>254.78112999999999</v>
       </c>
@@ -7971,7 +8807,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
         <v>234.31897000000001</v>
       </c>
@@ -7985,7 +8821,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
         <v>201.85758999999999</v>
       </c>
@@ -7999,7 +8835,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
         <v>412.42966000000001</v>
       </c>
@@ -8013,7 +8849,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
         <v>388.90449999999998</v>
       </c>
@@ -8027,7 +8863,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
         <v>378.89055999999999</v>
       </c>
@@ -8041,7 +8877,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
         <v>375.75745000000001</v>
       </c>
@@ -8055,7 +8891,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
         <v>359.53635000000003</v>
       </c>
@@ -8069,7 +8905,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
         <v>359.04486000000003</v>
       </c>
@@ -8083,7 +8919,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
         <v>351.57596000000001</v>
       </c>
@@ -8097,7 +8933,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
         <v>350.67970000000003</v>
       </c>
@@ -8111,7 +8947,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
         <v>348.84714000000002</v>
       </c>
@@ -8125,7 +8961,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
         <v>346.64746000000002</v>
       </c>
@@ -8139,7 +8975,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
         <v>340.96289999999999</v>
       </c>
@@ -8153,7 +8989,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
         <v>335.71597000000003</v>
       </c>
@@ -8167,7 +9003,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
         <v>334.69310000000002</v>
       </c>
@@ -8181,7 +9017,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
         <v>332.9051</v>
       </c>
@@ -8195,7 +9031,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
         <v>331.78951999999998</v>
       </c>
@@ -8209,7 +9045,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
         <v>330.98039999999997</v>
       </c>
@@ -8223,7 +9059,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
         <v>330.97899999999998</v>
       </c>
@@ -8237,7 +9073,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
         <v>328.94098000000002</v>
       </c>
@@ -8251,7 +9087,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
         <v>328.32137999999998</v>
       </c>
@@ -8265,7 +9101,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
         <v>327.98214999999999</v>
       </c>
@@ -8279,7 +9115,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
         <v>325.80446999999998</v>
       </c>
@@ -8293,7 +9129,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
         <v>324.33422999999999</v>
       </c>
@@ -8307,7 +9143,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
         <v>320.15359999999998</v>
       </c>
@@ -8321,7 +9157,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
         <v>319.02042</v>
       </c>
@@ -8335,7 +9171,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
         <v>317.09717000000001</v>
       </c>
@@ -8349,7 +9185,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
         <v>316.98219999999998</v>
       </c>
@@ -8363,7 +9199,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
         <v>309.26373000000001</v>
       </c>
@@ -8377,7 +9213,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
         <v>309.02614999999997</v>
       </c>
@@ -8391,7 +9227,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
         <v>308.78082000000001</v>
       </c>
@@ -8405,7 +9241,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" s="1">
         <v>306.12240000000003</v>
       </c>
@@ -8419,7 +9255,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" s="1">
         <v>300.94702000000001</v>
       </c>
@@ -8433,7 +9269,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
         <v>300.58987000000002</v>
       </c>
@@ -8447,7 +9283,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
         <v>299.25803000000002</v>
       </c>
@@ -8461,7 +9297,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
         <v>296.29930000000002</v>
       </c>
@@ -8475,7 +9311,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
         <v>294.9042</v>
       </c>
@@ -8489,7 +9325,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" s="1">
         <v>291.77699999999999</v>
       </c>
@@ -8503,7 +9339,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" s="1">
         <v>290.84426999999999</v>
       </c>
@@ -8517,7 +9353,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
         <v>289.06869999999998</v>
       </c>
@@ -8531,7 +9367,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
         <v>278.96872000000002</v>
       </c>
@@ -8545,7 +9381,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
         <v>276.43849999999998</v>
       </c>
@@ -8559,7 +9395,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
         <v>270.19193000000001</v>
       </c>
@@ -8573,7 +9409,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
         <v>270.07479999999998</v>
       </c>
@@ -8587,7 +9423,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
         <v>267.18813999999998</v>
       </c>
@@ -8601,7 +9437,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
         <v>245.10222999999999</v>
       </c>
@@ -8615,7 +9451,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
         <v>243.41831999999999</v>
       </c>
@@ -8629,7 +9465,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
         <v>384.13630000000001</v>
       </c>
@@ -8643,7 +9479,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
         <v>375.09998000000002</v>
       </c>
@@ -8657,7 +9493,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
         <v>360.91469999999998</v>
       </c>
@@ -8671,7 +9507,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
         <v>353.62795999999997</v>
       </c>
@@ -8685,7 +9521,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
         <v>344.53307999999998</v>
       </c>
@@ -8699,7 +9535,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
         <v>340.25873000000001</v>
       </c>
@@ -8713,7 +9549,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
         <v>337.63740000000001</v>
       </c>
@@ -8727,7 +9563,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
         <v>336.08102000000002</v>
       </c>
@@ -8741,7 +9577,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
         <v>331.00583</v>
       </c>
@@ -8755,7 +9591,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
         <v>327.15552000000002</v>
       </c>
@@ -8769,7 +9605,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
         <v>325.19765999999998</v>
       </c>
@@ -8783,7 +9619,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
         <v>324.9468</v>
       </c>
@@ -8797,7 +9633,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" s="1">
         <v>324.49083999999999</v>
       </c>
@@ -8811,7 +9647,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" s="1">
         <v>320.53757000000002</v>
       </c>
@@ -8825,7 +9661,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" s="1">
         <v>315.44607999999999</v>
       </c>
@@ -8839,7 +9675,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" s="1">
         <v>308.05110000000002</v>
       </c>
@@ -8853,7 +9689,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" s="1">
         <v>303.59915000000001</v>
       </c>
@@ -8867,7 +9703,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" s="1">
         <v>300.92397999999997</v>
       </c>
@@ -8881,7 +9717,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
         <v>300.08463</v>
       </c>
@@ -8895,7 +9731,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
         <v>299.97539999999998</v>
       </c>
@@ -8909,7 +9745,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
         <v>298.02843999999999</v>
       </c>
@@ -8923,7 +9759,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" s="1">
         <v>295.58553999999998</v>
       </c>
@@ -8937,7 +9773,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" s="1">
         <v>293.31842</v>
       </c>
@@ -8951,7 +9787,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" s="1">
         <v>292.86966000000001</v>
       </c>
@@ -8965,7 +9801,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" s="1">
         <v>292.09206999999998</v>
       </c>
@@ -8979,7 +9815,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
         <v>290.27050000000003</v>
       </c>
@@ -8993,7 +9829,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
         <v>289.45675999999997</v>
       </c>
@@ -9007,7 +9843,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
         <v>287.83704</v>
       </c>
@@ -9021,7 +9857,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" s="1">
         <v>282.88977</v>
       </c>
@@ -9035,7 +9871,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
         <v>282.83114999999998</v>
       </c>
@@ -9049,7 +9885,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
         <v>279.86743000000001</v>
       </c>
@@ -9063,7 +9899,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
         <v>276.93830000000003</v>
       </c>
@@ -9077,7 +9913,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
         <v>276.37966999999998</v>
       </c>
@@ -9091,7 +9927,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
         <v>276.28750000000002</v>
       </c>
@@ -9105,7 +9941,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
         <v>271.15012000000002</v>
       </c>
@@ -9119,7 +9955,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
         <v>264.19961999999998</v>
       </c>
@@ -9133,7 +9969,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
         <v>263.38528000000002</v>
       </c>
@@ -9147,7 +9983,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
         <v>262.84636999999998</v>
       </c>
@@ -9161,7 +9997,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" s="1">
         <v>255.26889</v>
       </c>
@@ -9175,7 +10011,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" s="1">
         <v>254.50862000000001</v>
       </c>
@@ -9189,7 +10025,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" s="1">
         <v>245.72756999999999</v>
       </c>
@@ -9203,7 +10039,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" s="1">
         <v>236.36233999999999</v>
       </c>
@@ -9217,7 +10053,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" s="1">
         <v>231.09157999999999</v>
       </c>
@@ -9231,7 +10067,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" s="1">
         <v>218.43191999999999</v>
       </c>
@@ -9245,7 +10081,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" s="1">
         <v>192.78855999999999</v>
       </c>
@@ -9257,6 +10093,1266 @@
       </c>
       <c r="D316" s="1" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A317" s="1">
+        <v>433.01137999999997</v>
+      </c>
+      <c r="B317" s="1">
+        <v>2010</v>
+      </c>
+      <c r="C317" s="1">
+        <v>106.41168</v>
+      </c>
+      <c r="D317" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A318" s="1">
+        <v>416.49036000000001</v>
+      </c>
+      <c r="B318" s="1">
+        <v>1988</v>
+      </c>
+      <c r="C318" s="1">
+        <v>89.890656000000007</v>
+      </c>
+      <c r="D318" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A319" s="1">
+        <v>403.6705</v>
+      </c>
+      <c r="B319" s="1">
+        <v>1999</v>
+      </c>
+      <c r="C319" s="1">
+        <v>77.070800000000006</v>
+      </c>
+      <c r="D319" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A320" s="1">
+        <v>394.81130000000002</v>
+      </c>
+      <c r="B320" s="1">
+        <v>1984</v>
+      </c>
+      <c r="C320" s="1">
+        <v>68.211609999999993</v>
+      </c>
+      <c r="D320" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A321" s="1">
+        <v>383.18975999999998</v>
+      </c>
+      <c r="B321" s="1">
+        <v>2005</v>
+      </c>
+      <c r="C321" s="1">
+        <v>56.590057000000002</v>
+      </c>
+      <c r="D321" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A322" s="1">
+        <v>380.15839999999997</v>
+      </c>
+      <c r="B322" s="1">
+        <v>2007</v>
+      </c>
+      <c r="C322" s="1">
+        <v>53.558684999999997</v>
+      </c>
+      <c r="D322" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A323" s="1">
+        <v>366.12844999999999</v>
+      </c>
+      <c r="B323" s="1">
+        <v>1981</v>
+      </c>
+      <c r="C323" s="1">
+        <v>39.528748</v>
+      </c>
+      <c r="D323" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A324" s="1">
+        <v>364.13904000000002</v>
+      </c>
+      <c r="B324" s="1">
+        <v>1990</v>
+      </c>
+      <c r="C324" s="1">
+        <v>37.539337000000003</v>
+      </c>
+      <c r="D324" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A325" s="1">
+        <v>362.57569999999998</v>
+      </c>
+      <c r="B325" s="1">
+        <v>1998</v>
+      </c>
+      <c r="C325" s="1">
+        <v>35.976013000000002</v>
+      </c>
+      <c r="D325" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A326" s="1">
+        <v>357.01028000000002</v>
+      </c>
+      <c r="B326" s="1">
+        <v>1989</v>
+      </c>
+      <c r="C326" s="1">
+        <v>30.410582999999999</v>
+      </c>
+      <c r="D326" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A327" s="1">
+        <v>356.98083000000003</v>
+      </c>
+      <c r="B327" s="1">
+        <v>2002</v>
+      </c>
+      <c r="C327" s="1">
+        <v>30.381133999999999</v>
+      </c>
+      <c r="D327" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A328" s="1">
+        <v>353.67563000000001</v>
+      </c>
+      <c r="B328" s="1">
+        <v>2020</v>
+      </c>
+      <c r="C328" s="1">
+        <v>27.075928000000001</v>
+      </c>
+      <c r="D328" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A329" s="1">
+        <v>350.06436000000002</v>
+      </c>
+      <c r="B329" s="1">
+        <v>2021</v>
+      </c>
+      <c r="C329" s="1">
+        <v>23.464659999999999</v>
+      </c>
+      <c r="D329" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A330" s="1">
+        <v>342.5412</v>
+      </c>
+      <c r="B330" s="1">
+        <v>2008</v>
+      </c>
+      <c r="C330" s="1">
+        <v>15.941497999999999</v>
+      </c>
+      <c r="D330" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A331" s="1">
+        <v>340.01609999999999</v>
+      </c>
+      <c r="B331" s="1">
+        <v>2003</v>
+      </c>
+      <c r="C331" s="1">
+        <v>13.416411999999999</v>
+      </c>
+      <c r="D331" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A332" s="1">
+        <v>337.74810000000002</v>
+      </c>
+      <c r="B332" s="1">
+        <v>1987</v>
+      </c>
+      <c r="C332" s="1">
+        <v>11.148407000000001</v>
+      </c>
+      <c r="D332" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A333" s="1">
+        <v>336.07641999999998</v>
+      </c>
+      <c r="B333" s="1">
+        <v>2024</v>
+      </c>
+      <c r="C333" s="1">
+        <v>9.4767150000000004</v>
+      </c>
+      <c r="D333" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A334" s="1">
+        <v>335.87862999999999</v>
+      </c>
+      <c r="B334" s="1">
+        <v>1994</v>
+      </c>
+      <c r="C334" s="1">
+        <v>9.278931</v>
+      </c>
+      <c r="D334" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A335" s="1">
+        <v>332.50567999999998</v>
+      </c>
+      <c r="B335" s="1">
+        <v>2009</v>
+      </c>
+      <c r="C335" s="1">
+        <v>5.9059752999999997</v>
+      </c>
+      <c r="D335" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A336" s="1">
+        <v>332.46690000000001</v>
+      </c>
+      <c r="B336" s="1">
+        <v>2022</v>
+      </c>
+      <c r="C336" s="1">
+        <v>5.8671875</v>
+      </c>
+      <c r="D336" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A337" s="1">
+        <v>332.34440000000001</v>
+      </c>
+      <c r="B337" s="1">
+        <v>1996</v>
+      </c>
+      <c r="C337" s="1">
+        <v>5.7446900000000003</v>
+      </c>
+      <c r="D337" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A338" s="1">
+        <v>329.17962999999997</v>
+      </c>
+      <c r="B338" s="1">
+        <v>2013</v>
+      </c>
+      <c r="C338" s="1">
+        <v>2.5799254999999999</v>
+      </c>
+      <c r="D338" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A339" s="1">
+        <v>329.14276000000001</v>
+      </c>
+      <c r="B339" s="1">
+        <v>1992</v>
+      </c>
+      <c r="C339" s="1">
+        <v>2.5430603000000001</v>
+      </c>
+      <c r="D339" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A340" s="1">
+        <v>327.99880000000002</v>
+      </c>
+      <c r="B340" s="1">
+        <v>2006</v>
+      </c>
+      <c r="C340" s="1">
+        <v>1.3991089000000001</v>
+      </c>
+      <c r="D340" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A341" s="1">
+        <v>326.71697999999998</v>
+      </c>
+      <c r="B341" s="1">
+        <v>2016</v>
+      </c>
+      <c r="C341" s="1">
+        <v>0.11727905</v>
+      </c>
+      <c r="D341" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A342" s="1">
+        <v>325.44272000000001</v>
+      </c>
+      <c r="B342" s="1">
+        <v>1985</v>
+      </c>
+      <c r="C342" s="1">
+        <v>-1.1569824</v>
+      </c>
+      <c r="D342" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A343" s="1">
+        <v>325.13085999999998</v>
+      </c>
+      <c r="B343" s="1">
+        <v>1993</v>
+      </c>
+      <c r="C343" s="1">
+        <v>-1.4688416</v>
+      </c>
+      <c r="D343" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A344" s="1">
+        <v>324.6728</v>
+      </c>
+      <c r="B344" s="1">
+        <v>1995</v>
+      </c>
+      <c r="C344" s="1">
+        <v>-1.9269103999999999</v>
+      </c>
+      <c r="D344" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A345" s="1">
+        <v>321.19556</v>
+      </c>
+      <c r="B345" s="1">
+        <v>1986</v>
+      </c>
+      <c r="C345" s="1">
+        <v>-5.4041442999999996</v>
+      </c>
+      <c r="D345" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A346" s="1">
+        <v>319.91144000000003</v>
+      </c>
+      <c r="B346" s="1">
+        <v>2000</v>
+      </c>
+      <c r="C346" s="1">
+        <v>-6.6882630000000001</v>
+      </c>
+      <c r="D346" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A347" s="1">
+        <v>318.54788000000002</v>
+      </c>
+      <c r="B347" s="1">
+        <v>2001</v>
+      </c>
+      <c r="C347" s="1">
+        <v>-8.0518190000000001</v>
+      </c>
+      <c r="D347" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A348" s="1">
+        <v>315.4545</v>
+      </c>
+      <c r="B348" s="1">
+        <v>2004</v>
+      </c>
+      <c r="C348" s="1">
+        <v>-11.145203</v>
+      </c>
+      <c r="D348" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A349" s="1">
+        <v>313.14992999999998</v>
+      </c>
+      <c r="B349" s="1">
+        <v>2011</v>
+      </c>
+      <c r="C349" s="1">
+        <v>-13.449768000000001</v>
+      </c>
+      <c r="D349" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A350" s="1">
+        <v>311.61016999999998</v>
+      </c>
+      <c r="B350" s="1">
+        <v>2017</v>
+      </c>
+      <c r="C350" s="1">
+        <v>-14.989532000000001</v>
+      </c>
+      <c r="D350" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A351" s="1">
+        <v>310.53924999999998</v>
+      </c>
+      <c r="B351" s="1">
+        <v>1991</v>
+      </c>
+      <c r="C351" s="1">
+        <v>-16.060455000000001</v>
+      </c>
+      <c r="D351" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A352" s="1">
+        <v>306.65964000000002</v>
+      </c>
+      <c r="B352" s="1">
+        <v>2012</v>
+      </c>
+      <c r="C352" s="1">
+        <v>-19.940062999999999</v>
+      </c>
+      <c r="D352" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A353" s="1">
+        <v>295.49286000000001</v>
+      </c>
+      <c r="B353" s="1">
+        <v>2025</v>
+      </c>
+      <c r="C353" s="1">
+        <v>-31.106842</v>
+      </c>
+      <c r="D353" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A354" s="1">
+        <v>290.94515999999999</v>
+      </c>
+      <c r="B354" s="1">
+        <v>2019</v>
+      </c>
+      <c r="C354" s="1">
+        <v>-35.654539999999997</v>
+      </c>
+      <c r="D354" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A355" s="1">
+        <v>286.34985</v>
+      </c>
+      <c r="B355" s="1">
+        <v>2014</v>
+      </c>
+      <c r="C355" s="1">
+        <v>-40.249847000000003</v>
+      </c>
+      <c r="D355" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A356" s="1">
+        <v>264.25006000000002</v>
+      </c>
+      <c r="B356" s="1">
+        <v>1983</v>
+      </c>
+      <c r="C356" s="1">
+        <v>-62.349640000000001</v>
+      </c>
+      <c r="D356" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A357" s="1">
+        <v>256.55040000000002</v>
+      </c>
+      <c r="B357" s="1">
+        <v>2023</v>
+      </c>
+      <c r="C357" s="1">
+        <v>-70.049285999999995</v>
+      </c>
+      <c r="D357" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A358" s="1">
+        <v>241.63086000000001</v>
+      </c>
+      <c r="B358" s="1">
+        <v>2018</v>
+      </c>
+      <c r="C358" s="1">
+        <v>-84.96884</v>
+      </c>
+      <c r="D358" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A359" s="1">
+        <v>241.50899000000001</v>
+      </c>
+      <c r="B359" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C359" s="1">
+        <v>-85.090710000000001</v>
+      </c>
+      <c r="D359" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A360" s="1">
+        <v>240.60686000000001</v>
+      </c>
+      <c r="B360" s="1">
+        <v>1982</v>
+      </c>
+      <c r="C360" s="1">
+        <v>-85.992840000000001</v>
+      </c>
+      <c r="D360" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A361" s="1">
+        <v>222.29355000000001</v>
+      </c>
+      <c r="B361" s="1">
+        <v>1997</v>
+      </c>
+      <c r="C361" s="1">
+        <v>-104.30615</v>
+      </c>
+      <c r="D361" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A362" s="1">
+        <v>291.67657000000003</v>
+      </c>
+      <c r="B362" s="1">
+        <v>1981</v>
+      </c>
+      <c r="C362" s="1">
+        <v>-60.690125000000002</v>
+      </c>
+      <c r="D362" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A363" s="1">
+        <v>332.40949999999998</v>
+      </c>
+      <c r="B363" s="1">
+        <v>1982</v>
+      </c>
+      <c r="C363" s="1">
+        <v>-19.957214</v>
+      </c>
+      <c r="D363" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A364" s="1">
+        <v>384.92752000000002</v>
+      </c>
+      <c r="B364" s="1">
+        <v>1983</v>
+      </c>
+      <c r="C364" s="1">
+        <v>32.56082</v>
+      </c>
+      <c r="D364" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A365" s="1">
+        <v>381.66262999999998</v>
+      </c>
+      <c r="B365" s="1">
+        <v>1984</v>
+      </c>
+      <c r="C365" s="1">
+        <v>29.295929000000001</v>
+      </c>
+      <c r="D365" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A366" s="1">
+        <v>336.99135999999999</v>
+      </c>
+      <c r="B366" s="1">
+        <v>1985</v>
+      </c>
+      <c r="C366" s="1">
+        <v>-15.375336000000001</v>
+      </c>
+      <c r="D366" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A367" s="1">
+        <v>347.18155000000002</v>
+      </c>
+      <c r="B367" s="1">
+        <v>1986</v>
+      </c>
+      <c r="C367" s="1">
+        <v>-5.1851500000000001</v>
+      </c>
+      <c r="D367" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A368" s="1">
+        <v>331.07742000000002</v>
+      </c>
+      <c r="B368" s="1">
+        <v>1987</v>
+      </c>
+      <c r="C368" s="1">
+        <v>-21.289276000000001</v>
+      </c>
+      <c r="D368" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A369" s="1">
+        <v>393.68340000000001</v>
+      </c>
+      <c r="B369" s="1">
+        <v>1988</v>
+      </c>
+      <c r="C369" s="1">
+        <v>41.31671</v>
+      </c>
+      <c r="D369" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A370" s="1">
+        <v>375.17043999999999</v>
+      </c>
+      <c r="B370" s="1">
+        <v>1989</v>
+      </c>
+      <c r="C370" s="1">
+        <v>22.803740999999999</v>
+      </c>
+      <c r="D370" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A371" s="1">
+        <v>355.55630000000002</v>
+      </c>
+      <c r="B371" s="1">
+        <v>1990</v>
+      </c>
+      <c r="C371" s="1">
+        <v>3.1896057</v>
+      </c>
+      <c r="D371" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A372" s="1">
+        <v>409.84793000000002</v>
+      </c>
+      <c r="B372" s="1">
+        <v>1991</v>
+      </c>
+      <c r="C372" s="1">
+        <v>57.481229999999996</v>
+      </c>
+      <c r="D372" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A373" s="1">
+        <v>360.9649</v>
+      </c>
+      <c r="B373" s="1">
+        <v>1992</v>
+      </c>
+      <c r="C373" s="1">
+        <v>8.5982059999999993</v>
+      </c>
+      <c r="D373" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A374" s="1">
+        <v>426.98923000000002</v>
+      </c>
+      <c r="B374" s="1">
+        <v>1993</v>
+      </c>
+      <c r="C374" s="1">
+        <v>74.622529999999998</v>
+      </c>
+      <c r="D374" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A375" s="1">
+        <v>350.16793999999999</v>
+      </c>
+      <c r="B375" s="1">
+        <v>1994</v>
+      </c>
+      <c r="C375" s="1">
+        <v>-2.1987610000000002</v>
+      </c>
+      <c r="D375" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A376" s="1">
+        <v>356.41604999999998</v>
+      </c>
+      <c r="B376" s="1">
+        <v>1995</v>
+      </c>
+      <c r="C376" s="1">
+        <v>4.049347</v>
+      </c>
+      <c r="D376" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A377" s="1">
+        <v>388.09305000000001</v>
+      </c>
+      <c r="B377" s="1">
+        <v>1996</v>
+      </c>
+      <c r="C377" s="1">
+        <v>35.726349999999996</v>
+      </c>
+      <c r="D377" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A378" s="1">
+        <v>352.10626000000002</v>
+      </c>
+      <c r="B378" s="1">
+        <v>1997</v>
+      </c>
+      <c r="C378" s="1">
+        <v>-0.26043699999999997</v>
+      </c>
+      <c r="D378" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A379" s="1">
+        <v>323.54962</v>
+      </c>
+      <c r="B379" s="1">
+        <v>1998</v>
+      </c>
+      <c r="C379" s="1">
+        <v>-28.817077999999999</v>
+      </c>
+      <c r="D379" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A380" s="1">
+        <v>437.72748000000001</v>
+      </c>
+      <c r="B380" s="1">
+        <v>1999</v>
+      </c>
+      <c r="C380" s="1">
+        <v>85.360780000000005</v>
+      </c>
+      <c r="D380" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A381" s="1">
+        <v>392.50963999999999</v>
+      </c>
+      <c r="B381" s="1">
+        <v>2000</v>
+      </c>
+      <c r="C381" s="1">
+        <v>40.142944</v>
+      </c>
+      <c r="D381" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A382" s="1">
+        <v>366.81040000000002</v>
+      </c>
+      <c r="B382" s="1">
+        <v>2001</v>
+      </c>
+      <c r="C382" s="1">
+        <v>14.443695</v>
+      </c>
+      <c r="D382" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A383" s="1">
+        <v>344.49774000000002</v>
+      </c>
+      <c r="B383" s="1">
+        <v>2002</v>
+      </c>
+      <c r="C383" s="1">
+        <v>-7.8689574999999996</v>
+      </c>
+      <c r="D383" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A384" s="1">
+        <v>342.80988000000002</v>
+      </c>
+      <c r="B384" s="1">
+        <v>2003</v>
+      </c>
+      <c r="C384" s="1">
+        <v>-9.5568240000000007</v>
+      </c>
+      <c r="D384" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A385" s="1">
+        <v>340.63772999999998</v>
+      </c>
+      <c r="B385" s="1">
+        <v>2004</v>
+      </c>
+      <c r="C385" s="1">
+        <v>-11.728973</v>
+      </c>
+      <c r="D385" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A386" s="1">
+        <v>388.71269999999998</v>
+      </c>
+      <c r="B386" s="1">
+        <v>2005</v>
+      </c>
+      <c r="C386" s="1">
+        <v>36.34601</v>
+      </c>
+      <c r="D386" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A387" s="1">
+        <v>298.40906000000001</v>
+      </c>
+      <c r="B387" s="1">
+        <v>2006</v>
+      </c>
+      <c r="C387" s="1">
+        <v>-53.957639999999998</v>
+      </c>
+      <c r="D387" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A388" s="1">
+        <v>380.37927000000002</v>
+      </c>
+      <c r="B388" s="1">
+        <v>2007</v>
+      </c>
+      <c r="C388" s="1">
+        <v>28.012573</v>
+      </c>
+      <c r="D388" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A389" s="1">
+        <v>340.36023</v>
+      </c>
+      <c r="B389" s="1">
+        <v>2008</v>
+      </c>
+      <c r="C389" s="1">
+        <v>-12.00647</v>
+      </c>
+      <c r="D389" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A390" s="1">
+        <v>292.10654</v>
+      </c>
+      <c r="B390" s="1">
+        <v>2009</v>
+      </c>
+      <c r="C390" s="1">
+        <v>-60.260162000000001</v>
+      </c>
+      <c r="D390" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A391" s="1">
+        <v>369.03043000000002</v>
+      </c>
+      <c r="B391" s="1">
+        <v>2010</v>
+      </c>
+      <c r="C391" s="1">
+        <v>16.663727000000002</v>
+      </c>
+      <c r="D391" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A392" s="1">
+        <v>334.85915999999997</v>
+      </c>
+      <c r="B392" s="1">
+        <v>2011</v>
+      </c>
+      <c r="C392" s="1">
+        <v>-17.507538</v>
+      </c>
+      <c r="D392" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A393" s="1">
+        <v>296.12786999999997</v>
+      </c>
+      <c r="B393" s="1">
+        <v>2012</v>
+      </c>
+      <c r="C393" s="1">
+        <v>-56.23883</v>
+      </c>
+      <c r="D393" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A394" s="1">
+        <v>352.0684</v>
+      </c>
+      <c r="B394" s="1">
+        <v>2013</v>
+      </c>
+      <c r="C394" s="1">
+        <v>-0.29830932999999998</v>
+      </c>
+      <c r="D394" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A395" s="1">
+        <v>373.51830000000001</v>
+      </c>
+      <c r="B395" s="1">
+        <v>2014</v>
+      </c>
+      <c r="C395" s="1">
+        <v>21.151610999999999</v>
+      </c>
+      <c r="D395" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A396" s="1">
+        <v>304.16595000000001</v>
+      </c>
+      <c r="B396" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C396" s="1">
+        <v>-48.200744999999998</v>
+      </c>
+      <c r="D396" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A397" s="1">
+        <v>298.6694</v>
+      </c>
+      <c r="B397" s="1">
+        <v>2016</v>
+      </c>
+      <c r="C397" s="1">
+        <v>-53.697296000000001</v>
+      </c>
+      <c r="D397" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A398" s="1">
+        <v>338.21289999999999</v>
+      </c>
+      <c r="B398" s="1">
+        <v>2017</v>
+      </c>
+      <c r="C398" s="1">
+        <v>-14.153809000000001</v>
+      </c>
+      <c r="D398" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A399" s="1">
+        <v>342.56313999999998</v>
+      </c>
+      <c r="B399" s="1">
+        <v>2018</v>
+      </c>
+      <c r="C399" s="1">
+        <v>-9.8035580000000007</v>
+      </c>
+      <c r="D399" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A400" s="1">
+        <v>341.74560000000002</v>
+      </c>
+      <c r="B400" s="1">
+        <v>2019</v>
+      </c>
+      <c r="C400" s="1">
+        <v>-10.621093999999999</v>
+      </c>
+      <c r="D400" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A401" s="1">
+        <v>326.94394</v>
+      </c>
+      <c r="B401" s="1">
+        <v>2020</v>
+      </c>
+      <c r="C401" s="1">
+        <v>-25.42276</v>
+      </c>
+      <c r="D401" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A402" s="1">
+        <v>289.89614999999998</v>
+      </c>
+      <c r="B402" s="1">
+        <v>2021</v>
+      </c>
+      <c r="C402" s="1">
+        <v>-62.470550000000003</v>
+      </c>
+      <c r="D402" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A403" s="1">
+        <v>321.73131999999998</v>
+      </c>
+      <c r="B403" s="1">
+        <v>2022</v>
+      </c>
+      <c r="C403" s="1">
+        <v>-30.635376000000001</v>
+      </c>
+      <c r="D403" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A404" s="1">
+        <v>270.20287999999999</v>
+      </c>
+      <c r="B404" s="1">
+        <v>2023</v>
+      </c>
+      <c r="C404" s="1">
+        <v>-82.163820000000001</v>
+      </c>
+      <c r="D404" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A405" s="1">
+        <v>380.12875000000003</v>
+      </c>
+      <c r="B405" s="1">
+        <v>2024</v>
+      </c>
+      <c r="C405" s="1">
+        <v>27.762053999999999</v>
+      </c>
+      <c r="D405" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A406" s="1">
+        <v>315.35678000000001</v>
+      </c>
+      <c r="B406" s="1">
+        <v>2025</v>
+      </c>
+      <c r="C406" s="1">
+        <v>-37.009920000000001</v>
+      </c>
+      <c r="D406" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/Precipitacion/2025/2025_Ppt_Resumen_Datos.xlsx
+++ b/Precipitacion/2025/2025_Ppt_Resumen_Datos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bobby\Documents\GitHub\Clima_Agua_Panama\Precipitacion\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04D0EE6F-3B82-46AB-9497-1223B4A23B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7AF97BF-0E57-4DA8-ACE2-04022F1AFDD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="10245" windowHeight="10920" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="36">
   <si>
     <t>Jan</t>
   </si>
@@ -582,12 +582,14 @@
       <c r="J2" s="4">
         <v>236.7088</v>
       </c>
-      <c r="K2" s="4"/>
+      <c r="K2" s="4">
+        <v>365.25959999999998</v>
+      </c>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
       <c r="N2" s="4">
         <f>SUM(B2:M2)</f>
-        <v>2433.6025</v>
+        <v>2798.8620999999998</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
@@ -621,12 +623,14 @@
       <c r="J3" s="4">
         <v>292.02276999999998</v>
       </c>
-      <c r="K3" s="4"/>
+      <c r="K3" s="4">
+        <v>403.24709999999999</v>
+      </c>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4">
         <f t="shared" ref="N3:N14" si="0">SUM(B3:M3)</f>
-        <v>1499.5438610000001</v>
+        <v>1902.7909610000002</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
@@ -660,12 +664,14 @@
       <c r="J4" s="4">
         <v>208.57945000000001</v>
       </c>
-      <c r="K4" s="4"/>
+      <c r="K4" s="4">
+        <v>317.72985999999997</v>
+      </c>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4">
         <f t="shared" si="0"/>
-        <v>2126.3665200000005</v>
+        <v>2444.0963800000004</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
@@ -699,12 +705,14 @@
       <c r="J5" s="4">
         <v>224.00785999999999</v>
       </c>
-      <c r="K5" s="4"/>
+      <c r="K5" s="4">
+        <v>284.12270000000001</v>
+      </c>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
       <c r="N5" s="4">
         <f t="shared" si="0"/>
-        <v>2202.57951</v>
+        <v>2486.7022099999999</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
@@ -738,12 +746,14 @@
       <c r="J6" s="4">
         <v>469.45013</v>
       </c>
-      <c r="K6" s="4"/>
+      <c r="K6" s="4">
+        <v>599.0838</v>
+      </c>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4">
         <f t="shared" si="0"/>
-        <v>2681.8490200000001</v>
+        <v>3280.93282</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
@@ -777,12 +787,14 @@
       <c r="J7" s="4">
         <v>268.71422999999999</v>
       </c>
-      <c r="K7" s="4"/>
+      <c r="K7" s="4">
+        <v>348.60214000000002</v>
+      </c>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
       <c r="N7" s="4">
         <f t="shared" si="0"/>
-        <v>2282.9851899999999</v>
+        <v>2631.5873299999998</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
@@ -816,12 +828,14 @@
       <c r="J8" s="4">
         <v>425.11250000000001</v>
       </c>
-      <c r="K8" s="4"/>
+      <c r="K8" s="4">
+        <v>565.58483999999999</v>
+      </c>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4">
         <f t="shared" si="0"/>
-        <v>3022.2072499999999</v>
+        <v>3587.7920899999999</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
@@ -855,12 +869,14 @@
       <c r="J9" s="4">
         <v>218.42221000000001</v>
       </c>
-      <c r="K9" s="4"/>
+      <c r="K9" s="4">
+        <v>342.06396000000001</v>
+      </c>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
       <c r="N9" s="4">
         <f t="shared" si="0"/>
-        <v>2155.3652400000001</v>
+        <v>2497.4292</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
@@ -894,12 +910,14 @@
       <c r="J10" s="4">
         <v>316.54852</v>
       </c>
-      <c r="K10" s="4"/>
+      <c r="K10" s="4">
+        <v>490.21019999999999</v>
+      </c>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4">
         <f t="shared" si="0"/>
-        <v>1407.2533246</v>
+        <v>1897.4635246</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
@@ -933,12 +951,14 @@
       <c r="J11" s="4">
         <v>279.64080000000001</v>
       </c>
-      <c r="K11" s="4"/>
+      <c r="K11" s="4">
+        <v>410.62869999999998</v>
+      </c>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
       <c r="N11" s="4">
         <f t="shared" si="0"/>
-        <v>1164.5733547</v>
+        <v>1575.2020547</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
@@ -972,12 +992,14 @@
       <c r="J12" s="4">
         <v>285.97573999999997</v>
       </c>
-      <c r="K12" s="4"/>
+      <c r="K12" s="4">
+        <v>355.18185</v>
+      </c>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
       <c r="N12" s="4">
         <f t="shared" si="0"/>
-        <v>1973.1618050000002</v>
+        <v>2328.3436550000001</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
@@ -1011,12 +1033,14 @@
       <c r="J13" s="4">
         <v>288.40285999999998</v>
       </c>
-      <c r="K13" s="4"/>
+      <c r="K13" s="4">
+        <v>299.47998000000001</v>
+      </c>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
       <c r="N13" s="4">
         <f t="shared" si="0"/>
-        <v>1523.1010569999999</v>
+        <v>1822.5810369999999</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
@@ -1050,12 +1074,14 @@
       <c r="J14" s="4">
         <v>433.15170000000001</v>
       </c>
-      <c r="K14" s="4"/>
+      <c r="K14" s="4">
+        <v>614.27369999999996</v>
+      </c>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
       <c r="N14" s="4">
         <f t="shared" si="0"/>
-        <v>2235.2585600000002</v>
+        <v>2849.53226</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
@@ -1063,7 +1089,7 @@
         <v>27</v>
       </c>
       <c r="B15" s="7">
-        <f t="shared" ref="B15:J15" si="1">AVERAGE(B2:B14)</f>
+        <f t="shared" ref="B15:K15" si="1">AVERAGE(B2:B14)</f>
         <v>119.60806099999999</v>
       </c>
       <c r="C15" s="7">
@@ -1098,12 +1124,15 @@
         <f t="shared" si="1"/>
         <v>303.59519769230769</v>
       </c>
-      <c r="K15" s="7"/>
+      <c r="K15" s="7">
+        <f t="shared" si="1"/>
+        <v>415.03603307692299</v>
+      </c>
       <c r="L15" s="7"/>
       <c r="M15" s="7"/>
       <c r="N15" s="7">
         <f>SUM(B15:M15)</f>
-        <v>2054.449784023077</v>
+        <v>2469.4858171000001</v>
       </c>
     </row>
   </sheetData>
@@ -1198,12 +1227,14 @@
       <c r="J2" s="4">
         <v>273.32483000000002</v>
       </c>
-      <c r="K2" s="4"/>
+      <c r="K2" s="4">
+        <v>317.81826999999998</v>
+      </c>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
       <c r="N2" s="4">
         <f>SUM(B2:M2)</f>
-        <v>2241.6332299999999</v>
+        <v>2559.4515000000001</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -1237,12 +1268,14 @@
       <c r="J3" s="4">
         <v>313.45443999999998</v>
       </c>
-      <c r="K3" s="4"/>
+      <c r="K3" s="4">
+        <v>354.74783000000002</v>
+      </c>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4">
         <f t="shared" ref="N3:N13" si="0">SUM(B3:M3)</f>
-        <v>1514.374591</v>
+        <v>1869.122421</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -1276,12 +1309,14 @@
       <c r="J4" s="4">
         <v>277.55306999999999</v>
       </c>
-      <c r="K4" s="4"/>
+      <c r="K4" s="4">
+        <v>325.58974999999998</v>
+      </c>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4">
         <f t="shared" si="0"/>
-        <v>1742.0370800000001</v>
+        <v>2067.6268300000002</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -1315,12 +1350,14 @@
       <c r="J5" s="4">
         <v>230.79230999999999</v>
       </c>
-      <c r="K5" s="4"/>
+      <c r="K5" s="4">
+        <v>279.45186999999999</v>
+      </c>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
       <c r="N5" s="4">
         <f t="shared" si="0"/>
-        <v>1550.254091</v>
+        <v>1829.7059610000001</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -1354,12 +1391,14 @@
       <c r="J6" s="4">
         <v>517.72249999999997</v>
       </c>
-      <c r="K6" s="4"/>
+      <c r="K6" s="4">
+        <v>590.82439999999997</v>
+      </c>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4">
         <f t="shared" si="0"/>
-        <v>2462.9063839999999</v>
+        <v>3053.7307839999999</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -1393,12 +1432,14 @@
       <c r="J7" s="4">
         <v>312.03244000000001</v>
       </c>
-      <c r="K7" s="4"/>
+      <c r="K7" s="4">
+        <v>383.06484999999998</v>
+      </c>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
       <c r="N7" s="4">
         <f t="shared" si="0"/>
-        <v>2146.74955</v>
+        <v>2529.8144000000002</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -1432,12 +1473,14 @@
       <c r="J8" s="4">
         <v>458.21069999999997</v>
       </c>
-      <c r="K8" s="4"/>
+      <c r="K8" s="4">
+        <v>483.60727000000003</v>
+      </c>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4">
         <f t="shared" si="0"/>
-        <v>2596.006805</v>
+        <v>3079.614075</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -1471,12 +1514,14 @@
       <c r="J9" s="4">
         <v>288.94130000000001</v>
       </c>
-      <c r="K9" s="4"/>
+      <c r="K9" s="4">
+        <v>366.76146999999997</v>
+      </c>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
       <c r="N9" s="4">
         <f t="shared" si="0"/>
-        <v>1724.7399929999999</v>
+        <v>2091.5014630000001</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1510,12 +1555,14 @@
       <c r="J10" s="4">
         <v>325.31155000000001</v>
       </c>
-      <c r="K10" s="4"/>
+      <c r="K10" s="4">
+        <v>363.06990000000002</v>
+      </c>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4">
         <f t="shared" si="0"/>
-        <v>1387.8748694999999</v>
+        <v>1750.9447694999999</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -1549,12 +1596,14 @@
       <c r="J11" s="4">
         <v>248.78128000000001</v>
       </c>
-      <c r="K11" s="4"/>
+      <c r="K11" s="4">
+        <v>309.19450000000001</v>
+      </c>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
       <c r="N11" s="4">
         <f t="shared" si="0"/>
-        <v>1097.111273</v>
+        <v>1406.305773</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -1588,12 +1637,14 @@
       <c r="J12" s="4">
         <v>300.47494999999998</v>
       </c>
-      <c r="K12" s="4"/>
+      <c r="K12" s="4">
+        <v>367.82285000000002</v>
+      </c>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
       <c r="N12" s="4">
         <f t="shared" si="0"/>
-        <v>1563.823709</v>
+        <v>1931.646559</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -1627,12 +1678,14 @@
       <c r="J13" s="4">
         <v>293.80295000000001</v>
       </c>
-      <c r="K13" s="4"/>
+      <c r="K13" s="4">
+        <v>372.15042</v>
+      </c>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
       <c r="N13" s="4">
         <f t="shared" si="0"/>
-        <v>1441.720253</v>
+        <v>1813.8706729999999</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1666,12 +1719,14 @@
       <c r="J14" s="4">
         <v>484.0908</v>
       </c>
-      <c r="K14" s="4"/>
+      <c r="K14" s="4">
+        <v>525.76415999999995</v>
+      </c>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
       <c r="N14" s="4">
         <f>SUM(B14:M14)</f>
-        <v>2152.271428</v>
+        <v>2678.0355879999997</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1683,7 +1738,7 @@
         <v>67.513827307692296</v>
       </c>
       <c r="C15" s="7">
-        <f t="shared" ref="C15:J15" si="1">AVERAGE(C2:C14)</f>
+        <f t="shared" ref="C15:K15" si="1">AVERAGE(C2:C14)</f>
         <v>41.752843615384613</v>
       </c>
       <c r="D15" s="7">
@@ -1714,12 +1769,15 @@
         <f t="shared" si="1"/>
         <v>332.65331692307694</v>
       </c>
-      <c r="K15" s="2"/>
+      <c r="K15" s="7">
+        <f t="shared" si="1"/>
+        <v>387.68211846153849</v>
+      </c>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
       <c r="N15" s="7">
         <f>SUM(B15:M15)</f>
-        <v>1817.0387120384617</v>
+        <v>2204.7208305000004</v>
       </c>
     </row>
   </sheetData>
@@ -1768,7 +1826,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
-        <v>5.2492599999999996</v>
+        <v>5.2492570000000001</v>
       </c>
       <c r="B2" s="3">
         <v>2024</v>
@@ -1786,7 +1844,7 @@
         <v>45658</v>
       </c>
       <c r="G2" s="3">
-        <v>5.2492599999999996</v>
+        <v>5.2492570000000001</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -1809,12 +1867,12 @@
         <v>45663</v>
       </c>
       <c r="G3" s="3">
-        <v>9.8455925000000004</v>
+        <v>9.8455899999999996</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
-        <v>9.417605</v>
+        <v>9.4176009999999994</v>
       </c>
       <c r="B4" s="3">
         <v>2024</v>
@@ -1832,12 +1890,12 @@
         <v>45668</v>
       </c>
       <c r="G4" s="3">
-        <v>19.263199</v>
+        <v>19.263190999999999</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
-        <v>3.945147</v>
+        <v>3.9451466000000002</v>
       </c>
       <c r="B5" s="3">
         <v>2024</v>
@@ -1855,12 +1913,12 @@
         <v>45673</v>
       </c>
       <c r="G5" s="3">
-        <v>23.208345000000001</v>
+        <v>23.208335999999999</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
-        <v>5.0826297</v>
+        <v>5.0826324999999999</v>
       </c>
       <c r="B6" s="3">
         <v>2024</v>
@@ -1878,12 +1936,12 @@
         <v>45678</v>
       </c>
       <c r="G6" s="3">
-        <v>28.290973999999999</v>
+        <v>28.290970000000002</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
-        <v>13.980487</v>
+        <v>13.980486000000001</v>
       </c>
       <c r="B7" s="3">
         <v>2024</v>
@@ -1901,12 +1959,12 @@
         <v>45683</v>
       </c>
       <c r="G7" s="3">
-        <v>42.271459999999998</v>
+        <v>42.271453999999999</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
-        <v>9.9413990000000005</v>
+        <v>9.941395</v>
       </c>
       <c r="B8" s="3">
         <v>2024</v>
@@ -1924,12 +1982,12 @@
         <v>45689</v>
       </c>
       <c r="G8" s="3">
-        <v>52.212859999999999</v>
+        <v>52.212851999999998</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
-        <v>4.7953580000000002</v>
+        <v>4.7953590000000004</v>
       </c>
       <c r="B9" s="3">
         <v>2024</v>
@@ -1947,7 +2005,7 @@
         <v>45694</v>
       </c>
       <c r="G9" s="3">
-        <v>57.008217000000002</v>
+        <v>57.008209999999998</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -1970,12 +2028,12 @@
         <v>45699</v>
       </c>
       <c r="G10" s="3">
-        <v>60.635666000000001</v>
+        <v>60.635660000000001</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
-        <v>7.8164879999999997</v>
+        <v>7.8164870000000004</v>
       </c>
       <c r="B11" s="3">
         <v>2024</v>
@@ -1993,12 +2051,12 @@
         <v>45704</v>
       </c>
       <c r="G11" s="3">
-        <v>68.452156000000002</v>
+        <v>68.452150000000003</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
-        <v>3.8636946999999999</v>
+        <v>3.8636959000000002</v>
       </c>
       <c r="B12" s="3">
         <v>2024</v>
@@ -2016,12 +2074,12 @@
         <v>45709</v>
       </c>
       <c r="G12" s="3">
-        <v>72.315849999999998</v>
+        <v>72.315839999999994</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
-        <v>3.0973334000000001</v>
+        <v>3.0973332</v>
       </c>
       <c r="B13" s="3">
         <v>2024</v>
@@ -2039,12 +2097,12 @@
         <v>45714</v>
       </c>
       <c r="G13" s="3">
-        <v>75.413184999999999</v>
+        <v>75.413179999999997</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
-        <v>2.8400240000000001</v>
+        <v>2.8400251999999999</v>
       </c>
       <c r="B14" s="3">
         <v>2024</v>
@@ -2062,12 +2120,12 @@
         <v>45717</v>
       </c>
       <c r="G14" s="3">
-        <v>78.253203999999997</v>
+        <v>78.253200000000007</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
-        <v>1.6105003</v>
+        <v>1.6105007</v>
       </c>
       <c r="B15" s="3">
         <v>2024</v>
@@ -2085,12 +2143,12 @@
         <v>45722</v>
       </c>
       <c r="G15" s="3">
-        <v>79.863709999999998</v>
+        <v>79.863699999999994</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
-        <v>2.9749854</v>
+        <v>2.9749859999999999</v>
       </c>
       <c r="B16" s="3">
         <v>2024</v>
@@ -2108,12 +2166,12 @@
         <v>45727</v>
       </c>
       <c r="G16" s="3">
-        <v>82.83869</v>
+        <v>82.838684000000001</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
-        <v>5.1857699999999998</v>
+        <v>5.1857705000000003</v>
       </c>
       <c r="B17" s="3">
         <v>2024</v>
@@ -2136,7 +2194,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
-        <v>4.8315444000000003</v>
+        <v>4.8315429999999999</v>
       </c>
       <c r="B18" s="3">
         <v>2024</v>
@@ -2154,12 +2212,12 @@
         <v>45737</v>
       </c>
       <c r="G18" s="3">
-        <v>92.856009999999998</v>
+        <v>92.855999999999995</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
-        <v>9.8148940000000007</v>
+        <v>9.8148970000000002</v>
       </c>
       <c r="B19" s="3">
         <v>2024</v>
@@ -2182,7 +2240,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
-        <v>8.4280430000000006</v>
+        <v>8.4280469999999994</v>
       </c>
       <c r="B20" s="3">
         <v>2024</v>
@@ -2205,7 +2263,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
-        <v>51.836410000000001</v>
+        <v>51.836436999999997</v>
       </c>
       <c r="B21" s="3">
         <v>2024</v>
@@ -2223,12 +2281,12 @@
         <v>45753</v>
       </c>
       <c r="G21" s="3">
-        <v>162.93536</v>
+        <v>162.93538000000001</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
-        <v>3.5840244000000001</v>
+        <v>3.5840266000000001</v>
       </c>
       <c r="B22" s="3">
         <v>2024</v>
@@ -2246,12 +2304,12 @@
         <v>45758</v>
       </c>
       <c r="G22" s="3">
-        <v>166.51938000000001</v>
+        <v>166.51940999999999</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
-        <v>4.5789790000000004</v>
+        <v>4.5789795</v>
       </c>
       <c r="B23" s="3">
         <v>2024</v>
@@ -2269,12 +2327,12 @@
         <v>45763</v>
       </c>
       <c r="G23" s="3">
-        <v>171.09836000000001</v>
+        <v>171.09838999999999</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
-        <v>35.190944999999999</v>
+        <v>35.190956</v>
       </c>
       <c r="B24" s="3">
         <v>2024</v>
@@ -2292,12 +2350,12 @@
         <v>45768</v>
       </c>
       <c r="G24" s="3">
-        <v>206.2893</v>
+        <v>206.28934000000001</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
-        <v>49.291473000000003</v>
+        <v>49.291491999999998</v>
       </c>
       <c r="B25" s="3">
         <v>2024</v>
@@ -2315,12 +2373,12 @@
         <v>45773</v>
       </c>
       <c r="G25" s="3">
-        <v>255.58078</v>
+        <v>255.58083999999999</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
-        <v>27.345006999999999</v>
+        <v>27.345015</v>
       </c>
       <c r="B26" s="3">
         <v>2024</v>
@@ -2338,12 +2396,12 @@
         <v>45778</v>
       </c>
       <c r="G26" s="3">
-        <v>282.92577999999997</v>
+        <v>282.92583999999999</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
-        <v>50.558692999999998</v>
+        <v>50.558684999999997</v>
       </c>
       <c r="B27" s="3">
         <v>2024</v>
@@ -2361,12 +2419,12 @@
         <v>45783</v>
       </c>
       <c r="G27" s="3">
-        <v>333.48446999999999</v>
+        <v>333.48453000000001</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
-        <v>68.892129999999995</v>
+        <v>68.892166000000003</v>
       </c>
       <c r="B28" s="3">
         <v>2024</v>
@@ -2384,12 +2442,12 @@
         <v>45788</v>
       </c>
       <c r="G28" s="3">
-        <v>402.3766</v>
+        <v>402.37670000000003</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
-        <v>51.808804000000002</v>
+        <v>51.80883</v>
       </c>
       <c r="B29" s="3">
         <v>2024</v>
@@ -2407,12 +2465,12 @@
         <v>45793</v>
       </c>
       <c r="G29" s="3">
-        <v>454.18540000000002</v>
+        <v>454.18554999999998</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
-        <v>52.960239999999999</v>
+        <v>52.960228000000001</v>
       </c>
       <c r="B30" s="3">
         <v>2024</v>
@@ -2430,12 +2488,12 @@
         <v>45798</v>
       </c>
       <c r="G30" s="3">
-        <v>507.14562999999998</v>
+        <v>507.14575000000002</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
-        <v>52.317590000000003</v>
+        <v>52.317616000000001</v>
       </c>
       <c r="B31" s="3">
         <v>2024</v>
@@ -2453,7 +2511,7 @@
         <v>45803</v>
       </c>
       <c r="G31" s="3">
-        <v>559.46325999999999</v>
+        <v>559.46339999999998</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -2476,12 +2534,12 @@
         <v>45809</v>
       </c>
       <c r="G32" s="3">
-        <v>609.90155000000004</v>
+        <v>609.90170000000001</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
-        <v>58.700417000000002</v>
+        <v>58.700428000000002</v>
       </c>
       <c r="B33" s="3">
         <v>2024</v>
@@ -2499,12 +2557,12 @@
         <v>45814</v>
       </c>
       <c r="G33" s="3">
-        <v>668.6019</v>
+        <v>668.60209999999995</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
-        <v>83.162800000000004</v>
+        <v>83.162850000000006</v>
       </c>
       <c r="B34" s="3">
         <v>2024</v>
@@ -2522,12 +2580,12 @@
         <v>45819</v>
       </c>
       <c r="G34" s="3">
-        <v>751.76480000000004</v>
+        <v>751.76495</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
-        <v>61.870980000000003</v>
+        <v>61.870975000000001</v>
       </c>
       <c r="B35" s="3">
         <v>2024</v>
@@ -2545,12 +2603,12 @@
         <v>45824</v>
       </c>
       <c r="G35" s="3">
-        <v>813.63574000000006</v>
+        <v>813.63589999999999</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
-        <v>43.194755999999998</v>
+        <v>43.194775</v>
       </c>
       <c r="B36" s="3">
         <v>2024</v>
@@ -2568,12 +2626,12 @@
         <v>45829</v>
       </c>
       <c r="G36" s="3">
-        <v>856.83050000000003</v>
+        <v>856.83069999999998</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
-        <v>33.611879999999999</v>
+        <v>33.611854999999998</v>
       </c>
       <c r="B37" s="3">
         <v>2024</v>
@@ -2591,12 +2649,12 @@
         <v>45834</v>
       </c>
       <c r="G37" s="3">
-        <v>890.44240000000002</v>
+        <v>890.44257000000005</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
-        <v>48.680484999999997</v>
+        <v>48.680500000000002</v>
       </c>
       <c r="B38" s="3">
         <v>2024</v>
@@ -2614,12 +2672,12 @@
         <v>45839</v>
       </c>
       <c r="G38" s="3">
-        <v>939.12285999999995</v>
+        <v>939.12305000000003</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
-        <v>35.615887000000001</v>
+        <v>35.615882999999997</v>
       </c>
       <c r="B39" s="3">
         <v>2024</v>
@@ -2637,12 +2695,12 @@
         <v>45844</v>
       </c>
       <c r="G39" s="3">
-        <v>974.73879999999997</v>
+        <v>974.73895000000005</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
-        <v>46.791220000000003</v>
+        <v>46.791237000000002</v>
       </c>
       <c r="B40" s="3">
         <v>2024</v>
@@ -2660,12 +2718,12 @@
         <v>45849</v>
       </c>
       <c r="G40" s="3">
-        <v>1021.52997</v>
+        <v>1021.53015</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
-        <v>50.363697000000002</v>
+        <v>50.363680000000002</v>
       </c>
       <c r="B41" s="3">
         <v>2024</v>
@@ -2683,12 +2741,12 @@
         <v>45854</v>
       </c>
       <c r="G41" s="3">
-        <v>1071.8937000000001</v>
+        <v>1071.8938000000001</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
-        <v>49.690550000000002</v>
+        <v>49.690567000000001</v>
       </c>
       <c r="B42" s="3">
         <v>2024</v>
@@ -2706,12 +2764,12 @@
         <v>45859</v>
       </c>
       <c r="G42" s="3">
-        <v>1121.5842</v>
+        <v>1121.5844999999999</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
-        <v>66.886579999999995</v>
+        <v>66.886566000000002</v>
       </c>
       <c r="B43" s="3">
         <v>2024</v>
@@ -2729,12 +2787,12 @@
         <v>45864</v>
       </c>
       <c r="G43" s="3">
-        <v>1188.4708000000001</v>
+        <v>1188.471</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
-        <v>48.587234000000002</v>
+        <v>48.587220000000002</v>
       </c>
       <c r="B44" s="3">
         <v>2024</v>
@@ -2752,12 +2810,12 @@
         <v>45870</v>
       </c>
       <c r="G44" s="3">
-        <v>1237.058</v>
+        <v>1237.0581999999999</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
-        <v>68.053039999999996</v>
+        <v>68.053060000000002</v>
       </c>
       <c r="B45" s="3">
         <v>2024</v>
@@ -2775,12 +2833,12 @@
         <v>45875</v>
       </c>
       <c r="G45" s="3">
-        <v>1305.1111000000001</v>
+        <v>1305.1113</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
-        <v>42.254092999999997</v>
+        <v>42.254086000000001</v>
       </c>
       <c r="B46" s="3">
         <v>2024</v>
@@ -2798,12 +2856,12 @@
         <v>45880</v>
       </c>
       <c r="G46" s="3">
-        <v>1347.3651</v>
+        <v>1347.3653999999999</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
-        <v>62.352615</v>
+        <v>62.352646</v>
       </c>
       <c r="B47" s="3">
         <v>2024</v>
@@ -2821,12 +2879,12 @@
         <v>45885</v>
       </c>
       <c r="G47" s="3">
-        <v>1409.7177999999999</v>
+        <v>1409.7180000000001</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
-        <v>66.438575999999998</v>
+        <v>66.438540000000003</v>
       </c>
       <c r="B48" s="3">
         <v>2024</v>
@@ -2844,12 +2902,12 @@
         <v>45890</v>
       </c>
       <c r="G48" s="3">
-        <v>1476.1564000000001</v>
+        <v>1476.1565000000001</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
-        <v>48.39085</v>
+        <v>48.390827000000002</v>
       </c>
       <c r="B49" s="3">
         <v>2024</v>
@@ -2867,12 +2925,12 @@
         <v>45895</v>
       </c>
       <c r="G49" s="3">
-        <v>1524.5472</v>
+        <v>1524.5473999999999</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
-        <v>61.745944999999999</v>
+        <v>61.745956</v>
       </c>
       <c r="B50" s="3">
         <v>2024</v>
@@ -2890,12 +2948,12 @@
         <v>45901</v>
       </c>
       <c r="G50" s="3">
-        <v>1586.2932000000001</v>
+        <v>1586.2933</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
-        <v>55.749302</v>
+        <v>55.749347999999998</v>
       </c>
       <c r="B51" s="3">
         <v>2024</v>
@@ -2913,12 +2971,12 @@
         <v>45906</v>
       </c>
       <c r="G51" s="3">
-        <v>1642.0425</v>
+        <v>1642.0427</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
-        <v>44.363680000000002</v>
+        <v>44.363678</v>
       </c>
       <c r="B52" s="3">
         <v>2024</v>
@@ -2936,12 +2994,12 @@
         <v>45911</v>
       </c>
       <c r="G52" s="3">
-        <v>1686.4060999999999</v>
+        <v>1686.4064000000001</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
-        <v>61.65296</v>
+        <v>61.652965999999999</v>
       </c>
       <c r="B53" s="3">
         <v>2024</v>
@@ -2959,12 +3017,12 @@
         <v>45916</v>
       </c>
       <c r="G53" s="3">
-        <v>1748.0590999999999</v>
+        <v>1748.0592999999999</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
-        <v>67.535849999999996</v>
+        <v>67.535835000000006</v>
       </c>
       <c r="B54" s="3">
         <v>2024</v>
@@ -2982,12 +3040,12 @@
         <v>45921</v>
       </c>
       <c r="G54" s="3">
-        <v>1815.595</v>
+        <v>1815.5952</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
-        <v>89.081023999999999</v>
+        <v>89.081029999999998</v>
       </c>
       <c r="B55" s="3">
         <v>2024</v>
@@ -3005,18 +3063,18 @@
         <v>45926</v>
       </c>
       <c r="G55" s="3">
-        <v>1904.6759999999999</v>
+        <v>1904.6760999999999</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
-        <v>51.443665000000003</v>
+        <v>43.125343000000001</v>
       </c>
       <c r="B56" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C56" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D56" s="3">
         <v>1</v>
@@ -3025,21 +3083,21 @@
         <v>1</v>
       </c>
       <c r="F56" s="5">
-        <v>45658</v>
+        <v>45931</v>
       </c>
       <c r="G56" s="3">
-        <v>51.443665000000003</v>
+        <v>1947.8015</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
-        <v>30.218014</v>
+        <v>39.753852999999999</v>
       </c>
       <c r="B57" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C57" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D57" s="3">
         <v>2</v>
@@ -3048,21 +3106,21 @@
         <v>6</v>
       </c>
       <c r="F57" s="5">
-        <v>45663</v>
+        <v>45936</v>
       </c>
       <c r="G57" s="3">
-        <v>81.661680000000004</v>
+        <v>1987.5554</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
-        <v>7.739935</v>
+        <v>95.955860000000001</v>
       </c>
       <c r="B58" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C58" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D58" s="3">
         <v>3</v>
@@ -3071,21 +3129,21 @@
         <v>11</v>
       </c>
       <c r="F58" s="5">
-        <v>45668</v>
+        <v>45941</v>
       </c>
       <c r="G58" s="3">
-        <v>89.401610000000005</v>
+        <v>2083.5111999999999</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
-        <v>11.712355000000001</v>
+        <v>84.293210000000002</v>
       </c>
       <c r="B59" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C59" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D59" s="3">
         <v>4</v>
@@ -3094,21 +3152,21 @@
         <v>16</v>
       </c>
       <c r="F59" s="5">
-        <v>45673</v>
+        <v>45946</v>
       </c>
       <c r="G59" s="3">
-        <v>101.11396999999999</v>
+        <v>2167.8044</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
-        <v>8.5210740000000005</v>
+        <v>49.366059999999997</v>
       </c>
       <c r="B60" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C60" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D60" s="3">
         <v>5</v>
@@ -3117,21 +3175,21 @@
         <v>21</v>
       </c>
       <c r="F60" s="5">
-        <v>45678</v>
+        <v>45951</v>
       </c>
       <c r="G60" s="3">
-        <v>109.63504</v>
+        <v>2217.1704</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
-        <v>9.6642499999999991</v>
+        <v>140.98303000000001</v>
       </c>
       <c r="B61" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C61" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D61" s="3">
         <v>6</v>
@@ -3140,21 +3198,21 @@
         <v>26</v>
       </c>
       <c r="F61" s="5">
-        <v>45683</v>
+        <v>45956</v>
       </c>
       <c r="G61" s="3">
-        <v>119.29929</v>
+        <v>2358.1536000000001</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
-        <v>14.432331</v>
+        <v>51.443686999999997</v>
       </c>
       <c r="B62" s="3">
         <v>2025</v>
       </c>
       <c r="C62" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D62" s="3">
         <v>1</v>
@@ -3163,21 +3221,21 @@
         <v>1</v>
       </c>
       <c r="F62" s="5">
-        <v>45689</v>
+        <v>45658</v>
       </c>
       <c r="G62" s="3">
-        <v>133.73163</v>
+        <v>51.443686999999997</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
-        <v>8.7800454999999999</v>
+        <v>30.218036999999999</v>
       </c>
       <c r="B63" s="3">
         <v>2025</v>
       </c>
       <c r="C63" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D63" s="3">
         <v>2</v>
@@ -3186,21 +3244,21 @@
         <v>6</v>
       </c>
       <c r="F63" s="5">
-        <v>45694</v>
+        <v>45663</v>
       </c>
       <c r="G63" s="3">
-        <v>142.51167000000001</v>
+        <v>81.661730000000006</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
-        <v>36.847520000000003</v>
+        <v>7.7399344000000001</v>
       </c>
       <c r="B64" s="3">
         <v>2025</v>
       </c>
       <c r="C64" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D64" s="3">
         <v>3</v>
@@ -3209,21 +3267,21 @@
         <v>11</v>
       </c>
       <c r="F64" s="5">
-        <v>45699</v>
+        <v>45668</v>
       </c>
       <c r="G64" s="3">
-        <v>179.35919000000001</v>
+        <v>89.401660000000007</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
-        <v>47.512675999999999</v>
+        <v>11.712353999999999</v>
       </c>
       <c r="B65" s="3">
         <v>2025</v>
       </c>
       <c r="C65" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D65" s="3">
         <v>4</v>
@@ -3232,21 +3290,21 @@
         <v>16</v>
       </c>
       <c r="F65" s="5">
-        <v>45704</v>
+        <v>45673</v>
       </c>
       <c r="G65" s="3">
-        <v>226.87186</v>
+        <v>101.11400999999999</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
-        <v>11.339198</v>
+        <v>8.5210749999999997</v>
       </c>
       <c r="B66" s="3">
         <v>2025</v>
       </c>
       <c r="C66" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D66" s="3">
         <v>5</v>
@@ -3255,21 +3313,21 @@
         <v>21</v>
       </c>
       <c r="F66" s="5">
-        <v>45709</v>
+        <v>45678</v>
       </c>
       <c r="G66" s="3">
-        <v>238.21106</v>
+        <v>109.635086</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
-        <v>5.0655340000000004</v>
+        <v>9.6642530000000004</v>
       </c>
       <c r="B67" s="3">
         <v>2025</v>
       </c>
       <c r="C67" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D67" s="3">
         <v>6</v>
@@ -3278,21 +3336,21 @@
         <v>26</v>
       </c>
       <c r="F67" s="5">
-        <v>45714</v>
+        <v>45683</v>
       </c>
       <c r="G67" s="3">
-        <v>243.2766</v>
+        <v>119.29934</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
-        <v>6.6873073999999999</v>
+        <v>14.432333</v>
       </c>
       <c r="B68" s="3">
         <v>2025</v>
       </c>
       <c r="C68" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D68" s="3">
         <v>1</v>
@@ -3301,21 +3359,21 @@
         <v>1</v>
       </c>
       <c r="F68" s="5">
-        <v>45717</v>
+        <v>45689</v>
       </c>
       <c r="G68" s="3">
-        <v>249.9639</v>
+        <v>133.73167000000001</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
-        <v>5.1503972999999998</v>
+        <v>8.7800480000000007</v>
       </c>
       <c r="B69" s="3">
         <v>2025</v>
       </c>
       <c r="C69" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D69" s="3">
         <v>2</v>
@@ -3324,21 +3382,21 @@
         <v>6</v>
       </c>
       <c r="F69" s="5">
-        <v>45722</v>
+        <v>45694</v>
       </c>
       <c r="G69" s="3">
-        <v>255.11429999999999</v>
+        <v>142.51172</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
-        <v>5.3021646000000002</v>
+        <v>36.847504000000001</v>
       </c>
       <c r="B70" s="3">
         <v>2025</v>
       </c>
       <c r="C70" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D70" s="3">
         <v>3</v>
@@ -3347,21 +3405,21 @@
         <v>11</v>
       </c>
       <c r="F70" s="5">
-        <v>45727</v>
+        <v>45699</v>
       </c>
       <c r="G70" s="3">
-        <v>260.41647</v>
+        <v>179.35921999999999</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
-        <v>7.7123600000000003</v>
+        <v>47.512680000000003</v>
       </c>
       <c r="B71" s="3">
         <v>2025</v>
       </c>
       <c r="C71" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D71" s="3">
         <v>4</v>
@@ -3370,21 +3428,21 @@
         <v>16</v>
       </c>
       <c r="F71" s="5">
-        <v>45732</v>
+        <v>45704</v>
       </c>
       <c r="G71" s="3">
-        <v>268.12880000000001</v>
+        <v>226.87190000000001</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
-        <v>24.789614</v>
+        <v>11.339199000000001</v>
       </c>
       <c r="B72" s="3">
         <v>2025</v>
       </c>
       <c r="C72" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D72" s="3">
         <v>5</v>
@@ -3393,21 +3451,21 @@
         <v>21</v>
       </c>
       <c r="F72" s="5">
-        <v>45737</v>
+        <v>45709</v>
       </c>
       <c r="G72" s="3">
-        <v>292.91843</v>
+        <v>238.21109999999999</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
-        <v>23.760328000000001</v>
+        <v>5.0655327000000003</v>
       </c>
       <c r="B73" s="3">
         <v>2025</v>
       </c>
       <c r="C73" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D73" s="3">
         <v>6</v>
@@ -3416,21 +3474,21 @@
         <v>26</v>
       </c>
       <c r="F73" s="5">
-        <v>45742</v>
+        <v>45714</v>
       </c>
       <c r="G73" s="3">
-        <v>316.67876999999999</v>
+        <v>243.27663999999999</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
-        <v>30.345040000000001</v>
+        <v>6.6873063999999998</v>
       </c>
       <c r="B74" s="3">
         <v>2025</v>
       </c>
       <c r="C74" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D74" s="3">
         <v>1</v>
@@ -3439,21 +3497,21 @@
         <v>1</v>
       </c>
       <c r="F74" s="5">
-        <v>45748</v>
+        <v>45717</v>
       </c>
       <c r="G74" s="3">
-        <v>347.02379999999999</v>
+        <v>249.96394000000001</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
-        <v>26.385967000000001</v>
+        <v>5.1503943999999997</v>
       </c>
       <c r="B75" s="3">
         <v>2025</v>
       </c>
       <c r="C75" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D75" s="3">
         <v>2</v>
@@ -3462,21 +3520,21 @@
         <v>6</v>
       </c>
       <c r="F75" s="5">
-        <v>45753</v>
+        <v>45722</v>
       </c>
       <c r="G75" s="3">
-        <v>373.40980000000002</v>
+        <v>255.11433</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
-        <v>14.766455000000001</v>
+        <v>5.3021630000000002</v>
       </c>
       <c r="B76" s="3">
         <v>2025</v>
       </c>
       <c r="C76" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D76" s="3">
         <v>3</v>
@@ -3485,21 +3543,21 @@
         <v>11</v>
       </c>
       <c r="F76" s="5">
-        <v>45758</v>
+        <v>45727</v>
       </c>
       <c r="G76" s="3">
-        <v>388.17624000000001</v>
+        <v>260.41649999999998</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
-        <v>13.573517000000001</v>
+        <v>7.7123569999999999</v>
       </c>
       <c r="B77" s="3">
         <v>2025</v>
       </c>
       <c r="C77" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D77" s="3">
         <v>4</v>
@@ -3508,21 +3566,21 @@
         <v>16</v>
       </c>
       <c r="F77" s="5">
-        <v>45763</v>
+        <v>45732</v>
       </c>
       <c r="G77" s="3">
-        <v>401.74975999999998</v>
+        <v>268.12885</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
-        <v>39.140994999999997</v>
+        <v>24.789594999999998</v>
       </c>
       <c r="B78" s="3">
         <v>2025</v>
       </c>
       <c r="C78" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D78" s="3">
         <v>5</v>
@@ -3531,21 +3589,21 @@
         <v>21</v>
       </c>
       <c r="F78" s="5">
-        <v>45768</v>
+        <v>45737</v>
       </c>
       <c r="G78" s="3">
-        <v>440.89075000000003</v>
+        <v>292.91845999999998</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
-        <v>41.962490000000003</v>
+        <v>23.760323</v>
       </c>
       <c r="B79" s="3">
         <v>2025</v>
       </c>
       <c r="C79" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D79" s="3">
         <v>6</v>
@@ -3554,21 +3612,21 @@
         <v>26</v>
       </c>
       <c r="F79" s="5">
-        <v>45773</v>
+        <v>45742</v>
       </c>
       <c r="G79" s="3">
-        <v>482.85324000000003</v>
+        <v>316.67876999999999</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
-        <v>55.322018</v>
+        <v>30.345040000000001</v>
       </c>
       <c r="B80" s="3">
         <v>2025</v>
       </c>
       <c r="C80" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D80" s="3">
         <v>1</v>
@@ -3577,21 +3635,21 @@
         <v>1</v>
       </c>
       <c r="F80" s="5">
-        <v>45778</v>
+        <v>45748</v>
       </c>
       <c r="G80" s="3">
-        <v>538.17523000000006</v>
+        <v>347.02379999999999</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
-        <v>48.162059999999997</v>
+        <v>26.385961999999999</v>
       </c>
       <c r="B81" s="3">
         <v>2025</v>
       </c>
       <c r="C81" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D81" s="3">
         <v>2</v>
@@ -3600,21 +3658,21 @@
         <v>6</v>
       </c>
       <c r="F81" s="5">
-        <v>45783</v>
+        <v>45753</v>
       </c>
       <c r="G81" s="3">
-        <v>586.33730000000003</v>
+        <v>373.40980000000002</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
-        <v>73.48912</v>
+        <v>14.766463</v>
       </c>
       <c r="B82" s="3">
         <v>2025</v>
       </c>
       <c r="C82" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D82" s="3">
         <v>3</v>
@@ -3623,21 +3681,21 @@
         <v>11</v>
       </c>
       <c r="F82" s="5">
-        <v>45788</v>
+        <v>45758</v>
       </c>
       <c r="G82" s="3">
-        <v>659.82640000000004</v>
+        <v>388.17624000000001</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
-        <v>73.519159999999999</v>
+        <v>13.573518999999999</v>
       </c>
       <c r="B83" s="3">
         <v>2025</v>
       </c>
       <c r="C83" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D83" s="3">
         <v>4</v>
@@ -3646,21 +3704,21 @@
         <v>16</v>
       </c>
       <c r="F83" s="5">
-        <v>45793</v>
+        <v>45763</v>
       </c>
       <c r="G83" s="3">
-        <v>733.34559999999999</v>
+        <v>401.74975999999998</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
-        <v>73.128389999999996</v>
+        <v>39.141010000000001</v>
       </c>
       <c r="B84" s="3">
         <v>2025</v>
       </c>
       <c r="C84" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D84" s="3">
         <v>5</v>
@@ -3669,21 +3727,21 @@
         <v>21</v>
       </c>
       <c r="F84" s="5">
-        <v>45798</v>
+        <v>45768</v>
       </c>
       <c r="G84" s="3">
-        <v>806.47400000000005</v>
+        <v>440.89078000000001</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
-        <v>50.314033999999999</v>
+        <v>41.962490000000003</v>
       </c>
       <c r="B85" s="3">
         <v>2025</v>
       </c>
       <c r="C85" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D85" s="3">
         <v>6</v>
@@ -3692,21 +3750,21 @@
         <v>26</v>
       </c>
       <c r="F85" s="5">
-        <v>45803</v>
+        <v>45773</v>
       </c>
       <c r="G85" s="3">
-        <v>856.78800000000001</v>
+        <v>482.85327000000001</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
-        <v>56.452938000000003</v>
+        <v>55.322009999999999</v>
       </c>
       <c r="B86" s="3">
         <v>2025</v>
       </c>
       <c r="C86" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D86" s="3">
         <v>1</v>
@@ -3715,21 +3773,21 @@
         <v>1</v>
       </c>
       <c r="F86" s="5">
-        <v>45809</v>
+        <v>45778</v>
       </c>
       <c r="G86" s="3">
-        <v>913.24096999999995</v>
+        <v>538.17529999999999</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
-        <v>77.087310000000002</v>
+        <v>48.162075000000002</v>
       </c>
       <c r="B87" s="3">
         <v>2025</v>
       </c>
       <c r="C87" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D87" s="3">
         <v>2</v>
@@ -3738,21 +3796,21 @@
         <v>6</v>
       </c>
       <c r="F87" s="5">
-        <v>45814</v>
+        <v>45783</v>
       </c>
       <c r="G87" s="3">
-        <v>990.32825000000003</v>
+        <v>586.33734000000004</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
-        <v>52.885773</v>
+        <v>73.489159999999998</v>
       </c>
       <c r="B88" s="3">
         <v>2025</v>
       </c>
       <c r="C88" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D88" s="3">
         <v>3</v>
@@ -3761,21 +3819,21 @@
         <v>11</v>
       </c>
       <c r="F88" s="5">
-        <v>45819</v>
+        <v>45788</v>
       </c>
       <c r="G88" s="3">
-        <v>1043.2139999999999</v>
+        <v>659.82654000000002</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
-        <v>39.925713000000002</v>
+        <v>73.519165000000001</v>
       </c>
       <c r="B89" s="3">
         <v>2025</v>
       </c>
       <c r="C89" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D89" s="3">
         <v>4</v>
@@ -3784,21 +3842,21 @@
         <v>16</v>
       </c>
       <c r="F89" s="5">
-        <v>45824</v>
+        <v>45793</v>
       </c>
       <c r="G89" s="3">
-        <v>1083.1397999999999</v>
+        <v>733.34569999999997</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
-        <v>77.791625999999994</v>
+        <v>73.128426000000005</v>
       </c>
       <c r="B90" s="3">
         <v>2025</v>
       </c>
       <c r="C90" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D90" s="3">
         <v>5</v>
@@ -3807,21 +3865,21 @@
         <v>21</v>
       </c>
       <c r="F90" s="5">
-        <v>45829</v>
+        <v>45798</v>
       </c>
       <c r="G90" s="3">
-        <v>1160.9313999999999</v>
+        <v>806.47410000000002</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
-        <v>36.81955</v>
+        <v>50.314039999999999</v>
       </c>
       <c r="B91" s="3">
         <v>2025</v>
       </c>
       <c r="C91" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D91" s="3">
         <v>6</v>
@@ -3830,21 +3888,21 @@
         <v>26</v>
       </c>
       <c r="F91" s="5">
-        <v>45834</v>
+        <v>45803</v>
       </c>
       <c r="G91" s="3">
-        <v>1197.751</v>
+        <v>856.78814999999997</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
-        <v>57.959434999999999</v>
+        <v>56.4529</v>
       </c>
       <c r="B92" s="3">
         <v>2025</v>
       </c>
       <c r="C92" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D92" s="3">
         <v>1</v>
@@ -3853,21 +3911,21 @@
         <v>1</v>
       </c>
       <c r="F92" s="5">
-        <v>45839</v>
+        <v>45809</v>
       </c>
       <c r="G92" s="3">
-        <v>1255.7103</v>
+        <v>913.24099999999999</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
-        <v>46.852519999999998</v>
+        <v>77.087370000000007</v>
       </c>
       <c r="B93" s="3">
         <v>2025</v>
       </c>
       <c r="C93" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D93" s="3">
         <v>2</v>
@@ -3876,21 +3934,21 @@
         <v>6</v>
       </c>
       <c r="F93" s="5">
-        <v>45844</v>
+        <v>45814</v>
       </c>
       <c r="G93" s="3">
-        <v>1302.5628999999999</v>
+        <v>990.32839999999999</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
-        <v>33.046756999999999</v>
+        <v>52.885750000000002</v>
       </c>
       <c r="B94" s="3">
         <v>2025</v>
       </c>
       <c r="C94" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D94" s="3">
         <v>3</v>
@@ -3899,21 +3957,21 @@
         <v>11</v>
       </c>
       <c r="F94" s="5">
-        <v>45849</v>
+        <v>45819</v>
       </c>
       <c r="G94" s="3">
-        <v>1335.6096</v>
+        <v>1043.2140999999999</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
-        <v>26.622537999999999</v>
+        <v>39.925694</v>
       </c>
       <c r="B95" s="3">
         <v>2025</v>
       </c>
       <c r="C95" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D95" s="3">
         <v>4</v>
@@ -3922,21 +3980,21 @@
         <v>16</v>
       </c>
       <c r="F95" s="5">
-        <v>45854</v>
+        <v>45824</v>
       </c>
       <c r="G95" s="3">
-        <v>1362.2321999999999</v>
+        <v>1083.1398999999999</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
-        <v>49.471690000000002</v>
+        <v>77.791659999999993</v>
       </c>
       <c r="B96" s="3">
         <v>2025</v>
       </c>
       <c r="C96" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D96" s="3">
         <v>5</v>
@@ -3945,21 +4003,21 @@
         <v>21</v>
       </c>
       <c r="F96" s="5">
-        <v>45859</v>
+        <v>45829</v>
       </c>
       <c r="G96" s="3">
-        <v>1411.7039</v>
+        <v>1160.9314999999999</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
-        <v>50.246704000000001</v>
+        <v>36.81955</v>
       </c>
       <c r="B97" s="3">
         <v>2025</v>
       </c>
       <c r="C97" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D97" s="3">
         <v>6</v>
@@ -3968,21 +4026,21 @@
         <v>26</v>
       </c>
       <c r="F97" s="5">
-        <v>45864</v>
+        <v>45834</v>
       </c>
       <c r="G97" s="3">
-        <v>1461.9505999999999</v>
+        <v>1197.7511</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
-        <v>65.807159999999996</v>
+        <v>57.959408000000003</v>
       </c>
       <c r="B98" s="3">
         <v>2025</v>
       </c>
       <c r="C98" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D98" s="3">
         <v>1</v>
@@ -3991,21 +4049,21 @@
         <v>1</v>
       </c>
       <c r="F98" s="5">
-        <v>45870</v>
+        <v>45839</v>
       </c>
       <c r="G98" s="3">
-        <v>1527.7577000000001</v>
+        <v>1255.7103999999999</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
-        <v>19.735720000000001</v>
+        <v>46.852511999999997</v>
       </c>
       <c r="B99" s="3">
         <v>2025</v>
       </c>
       <c r="C99" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D99" s="3">
         <v>2</v>
@@ -4014,21 +4072,21 @@
         <v>6</v>
       </c>
       <c r="F99" s="5">
-        <v>45875</v>
+        <v>45844</v>
       </c>
       <c r="G99" s="3">
-        <v>1547.4934000000001</v>
+        <v>1302.5630000000001</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
-        <v>53.463833000000001</v>
+        <v>33.046745000000001</v>
       </c>
       <c r="B100" s="3">
         <v>2025</v>
       </c>
       <c r="C100" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D100" s="3">
         <v>3</v>
@@ -4037,21 +4095,21 @@
         <v>11</v>
       </c>
       <c r="F100" s="5">
-        <v>45880</v>
+        <v>45849</v>
       </c>
       <c r="G100" s="3">
-        <v>1600.9573</v>
+        <v>1335.6097</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
-        <v>45.599589999999999</v>
+        <v>26.622522</v>
       </c>
       <c r="B101" s="3">
         <v>2025</v>
       </c>
       <c r="C101" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D101" s="3">
         <v>4</v>
@@ -4060,21 +4118,21 @@
         <v>16</v>
       </c>
       <c r="F101" s="5">
-        <v>45885</v>
+        <v>45854</v>
       </c>
       <c r="G101" s="3">
-        <v>1646.5569</v>
+        <v>1362.2322999999999</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
-        <v>47.053730000000002</v>
+        <v>49.471679999999999</v>
       </c>
       <c r="B102" s="3">
         <v>2025</v>
       </c>
       <c r="C102" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D102" s="3">
         <v>5</v>
@@ -4083,21 +4141,21 @@
         <v>21</v>
       </c>
       <c r="F102" s="5">
-        <v>45890</v>
+        <v>45859</v>
       </c>
       <c r="G102" s="3">
-        <v>1693.6106</v>
+        <v>1411.704</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
-        <v>63.832836</v>
+        <v>50.246727</v>
       </c>
       <c r="B103" s="3">
         <v>2025</v>
       </c>
       <c r="C103" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D103" s="3">
         <v>6</v>
@@ -4106,21 +4164,21 @@
         <v>26</v>
       </c>
       <c r="F103" s="5">
-        <v>45895</v>
+        <v>45864</v>
       </c>
       <c r="G103" s="3">
-        <v>1757.4435000000001</v>
+        <v>1461.9507000000001</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
-        <v>50.112952999999997</v>
+        <v>65.807190000000006</v>
       </c>
       <c r="B104" s="3">
         <v>2025</v>
       </c>
       <c r="C104" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D104" s="3">
         <v>1</v>
@@ -4129,21 +4187,21 @@
         <v>1</v>
       </c>
       <c r="F104" s="5">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="G104" s="3">
-        <v>1807.5563999999999</v>
+        <v>1527.7578000000001</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
-        <v>39.404277999999998</v>
+        <v>19.735703999999998</v>
       </c>
       <c r="B105" s="3">
         <v>2025</v>
       </c>
       <c r="C105" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D105" s="3">
         <v>2</v>
@@ -4152,21 +4210,21 @@
         <v>6</v>
       </c>
       <c r="F105" s="5">
-        <v>45906</v>
+        <v>45875</v>
       </c>
       <c r="G105" s="3">
-        <v>1846.9607000000001</v>
+        <v>1547.4935</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
-        <v>57.028472999999998</v>
+        <v>53.463810000000002</v>
       </c>
       <c r="B106" s="3">
         <v>2025</v>
       </c>
       <c r="C106" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D106" s="3">
         <v>3</v>
@@ -4175,21 +4233,21 @@
         <v>11</v>
       </c>
       <c r="F106" s="5">
-        <v>45911</v>
+        <v>45880</v>
       </c>
       <c r="G106" s="3">
-        <v>1903.9891</v>
+        <v>1600.9574</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
-        <v>52.184063000000002</v>
+        <v>45.599580000000003</v>
       </c>
       <c r="B107" s="3">
         <v>2025</v>
       </c>
       <c r="C107" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D107" s="3">
         <v>4</v>
@@ -4198,21 +4256,21 @@
         <v>16</v>
       </c>
       <c r="F107" s="5">
-        <v>45916</v>
+        <v>45885</v>
       </c>
       <c r="G107" s="3">
-        <v>1956.1732</v>
+        <v>1646.5569</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
-        <v>59.124560000000002</v>
+        <v>47.053714999999997</v>
       </c>
       <c r="B108" s="3">
         <v>2025</v>
       </c>
       <c r="C108" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D108" s="3">
         <v>5</v>
@@ -4221,21 +4279,21 @@
         <v>21</v>
       </c>
       <c r="F108" s="5">
-        <v>45921</v>
+        <v>45890</v>
       </c>
       <c r="G108" s="3">
-        <v>2015.2977000000001</v>
+        <v>1693.6107</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
-        <v>57.502459999999999</v>
+        <v>63.832892999999999</v>
       </c>
       <c r="B109" s="3">
         <v>2025</v>
       </c>
       <c r="C109" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D109" s="3">
         <v>6</v>
@@ -4244,21 +4302,21 @@
         <v>26</v>
       </c>
       <c r="F109" s="5">
-        <v>45926</v>
+        <v>45895</v>
       </c>
       <c r="G109" s="3">
-        <v>2072.8002999999999</v>
+        <v>1757.4436000000001</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="3">
-        <v>14.331683999999999</v>
+        <v>50.112946000000001</v>
       </c>
       <c r="B110" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C110" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D110" s="3">
         <v>1</v>
@@ -4267,21 +4325,21 @@
         <v>1</v>
       </c>
       <c r="F110" s="5">
-        <v>45658</v>
+        <v>45901</v>
       </c>
       <c r="G110" s="3">
-        <v>14.331683999999999</v>
+        <v>1807.5564999999999</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
-        <v>14.56471</v>
+        <v>39.404266</v>
       </c>
       <c r="B111" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C111" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D111" s="3">
         <v>2</v>
@@ -4290,21 +4348,21 @@
         <v>6</v>
       </c>
       <c r="F111" s="5">
-        <v>45663</v>
+        <v>45906</v>
       </c>
       <c r="G111" s="3">
-        <v>28.896393</v>
+        <v>1846.9608000000001</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
-        <v>10.498047</v>
+        <v>57.028472999999998</v>
       </c>
       <c r="B112" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C112" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D112" s="3">
         <v>3</v>
@@ -4313,21 +4371,21 @@
         <v>11</v>
       </c>
       <c r="F112" s="5">
-        <v>45668</v>
+        <v>45911</v>
       </c>
       <c r="G112" s="3">
-        <v>39.394440000000003</v>
+        <v>1903.9893</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
-        <v>10.599316999999999</v>
+        <v>52.184063000000002</v>
       </c>
       <c r="B113" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C113" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D113" s="3">
         <v>4</v>
@@ -4336,21 +4394,21 @@
         <v>16</v>
       </c>
       <c r="F113" s="5">
-        <v>45673</v>
+        <v>45916</v>
       </c>
       <c r="G113" s="3">
-        <v>49.993760000000002</v>
+        <v>1956.1732999999999</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="3">
-        <v>9.7497159999999994</v>
+        <v>59.124554000000003</v>
       </c>
       <c r="B114" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C114" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D114" s="3">
         <v>5</v>
@@ -4359,21 +4417,21 @@
         <v>21</v>
       </c>
       <c r="F114" s="5">
-        <v>45678</v>
+        <v>45921</v>
       </c>
       <c r="G114" s="3">
-        <v>59.743473000000002</v>
+        <v>2015.2979</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
-        <v>8.0435789999999994</v>
+        <v>57.502471999999997</v>
       </c>
       <c r="B115" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C115" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D115" s="3">
         <v>6</v>
@@ -4382,21 +4440,21 @@
         <v>26</v>
       </c>
       <c r="F115" s="5">
-        <v>45683</v>
+        <v>45926</v>
       </c>
       <c r="G115" s="3">
-        <v>67.787049999999994</v>
+        <v>2072.8002999999999</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="3">
-        <v>8.4454689999999992</v>
+        <v>66.375119999999995</v>
       </c>
       <c r="B116" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C116" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D116" s="3">
         <v>1</v>
@@ -4405,21 +4463,21 @@
         <v>1</v>
       </c>
       <c r="F116" s="5">
-        <v>45689</v>
+        <v>45931</v>
       </c>
       <c r="G116" s="3">
-        <v>76.232519999999994</v>
+        <v>2139.1754999999998</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
-        <v>8.741695</v>
+        <v>55.810270000000003</v>
       </c>
       <c r="B117" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C117" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D117" s="3">
         <v>2</v>
@@ -4428,21 +4486,21 @@
         <v>6</v>
       </c>
       <c r="F117" s="5">
-        <v>45694</v>
+        <v>45936</v>
       </c>
       <c r="G117" s="3">
-        <v>84.974209999999999</v>
+        <v>2194.9856</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="3">
-        <v>9.2340560000000007</v>
+        <v>56.237290000000002</v>
       </c>
       <c r="B118" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C118" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D118" s="3">
         <v>3</v>
@@ -4451,21 +4509,21 @@
         <v>11</v>
       </c>
       <c r="F118" s="5">
-        <v>45699</v>
+        <v>45941</v>
       </c>
       <c r="G118" s="3">
-        <v>94.208275</v>
+        <v>2251.223</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="3">
-        <v>8.82179</v>
+        <v>76.687889999999996</v>
       </c>
       <c r="B119" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C119" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D119" s="3">
         <v>4</v>
@@ -4474,21 +4532,21 @@
         <v>16</v>
       </c>
       <c r="F119" s="5">
-        <v>45704</v>
+        <v>45946</v>
       </c>
       <c r="G119" s="3">
-        <v>103.03006000000001</v>
+        <v>2327.9110000000001</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" s="3">
-        <v>7.0881604999999999</v>
+        <v>70.924989999999994</v>
       </c>
       <c r="B120" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C120" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D120" s="3">
         <v>5</v>
@@ -4497,21 +4555,21 @@
         <v>21</v>
       </c>
       <c r="F120" s="5">
-        <v>45709</v>
+        <v>45951</v>
       </c>
       <c r="G120" s="3">
-        <v>110.118225</v>
+        <v>2398.8359999999998</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" s="3">
-        <v>5.2113990000000001</v>
+        <v>108.46411000000001</v>
       </c>
       <c r="B121" s="3">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C121" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D121" s="3">
         <v>6</v>
@@ -4520,21 +4578,21 @@
         <v>26</v>
       </c>
       <c r="F121" s="5">
-        <v>45714</v>
+        <v>45956</v>
       </c>
       <c r="G121" s="3">
-        <v>115.32962000000001</v>
+        <v>2507.3000000000002</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" s="3">
-        <v>9.0188430000000004</v>
+        <v>14.331683999999999</v>
       </c>
       <c r="B122" s="3">
         <v>1991</v>
       </c>
       <c r="C122" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D122" s="3">
         <v>1</v>
@@ -4543,21 +4601,21 @@
         <v>1</v>
       </c>
       <c r="F122" s="5">
-        <v>45717</v>
+        <v>45658</v>
       </c>
       <c r="G122" s="3">
-        <v>124.348465</v>
+        <v>14.331683999999999</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" s="3">
-        <v>6.5476146000000002</v>
+        <v>14.564731</v>
       </c>
       <c r="B123" s="3">
         <v>1991</v>
       </c>
       <c r="C123" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D123" s="3">
         <v>2</v>
@@ -4566,21 +4624,21 @@
         <v>6</v>
       </c>
       <c r="F123" s="5">
-        <v>45722</v>
+        <v>45663</v>
       </c>
       <c r="G123" s="3">
-        <v>130.89607000000001</v>
+        <v>28.896415999999999</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" s="3">
-        <v>7.5543930000000001</v>
+        <v>10.498049</v>
       </c>
       <c r="B124" s="3">
         <v>1991</v>
       </c>
       <c r="C124" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D124" s="3">
         <v>3</v>
@@ -4589,21 +4647,21 @@
         <v>11</v>
       </c>
       <c r="F124" s="5">
-        <v>45727</v>
+        <v>45668</v>
       </c>
       <c r="G124" s="3">
-        <v>138.45047</v>
+        <v>39.394463000000002</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" s="3">
-        <v>10.259205</v>
+        <v>10.599313</v>
       </c>
       <c r="B125" s="3">
         <v>1991</v>
       </c>
       <c r="C125" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D125" s="3">
         <v>4</v>
@@ -4612,21 +4670,21 @@
         <v>16</v>
       </c>
       <c r="F125" s="5">
-        <v>45732</v>
+        <v>45673</v>
       </c>
       <c r="G125" s="3">
-        <v>148.70966999999999</v>
+        <v>49.993774000000002</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="3">
-        <v>8.8252400000000009</v>
+        <v>9.7497159999999994</v>
       </c>
       <c r="B126" s="3">
         <v>1991</v>
       </c>
       <c r="C126" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D126" s="3">
         <v>5</v>
@@ -4635,21 +4693,21 @@
         <v>21</v>
       </c>
       <c r="F126" s="5">
-        <v>45737</v>
+        <v>45678</v>
       </c>
       <c r="G126" s="3">
-        <v>157.53491</v>
+        <v>59.743492000000003</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" s="3">
-        <v>11.316477000000001</v>
+        <v>8.0435770000000009</v>
       </c>
       <c r="B127" s="3">
         <v>1991</v>
       </c>
       <c r="C127" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D127" s="3">
         <v>6</v>
@@ -4658,21 +4716,21 @@
         <v>26</v>
       </c>
       <c r="F127" s="5">
-        <v>45742</v>
+        <v>45683</v>
       </c>
       <c r="G127" s="3">
-        <v>168.85140000000001</v>
+        <v>67.78707</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" s="3">
-        <v>13.784653</v>
+        <v>8.4454740000000008</v>
       </c>
       <c r="B128" s="3">
         <v>1991</v>
       </c>
       <c r="C128" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D128" s="3">
         <v>1</v>
@@ -4681,21 +4739,21 @@
         <v>1</v>
       </c>
       <c r="F128" s="5">
-        <v>45748</v>
+        <v>45689</v>
       </c>
       <c r="G128" s="3">
-        <v>182.63605000000001</v>
+        <v>76.232544000000004</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" s="3">
-        <v>18.133655999999998</v>
+        <v>8.7416970000000003</v>
       </c>
       <c r="B129" s="3">
         <v>1991</v>
       </c>
       <c r="C129" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D129" s="3">
         <v>2</v>
@@ -4704,21 +4762,21 @@
         <v>6</v>
       </c>
       <c r="F129" s="5">
-        <v>45753</v>
+        <v>45694</v>
       </c>
       <c r="G129" s="3">
-        <v>200.7697</v>
+        <v>84.974239999999995</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" s="3">
-        <v>14.012309</v>
+        <v>9.234057</v>
       </c>
       <c r="B130" s="3">
         <v>1991</v>
       </c>
       <c r="C130" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D130" s="3">
         <v>3</v>
@@ -4727,21 +4785,21 @@
         <v>11</v>
       </c>
       <c r="F130" s="5">
-        <v>45758</v>
+        <v>45699</v>
       </c>
       <c r="G130" s="3">
-        <v>214.78201000000001</v>
+        <v>94.208299999999994</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" s="3">
-        <v>16.865026</v>
+        <v>8.8217879999999997</v>
       </c>
       <c r="B131" s="3">
         <v>1991</v>
       </c>
       <c r="C131" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D131" s="3">
         <v>4</v>
@@ -4750,21 +4808,21 @@
         <v>16</v>
       </c>
       <c r="F131" s="5">
-        <v>45763</v>
+        <v>45704</v>
       </c>
       <c r="G131" s="3">
-        <v>231.64703</v>
+        <v>103.03008</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" s="3">
-        <v>32.86842</v>
+        <v>7.0881577</v>
       </c>
       <c r="B132" s="3">
         <v>1991</v>
       </c>
       <c r="C132" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D132" s="3">
         <v>5</v>
@@ -4773,21 +4831,21 @@
         <v>21</v>
       </c>
       <c r="F132" s="5">
-        <v>45768</v>
+        <v>45709</v>
       </c>
       <c r="G132" s="3">
-        <v>264.51544000000001</v>
+        <v>110.11824</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" s="3">
-        <v>42.111977000000003</v>
+        <v>5.2113975999999997</v>
       </c>
       <c r="B133" s="3">
         <v>1991</v>
       </c>
       <c r="C133" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D133" s="3">
         <v>6</v>
@@ -4796,21 +4854,21 @@
         <v>26</v>
       </c>
       <c r="F133" s="5">
-        <v>45773</v>
+        <v>45714</v>
       </c>
       <c r="G133" s="3">
-        <v>306.62743999999998</v>
+        <v>115.32964</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" s="3">
-        <v>42.059685000000002</v>
+        <v>9.0188410000000001</v>
       </c>
       <c r="B134" s="3">
         <v>1991</v>
       </c>
       <c r="C134" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D134" s="3">
         <v>1</v>
@@ -4819,21 +4877,21 @@
         <v>1</v>
       </c>
       <c r="F134" s="5">
-        <v>45778</v>
+        <v>45717</v>
       </c>
       <c r="G134" s="3">
-        <v>348.68713000000002</v>
+        <v>124.34848</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" s="3">
-        <v>45.601883000000001</v>
+        <v>6.5476109999999998</v>
       </c>
       <c r="B135" s="3">
         <v>1991</v>
       </c>
       <c r="C135" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D135" s="3">
         <v>2</v>
@@ -4842,21 +4900,21 @@
         <v>6</v>
       </c>
       <c r="F135" s="5">
-        <v>45783</v>
+        <v>45722</v>
       </c>
       <c r="G135" s="3">
-        <v>394.28899999999999</v>
+        <v>130.89608999999999</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" s="3">
-        <v>50.457782999999999</v>
+        <v>7.5543903999999999</v>
       </c>
       <c r="B136" s="3">
         <v>1991</v>
       </c>
       <c r="C136" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D136" s="3">
         <v>3</v>
@@ -4865,21 +4923,21 @@
         <v>11</v>
       </c>
       <c r="F136" s="5">
-        <v>45788</v>
+        <v>45727</v>
       </c>
       <c r="G136" s="3">
-        <v>444.74680000000001</v>
+        <v>138.45049</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" s="3">
-        <v>60.332332999999998</v>
+        <v>10.259204</v>
       </c>
       <c r="B137" s="3">
         <v>1991</v>
       </c>
       <c r="C137" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D137" s="3">
         <v>4</v>
@@ -4888,21 +4946,21 @@
         <v>16</v>
       </c>
       <c r="F137" s="5">
-        <v>45793</v>
+        <v>45732</v>
       </c>
       <c r="G137" s="3">
-        <v>505.07909999999998</v>
+        <v>148.70968999999999</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" s="3">
-        <v>55.695149999999998</v>
+        <v>8.8252439999999996</v>
       </c>
       <c r="B138" s="3">
         <v>1991</v>
       </c>
       <c r="C138" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D138" s="3">
         <v>5</v>
@@ -4911,21 +4969,21 @@
         <v>21</v>
       </c>
       <c r="F138" s="5">
-        <v>45798</v>
+        <v>45737</v>
       </c>
       <c r="G138" s="3">
-        <v>560.77430000000004</v>
+        <v>157.53493</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" s="3">
-        <v>70.140854000000004</v>
+        <v>11.316482000000001</v>
       </c>
       <c r="B139" s="3">
         <v>1991</v>
       </c>
       <c r="C139" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D139" s="3">
         <v>6</v>
@@ -4934,21 +4992,21 @@
         <v>26</v>
       </c>
       <c r="F139" s="5">
-        <v>45803</v>
+        <v>45742</v>
       </c>
       <c r="G139" s="3">
-        <v>630.91510000000005</v>
+        <v>168.85140999999999</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" s="3">
-        <v>53.365290000000002</v>
+        <v>13.784658</v>
       </c>
       <c r="B140" s="3">
         <v>1991</v>
       </c>
       <c r="C140" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D140" s="3">
         <v>1</v>
@@ -4957,21 +5015,21 @@
         <v>1</v>
       </c>
       <c r="F140" s="5">
-        <v>45809</v>
+        <v>45748</v>
       </c>
       <c r="G140" s="3">
-        <v>684.28039999999999</v>
+        <v>182.63607999999999</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" s="3">
-        <v>50.324066000000002</v>
+        <v>18.13364</v>
       </c>
       <c r="B141" s="3">
         <v>1991</v>
       </c>
       <c r="C141" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D141" s="3">
         <v>2</v>
@@ -4980,21 +5038,21 @@
         <v>6</v>
       </c>
       <c r="F141" s="5">
-        <v>45814</v>
+        <v>45753</v>
       </c>
       <c r="G141" s="3">
-        <v>734.60450000000003</v>
+        <v>200.76971</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" s="3">
-        <v>54.202564000000002</v>
+        <v>14.012308000000001</v>
       </c>
       <c r="B142" s="3">
         <v>1991</v>
       </c>
       <c r="C142" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D142" s="3">
         <v>3</v>
@@ -5003,21 +5061,21 @@
         <v>11</v>
       </c>
       <c r="F142" s="5">
-        <v>45819</v>
+        <v>45758</v>
       </c>
       <c r="G142" s="3">
-        <v>788.80700000000002</v>
+        <v>214.78201000000001</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" s="3">
-        <v>52.986739999999998</v>
+        <v>16.865030000000001</v>
       </c>
       <c r="B143" s="3">
         <v>1991</v>
       </c>
       <c r="C143" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D143" s="3">
         <v>4</v>
@@ -5026,21 +5084,21 @@
         <v>16</v>
       </c>
       <c r="F143" s="5">
-        <v>45824</v>
+        <v>45763</v>
       </c>
       <c r="G143" s="3">
-        <v>841.79376000000002</v>
+        <v>231.64705000000001</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" s="3">
-        <v>54.639823999999997</v>
+        <v>32.868423</v>
       </c>
       <c r="B144" s="3">
         <v>1991</v>
       </c>
       <c r="C144" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D144" s="3">
         <v>5</v>
@@ -5049,21 +5107,21 @@
         <v>21</v>
       </c>
       <c r="F144" s="5">
-        <v>45829</v>
+        <v>45768</v>
       </c>
       <c r="G144" s="3">
-        <v>896.43359999999996</v>
+        <v>264.51546999999999</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" s="3">
-        <v>53.125689999999999</v>
+        <v>42.111977000000003</v>
       </c>
       <c r="B145" s="3">
         <v>1991</v>
       </c>
       <c r="C145" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D145" s="3">
         <v>6</v>
@@ -5072,21 +5130,21 @@
         <v>26</v>
       </c>
       <c r="F145" s="5">
-        <v>45834</v>
+        <v>45773</v>
       </c>
       <c r="G145" s="3">
-        <v>949.55926999999997</v>
+        <v>306.62743999999998</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" s="3">
-        <v>46.782573999999997</v>
+        <v>42.059672999999997</v>
       </c>
       <c r="B146" s="3">
         <v>1991</v>
       </c>
       <c r="C146" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D146" s="3">
         <v>1</v>
@@ -5095,21 +5153,21 @@
         <v>1</v>
       </c>
       <c r="F146" s="5">
-        <v>45839</v>
+        <v>45778</v>
       </c>
       <c r="G146" s="3">
-        <v>996.34186</v>
+        <v>348.68713000000002</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" s="3">
-        <v>47.738422</v>
+        <v>45.601909999999997</v>
       </c>
       <c r="B147" s="3">
         <v>1991</v>
       </c>
       <c r="C147" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D147" s="3">
         <v>2</v>
@@ -5118,21 +5176,21 @@
         <v>6</v>
       </c>
       <c r="F147" s="5">
-        <v>45844</v>
+        <v>45783</v>
       </c>
       <c r="G147" s="3">
-        <v>1044.0803000000001</v>
+        <v>394.28903000000003</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" s="3">
-        <v>48.982067000000001</v>
+        <v>50.457825</v>
       </c>
       <c r="B148" s="3">
         <v>1991</v>
       </c>
       <c r="C148" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D148" s="3">
         <v>3</v>
@@ -5141,21 +5199,21 @@
         <v>11</v>
       </c>
       <c r="F148" s="5">
-        <v>45849</v>
+        <v>45788</v>
       </c>
       <c r="G148" s="3">
-        <v>1093.0624</v>
+        <v>444.74686000000003</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" s="3">
-        <v>45.302653999999997</v>
+        <v>60.332355</v>
       </c>
       <c r="B149" s="3">
         <v>1991</v>
       </c>
       <c r="C149" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D149" s="3">
         <v>4</v>
@@ -5164,21 +5222,21 @@
         <v>16</v>
       </c>
       <c r="F149" s="5">
-        <v>45854</v>
+        <v>45793</v>
       </c>
       <c r="G149" s="3">
-        <v>1138.365</v>
+        <v>505.07922000000002</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" s="3">
-        <v>45.867170000000002</v>
+        <v>55.695160000000001</v>
       </c>
       <c r="B150" s="3">
         <v>1991</v>
       </c>
       <c r="C150" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D150" s="3">
         <v>5</v>
@@ -5187,21 +5245,21 @@
         <v>21</v>
       </c>
       <c r="F150" s="5">
-        <v>45859</v>
+        <v>45798</v>
       </c>
       <c r="G150" s="3">
-        <v>1184.2321999999999</v>
+        <v>560.77435000000003</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" s="3">
-        <v>62.54598</v>
+        <v>70.140879999999996</v>
       </c>
       <c r="B151" s="3">
         <v>1991</v>
       </c>
       <c r="C151" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D151" s="3">
         <v>6</v>
@@ -5210,21 +5268,21 @@
         <v>26</v>
       </c>
       <c r="F151" s="5">
-        <v>45864</v>
+        <v>45803</v>
       </c>
       <c r="G151" s="3">
-        <v>1246.7782</v>
+        <v>630.9153</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" s="3">
-        <v>45.043132999999997</v>
+        <v>53.365273000000002</v>
       </c>
       <c r="B152" s="3">
         <v>1991</v>
       </c>
       <c r="C152" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D152" s="3">
         <v>1</v>
@@ -5233,21 +5291,21 @@
         <v>1</v>
       </c>
       <c r="F152" s="5">
-        <v>45870</v>
+        <v>45809</v>
       </c>
       <c r="G152" s="3">
-        <v>1291.8213000000001</v>
+        <v>684.28049999999996</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" s="3">
-        <v>53.149116999999997</v>
+        <v>50.324043000000003</v>
       </c>
       <c r="B153" s="3">
         <v>1991</v>
       </c>
       <c r="C153" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D153" s="3">
         <v>2</v>
@@ -5256,21 +5314,21 @@
         <v>6</v>
       </c>
       <c r="F153" s="5">
-        <v>45875</v>
+        <v>45814</v>
       </c>
       <c r="G153" s="3">
-        <v>1344.9704999999999</v>
+        <v>734.60455000000002</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" s="3">
-        <v>55.673830000000002</v>
+        <v>54.202570000000001</v>
       </c>
       <c r="B154" s="3">
         <v>1991</v>
       </c>
       <c r="C154" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D154" s="3">
         <v>3</v>
@@ -5279,21 +5337,21 @@
         <v>11</v>
       </c>
       <c r="F154" s="5">
-        <v>45880</v>
+        <v>45819</v>
       </c>
       <c r="G154" s="3">
-        <v>1400.6442999999999</v>
+        <v>788.80709999999999</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" s="3">
-        <v>51.891243000000003</v>
+        <v>52.986744000000002</v>
       </c>
       <c r="B155" s="3">
         <v>1991</v>
       </c>
       <c r="C155" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D155" s="3">
         <v>4</v>
@@ -5302,21 +5360,21 @@
         <v>16</v>
       </c>
       <c r="F155" s="5">
-        <v>45885</v>
+        <v>45824</v>
       </c>
       <c r="G155" s="3">
-        <v>1452.5355</v>
+        <v>841.79390000000001</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" s="3">
-        <v>55.258389999999999</v>
+        <v>54.639809999999997</v>
       </c>
       <c r="B156" s="3">
         <v>1991</v>
       </c>
       <c r="C156" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D156" s="3">
         <v>5</v>
@@ -5325,21 +5383,21 @@
         <v>21</v>
       </c>
       <c r="F156" s="5">
-        <v>45890</v>
+        <v>45829</v>
       </c>
       <c r="G156" s="3">
-        <v>1507.7937999999999</v>
+        <v>896.43370000000004</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" s="3">
-        <v>65.58399</v>
+        <v>53.125706000000001</v>
       </c>
       <c r="B157" s="3">
         <v>1991</v>
       </c>
       <c r="C157" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D157" s="3">
         <v>6</v>
@@ -5348,21 +5406,21 @@
         <v>26</v>
       </c>
       <c r="F157" s="5">
-        <v>45895</v>
+        <v>45834</v>
       </c>
       <c r="G157" s="3">
-        <v>1573.3778</v>
+        <v>949.55939999999998</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" s="3">
-        <v>54.274096999999998</v>
+        <v>46.782597000000003</v>
       </c>
       <c r="B158" s="3">
         <v>1991</v>
       </c>
       <c r="C158" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D158" s="3">
         <v>1</v>
@@ -5371,21 +5429,21 @@
         <v>1</v>
       </c>
       <c r="F158" s="5">
-        <v>45901</v>
+        <v>45839</v>
       </c>
       <c r="G158" s="3">
-        <v>1627.652</v>
+        <v>996.34199999999998</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" s="3">
-        <v>54.068072999999998</v>
+        <v>47.738444999999999</v>
       </c>
       <c r="B159" s="3">
         <v>1991</v>
       </c>
       <c r="C159" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D159" s="3">
         <v>2</v>
@@ -5394,21 +5452,21 @@
         <v>6</v>
       </c>
       <c r="F159" s="5">
-        <v>45906</v>
+        <v>45844</v>
       </c>
       <c r="G159" s="3">
-        <v>1681.72</v>
+        <v>1044.0804000000001</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" s="3">
-        <v>62.027008000000002</v>
+        <v>48.982050000000001</v>
       </c>
       <c r="B160" s="3">
         <v>1991</v>
       </c>
       <c r="C160" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D160" s="3">
         <v>3</v>
@@ -5417,21 +5475,21 @@
         <v>11</v>
       </c>
       <c r="F160" s="5">
-        <v>45911</v>
+        <v>45849</v>
       </c>
       <c r="G160" s="3">
-        <v>1743.7471</v>
+        <v>1093.0625</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" s="3">
-        <v>60.091434</v>
+        <v>45.302666000000002</v>
       </c>
       <c r="B161" s="3">
         <v>1991</v>
       </c>
       <c r="C161" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D161" s="3">
         <v>4</v>
@@ -5440,21 +5498,21 @@
         <v>16</v>
       </c>
       <c r="F161" s="5">
-        <v>45916</v>
+        <v>45854</v>
       </c>
       <c r="G161" s="3">
-        <v>1803.8385000000001</v>
+        <v>1138.3651</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" s="3">
-        <v>61.807850000000002</v>
+        <v>45.867165</v>
       </c>
       <c r="B162" s="3">
         <v>1991</v>
       </c>
       <c r="C162" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D162" s="3">
         <v>5</v>
@@ -5463,21 +5521,21 @@
         <v>21</v>
       </c>
       <c r="F162" s="5">
-        <v>45921</v>
+        <v>45859</v>
       </c>
       <c r="G162" s="3">
-        <v>1865.6464000000001</v>
+        <v>1184.2322999999999</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" s="3">
-        <v>60.098236</v>
+        <v>62.545997999999997</v>
       </c>
       <c r="B163" s="3">
         <v>1991</v>
       </c>
       <c r="C163" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D163" s="3">
         <v>6</v>
@@ -5486,97 +5544,457 @@
         <v>26</v>
       </c>
       <c r="F163" s="5">
+        <v>45864</v>
+      </c>
+      <c r="G163" s="3">
+        <v>1246.7782999999999</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A164" s="3">
+        <v>45.043163</v>
+      </c>
+      <c r="B164" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C164" s="3">
+        <v>8</v>
+      </c>
+      <c r="D164" s="3">
+        <v>1</v>
+      </c>
+      <c r="E164" s="3">
+        <v>1</v>
+      </c>
+      <c r="F164" s="5">
+        <v>45870</v>
+      </c>
+      <c r="G164" s="3">
+        <v>1291.8215</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A165" s="3">
+        <v>53.149127999999997</v>
+      </c>
+      <c r="B165" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C165" s="3">
+        <v>8</v>
+      </c>
+      <c r="D165" s="3">
+        <v>2</v>
+      </c>
+      <c r="E165" s="3">
+        <v>6</v>
+      </c>
+      <c r="F165" s="5">
+        <v>45875</v>
+      </c>
+      <c r="G165" s="3">
+        <v>1344.9706000000001</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A166" s="3">
+        <v>55.673817</v>
+      </c>
+      <c r="B166" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C166" s="3">
+        <v>8</v>
+      </c>
+      <c r="D166" s="3">
+        <v>3</v>
+      </c>
+      <c r="E166" s="3">
+        <v>11</v>
+      </c>
+      <c r="F166" s="5">
+        <v>45880</v>
+      </c>
+      <c r="G166" s="3">
+        <v>1400.6443999999999</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A167" s="3">
+        <v>51.891243000000003</v>
+      </c>
+      <c r="B167" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C167" s="3">
+        <v>8</v>
+      </c>
+      <c r="D167" s="3">
+        <v>4</v>
+      </c>
+      <c r="E167" s="3">
+        <v>16</v>
+      </c>
+      <c r="F167" s="5">
+        <v>45885</v>
+      </c>
+      <c r="G167" s="3">
+        <v>1452.5355999999999</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A168" s="3">
+        <v>55.258395999999998</v>
+      </c>
+      <c r="B168" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C168" s="3">
+        <v>8</v>
+      </c>
+      <c r="D168" s="3">
+        <v>5</v>
+      </c>
+      <c r="E168" s="3">
+        <v>21</v>
+      </c>
+      <c r="F168" s="5">
+        <v>45890</v>
+      </c>
+      <c r="G168" s="3">
+        <v>1507.7941000000001</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A169" s="3">
+        <v>65.583979999999997</v>
+      </c>
+      <c r="B169" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C169" s="3">
+        <v>8</v>
+      </c>
+      <c r="D169" s="3">
+        <v>6</v>
+      </c>
+      <c r="E169" s="3">
+        <v>26</v>
+      </c>
+      <c r="F169" s="5">
+        <v>45895</v>
+      </c>
+      <c r="G169" s="3">
+        <v>1573.3779999999999</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A170" s="3">
+        <v>54.274093999999998</v>
+      </c>
+      <c r="B170" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C170" s="3">
+        <v>9</v>
+      </c>
+      <c r="D170" s="3">
+        <v>1</v>
+      </c>
+      <c r="E170" s="3">
+        <v>1</v>
+      </c>
+      <c r="F170" s="5">
+        <v>45901</v>
+      </c>
+      <c r="G170" s="3">
+        <v>1627.6521</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A171" s="3">
+        <v>54.068080000000002</v>
+      </c>
+      <c r="B171" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C171" s="3">
+        <v>9</v>
+      </c>
+      <c r="D171" s="3">
+        <v>2</v>
+      </c>
+      <c r="E171" s="3">
+        <v>6</v>
+      </c>
+      <c r="F171" s="5">
+        <v>45906</v>
+      </c>
+      <c r="G171" s="3">
+        <v>1681.7202</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A172" s="3">
+        <v>62.02702</v>
+      </c>
+      <c r="B172" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C172" s="3">
+        <v>9</v>
+      </c>
+      <c r="D172" s="3">
+        <v>3</v>
+      </c>
+      <c r="E172" s="3">
+        <v>11</v>
+      </c>
+      <c r="F172" s="5">
+        <v>45911</v>
+      </c>
+      <c r="G172" s="3">
+        <v>1743.7472</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A173" s="3">
+        <v>60.091414999999998</v>
+      </c>
+      <c r="B173" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C173" s="3">
+        <v>9</v>
+      </c>
+      <c r="D173" s="3">
+        <v>4</v>
+      </c>
+      <c r="E173" s="3">
+        <v>16</v>
+      </c>
+      <c r="F173" s="5">
+        <v>45916</v>
+      </c>
+      <c r="G173" s="3">
+        <v>1803.8386</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A174" s="3">
+        <v>61.807834999999997</v>
+      </c>
+      <c r="B174" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C174" s="3">
+        <v>9</v>
+      </c>
+      <c r="D174" s="3">
+        <v>5</v>
+      </c>
+      <c r="E174" s="3">
+        <v>21</v>
+      </c>
+      <c r="F174" s="5">
+        <v>45921</v>
+      </c>
+      <c r="G174" s="3">
+        <v>1865.6465000000001</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A175" s="3">
+        <v>60.098210000000002</v>
+      </c>
+      <c r="B175" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C175" s="3">
+        <v>9</v>
+      </c>
+      <c r="D175" s="3">
+        <v>6</v>
+      </c>
+      <c r="E175" s="3">
+        <v>26</v>
+      </c>
+      <c r="F175" s="5">
         <v>45926</v>
       </c>
-      <c r="G163" s="3">
-        <v>1925.7445</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F164" s="5"/>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F165" s="5"/>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F166" s="5"/>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F167" s="5"/>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F168" s="5"/>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F169" s="5"/>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F170" s="5"/>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F171" s="5"/>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F172" s="5"/>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F173" s="5"/>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F174" s="5"/>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F175" s="5"/>
+      <c r="G175" s="3">
+        <v>1925.7447999999999</v>
+      </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F176" s="5"/>
-    </row>
-    <row r="177" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F177" s="5"/>
-    </row>
-    <row r="178" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F178" s="5"/>
-    </row>
-    <row r="179" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F179" s="5"/>
-    </row>
-    <row r="180" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F180" s="5"/>
-    </row>
-    <row r="181" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F181" s="5"/>
-    </row>
-    <row r="182" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="A176" s="3">
+        <v>58.112094999999997</v>
+      </c>
+      <c r="B176" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C176" s="3">
+        <v>10</v>
+      </c>
+      <c r="D176" s="3">
+        <v>1</v>
+      </c>
+      <c r="E176" s="3">
+        <v>1</v>
+      </c>
+      <c r="F176" s="5">
+        <v>45931</v>
+      </c>
+      <c r="G176" s="3">
+        <v>1983.8568</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A177" s="3">
+        <v>65.605896000000001</v>
+      </c>
+      <c r="B177" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C177" s="3">
+        <v>10</v>
+      </c>
+      <c r="D177" s="3">
+        <v>2</v>
+      </c>
+      <c r="E177" s="3">
+        <v>6</v>
+      </c>
+      <c r="F177" s="5">
+        <v>45936</v>
+      </c>
+      <c r="G177" s="3">
+        <v>2049.4625999999998</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A178" s="3">
+        <v>70.510800000000003</v>
+      </c>
+      <c r="B178" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C178" s="3">
+        <v>10</v>
+      </c>
+      <c r="D178" s="3">
+        <v>3</v>
+      </c>
+      <c r="E178" s="3">
+        <v>11</v>
+      </c>
+      <c r="F178" s="5">
+        <v>45941</v>
+      </c>
+      <c r="G178" s="3">
+        <v>2119.9733999999999</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A179" s="3">
+        <v>66.483153999999999</v>
+      </c>
+      <c r="B179" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C179" s="3">
+        <v>10</v>
+      </c>
+      <c r="D179" s="3">
+        <v>4</v>
+      </c>
+      <c r="E179" s="3">
+        <v>16</v>
+      </c>
+      <c r="F179" s="5">
+        <v>45946</v>
+      </c>
+      <c r="G179" s="3">
+        <v>2186.4564999999998</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A180" s="3">
+        <v>68.955246000000002</v>
+      </c>
+      <c r="B180" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C180" s="3">
+        <v>10</v>
+      </c>
+      <c r="D180" s="3">
+        <v>5</v>
+      </c>
+      <c r="E180" s="3">
+        <v>21</v>
+      </c>
+      <c r="F180" s="5">
+        <v>45951</v>
+      </c>
+      <c r="G180" s="3">
+        <v>2255.4119000000001</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A181" s="3">
+        <v>79.380849999999995</v>
+      </c>
+      <c r="B181" s="3">
+        <v>1991</v>
+      </c>
+      <c r="C181" s="3">
+        <v>10</v>
+      </c>
+      <c r="D181" s="3">
+        <v>6</v>
+      </c>
+      <c r="E181" s="3">
+        <v>26</v>
+      </c>
+      <c r="F181" s="5">
+        <v>45956</v>
+      </c>
+      <c r="G181" s="3">
+        <v>2334.7927</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F182" s="5"/>
     </row>
-    <row r="183" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F183" s="5"/>
     </row>
-    <row r="184" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F184" s="5"/>
     </row>
-    <row r="185" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F185" s="5"/>
     </row>
-    <row r="186" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F186" s="5"/>
     </row>
-    <row r="187" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F187" s="5"/>
     </row>
-    <row r="188" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F188" s="5"/>
     </row>
-    <row r="189" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F189" s="5"/>
     </row>
-    <row r="190" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F190" s="5"/>
     </row>
-    <row r="191" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F191" s="5"/>
     </row>
-    <row r="192" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F192" s="5"/>
     </row>
     <row r="193" spans="6:6" x14ac:dyDescent="0.3">
@@ -5661,7 +6079,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FB690C8-F874-4A1B-874A-043689354636}">
-  <dimension ref="A1:D406"/>
+  <dimension ref="A1:D451"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -10097,13 +10515,13 @@
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" s="1">
-        <v>433.01137999999997</v>
+        <v>222.29355000000001</v>
       </c>
       <c r="B317" s="1">
-        <v>2010</v>
+        <v>1997</v>
       </c>
       <c r="C317" s="1">
-        <v>106.41168</v>
+        <v>-104.30615</v>
       </c>
       <c r="D317" s="1" t="s">
         <v>21</v>
@@ -10111,13 +10529,13 @@
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" s="1">
-        <v>416.49036000000001</v>
+        <v>240.60686000000001</v>
       </c>
       <c r="B318" s="1">
-        <v>1988</v>
+        <v>1982</v>
       </c>
       <c r="C318" s="1">
-        <v>89.890656000000007</v>
+        <v>-85.992840000000001</v>
       </c>
       <c r="D318" s="1" t="s">
         <v>21</v>
@@ -10125,13 +10543,13 @@
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" s="1">
-        <v>403.6705</v>
+        <v>241.50899000000001</v>
       </c>
       <c r="B319" s="1">
-        <v>1999</v>
+        <v>2015</v>
       </c>
       <c r="C319" s="1">
-        <v>77.070800000000006</v>
+        <v>-85.090710000000001</v>
       </c>
       <c r="D319" s="1" t="s">
         <v>21</v>
@@ -10139,13 +10557,13 @@
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" s="1">
-        <v>394.81130000000002</v>
+        <v>241.63086000000001</v>
       </c>
       <c r="B320" s="1">
-        <v>1984</v>
+        <v>2018</v>
       </c>
       <c r="C320" s="1">
-        <v>68.211609999999993</v>
+        <v>-84.96884</v>
       </c>
       <c r="D320" s="1" t="s">
         <v>21</v>
@@ -10153,13 +10571,13 @@
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" s="1">
-        <v>383.18975999999998</v>
+        <v>256.55040000000002</v>
       </c>
       <c r="B321" s="1">
-        <v>2005</v>
+        <v>2023</v>
       </c>
       <c r="C321" s="1">
-        <v>56.590057000000002</v>
+        <v>-70.049285999999995</v>
       </c>
       <c r="D321" s="1" t="s">
         <v>21</v>
@@ -10167,13 +10585,13 @@
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" s="1">
-        <v>380.15839999999997</v>
+        <v>264.25006000000002</v>
       </c>
       <c r="B322" s="1">
-        <v>2007</v>
+        <v>1983</v>
       </c>
       <c r="C322" s="1">
-        <v>53.558684999999997</v>
+        <v>-62.349640000000001</v>
       </c>
       <c r="D322" s="1" t="s">
         <v>21</v>
@@ -10181,13 +10599,13 @@
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" s="1">
-        <v>366.12844999999999</v>
+        <v>286.34985</v>
       </c>
       <c r="B323" s="1">
-        <v>1981</v>
+        <v>2014</v>
       </c>
       <c r="C323" s="1">
-        <v>39.528748</v>
+        <v>-40.249847000000003</v>
       </c>
       <c r="D323" s="1" t="s">
         <v>21</v>
@@ -10195,13 +10613,13 @@
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" s="1">
-        <v>364.13904000000002</v>
+        <v>290.94515999999999</v>
       </c>
       <c r="B324" s="1">
-        <v>1990</v>
+        <v>2019</v>
       </c>
       <c r="C324" s="1">
-        <v>37.539337000000003</v>
+        <v>-35.654539999999997</v>
       </c>
       <c r="D324" s="1" t="s">
         <v>21</v>
@@ -10209,13 +10627,13 @@
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" s="1">
-        <v>362.57569999999998</v>
+        <v>295.49286000000001</v>
       </c>
       <c r="B325" s="1">
-        <v>1998</v>
+        <v>2025</v>
       </c>
       <c r="C325" s="1">
-        <v>35.976013000000002</v>
+        <v>-31.106842</v>
       </c>
       <c r="D325" s="1" t="s">
         <v>21</v>
@@ -10223,13 +10641,13 @@
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" s="1">
-        <v>357.01028000000002</v>
+        <v>306.65964000000002</v>
       </c>
       <c r="B326" s="1">
-        <v>1989</v>
+        <v>2012</v>
       </c>
       <c r="C326" s="1">
-        <v>30.410582999999999</v>
+        <v>-19.940062999999999</v>
       </c>
       <c r="D326" s="1" t="s">
         <v>21</v>
@@ -10237,13 +10655,13 @@
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" s="1">
-        <v>356.98083000000003</v>
+        <v>310.53924999999998</v>
       </c>
       <c r="B327" s="1">
-        <v>2002</v>
+        <v>1991</v>
       </c>
       <c r="C327" s="1">
-        <v>30.381133999999999</v>
+        <v>-16.060455000000001</v>
       </c>
       <c r="D327" s="1" t="s">
         <v>21</v>
@@ -10251,13 +10669,13 @@
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" s="1">
-        <v>353.67563000000001</v>
+        <v>311.61016999999998</v>
       </c>
       <c r="B328" s="1">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="C328" s="1">
-        <v>27.075928000000001</v>
+        <v>-14.989532000000001</v>
       </c>
       <c r="D328" s="1" t="s">
         <v>21</v>
@@ -10265,13 +10683,13 @@
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" s="1">
-        <v>350.06436000000002</v>
+        <v>313.14992999999998</v>
       </c>
       <c r="B329" s="1">
-        <v>2021</v>
+        <v>2011</v>
       </c>
       <c r="C329" s="1">
-        <v>23.464659999999999</v>
+        <v>-13.449768000000001</v>
       </c>
       <c r="D329" s="1" t="s">
         <v>21</v>
@@ -10279,13 +10697,13 @@
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" s="1">
-        <v>342.5412</v>
+        <v>315.4545</v>
       </c>
       <c r="B330" s="1">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="C330" s="1">
-        <v>15.941497999999999</v>
+        <v>-11.145203</v>
       </c>
       <c r="D330" s="1" t="s">
         <v>21</v>
@@ -10293,13 +10711,13 @@
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" s="1">
-        <v>340.01609999999999</v>
+        <v>318.54788000000002</v>
       </c>
       <c r="B331" s="1">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="C331" s="1">
-        <v>13.416411999999999</v>
+        <v>-8.0518190000000001</v>
       </c>
       <c r="D331" s="1" t="s">
         <v>21</v>
@@ -10307,13 +10725,13 @@
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" s="1">
-        <v>337.74810000000002</v>
+        <v>319.91144000000003</v>
       </c>
       <c r="B332" s="1">
-        <v>1987</v>
+        <v>2000</v>
       </c>
       <c r="C332" s="1">
-        <v>11.148407000000001</v>
+        <v>-6.6882630000000001</v>
       </c>
       <c r="D332" s="1" t="s">
         <v>21</v>
@@ -10321,13 +10739,13 @@
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" s="1">
-        <v>336.07641999999998</v>
+        <v>321.19556</v>
       </c>
       <c r="B333" s="1">
-        <v>2024</v>
+        <v>1986</v>
       </c>
       <c r="C333" s="1">
-        <v>9.4767150000000004</v>
+        <v>-5.4041442999999996</v>
       </c>
       <c r="D333" s="1" t="s">
         <v>21</v>
@@ -10335,13 +10753,13 @@
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" s="1">
-        <v>335.87862999999999</v>
+        <v>324.6728</v>
       </c>
       <c r="B334" s="1">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="C334" s="1">
-        <v>9.278931</v>
+        <v>-1.9269103999999999</v>
       </c>
       <c r="D334" s="1" t="s">
         <v>21</v>
@@ -10349,13 +10767,13 @@
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" s="1">
-        <v>332.50567999999998</v>
+        <v>325.13085999999998</v>
       </c>
       <c r="B335" s="1">
-        <v>2009</v>
+        <v>1993</v>
       </c>
       <c r="C335" s="1">
-        <v>5.9059752999999997</v>
+        <v>-1.4688416</v>
       </c>
       <c r="D335" s="1" t="s">
         <v>21</v>
@@ -10363,13 +10781,13 @@
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" s="1">
-        <v>332.46690000000001</v>
+        <v>325.44272000000001</v>
       </c>
       <c r="B336" s="1">
-        <v>2022</v>
+        <v>1985</v>
       </c>
       <c r="C336" s="1">
-        <v>5.8671875</v>
+        <v>-1.1569824</v>
       </c>
       <c r="D336" s="1" t="s">
         <v>21</v>
@@ -10377,13 +10795,13 @@
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A337" s="1">
-        <v>332.34440000000001</v>
+        <v>326.71697999999998</v>
       </c>
       <c r="B337" s="1">
-        <v>1996</v>
+        <v>2016</v>
       </c>
       <c r="C337" s="1">
-        <v>5.7446900000000003</v>
+        <v>0.11727905</v>
       </c>
       <c r="D337" s="1" t="s">
         <v>21</v>
@@ -10391,13 +10809,13 @@
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" s="1">
-        <v>329.17962999999997</v>
+        <v>327.99880000000002</v>
       </c>
       <c r="B338" s="1">
-        <v>2013</v>
+        <v>2006</v>
       </c>
       <c r="C338" s="1">
-        <v>2.5799254999999999</v>
+        <v>1.3991089000000001</v>
       </c>
       <c r="D338" s="1" t="s">
         <v>21</v>
@@ -10419,13 +10837,13 @@
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A340" s="1">
-        <v>327.99880000000002</v>
+        <v>329.17962999999997</v>
       </c>
       <c r="B340" s="1">
-        <v>2006</v>
+        <v>2013</v>
       </c>
       <c r="C340" s="1">
-        <v>1.3991089000000001</v>
+        <v>2.5799254999999999</v>
       </c>
       <c r="D340" s="1" t="s">
         <v>21</v>
@@ -10433,13 +10851,13 @@
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A341" s="1">
-        <v>326.71697999999998</v>
+        <v>332.34440000000001</v>
       </c>
       <c r="B341" s="1">
-        <v>2016</v>
+        <v>1996</v>
       </c>
       <c r="C341" s="1">
-        <v>0.11727905</v>
+        <v>5.7446900000000003</v>
       </c>
       <c r="D341" s="1" t="s">
         <v>21</v>
@@ -10447,13 +10865,13 @@
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A342" s="1">
-        <v>325.44272000000001</v>
+        <v>332.46690000000001</v>
       </c>
       <c r="B342" s="1">
-        <v>1985</v>
+        <v>2022</v>
       </c>
       <c r="C342" s="1">
-        <v>-1.1569824</v>
+        <v>5.8671875</v>
       </c>
       <c r="D342" s="1" t="s">
         <v>21</v>
@@ -10461,13 +10879,13 @@
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343" s="1">
-        <v>325.13085999999998</v>
+        <v>332.50567999999998</v>
       </c>
       <c r="B343" s="1">
-        <v>1993</v>
+        <v>2009</v>
       </c>
       <c r="C343" s="1">
-        <v>-1.4688416</v>
+        <v>5.9059752999999997</v>
       </c>
       <c r="D343" s="1" t="s">
         <v>21</v>
@@ -10475,13 +10893,13 @@
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" s="1">
-        <v>324.6728</v>
+        <v>335.87862999999999</v>
       </c>
       <c r="B344" s="1">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="C344" s="1">
-        <v>-1.9269103999999999</v>
+        <v>9.278931</v>
       </c>
       <c r="D344" s="1" t="s">
         <v>21</v>
@@ -10489,13 +10907,13 @@
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A345" s="1">
-        <v>321.19556</v>
+        <v>336.07641999999998</v>
       </c>
       <c r="B345" s="1">
-        <v>1986</v>
+        <v>2024</v>
       </c>
       <c r="C345" s="1">
-        <v>-5.4041442999999996</v>
+        <v>9.4767150000000004</v>
       </c>
       <c r="D345" s="1" t="s">
         <v>21</v>
@@ -10503,13 +10921,13 @@
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346" s="1">
-        <v>319.91144000000003</v>
+        <v>337.74810000000002</v>
       </c>
       <c r="B346" s="1">
-        <v>2000</v>
+        <v>1987</v>
       </c>
       <c r="C346" s="1">
-        <v>-6.6882630000000001</v>
+        <v>11.148407000000001</v>
       </c>
       <c r="D346" s="1" t="s">
         <v>21</v>
@@ -10517,13 +10935,13 @@
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347" s="1">
-        <v>318.54788000000002</v>
+        <v>340.01609999999999</v>
       </c>
       <c r="B347" s="1">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="C347" s="1">
-        <v>-8.0518190000000001</v>
+        <v>13.416411999999999</v>
       </c>
       <c r="D347" s="1" t="s">
         <v>21</v>
@@ -10531,13 +10949,13 @@
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A348" s="1">
-        <v>315.4545</v>
+        <v>342.5412</v>
       </c>
       <c r="B348" s="1">
-        <v>2004</v>
+        <v>2008</v>
       </c>
       <c r="C348" s="1">
-        <v>-11.145203</v>
+        <v>15.941497999999999</v>
       </c>
       <c r="D348" s="1" t="s">
         <v>21</v>
@@ -10545,13 +10963,13 @@
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A349" s="1">
-        <v>313.14992999999998</v>
+        <v>350.06436000000002</v>
       </c>
       <c r="B349" s="1">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="C349" s="1">
-        <v>-13.449768000000001</v>
+        <v>23.464659999999999</v>
       </c>
       <c r="D349" s="1" t="s">
         <v>21</v>
@@ -10559,13 +10977,13 @@
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" s="1">
-        <v>311.61016999999998</v>
+        <v>353.67563000000001</v>
       </c>
       <c r="B350" s="1">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="C350" s="1">
-        <v>-14.989532000000001</v>
+        <v>27.075928000000001</v>
       </c>
       <c r="D350" s="1" t="s">
         <v>21</v>
@@ -10573,13 +10991,13 @@
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" s="1">
-        <v>310.53924999999998</v>
+        <v>356.98083000000003</v>
       </c>
       <c r="B351" s="1">
-        <v>1991</v>
+        <v>2002</v>
       </c>
       <c r="C351" s="1">
-        <v>-16.060455000000001</v>
+        <v>30.381133999999999</v>
       </c>
       <c r="D351" s="1" t="s">
         <v>21</v>
@@ -10587,13 +11005,13 @@
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352" s="1">
-        <v>306.65964000000002</v>
+        <v>357.01028000000002</v>
       </c>
       <c r="B352" s="1">
-        <v>2012</v>
+        <v>1989</v>
       </c>
       <c r="C352" s="1">
-        <v>-19.940062999999999</v>
+        <v>30.410582999999999</v>
       </c>
       <c r="D352" s="1" t="s">
         <v>21</v>
@@ -10601,13 +11019,13 @@
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A353" s="1">
-        <v>295.49286000000001</v>
+        <v>362.57569999999998</v>
       </c>
       <c r="B353" s="1">
-        <v>2025</v>
+        <v>1998</v>
       </c>
       <c r="C353" s="1">
-        <v>-31.106842</v>
+        <v>35.976013000000002</v>
       </c>
       <c r="D353" s="1" t="s">
         <v>21</v>
@@ -10615,13 +11033,13 @@
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354" s="1">
-        <v>290.94515999999999</v>
+        <v>364.13904000000002</v>
       </c>
       <c r="B354" s="1">
-        <v>2019</v>
+        <v>1990</v>
       </c>
       <c r="C354" s="1">
-        <v>-35.654539999999997</v>
+        <v>37.539337000000003</v>
       </c>
       <c r="D354" s="1" t="s">
         <v>21</v>
@@ -10629,13 +11047,13 @@
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A355" s="1">
-        <v>286.34985</v>
+        <v>366.12844999999999</v>
       </c>
       <c r="B355" s="1">
-        <v>2014</v>
+        <v>1981</v>
       </c>
       <c r="C355" s="1">
-        <v>-40.249847000000003</v>
+        <v>39.528748</v>
       </c>
       <c r="D355" s="1" t="s">
         <v>21</v>
@@ -10643,13 +11061,13 @@
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A356" s="1">
-        <v>264.25006000000002</v>
+        <v>380.15839999999997</v>
       </c>
       <c r="B356" s="1">
-        <v>1983</v>
+        <v>2007</v>
       </c>
       <c r="C356" s="1">
-        <v>-62.349640000000001</v>
+        <v>53.558684999999997</v>
       </c>
       <c r="D356" s="1" t="s">
         <v>21</v>
@@ -10657,13 +11075,13 @@
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A357" s="1">
-        <v>256.55040000000002</v>
+        <v>383.18975999999998</v>
       </c>
       <c r="B357" s="1">
-        <v>2023</v>
+        <v>2005</v>
       </c>
       <c r="C357" s="1">
-        <v>-70.049285999999995</v>
+        <v>56.590057000000002</v>
       </c>
       <c r="D357" s="1" t="s">
         <v>21</v>
@@ -10671,13 +11089,13 @@
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A358" s="1">
-        <v>241.63086000000001</v>
+        <v>394.81130000000002</v>
       </c>
       <c r="B358" s="1">
-        <v>2018</v>
+        <v>1984</v>
       </c>
       <c r="C358" s="1">
-        <v>-84.96884</v>
+        <v>68.211609999999993</v>
       </c>
       <c r="D358" s="1" t="s">
         <v>21</v>
@@ -10685,13 +11103,13 @@
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A359" s="1">
-        <v>241.50899000000001</v>
+        <v>403.6705</v>
       </c>
       <c r="B359" s="1">
-        <v>2015</v>
+        <v>1999</v>
       </c>
       <c r="C359" s="1">
-        <v>-85.090710000000001</v>
+        <v>77.070800000000006</v>
       </c>
       <c r="D359" s="1" t="s">
         <v>21</v>
@@ -10699,13 +11117,13 @@
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A360" s="1">
-        <v>240.60686000000001</v>
+        <v>416.49036000000001</v>
       </c>
       <c r="B360" s="1">
-        <v>1982</v>
+        <v>1988</v>
       </c>
       <c r="C360" s="1">
-        <v>-85.992840000000001</v>
+        <v>89.890656000000007</v>
       </c>
       <c r="D360" s="1" t="s">
         <v>21</v>
@@ -10713,13 +11131,13 @@
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A361" s="1">
-        <v>222.29355000000001</v>
+        <v>433.01137999999997</v>
       </c>
       <c r="B361" s="1">
-        <v>1997</v>
+        <v>2010</v>
       </c>
       <c r="C361" s="1">
-        <v>-104.30615</v>
+        <v>106.41168</v>
       </c>
       <c r="D361" s="1" t="s">
         <v>21</v>
@@ -10727,13 +11145,13 @@
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A362" s="1">
-        <v>291.67657000000003</v>
+        <v>270.20287999999999</v>
       </c>
       <c r="B362" s="1">
-        <v>1981</v>
+        <v>2023</v>
       </c>
       <c r="C362" s="1">
-        <v>-60.690125000000002</v>
+        <v>-82.163820000000001</v>
       </c>
       <c r="D362" s="1" t="s">
         <v>22</v>
@@ -10741,13 +11159,13 @@
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A363" s="1">
-        <v>332.40949999999998</v>
+        <v>289.89614999999998</v>
       </c>
       <c r="B363" s="1">
-        <v>1982</v>
+        <v>2021</v>
       </c>
       <c r="C363" s="1">
-        <v>-19.957214</v>
+        <v>-62.470550000000003</v>
       </c>
       <c r="D363" s="1" t="s">
         <v>22</v>
@@ -10755,13 +11173,13 @@
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A364" s="1">
-        <v>384.92752000000002</v>
+        <v>291.67657000000003</v>
       </c>
       <c r="B364" s="1">
-        <v>1983</v>
+        <v>1981</v>
       </c>
       <c r="C364" s="1">
-        <v>32.56082</v>
+        <v>-60.690125000000002</v>
       </c>
       <c r="D364" s="1" t="s">
         <v>22</v>
@@ -10769,13 +11187,13 @@
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A365" s="1">
-        <v>381.66262999999998</v>
+        <v>292.10654</v>
       </c>
       <c r="B365" s="1">
-        <v>1984</v>
+        <v>2009</v>
       </c>
       <c r="C365" s="1">
-        <v>29.295929000000001</v>
+        <v>-60.260162000000001</v>
       </c>
       <c r="D365" s="1" t="s">
         <v>22</v>
@@ -10783,13 +11201,13 @@
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A366" s="1">
-        <v>336.99135999999999</v>
+        <v>296.12786999999997</v>
       </c>
       <c r="B366" s="1">
-        <v>1985</v>
+        <v>2012</v>
       </c>
       <c r="C366" s="1">
-        <v>-15.375336000000001</v>
+        <v>-56.23883</v>
       </c>
       <c r="D366" s="1" t="s">
         <v>22</v>
@@ -10797,13 +11215,13 @@
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A367" s="1">
-        <v>347.18155000000002</v>
+        <v>298.40906000000001</v>
       </c>
       <c r="B367" s="1">
-        <v>1986</v>
+        <v>2006</v>
       </c>
       <c r="C367" s="1">
-        <v>-5.1851500000000001</v>
+        <v>-53.957639999999998</v>
       </c>
       <c r="D367" s="1" t="s">
         <v>22</v>
@@ -10811,13 +11229,13 @@
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A368" s="1">
-        <v>331.07742000000002</v>
+        <v>298.6694</v>
       </c>
       <c r="B368" s="1">
-        <v>1987</v>
+        <v>2016</v>
       </c>
       <c r="C368" s="1">
-        <v>-21.289276000000001</v>
+        <v>-53.697296000000001</v>
       </c>
       <c r="D368" s="1" t="s">
         <v>22</v>
@@ -10825,13 +11243,13 @@
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A369" s="1">
-        <v>393.68340000000001</v>
+        <v>304.16595000000001</v>
       </c>
       <c r="B369" s="1">
-        <v>1988</v>
+        <v>2015</v>
       </c>
       <c r="C369" s="1">
-        <v>41.31671</v>
+        <v>-48.200744999999998</v>
       </c>
       <c r="D369" s="1" t="s">
         <v>22</v>
@@ -10839,13 +11257,13 @@
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A370" s="1">
-        <v>375.17043999999999</v>
+        <v>315.35678000000001</v>
       </c>
       <c r="B370" s="1">
-        <v>1989</v>
+        <v>2025</v>
       </c>
       <c r="C370" s="1">
-        <v>22.803740999999999</v>
+        <v>-37.009920000000001</v>
       </c>
       <c r="D370" s="1" t="s">
         <v>22</v>
@@ -10853,13 +11271,13 @@
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A371" s="1">
-        <v>355.55630000000002</v>
+        <v>321.73131999999998</v>
       </c>
       <c r="B371" s="1">
-        <v>1990</v>
+        <v>2022</v>
       </c>
       <c r="C371" s="1">
-        <v>3.1896057</v>
+        <v>-30.635376000000001</v>
       </c>
       <c r="D371" s="1" t="s">
         <v>22</v>
@@ -10867,13 +11285,13 @@
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A372" s="1">
-        <v>409.84793000000002</v>
+        <v>323.54962</v>
       </c>
       <c r="B372" s="1">
-        <v>1991</v>
+        <v>1998</v>
       </c>
       <c r="C372" s="1">
-        <v>57.481229999999996</v>
+        <v>-28.817077999999999</v>
       </c>
       <c r="D372" s="1" t="s">
         <v>22</v>
@@ -10881,13 +11299,13 @@
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A373" s="1">
-        <v>360.9649</v>
+        <v>326.94394</v>
       </c>
       <c r="B373" s="1">
-        <v>1992</v>
+        <v>2020</v>
       </c>
       <c r="C373" s="1">
-        <v>8.5982059999999993</v>
+        <v>-25.42276</v>
       </c>
       <c r="D373" s="1" t="s">
         <v>22</v>
@@ -10895,13 +11313,13 @@
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A374" s="1">
-        <v>426.98923000000002</v>
+        <v>331.07742000000002</v>
       </c>
       <c r="B374" s="1">
-        <v>1993</v>
+        <v>1987</v>
       </c>
       <c r="C374" s="1">
-        <v>74.622529999999998</v>
+        <v>-21.289276000000001</v>
       </c>
       <c r="D374" s="1" t="s">
         <v>22</v>
@@ -10909,13 +11327,13 @@
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A375" s="1">
-        <v>350.16793999999999</v>
+        <v>332.40949999999998</v>
       </c>
       <c r="B375" s="1">
-        <v>1994</v>
+        <v>1982</v>
       </c>
       <c r="C375" s="1">
-        <v>-2.1987610000000002</v>
+        <v>-19.957214</v>
       </c>
       <c r="D375" s="1" t="s">
         <v>22</v>
@@ -10923,13 +11341,13 @@
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A376" s="1">
-        <v>356.41604999999998</v>
+        <v>334.85915999999997</v>
       </c>
       <c r="B376" s="1">
-        <v>1995</v>
+        <v>2011</v>
       </c>
       <c r="C376" s="1">
-        <v>4.049347</v>
+        <v>-17.507538</v>
       </c>
       <c r="D376" s="1" t="s">
         <v>22</v>
@@ -10937,13 +11355,13 @@
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A377" s="1">
-        <v>388.09305000000001</v>
+        <v>336.99135999999999</v>
       </c>
       <c r="B377" s="1">
-        <v>1996</v>
+        <v>1985</v>
       </c>
       <c r="C377" s="1">
-        <v>35.726349999999996</v>
+        <v>-15.375336000000001</v>
       </c>
       <c r="D377" s="1" t="s">
         <v>22</v>
@@ -10951,13 +11369,13 @@
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A378" s="1">
-        <v>352.10626000000002</v>
+        <v>338.21289999999999</v>
       </c>
       <c r="B378" s="1">
-        <v>1997</v>
+        <v>2017</v>
       </c>
       <c r="C378" s="1">
-        <v>-0.26043699999999997</v>
+        <v>-14.153809000000001</v>
       </c>
       <c r="D378" s="1" t="s">
         <v>22</v>
@@ -10965,13 +11383,13 @@
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A379" s="1">
-        <v>323.54962</v>
+        <v>340.36023</v>
       </c>
       <c r="B379" s="1">
-        <v>1998</v>
+        <v>2008</v>
       </c>
       <c r="C379" s="1">
-        <v>-28.817077999999999</v>
+        <v>-12.00647</v>
       </c>
       <c r="D379" s="1" t="s">
         <v>22</v>
@@ -10979,13 +11397,13 @@
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A380" s="1">
-        <v>437.72748000000001</v>
+        <v>340.63772999999998</v>
       </c>
       <c r="B380" s="1">
-        <v>1999</v>
+        <v>2004</v>
       </c>
       <c r="C380" s="1">
-        <v>85.360780000000005</v>
+        <v>-11.728973</v>
       </c>
       <c r="D380" s="1" t="s">
         <v>22</v>
@@ -10993,13 +11411,13 @@
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A381" s="1">
-        <v>392.50963999999999</v>
+        <v>341.74560000000002</v>
       </c>
       <c r="B381" s="1">
-        <v>2000</v>
+        <v>2019</v>
       </c>
       <c r="C381" s="1">
-        <v>40.142944</v>
+        <v>-10.621093999999999</v>
       </c>
       <c r="D381" s="1" t="s">
         <v>22</v>
@@ -11007,13 +11425,13 @@
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A382" s="1">
-        <v>366.81040000000002</v>
+        <v>342.56313999999998</v>
       </c>
       <c r="B382" s="1">
-        <v>2001</v>
+        <v>2018</v>
       </c>
       <c r="C382" s="1">
-        <v>14.443695</v>
+        <v>-9.8035580000000007</v>
       </c>
       <c r="D382" s="1" t="s">
         <v>22</v>
@@ -11021,13 +11439,13 @@
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A383" s="1">
-        <v>344.49774000000002</v>
+        <v>342.80988000000002</v>
       </c>
       <c r="B383" s="1">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="C383" s="1">
-        <v>-7.8689574999999996</v>
+        <v>-9.5568240000000007</v>
       </c>
       <c r="D383" s="1" t="s">
         <v>22</v>
@@ -11035,13 +11453,13 @@
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A384" s="1">
-        <v>342.80988000000002</v>
+        <v>344.49774000000002</v>
       </c>
       <c r="B384" s="1">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="C384" s="1">
-        <v>-9.5568240000000007</v>
+        <v>-7.8689574999999996</v>
       </c>
       <c r="D384" s="1" t="s">
         <v>22</v>
@@ -11049,13 +11467,13 @@
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A385" s="1">
-        <v>340.63772999999998</v>
+        <v>347.18155000000002</v>
       </c>
       <c r="B385" s="1">
-        <v>2004</v>
+        <v>1986</v>
       </c>
       <c r="C385" s="1">
-        <v>-11.728973</v>
+        <v>-5.1851500000000001</v>
       </c>
       <c r="D385" s="1" t="s">
         <v>22</v>
@@ -11063,13 +11481,13 @@
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A386" s="1">
-        <v>388.71269999999998</v>
+        <v>350.16793999999999</v>
       </c>
       <c r="B386" s="1">
-        <v>2005</v>
+        <v>1994</v>
       </c>
       <c r="C386" s="1">
-        <v>36.34601</v>
+        <v>-2.1987610000000002</v>
       </c>
       <c r="D386" s="1" t="s">
         <v>22</v>
@@ -11077,13 +11495,13 @@
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A387" s="1">
-        <v>298.40906000000001</v>
+        <v>352.0684</v>
       </c>
       <c r="B387" s="1">
-        <v>2006</v>
+        <v>2013</v>
       </c>
       <c r="C387" s="1">
-        <v>-53.957639999999998</v>
+        <v>-0.29830932999999998</v>
       </c>
       <c r="D387" s="1" t="s">
         <v>22</v>
@@ -11091,13 +11509,13 @@
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A388" s="1">
-        <v>380.37927000000002</v>
+        <v>352.10626000000002</v>
       </c>
       <c r="B388" s="1">
-        <v>2007</v>
+        <v>1997</v>
       </c>
       <c r="C388" s="1">
-        <v>28.012573</v>
+        <v>-0.26043699999999997</v>
       </c>
       <c r="D388" s="1" t="s">
         <v>22</v>
@@ -11105,13 +11523,13 @@
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A389" s="1">
-        <v>340.36023</v>
+        <v>355.55630000000002</v>
       </c>
       <c r="B389" s="1">
-        <v>2008</v>
+        <v>1990</v>
       </c>
       <c r="C389" s="1">
-        <v>-12.00647</v>
+        <v>3.1896057</v>
       </c>
       <c r="D389" s="1" t="s">
         <v>22</v>
@@ -11119,13 +11537,13 @@
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A390" s="1">
-        <v>292.10654</v>
+        <v>356.41604999999998</v>
       </c>
       <c r="B390" s="1">
-        <v>2009</v>
+        <v>1995</v>
       </c>
       <c r="C390" s="1">
-        <v>-60.260162000000001</v>
+        <v>4.049347</v>
       </c>
       <c r="D390" s="1" t="s">
         <v>22</v>
@@ -11133,13 +11551,13 @@
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A391" s="1">
-        <v>369.03043000000002</v>
+        <v>360.9649</v>
       </c>
       <c r="B391" s="1">
-        <v>2010</v>
+        <v>1992</v>
       </c>
       <c r="C391" s="1">
-        <v>16.663727000000002</v>
+        <v>8.5982059999999993</v>
       </c>
       <c r="D391" s="1" t="s">
         <v>22</v>
@@ -11147,13 +11565,13 @@
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A392" s="1">
-        <v>334.85915999999997</v>
+        <v>366.81040000000002</v>
       </c>
       <c r="B392" s="1">
-        <v>2011</v>
+        <v>2001</v>
       </c>
       <c r="C392" s="1">
-        <v>-17.507538</v>
+        <v>14.443695</v>
       </c>
       <c r="D392" s="1" t="s">
         <v>22</v>
@@ -11161,13 +11579,13 @@
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A393" s="1">
-        <v>296.12786999999997</v>
+        <v>369.03043000000002</v>
       </c>
       <c r="B393" s="1">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C393" s="1">
-        <v>-56.23883</v>
+        <v>16.663727000000002</v>
       </c>
       <c r="D393" s="1" t="s">
         <v>22</v>
@@ -11175,13 +11593,13 @@
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A394" s="1">
-        <v>352.0684</v>
+        <v>373.51830000000001</v>
       </c>
       <c r="B394" s="1">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="C394" s="1">
-        <v>-0.29830932999999998</v>
+        <v>21.151610999999999</v>
       </c>
       <c r="D394" s="1" t="s">
         <v>22</v>
@@ -11189,13 +11607,13 @@
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A395" s="1">
-        <v>373.51830000000001</v>
+        <v>375.17043999999999</v>
       </c>
       <c r="B395" s="1">
-        <v>2014</v>
+        <v>1989</v>
       </c>
       <c r="C395" s="1">
-        <v>21.151610999999999</v>
+        <v>22.803740999999999</v>
       </c>
       <c r="D395" s="1" t="s">
         <v>22</v>
@@ -11203,13 +11621,13 @@
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A396" s="1">
-        <v>304.16595000000001</v>
+        <v>380.12875000000003</v>
       </c>
       <c r="B396" s="1">
-        <v>2015</v>
+        <v>2024</v>
       </c>
       <c r="C396" s="1">
-        <v>-48.200744999999998</v>
+        <v>27.762053999999999</v>
       </c>
       <c r="D396" s="1" t="s">
         <v>22</v>
@@ -11217,13 +11635,13 @@
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A397" s="1">
-        <v>298.6694</v>
+        <v>380.37927000000002</v>
       </c>
       <c r="B397" s="1">
-        <v>2016</v>
+        <v>2007</v>
       </c>
       <c r="C397" s="1">
-        <v>-53.697296000000001</v>
+        <v>28.012573</v>
       </c>
       <c r="D397" s="1" t="s">
         <v>22</v>
@@ -11231,13 +11649,13 @@
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A398" s="1">
-        <v>338.21289999999999</v>
+        <v>381.66262999999998</v>
       </c>
       <c r="B398" s="1">
-        <v>2017</v>
+        <v>1984</v>
       </c>
       <c r="C398" s="1">
-        <v>-14.153809000000001</v>
+        <v>29.295929000000001</v>
       </c>
       <c r="D398" s="1" t="s">
         <v>22</v>
@@ -11245,13 +11663,13 @@
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A399" s="1">
-        <v>342.56313999999998</v>
+        <v>384.92752000000002</v>
       </c>
       <c r="B399" s="1">
-        <v>2018</v>
+        <v>1983</v>
       </c>
       <c r="C399" s="1">
-        <v>-9.8035580000000007</v>
+        <v>32.56082</v>
       </c>
       <c r="D399" s="1" t="s">
         <v>22</v>
@@ -11259,13 +11677,13 @@
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A400" s="1">
-        <v>341.74560000000002</v>
+        <v>388.09305000000001</v>
       </c>
       <c r="B400" s="1">
-        <v>2019</v>
+        <v>1996</v>
       </c>
       <c r="C400" s="1">
-        <v>-10.621093999999999</v>
+        <v>35.726349999999996</v>
       </c>
       <c r="D400" s="1" t="s">
         <v>22</v>
@@ -11273,13 +11691,13 @@
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A401" s="1">
-        <v>326.94394</v>
+        <v>388.71269999999998</v>
       </c>
       <c r="B401" s="1">
-        <v>2020</v>
+        <v>2005</v>
       </c>
       <c r="C401" s="1">
-        <v>-25.42276</v>
+        <v>36.34601</v>
       </c>
       <c r="D401" s="1" t="s">
         <v>22</v>
@@ -11287,13 +11705,13 @@
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A402" s="1">
-        <v>289.89614999999998</v>
+        <v>392.50963999999999</v>
       </c>
       <c r="B402" s="1">
-        <v>2021</v>
+        <v>2000</v>
       </c>
       <c r="C402" s="1">
-        <v>-62.470550000000003</v>
+        <v>40.142944</v>
       </c>
       <c r="D402" s="1" t="s">
         <v>22</v>
@@ -11301,13 +11719,13 @@
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A403" s="1">
-        <v>321.73131999999998</v>
+        <v>393.68340000000001</v>
       </c>
       <c r="B403" s="1">
-        <v>2022</v>
+        <v>1988</v>
       </c>
       <c r="C403" s="1">
-        <v>-30.635376000000001</v>
+        <v>41.31671</v>
       </c>
       <c r="D403" s="1" t="s">
         <v>22</v>
@@ -11315,13 +11733,13 @@
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A404" s="1">
-        <v>270.20287999999999</v>
+        <v>409.84793000000002</v>
       </c>
       <c r="B404" s="1">
-        <v>2023</v>
+        <v>1991</v>
       </c>
       <c r="C404" s="1">
-        <v>-82.163820000000001</v>
+        <v>57.481229999999996</v>
       </c>
       <c r="D404" s="1" t="s">
         <v>22</v>
@@ -11329,13 +11747,13 @@
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A405" s="1">
-        <v>380.12875000000003</v>
+        <v>426.98923000000002</v>
       </c>
       <c r="B405" s="1">
-        <v>2024</v>
+        <v>1993</v>
       </c>
       <c r="C405" s="1">
-        <v>27.762053999999999</v>
+        <v>74.622529999999998</v>
       </c>
       <c r="D405" s="1" t="s">
         <v>22</v>
@@ -11343,16 +11761,646 @@
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A406" s="1">
-        <v>315.35678000000001</v>
+        <v>437.72748000000001</v>
       </c>
       <c r="B406" s="1">
-        <v>2025</v>
+        <v>1999</v>
       </c>
       <c r="C406" s="1">
-        <v>-37.009920000000001</v>
+        <v>85.360780000000005</v>
       </c>
       <c r="D406" s="1" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A407" s="1">
+        <v>343.63463999999999</v>
+      </c>
+      <c r="B407" s="1">
+        <v>2018</v>
+      </c>
+      <c r="C407" s="1">
+        <v>-65.413359999999997</v>
+      </c>
+      <c r="D407" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A408" s="1">
+        <v>352.96589999999998</v>
+      </c>
+      <c r="B408" s="1">
+        <v>1991</v>
+      </c>
+      <c r="C408" s="1">
+        <v>-56.082092000000003</v>
+      </c>
+      <c r="D408" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A409" s="1">
+        <v>353.86070000000001</v>
+      </c>
+      <c r="B409" s="1">
+        <v>2000</v>
+      </c>
+      <c r="C409" s="1">
+        <v>-55.187317</v>
+      </c>
+      <c r="D409" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A410" s="1">
+        <v>362.18615999999997</v>
+      </c>
+      <c r="B410" s="1">
+        <v>2020</v>
+      </c>
+      <c r="C410" s="1">
+        <v>-46.861846999999997</v>
+      </c>
+      <c r="D410" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A411" s="1">
+        <v>364.29037</v>
+      </c>
+      <c r="B411" s="1">
+        <v>2002</v>
+      </c>
+      <c r="C411" s="1">
+        <v>-44.757629999999999</v>
+      </c>
+      <c r="D411" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A412" s="1">
+        <v>370.98779999999999</v>
+      </c>
+      <c r="B412" s="1">
+        <v>1989</v>
+      </c>
+      <c r="C412" s="1">
+        <v>-38.060209999999998</v>
+      </c>
+      <c r="D412" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A413" s="1">
+        <v>372.16244999999998</v>
+      </c>
+      <c r="B413" s="1">
+        <v>2005</v>
+      </c>
+      <c r="C413" s="1">
+        <v>-36.885559999999998</v>
+      </c>
+      <c r="D413" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A414" s="1">
+        <v>379.4212</v>
+      </c>
+      <c r="B414" s="1">
+        <v>1996</v>
+      </c>
+      <c r="C414" s="1">
+        <v>-29.626799999999999</v>
+      </c>
+      <c r="D414" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A415" s="1">
+        <v>381.60723999999999</v>
+      </c>
+      <c r="B415" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C415" s="1">
+        <v>-27.440764999999999</v>
+      </c>
+      <c r="D415" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A416" s="1">
+        <v>382.57825000000003</v>
+      </c>
+      <c r="B416" s="1">
+        <v>1993</v>
+      </c>
+      <c r="C416" s="1">
+        <v>-26.469757000000001</v>
+      </c>
+      <c r="D416" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A417" s="1">
+        <v>385.20513999999997</v>
+      </c>
+      <c r="B417" s="1">
+        <v>2022</v>
+      </c>
+      <c r="C417" s="1">
+        <v>-23.842865</v>
+      </c>
+      <c r="D417" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A418" s="1">
+        <v>389.10140000000001</v>
+      </c>
+      <c r="B418" s="1">
+        <v>2006</v>
+      </c>
+      <c r="C418" s="1">
+        <v>-19.946594000000001</v>
+      </c>
+      <c r="D418" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A419" s="1">
+        <v>393.1952</v>
+      </c>
+      <c r="B419" s="1">
+        <v>2019</v>
+      </c>
+      <c r="C419" s="1">
+        <v>-15.852814</v>
+      </c>
+      <c r="D419" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A420" s="1">
+        <v>397.24900000000002</v>
+      </c>
+      <c r="B420" s="1">
+        <v>1997</v>
+      </c>
+      <c r="C420" s="1">
+        <v>-11.799011</v>
+      </c>
+      <c r="D420" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A421" s="1">
+        <v>399.34809999999999</v>
+      </c>
+      <c r="B421" s="1">
+        <v>2014</v>
+      </c>
+      <c r="C421" s="1">
+        <v>-9.6998899999999999</v>
+      </c>
+      <c r="D421" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A422" s="1">
+        <v>399.97597999999999</v>
+      </c>
+      <c r="B422" s="1">
+        <v>1992</v>
+      </c>
+      <c r="C422" s="1">
+        <v>-9.0720215</v>
+      </c>
+      <c r="D422" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A423" s="1">
+        <v>407.84246999999999</v>
+      </c>
+      <c r="B423" s="1">
+        <v>2008</v>
+      </c>
+      <c r="C423" s="1">
+        <v>-1.2055359000000001</v>
+      </c>
+      <c r="D423" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A424" s="1">
+        <v>410.68896000000001</v>
+      </c>
+      <c r="B424" s="1">
+        <v>2013</v>
+      </c>
+      <c r="C424" s="1">
+        <v>1.6409606999999999</v>
+      </c>
+      <c r="D424" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A425" s="1">
+        <v>414.31542999999999</v>
+      </c>
+      <c r="B425" s="1">
+        <v>2001</v>
+      </c>
+      <c r="C425" s="1">
+        <v>5.2674254999999999</v>
+      </c>
+      <c r="D425" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A426" s="1">
+        <v>416.63506999999998</v>
+      </c>
+      <c r="B426" s="1">
+        <v>2009</v>
+      </c>
+      <c r="C426" s="1">
+        <v>7.5870667000000003</v>
+      </c>
+      <c r="D426" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A427" s="1">
+        <v>417.09500000000003</v>
+      </c>
+      <c r="B427" s="1">
+        <v>1994</v>
+      </c>
+      <c r="C427" s="1">
+        <v>8.0469969999999993</v>
+      </c>
+      <c r="D427" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A428" s="1">
+        <v>418.89749999999998</v>
+      </c>
+      <c r="B428" s="1">
+        <v>2010</v>
+      </c>
+      <c r="C428" s="1">
+        <v>9.8494869999999999</v>
+      </c>
+      <c r="D428" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A429" s="1">
+        <v>423.17926</v>
+      </c>
+      <c r="B429" s="1">
+        <v>1982</v>
+      </c>
+      <c r="C429" s="1">
+        <v>14.131256</v>
+      </c>
+      <c r="D429" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A430" s="1">
+        <v>425.02760000000001</v>
+      </c>
+      <c r="B430" s="1">
+        <v>2021</v>
+      </c>
+      <c r="C430" s="1">
+        <v>15.979583999999999</v>
+      </c>
+      <c r="D430" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A431" s="1">
+        <v>426.58864999999997</v>
+      </c>
+      <c r="B431" s="1">
+        <v>2017</v>
+      </c>
+      <c r="C431" s="1">
+        <v>17.540649999999999</v>
+      </c>
+      <c r="D431" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A432" s="1">
+        <v>427.70578</v>
+      </c>
+      <c r="B432" s="1">
+        <v>1998</v>
+      </c>
+      <c r="C432" s="1">
+        <v>18.657775999999998</v>
+      </c>
+      <c r="D432" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="433" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A433" s="1">
+        <v>432.92728</v>
+      </c>
+      <c r="B433" s="1">
+        <v>1983</v>
+      </c>
+      <c r="C433" s="1">
+        <v>23.879272</v>
+      </c>
+      <c r="D433" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="434" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A434" s="1">
+        <v>434.49963000000002</v>
+      </c>
+      <c r="B434" s="1">
+        <v>2025</v>
+      </c>
+      <c r="C434" s="1">
+        <v>25.451630000000002</v>
+      </c>
+      <c r="D434" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="435" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A435" s="1">
+        <v>436.21262000000002</v>
+      </c>
+      <c r="B435" s="1">
+        <v>2012</v>
+      </c>
+      <c r="C435" s="1">
+        <v>27.164612000000002</v>
+      </c>
+      <c r="D435" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="436" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A436" s="1">
+        <v>438.12094000000002</v>
+      </c>
+      <c r="B436" s="1">
+        <v>2004</v>
+      </c>
+      <c r="C436" s="1">
+        <v>29.072937</v>
+      </c>
+      <c r="D436" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A437" s="1">
+        <v>441.76584000000003</v>
+      </c>
+      <c r="B437" s="1">
+        <v>1985</v>
+      </c>
+      <c r="C437" s="1">
+        <v>32.717834000000003</v>
+      </c>
+      <c r="D437" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="438" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A438" s="1">
+        <v>446.57850000000002</v>
+      </c>
+      <c r="B438" s="1">
+        <v>2011</v>
+      </c>
+      <c r="C438" s="1">
+        <v>37.530487000000001</v>
+      </c>
+      <c r="D438" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="439" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A439" s="1">
+        <v>452.97232000000002</v>
+      </c>
+      <c r="B439" s="1">
+        <v>1999</v>
+      </c>
+      <c r="C439" s="1">
+        <v>43.924315999999997</v>
+      </c>
+      <c r="D439" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="440" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A440" s="1">
+        <v>453.47742</v>
+      </c>
+      <c r="B440" s="1">
+        <v>2024</v>
+      </c>
+      <c r="C440" s="1">
+        <v>44.429412999999997</v>
+      </c>
+      <c r="D440" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="441" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A441" s="1">
+        <v>456.67023</v>
+      </c>
+      <c r="B441" s="1">
+        <v>2003</v>
+      </c>
+      <c r="C441" s="1">
+        <v>47.622222999999998</v>
+      </c>
+      <c r="D441" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="442" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A442" s="1">
+        <v>461.67545000000001</v>
+      </c>
+      <c r="B442" s="1">
+        <v>1995</v>
+      </c>
+      <c r="C442" s="1">
+        <v>52.62744</v>
+      </c>
+      <c r="D442" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="443" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A443" s="1">
+        <v>476.80437999999998</v>
+      </c>
+      <c r="B443" s="1">
+        <v>2007</v>
+      </c>
+      <c r="C443" s="1">
+        <v>67.756379999999993</v>
+      </c>
+      <c r="D443" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A444" s="1">
+        <v>477.72140000000002</v>
+      </c>
+      <c r="B444" s="1">
+        <v>1981</v>
+      </c>
+      <c r="C444" s="1">
+        <v>68.673400000000001</v>
+      </c>
+      <c r="D444" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A445" s="1">
+        <v>482.58267000000001</v>
+      </c>
+      <c r="B445" s="1">
+        <v>2023</v>
+      </c>
+      <c r="C445" s="1">
+        <v>73.534670000000006</v>
+      </c>
+      <c r="D445" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="446" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A446" s="1">
+        <v>486.8897</v>
+      </c>
+      <c r="B446" s="1">
+        <v>1990</v>
+      </c>
+      <c r="C446" s="1">
+        <v>77.841705000000005</v>
+      </c>
+      <c r="D446" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="447" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A447" s="1">
+        <v>491.05950000000001</v>
+      </c>
+      <c r="B447" s="1">
+        <v>2016</v>
+      </c>
+      <c r="C447" s="1">
+        <v>82.011505</v>
+      </c>
+      <c r="D447" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A448" s="1">
+        <v>492.95218</v>
+      </c>
+      <c r="B448" s="1">
+        <v>1984</v>
+      </c>
+      <c r="C448" s="1">
+        <v>83.904174999999995</v>
+      </c>
+      <c r="D448" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A449" s="1">
+        <v>496.95084000000003</v>
+      </c>
+      <c r="B449" s="1">
+        <v>1988</v>
+      </c>
+      <c r="C449" s="1">
+        <v>87.902829999999994</v>
+      </c>
+      <c r="D449" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A450" s="1">
+        <v>515.2627</v>
+      </c>
+      <c r="B450" s="1">
+        <v>1987</v>
+      </c>
+      <c r="C450" s="1">
+        <v>106.21469</v>
+      </c>
+      <c r="D450" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A451" s="1">
+        <v>553.87760000000003</v>
+      </c>
+      <c r="B451" s="1">
+        <v>1986</v>
+      </c>
+      <c r="C451" s="1">
+        <v>144.82962000000001</v>
+      </c>
+      <c r="D451" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
